--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -15,12 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="183">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
   <si>
-    <t>Period: 03/01/26 00:00 EST - 03/31/26 23:59 EDT</t>
+    <t>Period: 01/01/26 00:00 EST - 12/31/26 23:59 EST</t>
   </si>
   <si>
     <t>Datetime</t>
@@ -62,19 +62,16 @@
     <t>Coaching Completed At</t>
   </si>
   <si>
-    <t>03/04/26 21:33 EST</t>
-  </si>
-  <si>
-    <t>Levi  Bennett</t>
-  </si>
-  <si>
-    <t>'1189363845995593728</t>
-  </si>
-  <si>
-    <t>NO-SEATBELT</t>
-  </si>
-  <si>
-    <t>4.1mi S of San Angelo TX</t>
+    <t>01/02/26 15:34 EST</t>
+  </si>
+  <si>
+    <t>Adam  Anglin</t>
+  </si>
+  <si>
+    <t>TRAFFIC-LIGHT-VIOLATION</t>
+  </si>
+  <si>
+    <t>5.3mi S of Seguin TX</t>
   </si>
   <si>
     <t>Coachable</t>
@@ -86,115 +83,487 @@
     <t>Driver Education Network Service user</t>
   </si>
   <si>
-    <t>03/05/26 07:33 EST</t>
-  </si>
-  <si>
-    <t>03/05/26 11:17 EST</t>
-  </si>
-  <si>
-    <t>'1189571033456345088</t>
-  </si>
-  <si>
-    <t>2.3mi SE of San Angelo TX</t>
-  </si>
-  <si>
-    <t>03/06/26 07:37 EST</t>
-  </si>
-  <si>
-    <t>03/05/26 13:19 EST</t>
-  </si>
-  <si>
-    <t>Mark Stevens</t>
-  </si>
-  <si>
-    <t>'1189601818964033536</t>
-  </si>
-  <si>
-    <t>USING-PHONE</t>
-  </si>
-  <si>
-    <t>31.2mi NW of San Angelo TX</t>
-  </si>
-  <si>
-    <t>03/06/26 07:35 EST</t>
-  </si>
-  <si>
-    <t>03/05/26 18:48 EST</t>
-  </si>
-  <si>
-    <t>'1189684566525378560</t>
-  </si>
-  <si>
-    <t>19.5mi NW of Big Spring TX</t>
-  </si>
-  <si>
-    <t>03/06/26 07:31 EST</t>
-  </si>
-  <si>
-    <t>03/06/26 16:00 EST</t>
-  </si>
-  <si>
-    <t>'1190004682140057600</t>
-  </si>
-  <si>
-    <t>2.2mi S of San Angelo TX</t>
-  </si>
-  <si>
-    <t>03/09/26 10:47 EDT</t>
-  </si>
-  <si>
-    <t>03/09/26 11:52 EDT</t>
-  </si>
-  <si>
-    <t>'1191014431711199232</t>
-  </si>
-  <si>
-    <t>0.7mi S of Boerne TX</t>
-  </si>
-  <si>
-    <t>03/10/26 07:48 EDT</t>
-  </si>
-  <si>
-    <t>03/09/26 14:16 EDT</t>
-  </si>
-  <si>
-    <t>'1191050708246495232</t>
-  </si>
-  <si>
-    <t>27.9mi W of Sealy TX</t>
-  </si>
-  <si>
-    <t>03/10/26 07:49 EDT</t>
-  </si>
-  <si>
-    <t>03/09/26 19:57 EDT</t>
-  </si>
-  <si>
-    <t>Efren Pena</t>
-  </si>
-  <si>
-    <t>'1191136474662338560</t>
-  </si>
-  <si>
-    <t>STOP-SIGN-VIOLATION</t>
-  </si>
-  <si>
-    <t>3.5mi N of San Angelo TX</t>
-  </si>
-  <si>
-    <t>03/10/26 09:00 EDT</t>
-  </si>
-  <si>
-    <t>03/11/26 19:30 EDT</t>
-  </si>
-  <si>
-    <t>'1191854377728638976</t>
-  </si>
-  <si>
-    <t>27mi W of Brady TX</t>
-  </si>
-  <si>
-    <t>03/12/26 10:35 EDT</t>
+    <t>01/14/26 08:29 EST</t>
+  </si>
+  <si>
+    <t>01/05/26 09:34 EST</t>
+  </si>
+  <si>
+    <t>Jimmy  Mott</t>
+  </si>
+  <si>
+    <t>SEATBELT-COMPLIANCE</t>
+  </si>
+  <si>
+    <t>6mi SE of Cibolo TX</t>
+  </si>
+  <si>
+    <t>01/05/26 12:42 EST</t>
+  </si>
+  <si>
+    <t>DRIVER-DISTRACTION</t>
+  </si>
+  <si>
+    <t>5mi W of Lackland AFB TX</t>
+  </si>
+  <si>
+    <t>01/06/26 09:08 EST</t>
+  </si>
+  <si>
+    <t>5.7mi SE of Cibolo TX</t>
+  </si>
+  <si>
+    <t>01/14/26 08:28 EST</t>
+  </si>
+  <si>
+    <t>01/06/26 11:13 EST</t>
+  </si>
+  <si>
+    <t>5.9mi SE of Cibolo TX</t>
+  </si>
+  <si>
+    <t>01/06/26 13:46 EST</t>
+  </si>
+  <si>
+    <t>7.1mi SW of Seguin TX</t>
+  </si>
+  <si>
+    <t>01/06/26 14:42 EST</t>
+  </si>
+  <si>
+    <t>Zachary  Hill</t>
+  </si>
+  <si>
+    <t>4.2mi SE of Kirby TX</t>
+  </si>
+  <si>
+    <t>01/14/26 08:27 EST</t>
+  </si>
+  <si>
+    <t>01/06/26 20:30 EST</t>
+  </si>
+  <si>
+    <t>DRIVER-DROWSINESS</t>
+  </si>
+  <si>
+    <t>3.2mi S of Converse TX</t>
+  </si>
+  <si>
+    <t>01/07/26 09:16 EST</t>
+  </si>
+  <si>
+    <t>01/14/26 08:26 EST</t>
+  </si>
+  <si>
+    <t>01/07/26 13:37 EST</t>
+  </si>
+  <si>
+    <t>4mi SE of Converse TX</t>
+  </si>
+  <si>
+    <t>01/14/26 08:24 EST</t>
+  </si>
+  <si>
+    <t>01/07/26 16:08 EST</t>
+  </si>
+  <si>
+    <t>2.8mi NE of Uvalde TX</t>
+  </si>
+  <si>
+    <t>01/08/26 12:08 EST</t>
+  </si>
+  <si>
+    <t>LANE-CONDUCT</t>
+  </si>
+  <si>
+    <t>5.5mi SE of Cibolo TX</t>
+  </si>
+  <si>
+    <t>01/14/26 08:23 EST</t>
+  </si>
+  <si>
+    <t>01/08/26 14:41 EST</t>
+  </si>
+  <si>
+    <t>4.6mi SE of Cibolo TX</t>
+  </si>
+  <si>
+    <t>01/09/26 18:11 EST</t>
+  </si>
+  <si>
+    <t>01/14/26 08:22 EST</t>
+  </si>
+  <si>
+    <t>01/11/26 11:55 EST</t>
+  </si>
+  <si>
+    <t>6.2mi SE of Cibolo TX</t>
+  </si>
+  <si>
+    <t>01/13/26 12:44 EST</t>
+  </si>
+  <si>
+    <t>3.7mi SW of Kirby TX</t>
+  </si>
+  <si>
+    <t>01/14/26 08:20 EST</t>
+  </si>
+  <si>
+    <t>01/14/26 09:59 EST</t>
+  </si>
+  <si>
+    <t>5.8mi SE of Cibolo TX</t>
+  </si>
+  <si>
+    <t>01/15/26 09:10 EST</t>
+  </si>
+  <si>
+    <t>01/20/26 15:25 EST</t>
+  </si>
+  <si>
+    <t>6.8mi E of Cibolo TX</t>
+  </si>
+  <si>
+    <t>01/21/26 07:58 EST</t>
+  </si>
+  <si>
+    <t>01/20/26 17:59 EST</t>
+  </si>
+  <si>
+    <t>01/21/26 07:59 EST</t>
+  </si>
+  <si>
+    <t>01/21/26 15:20 EST</t>
+  </si>
+  <si>
+    <t>2.2mi NE of Primera TX</t>
+  </si>
+  <si>
+    <t>01/22/26 10:06 EST</t>
+  </si>
+  <si>
+    <t>01/21/26 17:32 EST</t>
+  </si>
+  <si>
+    <t>6.3mi N of Raymondville TX</t>
+  </si>
+  <si>
+    <t>01/22/26 10:07 EST</t>
+  </si>
+  <si>
+    <t>01/22/26 17:04 EST</t>
+  </si>
+  <si>
+    <t>6.7mi S of Kirby TX</t>
+  </si>
+  <si>
+    <t>01/23/26 07:37 EST</t>
+  </si>
+  <si>
+    <t>01/23/26 21:12 EST</t>
+  </si>
+  <si>
+    <t>11.3mi N of Gonzales TX</t>
+  </si>
+  <si>
+    <t>01/26/26 10:29 EST</t>
+  </si>
+  <si>
+    <t>01/27/26 12:09 EST</t>
+  </si>
+  <si>
+    <t>Frank  Almendarez</t>
+  </si>
+  <si>
+    <t>7.4mi SW of Seguin TX</t>
+  </si>
+  <si>
+    <t>01/28/26 09:15 EST</t>
+  </si>
+  <si>
+    <t>01/27/26 13:27 EST</t>
+  </si>
+  <si>
+    <t>1.6mi N of Live Oak TX</t>
+  </si>
+  <si>
+    <t>01/28/26 09:16 EST</t>
+  </si>
+  <si>
+    <t>02/01/26 09:26 EST</t>
+  </si>
+  <si>
+    <t>5.7mi SW of Seguin TX</t>
+  </si>
+  <si>
+    <t>02/02/26 10:39 EST</t>
+  </si>
+  <si>
+    <t>02/01/26 15:29 EST</t>
+  </si>
+  <si>
+    <t>4.8mi SW of Seguin TX</t>
+  </si>
+  <si>
+    <t>02/02/26 10:43 EST</t>
+  </si>
+  <si>
+    <t>02/02/26 19:07 EST</t>
+  </si>
+  <si>
+    <t>02/03/26 10:35 EST</t>
+  </si>
+  <si>
+    <t>02/03/26 09:09 EST</t>
+  </si>
+  <si>
+    <t>02/03/26 10:36 EST</t>
+  </si>
+  <si>
+    <t>02/03/26 19:47 EST</t>
+  </si>
+  <si>
+    <t>02/04/26 10:31 EST</t>
+  </si>
+  <si>
+    <t>02/04/26 17:58 EST</t>
+  </si>
+  <si>
+    <t>02/05/26 10:53 EST</t>
+  </si>
+  <si>
+    <t>02/09/26 08:06 EST</t>
+  </si>
+  <si>
+    <t>02/10/26 10:11 EST</t>
+  </si>
+  <si>
+    <t>02/09/26 14:01 EST</t>
+  </si>
+  <si>
+    <t>02/10/26 10:13 EST</t>
+  </si>
+  <si>
+    <t>02/09/26 14:04 EST</t>
+  </si>
+  <si>
+    <t>3.4mi E of Kirby TX</t>
+  </si>
+  <si>
+    <t>02/10/26 10:14 EST</t>
+  </si>
+  <si>
+    <t>02/10/26 11:53 EST</t>
+  </si>
+  <si>
+    <t>0.7mi NE of San Marcos TX</t>
+  </si>
+  <si>
+    <t>02/11/26 08:13 EST</t>
+  </si>
+  <si>
+    <t>02/10/26 12:32 EST</t>
+  </si>
+  <si>
+    <t>7.5mi E of Cibolo TX</t>
+  </si>
+  <si>
+    <t>02/11/26 08:14 EST</t>
+  </si>
+  <si>
+    <t>02/11/26 15:01 EST</t>
+  </si>
+  <si>
+    <t>1mi NE of Seguin TX</t>
+  </si>
+  <si>
+    <t>02/12/26 12:02 EST</t>
+  </si>
+  <si>
+    <t>02/14/26 14:09 EST</t>
+  </si>
+  <si>
+    <t>0.6mi SW of Schertz TX</t>
+  </si>
+  <si>
+    <t>02/16/26 11:08 EST</t>
+  </si>
+  <si>
+    <t>02/17/26 15:36 EST</t>
+  </si>
+  <si>
+    <t>3.7mi NW of Seguin TX</t>
+  </si>
+  <si>
+    <t>02/18/26 08:31 EST</t>
+  </si>
+  <si>
+    <t>02/18/26 18:25 EST</t>
+  </si>
+  <si>
+    <t>3.2mi SE of Converse TX</t>
+  </si>
+  <si>
+    <t>02/19/26 10:09 EST</t>
+  </si>
+  <si>
+    <t>02/19/26 09:37 EST</t>
+  </si>
+  <si>
+    <t>5.6mi SE of Cibolo TX</t>
+  </si>
+  <si>
+    <t>02/19/26 10:11 EST</t>
+  </si>
+  <si>
+    <t>02/19/26 14:18 EST</t>
+  </si>
+  <si>
+    <t>4.6mi S of Cibolo TX</t>
+  </si>
+  <si>
+    <t>02/20/26 10:12 EST</t>
+  </si>
+  <si>
+    <t>02/19/26 16:56 EST</t>
+  </si>
+  <si>
+    <t>3.4mi SW of Alice TX</t>
+  </si>
+  <si>
+    <t>02/20/26 10:13 EST</t>
+  </si>
+  <si>
+    <t>02/20/26 12:16 EST</t>
+  </si>
+  <si>
+    <t>4.6mi SW of Seguin TX</t>
+  </si>
+  <si>
+    <t>02/23/26 09:39 EST</t>
+  </si>
+  <si>
+    <t>02/24/26 09:44 EST</t>
+  </si>
+  <si>
+    <t>2.7mi E of Kirby TX</t>
+  </si>
+  <si>
+    <t>02/25/26 10:00 EST</t>
+  </si>
+  <si>
+    <t>02/25/26 10:02 EST</t>
+  </si>
+  <si>
+    <t>02/24/26 21:23 EST</t>
+  </si>
+  <si>
+    <t>4.7mi S of Cibolo TX</t>
+  </si>
+  <si>
+    <t>02/25/26 10:01 EST</t>
+  </si>
+  <si>
+    <t>02/25/26 10:45 EST</t>
+  </si>
+  <si>
+    <t>02/25/26 11:30 EST</t>
+  </si>
+  <si>
+    <t>1.5mi S of Kirby TX</t>
+  </si>
+  <si>
+    <t>02/26/26 08:29 EST</t>
+  </si>
+  <si>
+    <t>02/25/26 18:16 EST</t>
+  </si>
+  <si>
+    <t>3mi SW of New Braunfels TX</t>
+  </si>
+  <si>
+    <t>02/26/26 08:30 EST</t>
+  </si>
+  <si>
+    <t>02/26/26 07:59 EST</t>
+  </si>
+  <si>
+    <t>02/26/26 08:31 EST</t>
+  </si>
+  <si>
+    <t>02/26/26 10:16 EST</t>
+  </si>
+  <si>
+    <t>02/26/26 14:16 EST</t>
+  </si>
+  <si>
+    <t>5mi W of Seguin TX</t>
+  </si>
+  <si>
+    <t>02/27/26 07:29 EST</t>
+  </si>
+  <si>
+    <t>02/27/26 08:15 EST</t>
+  </si>
+  <si>
+    <t>02/27/26 12:22 EST</t>
+  </si>
+  <si>
+    <t>2mi S of Converse TX</t>
+  </si>
+  <si>
+    <t>03/02/26 11:03 EST</t>
+  </si>
+  <si>
+    <t>03/02/26 11:12 EST</t>
+  </si>
+  <si>
+    <t>02/27/26 19:37 EST</t>
+  </si>
+  <si>
+    <t>1mi W of Seguin TX</t>
+  </si>
+  <si>
+    <t>03/02/26 11:08 EST</t>
+  </si>
+  <si>
+    <t>03/02/26 11:49 EST</t>
+  </si>
+  <si>
+    <t>03/03/26 08:41 EST</t>
+  </si>
+  <si>
+    <t>03/03/26 08:44 EST</t>
+  </si>
+  <si>
+    <t>03/04/26 11:41 EST</t>
+  </si>
+  <si>
+    <t>03/05/26 07:32 EST</t>
+  </si>
+  <si>
+    <t>03/05/26 07:39 EST</t>
+  </si>
+  <si>
+    <t>03/05/26 12:22 EST</t>
+  </si>
+  <si>
+    <t>23.4mi S of Pearsall TX</t>
+  </si>
+  <si>
+    <t>03/06/26 07:39 EST</t>
+  </si>
+  <si>
+    <t>03/09/26 12:54 EDT</t>
+  </si>
+  <si>
+    <t>16mi NE of Pearsall TX</t>
+  </si>
+  <si>
+    <t>03/10/26 09:03 EDT</t>
+  </si>
+  <si>
+    <t>03/10/26 09:34 EDT</t>
   </si>
 </sst>
 </file>
@@ -560,7 +929,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="true" style="1"/>
@@ -637,328 +1006,1971 @@
         <v>16</v>
       </c>
       <c r="C4" s="4">
-        <v>411</v>
-      </c>
-      <c r="D4" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="4">
+        <v>5001912988</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="G4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="4">
-        <v>39</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="M4" s="4"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="C5" s="4">
-        <v>403</v>
-      </c>
-      <c r="D5" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" s="4">
+        <v>5012724655</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="4">
-        <v>28</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H5" s="4"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="M5" s="4"/>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="4">
+        <v>111</v>
+      </c>
+      <c r="D6" s="4">
+        <v>5014045676</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="4">
-        <v>406</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="G6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="4">
-        <v>74</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>33</v>
       </c>
       <c r="M6" s="4"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="4">
-        <v>403</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>35</v>
+        <v>301</v>
+      </c>
+      <c r="D7" s="4">
+        <v>5018915355</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="G7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="4">
-        <v>73</v>
-      </c>
-      <c r="I7" s="4">
-        <v>75</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
       <c r="J7" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="M7" s="4"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="4" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="4">
-        <v>413</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>39</v>
+        <v>111</v>
+      </c>
+      <c r="D8" s="4">
+        <v>5019699676</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="4">
-        <v>48</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="M8" s="4"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C9" s="4">
-        <v>406</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>43</v>
+        <v>110</v>
+      </c>
+      <c r="D9" s="4">
+        <v>5021015870</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="M9" s="4"/>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="4" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C10" s="4">
-        <v>406</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>47</v>
+        <v>112</v>
+      </c>
+      <c r="D10" s="4">
+        <v>5021546241</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="4">
-        <v>75</v>
-      </c>
-      <c r="I10" s="4">
-        <v>75</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
       <c r="J10" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="M10" s="4"/>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="4" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C11" s="4">
-        <v>409</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>52</v>
+        <v>112</v>
+      </c>
+      <c r="D11" s="4">
+        <v>5023845243</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="M11" s="4"/>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="4" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C12" s="4">
-        <v>403</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>57</v>
+        <v>111</v>
+      </c>
+      <c r="D12" s="4">
+        <v>5025459813</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M12" s="4"/>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="4">
+        <v>301</v>
+      </c>
+      <c r="D13" s="4">
+        <v>5027410344</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M13" s="4"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="4">
+        <v>112</v>
+      </c>
+      <c r="D14" s="4">
+        <v>5028822223</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M14" s="4"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="4">
+        <v>112</v>
+      </c>
+      <c r="D15" s="4">
+        <v>5033153504</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15" s="4"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="4">
+        <v>110</v>
+      </c>
+      <c r="D16" s="4">
+        <v>5034518310</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="M16" s="4"/>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="4">
+        <v>112</v>
+      </c>
+      <c r="D17" s="4">
+        <v>5042484121</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="M17" s="4"/>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="M12" s="4"/>
+      <c r="B18" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="4">
+        <v>112</v>
+      </c>
+      <c r="D18" s="4">
+        <v>5048577916</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="M18" s="4"/>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="4">
+        <v>301</v>
+      </c>
+      <c r="D19" s="4">
+        <v>5060271507</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="M19" s="4"/>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="4">
+        <v>112</v>
+      </c>
+      <c r="D20" s="4">
+        <v>5065583844</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="M20" s="4"/>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="4">
+        <v>110</v>
+      </c>
+      <c r="D21" s="4">
+        <v>5100237567</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="M21" s="4"/>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="4">
+        <v>112</v>
+      </c>
+      <c r="D22" s="4">
+        <v>5101465304</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="M22" s="4"/>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="4">
+        <v>112</v>
+      </c>
+      <c r="D23" s="4">
+        <v>5106751495</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="M23" s="4"/>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="4">
+        <v>112</v>
+      </c>
+      <c r="D24" s="4">
+        <v>5107862306</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="M24" s="4"/>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="4">
+        <v>111</v>
+      </c>
+      <c r="D25" s="4">
+        <v>5114256434</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="M25" s="4"/>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="4">
+        <v>112</v>
+      </c>
+      <c r="D26" s="4">
+        <v>5121665545</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="M26" s="4"/>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="4">
+        <v>301</v>
+      </c>
+      <c r="D27" s="4">
+        <v>5133605271</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="M27" s="4"/>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="4">
+        <v>113</v>
+      </c>
+      <c r="D28" s="4">
+        <v>5134154922</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="M28" s="4"/>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="4">
+        <v>110</v>
+      </c>
+      <c r="D29" s="4">
+        <v>5160042047</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M29" s="4"/>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C30" s="4">
+        <v>301</v>
+      </c>
+      <c r="D30" s="4">
+        <v>5161466800</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="M30" s="4"/>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" s="4">
+        <v>112</v>
+      </c>
+      <c r="D31" s="4">
+        <v>5168199288</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="M31" s="4"/>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="4">
+        <v>301</v>
+      </c>
+      <c r="D32" s="4">
+        <v>5170090230</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M32" s="4"/>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="4">
+        <v>110</v>
+      </c>
+      <c r="D33" s="4">
+        <v>5174829578</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M33" s="4"/>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="4">
+        <v>110</v>
+      </c>
+      <c r="D34" s="4">
+        <v>5180830801</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="M34" s="4"/>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" s="4">
+        <v>110</v>
+      </c>
+      <c r="D35" s="4">
+        <v>5203835458</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L35" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="M35" s="4"/>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" s="4">
+        <v>112</v>
+      </c>
+      <c r="D36" s="4">
+        <v>5206231644</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="M36" s="4"/>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C37" s="4">
+        <v>112</v>
+      </c>
+      <c r="D37" s="4">
+        <v>5206259061</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L37" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="M37" s="4"/>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" s="4">
+        <v>111</v>
+      </c>
+      <c r="D38" s="4">
+        <v>5211779691</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L38" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="M38" s="4"/>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="4">
+        <v>301</v>
+      </c>
+      <c r="D39" s="4">
+        <v>5212121113</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L39" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="M39" s="4"/>
+    </row>
+    <row r="40" spans="1:13">
+      <c r="A40" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="4">
+        <v>110</v>
+      </c>
+      <c r="D40" s="4">
+        <v>5220297071</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L40" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="M40" s="4"/>
+    </row>
+    <row r="41" spans="1:13">
+      <c r="A41" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="4">
+        <v>110</v>
+      </c>
+      <c r="D41" s="4">
+        <v>5238353442</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L41" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M41" s="4"/>
+    </row>
+    <row r="42" spans="1:13">
+      <c r="A42" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C42" s="4">
+        <v>112</v>
+      </c>
+      <c r="D42" s="4">
+        <v>5254543722</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L42" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="M42" s="4"/>
+    </row>
+    <row r="43" spans="1:13">
+      <c r="A43" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C43" s="4">
+        <v>112</v>
+      </c>
+      <c r="D43" s="4">
+        <v>5262654432</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="M43" s="4"/>
+    </row>
+    <row r="44" spans="1:13">
+      <c r="A44" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="4">
+        <v>110</v>
+      </c>
+      <c r="D44" s="4">
+        <v>5265044352</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="M44" s="4"/>
+    </row>
+    <row r="45" spans="1:13">
+      <c r="A45" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C45" s="4">
+        <v>112</v>
+      </c>
+      <c r="D45" s="4">
+        <v>5267281540</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="M45" s="4"/>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="A46" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" s="4">
+        <v>111</v>
+      </c>
+      <c r="D46" s="4">
+        <v>5268658556</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L46" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M46" s="4"/>
+    </row>
+    <row r="47" spans="1:13">
+      <c r="A47" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C47" s="4">
+        <v>112</v>
+      </c>
+      <c r="D47" s="4">
+        <v>5272725026</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L47" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="M47" s="4"/>
+    </row>
+    <row r="48" spans="1:13">
+      <c r="A48" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C48" s="4">
+        <v>112</v>
+      </c>
+      <c r="D48" s="4">
+        <v>5291991975</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
+      <c r="A49" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="4">
+        <v>110</v>
+      </c>
+      <c r="D49" s="4">
+        <v>5296674307</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L49" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="M49" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13">
+      <c r="A50" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" s="4">
+        <v>111</v>
+      </c>
+      <c r="D50" s="4">
+        <v>5299186078</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L50" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="M50" s="4"/>
+    </row>
+    <row r="51" spans="1:13">
+      <c r="A51" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C51" s="4">
+        <v>112</v>
+      </c>
+      <c r="D51" s="4">
+        <v>5302786279</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L51" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="M51" s="4"/>
+    </row>
+    <row r="52" spans="1:13">
+      <c r="A52" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="4">
+        <v>110</v>
+      </c>
+      <c r="D52" s="4">
+        <v>5304829908</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L52" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="M52" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13">
+      <c r="A53" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C53" s="4">
+        <v>112</v>
+      </c>
+      <c r="D53" s="4">
+        <v>5307546103</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L53" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="M53" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13">
+      <c r="A54" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="4">
+        <v>110</v>
+      </c>
+      <c r="D54" s="4">
+        <v>5313359492</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L54" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="M54" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13">
+      <c r="A55" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" s="4">
+        <v>111</v>
+      </c>
+      <c r="D55" s="4">
+        <v>5316784489</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L55" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="M55" s="4"/>
+    </row>
+    <row r="56" spans="1:13">
+      <c r="A56" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="4">
+        <v>110</v>
+      </c>
+      <c r="D56" s="4">
+        <v>5328380737</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L56" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="M56" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13">
+      <c r="A57" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C57" s="4">
+        <v>112</v>
+      </c>
+      <c r="D57" s="4">
+        <v>5341988170</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L57" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="M57" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13">
+      <c r="A58" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" s="4">
+        <v>111</v>
+      </c>
+      <c r="D58" s="4">
+        <v>5349375228</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L58" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="M58" s="4"/>
+    </row>
+    <row r="59" spans="1:13">
+      <c r="A59" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C59" s="4">
+        <v>112</v>
+      </c>
+      <c r="D59" s="4">
+        <v>5371436091</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L59" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="M59" s="4" t="s">
+        <v>182</v>
+      </c>
     </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Home Motors\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Home Motors\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{27F6843C-9530-45BC-9EA2-37230E05B5E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{66026AAF-5E04-4903-9B1A-D0256A5E799C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6165" yWindow="1860" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="304">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -274,6 +274,18 @@
     <t>03/10/26 07:49 EDT</t>
   </si>
   <si>
+    <t>03/09/26 19:39 EDT</t>
+  </si>
+  <si>
+    <t>'1191131965336748032</t>
+  </si>
+  <si>
+    <t>5.3mi N of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/11/26 10:05 EDT</t>
+  </si>
+  <si>
     <t>03/09/26 19:57 EDT</t>
   </si>
   <si>
@@ -286,6 +298,30 @@
     <t>03/10/26 09:00 EDT</t>
   </si>
   <si>
+    <t>03/09/26 20:07 EDT</t>
+  </si>
+  <si>
+    <t>'1191138989990641664</t>
+  </si>
+  <si>
+    <t>12mi NW of Brady TX</t>
+  </si>
+  <si>
+    <t>03/11/26 10:03 EDT</t>
+  </si>
+  <si>
+    <t>03/10/26 20:46 EDT</t>
+  </si>
+  <si>
+    <t>'1191511032686870528</t>
+  </si>
+  <si>
+    <t>3.4mi SE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/11/26 10:04 EDT</t>
+  </si>
+  <si>
     <t>03/11/26 19:30 EDT</t>
   </si>
   <si>
@@ -391,6 +427,24 @@
     <t>03/17/26 09:37 EDT</t>
   </si>
   <si>
+    <t>03/16/26 16:25 EDT</t>
+  </si>
+  <si>
+    <t>'1193619878112821248</t>
+  </si>
+  <si>
+    <t>1.7mi SW of North Richland Hills TX</t>
+  </si>
+  <si>
+    <t>Non-Coachable</t>
+  </si>
+  <si>
+    <t>Truckspy Testing</t>
+  </si>
+  <si>
+    <t>03/16/26 16:30 EDT</t>
+  </si>
+  <si>
     <t>03/16/26 17:26 EDT</t>
   </si>
   <si>
@@ -485,6 +539,399 @@
   </si>
   <si>
     <t>03/20/26 07:50 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 14:10 EDT</t>
+  </si>
+  <si>
+    <t>'1195035471563096064</t>
+  </si>
+  <si>
+    <t>0.5mi SE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/23/26 09:59 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 15:14 EDT</t>
+  </si>
+  <si>
+    <t>'1195051355853717504</t>
+  </si>
+  <si>
+    <t>2.1mi SE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/23/26 10:01 EDT</t>
+  </si>
+  <si>
+    <t>03/21/26 22:03 EDT</t>
+  </si>
+  <si>
+    <t>'1195516806719242240</t>
+  </si>
+  <si>
+    <t>4.7mi E of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/23/26 10:03 EDT</t>
+  </si>
+  <si>
+    <t>03/23/26 02:23 EDT</t>
+  </si>
+  <si>
+    <t>'1195945115575812096</t>
+  </si>
+  <si>
+    <t>33.3mi S of Sweetwater TX</t>
+  </si>
+  <si>
+    <t>03/24/26 07:50 EDT</t>
+  </si>
+  <si>
+    <t>03/23/26 09:35 EDT</t>
+  </si>
+  <si>
+    <t>'1196053345740161024</t>
+  </si>
+  <si>
+    <t>33mi W of Brady TX</t>
+  </si>
+  <si>
+    <t>03/24/26 07:51 EDT</t>
+  </si>
+  <si>
+    <t>03/24/26 08:40 EDT</t>
+  </si>
+  <si>
+    <t>Alexis Vega</t>
+  </si>
+  <si>
+    <t>'1196401814933766144</t>
+  </si>
+  <si>
+    <t>Toby Taylor</t>
+  </si>
+  <si>
+    <t>03/25/26 15:13 EDT</t>
+  </si>
+  <si>
+    <t>03/24/26 09:40 EDT</t>
+  </si>
+  <si>
+    <t>'1196417017880674304</t>
+  </si>
+  <si>
+    <t>3.6mi S of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/25/26 08:08 EDT</t>
+  </si>
+  <si>
+    <t>03/24/26 11:19 EDT</t>
+  </si>
+  <si>
+    <t>'1196441920877002752</t>
+  </si>
+  <si>
+    <t>43.3mi S of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/25/26 12:57 EDT</t>
+  </si>
+  <si>
+    <t>'1196828882653839360</t>
+  </si>
+  <si>
+    <t>3.1mi W of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/26/26 09:45 EDT</t>
+  </si>
+  <si>
+    <t>03/25/26 14:06 EDT</t>
+  </si>
+  <si>
+    <t>'1196846145482162176</t>
+  </si>
+  <si>
+    <t>4.6mi N of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/25/26 15:07 EDT</t>
+  </si>
+  <si>
+    <t>03/25/26 14:07 EDT</t>
+  </si>
+  <si>
+    <t>'1196846411677859840</t>
+  </si>
+  <si>
+    <t>5.9mi N of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/25/26 15:12 EDT</t>
+  </si>
+  <si>
+    <t>03/25/26 21:01 EDT</t>
+  </si>
+  <si>
+    <t>'1196950759627980800</t>
+  </si>
+  <si>
+    <t>16.7mi E of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/26/26 09:47 EDT</t>
+  </si>
+  <si>
+    <t>03/30/26 13:27 EDT</t>
+  </si>
+  <si>
+    <t>03/26/26 11:54 EDT</t>
+  </si>
+  <si>
+    <t>'1197175315382829056</t>
+  </si>
+  <si>
+    <t>0.7mi W of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/26/26 12:30 EDT</t>
+  </si>
+  <si>
+    <t>'1197184519321583616</t>
+  </si>
+  <si>
+    <t>34.6mi NE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/27/26 09:34 EDT</t>
+  </si>
+  <si>
+    <t>03/27/26 09:35 EDT</t>
+  </si>
+  <si>
+    <t>03/26/26 13:09 EDT</t>
+  </si>
+  <si>
+    <t>'1197194227386318848</t>
+  </si>
+  <si>
+    <t>4.1mi E of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/27/26 09:36 EDT</t>
+  </si>
+  <si>
+    <t>03/27/26 14:47 EDT</t>
+  </si>
+  <si>
+    <t>'1197581297262952448</t>
+  </si>
+  <si>
+    <t>2.8mi SW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/30/26 11:38 EDT</t>
+  </si>
+  <si>
+    <t>03/30/26 11:56 EDT</t>
+  </si>
+  <si>
+    <t>03/27/26 19:36 EDT</t>
+  </si>
+  <si>
+    <t>'1197653971033030656</t>
+  </si>
+  <si>
+    <t>7.4mi N of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/30/26 11:40 EDT</t>
+  </si>
+  <si>
+    <t>03/30/26 11:58 EDT</t>
+  </si>
+  <si>
+    <t>03/27/26 21:02 EDT</t>
+  </si>
+  <si>
+    <t>'1197675701118074880</t>
+  </si>
+  <si>
+    <t>31.5mi N of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/28/26 08:51 EDT</t>
+  </si>
+  <si>
+    <t>'1197854108720201728</t>
+  </si>
+  <si>
+    <t>03/30/26 11:46 EDT</t>
+  </si>
+  <si>
+    <t>03/28/26 11:28 EDT</t>
+  </si>
+  <si>
+    <t>'1197893765877104640</t>
+  </si>
+  <si>
+    <t>32mi N of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/30/26 11:48 EDT</t>
+  </si>
+  <si>
+    <t>03/28/26 12:53 EDT</t>
+  </si>
+  <si>
+    <t>'1197915089001414656</t>
+  </si>
+  <si>
+    <t>03/30/26 11:50 EDT</t>
+  </si>
+  <si>
+    <t>03/28/26 12:57 EDT</t>
+  </si>
+  <si>
+    <t>'1197916033017610240</t>
+  </si>
+  <si>
+    <t>3.6mi SE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/30/26 11:49 EDT</t>
+  </si>
+  <si>
+    <t>03/28/26 15:14 EDT</t>
+  </si>
+  <si>
+    <t>'1197950481553588224</t>
+  </si>
+  <si>
+    <t>6.5mi NE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/30/26 11:52 EDT</t>
+  </si>
+  <si>
+    <t>03/30/26 09:42 EDT</t>
+  </si>
+  <si>
+    <t>'1198591744141328384</t>
+  </si>
+  <si>
+    <t>03/30/26 10:46 EDT</t>
+  </si>
+  <si>
+    <t>'1198607886381645824</t>
+  </si>
+  <si>
+    <t>2.7mi S of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/30/26 11:29 EDT</t>
+  </si>
+  <si>
+    <t>'1198618635862704128</t>
+  </si>
+  <si>
+    <t>SEVERE-TURN</t>
+  </si>
+  <si>
+    <t>3.8mi S of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/30/26 12:06 EDT</t>
+  </si>
+  <si>
+    <t>'1198627998912380928</t>
+  </si>
+  <si>
+    <t>6.4mi N of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/30/26 13:17 EDT</t>
+  </si>
+  <si>
+    <t>'1198645993827106816</t>
+  </si>
+  <si>
+    <t>32.9mi N of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/30/26 14:20 EDT</t>
+  </si>
+  <si>
+    <t>'1198661751583965184</t>
+  </si>
+  <si>
+    <t>3.2mi S of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/30/26 15:57 EDT</t>
+  </si>
+  <si>
+    <t>'1198686262815522816</t>
+  </si>
+  <si>
+    <t>37.2mi NE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/30/26 16:16 EDT</t>
+  </si>
+  <si>
+    <t>'1198690897336893440</t>
+  </si>
+  <si>
+    <t>1.3mi SE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/30/26 16:24 EDT</t>
+  </si>
+  <si>
+    <t>'1198692956895346688</t>
+  </si>
+  <si>
+    <t>6.1mi NE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/30/26 16:31 EDT</t>
+  </si>
+  <si>
+    <t>'1198694734030340096</t>
+  </si>
+  <si>
+    <t>03/30/26 18:06 EDT</t>
+  </si>
+  <si>
+    <t>'1198718646986375168</t>
+  </si>
+  <si>
+    <t>2.5mi SE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>03/30/26 18:09 EDT</t>
+  </si>
+  <si>
+    <t>'1198719407753428992</t>
+  </si>
+  <si>
+    <t>03/30/26 18:13 EDT</t>
+  </si>
+  <si>
+    <t>'1198720351492800512</t>
+  </si>
+  <si>
+    <t>03/30/26 18:17 EDT</t>
+  </si>
+  <si>
+    <t>'1198721383874592768</t>
+  </si>
+  <si>
+    <t>3.9mi SW of San Angelo TX</t>
   </si>
 </sst>
 </file>
@@ -846,7 +1293,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="13" width="15" customWidth="1"/>
@@ -1436,17 +1883,15 @@
       <c r="A19" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>47</v>
-      </c>
+      <c r="B19" s="3"/>
       <c r="C19" s="3">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>85</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>86</v>
@@ -1454,7 +1899,9 @@
       <c r="G19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H19" s="3"/>
+      <c r="H19" s="3">
+        <v>34</v>
+      </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
         <v>32</v>
@@ -1472,16 +1919,16 @@
         <v>88</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C20" s="3">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>89</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>90</v>
@@ -1506,17 +1953,15 @@
       <c r="A21" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="B21" s="3"/>
       <c r="C21" s="3">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>93</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>94</v>
@@ -1525,7 +1970,7 @@
         <v>31</v>
       </c>
       <c r="H21" s="3">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="s">
@@ -1543,11 +1988,9 @@
       <c r="A22" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>47</v>
-      </c>
+      <c r="B22" s="3"/>
       <c r="C22" s="3">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>97</v>
@@ -1556,14 +1999,12 @@
         <v>49</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H22" s="3">
-        <v>23</v>
-      </c>
+      <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="s">
         <v>32</v>
@@ -1572,19 +2013,19 @@
         <v>33</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M22" s="3"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="C23" s="3">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>101</v>
@@ -1598,9 +2039,7 @@
       <c r="G23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H23" s="3">
-        <v>49</v>
-      </c>
+      <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="s">
         <v>32</v>
@@ -1618,16 +2057,16 @@
         <v>104</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C24" s="3">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>105</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>106</v>
@@ -1636,7 +2075,7 @@
         <v>31</v>
       </c>
       <c r="H24" s="3">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
@@ -1655,25 +2094,25 @@
         <v>108</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C25" s="3">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>109</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="H25" s="3">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
@@ -1683,71 +2122,71 @@
         <v>33</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M25" s="3"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="C26" s="3">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>113</v>
       </c>
       <c r="E26" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H26" s="3">
+        <v>49</v>
+      </c>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L26" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H26" s="3">
-        <v>63</v>
-      </c>
-      <c r="I26" s="3">
-        <v>65</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="M26" s="3"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="3">
+        <v>409</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="E27" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C27" s="3">
-        <v>410</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G27" s="3"/>
+      <c r="G27" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="H27" s="3">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
@@ -1757,38 +2196,36 @@
         <v>33</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="M27" s="3"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C28" s="3">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>54</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="H28" s="3">
-        <v>70</v>
-      </c>
-      <c r="I28" s="3">
-        <v>70</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I28" s="3"/>
       <c r="J28" s="3" t="s">
         <v>32</v>
       </c>
@@ -1796,73 +2233,71 @@
         <v>33</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="M28" s="3"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" s="3">
+        <v>414</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" s="3">
-        <v>413</v>
-      </c>
-      <c r="D29" s="3" t="s">
+      <c r="G29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H29" s="3">
+        <v>63</v>
+      </c>
+      <c r="I29" s="3">
+        <v>65</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L29" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H29" s="3">
-        <v>55</v>
-      </c>
-      <c r="I29" s="3">
-        <v>75</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="M29" s="3"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C30" s="3">
+        <v>410</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C30" s="3">
-        <v>414</v>
-      </c>
-      <c r="D30" s="3" t="s">
+      <c r="F30" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E30" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>31</v>
-      </c>
+      <c r="G30" s="3"/>
       <c r="H30" s="3">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="s">
@@ -1872,58 +2307,56 @@
         <v>33</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M30" s="3"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3">
+        <v>411</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31" s="3">
-        <v>408</v>
-      </c>
-      <c r="D31" s="3" t="s">
+      <c r="E31" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F31" s="3" t="s">
+      <c r="G31" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="H31" s="3">
+        <v>63</v>
+      </c>
+      <c r="I31" s="3">
         <v>75</v>
       </c>
-      <c r="I31" s="3">
-        <v>60</v>
-      </c>
       <c r="J31" s="3" t="s">
         <v>32</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>33</v>
+        <v>139</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M31" s="3"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>141</v>
+        <v>16</v>
       </c>
       <c r="C32" s="3">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>142</v>
@@ -1938,9 +2371,11 @@
         <v>31</v>
       </c>
       <c r="H32" s="3">
-        <v>43</v>
-      </c>
-      <c r="I32" s="3"/>
+        <v>70</v>
+      </c>
+      <c r="I32" s="3">
+        <v>70</v>
+      </c>
       <c r="J32" s="3" t="s">
         <v>32</v>
       </c>
@@ -1957,27 +2392,29 @@
         <v>145</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="C33" s="3">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>146</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>49</v>
+        <v>147</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="H33" s="3">
-        <v>10</v>
-      </c>
-      <c r="I33" s="3"/>
+        <v>55</v>
+      </c>
+      <c r="I33" s="3">
+        <v>75</v>
+      </c>
       <c r="J33" s="3" t="s">
         <v>32</v>
       </c>
@@ -1985,34 +2422,34 @@
         <v>33</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M33" s="3"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="C34" s="3">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>54</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>31</v>
       </c>
       <c r="H34" s="3">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
@@ -2022,46 +2459,1473 @@
         <v>33</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M34" s="3"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>27</v>
       </c>
       <c r="C35" s="3">
+        <v>408</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H35" s="3">
+        <v>75</v>
+      </c>
+      <c r="I35" s="3">
+        <v>60</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C36" s="3">
+        <v>404</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H36" s="3">
+        <v>43</v>
+      </c>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="M36" s="3"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C37" s="3">
+        <v>414</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H37" s="3">
+        <v>10</v>
+      </c>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="M37" s="3"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" s="3">
+        <v>403</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H38" s="3">
+        <v>73</v>
+      </c>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="M38" s="3"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="3">
         <v>405</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E35" s="3" t="s">
+      <c r="D39" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F39" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="G39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H39" s="3">
         <v>44</v>
       </c>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="M35" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" s="3">
+        <v>413</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H40" s="3">
+        <v>33</v>
+      </c>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" s="3">
+        <v>405</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H41" s="3">
+        <v>33</v>
+      </c>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42" s="3">
+        <v>413</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H42" s="3">
+        <v>27</v>
+      </c>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C43" s="3">
+        <v>404</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H43" s="3">
+        <v>60</v>
+      </c>
+      <c r="I43" s="3">
+        <v>75</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C44" s="3">
+        <v>403</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H44" s="3">
+        <v>70</v>
+      </c>
+      <c r="I44" s="3">
+        <v>75</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C45" s="3">
+        <v>409</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H45" s="3">
+        <v>24</v>
+      </c>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C46" s="3">
+        <v>408</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H46" s="3">
+        <v>45</v>
+      </c>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" s="3">
+        <v>403</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H47" s="3">
+        <v>49</v>
+      </c>
+      <c r="I47" s="3">
+        <v>75</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C48" s="3">
+        <v>414</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H48" s="3">
+        <v>48</v>
+      </c>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C49" s="3">
+        <v>413</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H49" s="3">
+        <v>78</v>
+      </c>
+      <c r="I49" s="3">
+        <v>65</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C50" s="3">
+        <v>413</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H50" s="3">
+        <v>78</v>
+      </c>
+      <c r="I50" s="3">
+        <v>65</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" s="3">
+        <v>400</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H51" s="3">
+        <v>39</v>
+      </c>
+      <c r="I51" s="3">
+        <v>75</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3">
+        <v>409</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3">
+        <v>7</v>
+      </c>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C53" s="3">
+        <v>406</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H53" s="3">
+        <v>26</v>
+      </c>
+      <c r="I53" s="3">
+        <v>75</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C54" s="3">
+        <v>406</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H54" s="3">
+        <v>70</v>
+      </c>
+      <c r="I54" s="3">
+        <v>70</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C55" s="3">
+        <v>404</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H55" s="3">
+        <v>47</v>
+      </c>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C56" s="3">
+        <v>410</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H56" s="3">
+        <v>26</v>
+      </c>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3">
+        <v>405</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3">
+        <v>37</v>
+      </c>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K57" s="3"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C58" s="3">
+        <v>409</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H58" s="3">
+        <v>14</v>
+      </c>
+      <c r="I58" s="3"/>
+      <c r="J58" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" s="3">
+        <v>405</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H59" s="3">
+        <v>22</v>
+      </c>
+      <c r="I59" s="3"/>
+      <c r="J59" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C60" s="3">
+        <v>403</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H60" s="3"/>
+      <c r="I60" s="3"/>
+      <c r="J60" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C61" s="3">
+        <v>403</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H61" s="3">
+        <v>55</v>
+      </c>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" s="3">
+        <v>400</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H62" s="3">
+        <v>33</v>
+      </c>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3">
+        <v>408</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3">
+        <v>12</v>
+      </c>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K63" s="3"/>
+      <c r="L63" s="3"/>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3">
+        <v>413</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="G64" s="3"/>
+      <c r="H64" s="3">
+        <v>63</v>
+      </c>
+      <c r="I64" s="3">
+        <v>65</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K64" s="3"/>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3">
+        <v>414</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="G65" s="3"/>
+      <c r="H65" s="3">
+        <v>49</v>
+      </c>
+      <c r="I65" s="3"/>
+      <c r="J65" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K65" s="3"/>
+      <c r="L65" s="3"/>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3">
+        <v>413</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3">
+        <v>78</v>
+      </c>
+      <c r="I66" s="3">
+        <v>65</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K66" s="3"/>
+      <c r="L66" s="3"/>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3">
+        <v>413</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3">
+        <v>72</v>
+      </c>
+      <c r="I67" s="3">
+        <v>55</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K67" s="3"/>
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3">
+        <v>404</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="G68" s="3"/>
+      <c r="H68" s="3">
+        <v>16</v>
+      </c>
+      <c r="I68" s="3"/>
+      <c r="J68" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K68" s="3"/>
+      <c r="L68" s="3"/>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3">
+        <v>413</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3">
+        <v>76</v>
+      </c>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K69" s="3"/>
+      <c r="L69" s="3"/>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3">
+        <v>414</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3">
+        <v>65</v>
+      </c>
+      <c r="I70" s="3"/>
+      <c r="J70" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K70" s="3"/>
+      <c r="L70" s="3"/>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3">
+        <v>413</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3">
+        <v>78</v>
+      </c>
+      <c r="I71" s="3">
+        <v>65</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K71" s="3"/>
+      <c r="L71" s="3"/>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3">
+        <v>413</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3">
+        <v>31</v>
+      </c>
+      <c r="I72" s="3"/>
+      <c r="J72" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K72" s="3"/>
+      <c r="L72" s="3"/>
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3">
+        <v>414</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="G73" s="3"/>
+      <c r="H73" s="3">
+        <v>44</v>
+      </c>
+      <c r="I73" s="3"/>
+      <c r="J73" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K73" s="3"/>
+      <c r="L73" s="3"/>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3">
+        <v>409</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="G74" s="3"/>
+      <c r="H74" s="3">
+        <v>40</v>
+      </c>
+      <c r="I74" s="3"/>
+      <c r="J74" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K74" s="3"/>
+      <c r="L74" s="3"/>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3">
+        <v>414</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3">
+        <v>60</v>
+      </c>
+      <c r="I75" s="3">
+        <v>65</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K75" s="3"/>
+      <c r="L75" s="3"/>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3">
+        <v>414</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3">
+        <v>46</v>
+      </c>
+      <c r="I76" s="3"/>
+      <c r="J76" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K76" s="3"/>
+      <c r="L76" s="3"/>
+      <c r="M76" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Home Motors\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF5BA78C-6144-41DC-9DBF-9CA7FD7704A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{014E24AD-915D-4720-927A-C8DEF22933F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="16920" windowHeight="14565" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6718" uniqueCount="2990">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7652" uniqueCount="3337">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -8629,6 +8629,9 @@
     <t>31.470065, -100.441974</t>
   </si>
   <si>
+    <t>04/27/26 10:15 CDT</t>
+  </si>
+  <si>
     <t>04/24/26 05:35 CDT</t>
   </si>
   <si>
@@ -8638,6 +8641,9 @@
     <t>31.445203, -100.441968</t>
   </si>
   <si>
+    <t>04/27/26 10:16 CDT</t>
+  </si>
+  <si>
     <t>04/24/26 07:35 CDT</t>
   </si>
   <si>
@@ -8695,6 +8701,9 @@
     <t>31.375724, -100.345809</t>
   </si>
   <si>
+    <t>04/27/26 10:17 CDT</t>
+  </si>
+  <si>
     <t>04/24/26 11:44 CDT</t>
   </si>
   <si>
@@ -8704,6 +8713,9 @@
     <t>31.397901, -100.432990</t>
   </si>
   <si>
+    <t>04/27/26 10:18 CDT</t>
+  </si>
+  <si>
     <t>04/24/26 11:46 CDT</t>
   </si>
   <si>
@@ -8713,6 +8725,9 @@
     <t>31.419144, -100.424738</t>
   </si>
   <si>
+    <t>04/27/26 10:22 CDT</t>
+  </si>
+  <si>
     <t>04/24/26 13:08 CDT</t>
   </si>
   <si>
@@ -8737,6 +8752,9 @@
     <t>32.229430, -99.759544</t>
   </si>
   <si>
+    <t>04/27/26 10:23 CDT</t>
+  </si>
+  <si>
     <t>04/24/26 13:56 CDT</t>
   </si>
   <si>
@@ -8794,6 +8812,9 @@
     <t>31.418867, -100.401333</t>
   </si>
   <si>
+    <t>04/27/26 10:24 CDT</t>
+  </si>
+  <si>
     <t>04/24/26 16:31 CDT</t>
   </si>
   <si>
@@ -8827,6 +8848,9 @@
     <t>31.270622, -100.026358</t>
   </si>
   <si>
+    <t>04/27/26 10:25 CDT</t>
+  </si>
+  <si>
     <t>04/24/26 18:03 CDT</t>
   </si>
   <si>
@@ -8923,6 +8947,9 @@
     <t>31.424868, -100.498300</t>
   </si>
   <si>
+    <t>04/27/26 10:26 CDT</t>
+  </si>
+  <si>
     <t>04/25/26 12:51 CDT</t>
   </si>
   <si>
@@ -8935,6 +8962,9 @@
     <t>31.510086, -100.480236</t>
   </si>
   <si>
+    <t>04/27/26 10:21 CDT</t>
+  </si>
+  <si>
     <t>04/25/26 12:54 CDT</t>
   </si>
   <si>
@@ -8990,6 +9020,1017 @@
   </si>
   <si>
     <t>31.434112, -100.433858</t>
+  </si>
+  <si>
+    <t>04/26/26 15:38 CDT</t>
+  </si>
+  <si>
+    <t>'1208481023608913920</t>
+  </si>
+  <si>
+    <t>31.491380, -100.472398</t>
+  </si>
+  <si>
+    <t>04/27/26 07:19 CDT</t>
+  </si>
+  <si>
+    <t>'1208717656371396608</t>
+  </si>
+  <si>
+    <t>5.4mi W of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.416064, -100.536092</t>
+  </si>
+  <si>
+    <t>04/27/26 07:22 CDT</t>
+  </si>
+  <si>
+    <t>'1208718537074573312</t>
+  </si>
+  <si>
+    <t>3.3mi W of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.429927, -100.503983</t>
+  </si>
+  <si>
+    <t>04/28/26 06:14 CDT</t>
+  </si>
+  <si>
+    <t>04/27/26 08:58 CDT</t>
+  </si>
+  <si>
+    <t>'1208742679727472640</t>
+  </si>
+  <si>
+    <t>31.433640, -100.433447</t>
+  </si>
+  <si>
+    <t>04/28/26 05:53 CDT</t>
+  </si>
+  <si>
+    <t>04/27/26 10:06 CDT</t>
+  </si>
+  <si>
+    <t>'1208759668109901824</t>
+  </si>
+  <si>
+    <t>31.424309, -100.423055</t>
+  </si>
+  <si>
+    <t>04/27/26 10:08 CDT</t>
+  </si>
+  <si>
+    <t>'1208760303534374912</t>
+  </si>
+  <si>
+    <t>31.424221, -100.422999</t>
+  </si>
+  <si>
+    <t>04/27/26 11:12 CDT</t>
+  </si>
+  <si>
+    <t>'1208776472857313280</t>
+  </si>
+  <si>
+    <t>0.8mi S of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.431721, -100.455023</t>
+  </si>
+  <si>
+    <t>04/28/26 05:54 CDT</t>
+  </si>
+  <si>
+    <t>04/27/26 11:17 CDT</t>
+  </si>
+  <si>
+    <t>'1208777556258619392</t>
+  </si>
+  <si>
+    <t>31.6mi NE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.682560, -99.993077</t>
+  </si>
+  <si>
+    <t>04/28/26 06:15 CDT</t>
+  </si>
+  <si>
+    <t>04/27/26 13:03 CDT</t>
+  </si>
+  <si>
+    <t>'1208804319323914240</t>
+  </si>
+  <si>
+    <t>17.4mi NE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.670884, -100.325949</t>
+  </si>
+  <si>
+    <t>04/28/26 06:16 CDT</t>
+  </si>
+  <si>
+    <t>04/28/26 06:31 CDT</t>
+  </si>
+  <si>
+    <t>04/27/26 16:43 CDT</t>
+  </si>
+  <si>
+    <t>'1208859675169292288</t>
+  </si>
+  <si>
+    <t>31.422015, -100.423661</t>
+  </si>
+  <si>
+    <t>04/27/26 16:53 CDT</t>
+  </si>
+  <si>
+    <t>'1208862287306326016</t>
+  </si>
+  <si>
+    <t>8mi NW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.504630, -100.564088</t>
+  </si>
+  <si>
+    <t>04/28/26 06:17 CDT</t>
+  </si>
+  <si>
+    <t>04/27/26 18:38 CDT</t>
+  </si>
+  <si>
+    <t>'1208888609629962240</t>
+  </si>
+  <si>
+    <t>29.7mi S of Abilene TX</t>
+  </si>
+  <si>
+    <t>32.057697, -99.934395</t>
+  </si>
+  <si>
+    <t>04/28/26 08:33 CDT</t>
+  </si>
+  <si>
+    <t>'1209098747615805440</t>
+  </si>
+  <si>
+    <t>6.1mi S of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.355228, -100.434002</t>
+  </si>
+  <si>
+    <t>04/29/26 07:19 CDT</t>
+  </si>
+  <si>
+    <t>04/28/26 10:06 CDT</t>
+  </si>
+  <si>
+    <t>'1209122174502338560</t>
+  </si>
+  <si>
+    <t>19.2mi NE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.596993, -100.178734</t>
+  </si>
+  <si>
+    <t>04/28/26 10:19 CDT</t>
+  </si>
+  <si>
+    <t>'1209125527261184000</t>
+  </si>
+  <si>
+    <t>31.429831, -100.507263</t>
+  </si>
+  <si>
+    <t>04/29/26 07:20 CDT</t>
+  </si>
+  <si>
+    <t>04/28/26 10:27 CDT</t>
+  </si>
+  <si>
+    <t>'1209127497216720896</t>
+  </si>
+  <si>
+    <t>31.420974, -100.403102</t>
+  </si>
+  <si>
+    <t>04/28/26 10:33 CDT</t>
+  </si>
+  <si>
+    <t>'1209128921027739648</t>
+  </si>
+  <si>
+    <t>31.470241, -100.386301</t>
+  </si>
+  <si>
+    <t>04/29/26 07:21 CDT</t>
+  </si>
+  <si>
+    <t>04/28/26 12:09 CDT</t>
+  </si>
+  <si>
+    <t>'1209153107142017024</t>
+  </si>
+  <si>
+    <t>31.398244, -100.432832</t>
+  </si>
+  <si>
+    <t>04/28/26 12:27 CDT</t>
+  </si>
+  <si>
+    <t>'1209157796587798528</t>
+  </si>
+  <si>
+    <t>2.9mi W of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.440980, -100.499344</t>
+  </si>
+  <si>
+    <t>04/28/26 12:51 CDT</t>
+  </si>
+  <si>
+    <t>'1209163667468353536</t>
+  </si>
+  <si>
+    <t>31.442664, -100.434559</t>
+  </si>
+  <si>
+    <t>04/29/26 07:22 CDT</t>
+  </si>
+  <si>
+    <t>04/28/26 13:47 CDT</t>
+  </si>
+  <si>
+    <t>'1209177717615001600</t>
+  </si>
+  <si>
+    <t>12.4mi E of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.373269, -100.255611</t>
+  </si>
+  <si>
+    <t>04/28/26 14:04 CDT</t>
+  </si>
+  <si>
+    <t>'1209182081528266752</t>
+  </si>
+  <si>
+    <t>27.2mi NE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.646126, -100.054399</t>
+  </si>
+  <si>
+    <t>04/28/26 16:39 CDT</t>
+  </si>
+  <si>
+    <t>'1209221177889947648</t>
+  </si>
+  <si>
+    <t>31.424394, -100.422995</t>
+  </si>
+  <si>
+    <t>04/29/26 07:23 CDT</t>
+  </si>
+  <si>
+    <t>04/28/26 16:45 CDT</t>
+  </si>
+  <si>
+    <t>'1209222611964428288</t>
+  </si>
+  <si>
+    <t>31.468738, -100.442297</t>
+  </si>
+  <si>
+    <t>04/28/26 16:46 CDT</t>
+  </si>
+  <si>
+    <t>'1209222953775038464</t>
+  </si>
+  <si>
+    <t>31.482877, -100.459454</t>
+  </si>
+  <si>
+    <t>04/28/26 19:11 CDT</t>
+  </si>
+  <si>
+    <t>'1209259424154288128</t>
+  </si>
+  <si>
+    <t>11.9mi NW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.572811, -100.581908</t>
+  </si>
+  <si>
+    <t>04/29/26 08:04 CDT</t>
+  </si>
+  <si>
+    <t>'1209453963267702784</t>
+  </si>
+  <si>
+    <t>31.522620, -100.483902</t>
+  </si>
+  <si>
+    <t>04/30/26 11:32 CDT</t>
+  </si>
+  <si>
+    <t>04/29/26 13:20 CDT</t>
+  </si>
+  <si>
+    <t>'1209533278382620672</t>
+  </si>
+  <si>
+    <t>31.432825, -100.480395</t>
+  </si>
+  <si>
+    <t>04/29/26 14:46 CDT</t>
+  </si>
+  <si>
+    <t>'1209555142110773248</t>
+  </si>
+  <si>
+    <t>31.451950, -100.488600</t>
+  </si>
+  <si>
+    <t>04/29/26 17:30 CDT</t>
+  </si>
+  <si>
+    <t>'1209596224345374720</t>
+  </si>
+  <si>
+    <t>31.421226, -100.424009</t>
+  </si>
+  <si>
+    <t>04/30/26 11:34 CDT</t>
+  </si>
+  <si>
+    <t>04/30/26 11:35 CDT</t>
+  </si>
+  <si>
+    <t>04/29/26 18:33 CDT</t>
+  </si>
+  <si>
+    <t>'1209612184267685888</t>
+  </si>
+  <si>
+    <t>31.445201, -100.441976</t>
+  </si>
+  <si>
+    <t>04/30/26 08:28 CDT</t>
+  </si>
+  <si>
+    <t>'1209822278678904832</t>
+  </si>
+  <si>
+    <t>31.399352, -100.432416</t>
+  </si>
+  <si>
+    <t>04/30/26 11:33 CDT</t>
+  </si>
+  <si>
+    <t>04/30/26 08:30 CDT</t>
+  </si>
+  <si>
+    <t>'1209822910819237888</t>
+  </si>
+  <si>
+    <t>31.396330, -100.433653</t>
+  </si>
+  <si>
+    <t>04/30/26 08:31 CDT</t>
+  </si>
+  <si>
+    <t>'1209822939768324096</t>
+  </si>
+  <si>
+    <t>31.396191, -100.433430</t>
+  </si>
+  <si>
+    <t>04/30/26 08:56 CDT</t>
+  </si>
+  <si>
+    <t>'1209829310551195648</t>
+  </si>
+  <si>
+    <t>31.422377, -100.423546</t>
+  </si>
+  <si>
+    <t>05/01/26 09:22 CDT</t>
+  </si>
+  <si>
+    <t>05/01/26 09:31 CDT</t>
+  </si>
+  <si>
+    <t>04/30/26 09:07 CDT</t>
+  </si>
+  <si>
+    <t>'1209832123268235264</t>
+  </si>
+  <si>
+    <t>31.526258, -100.373293</t>
+  </si>
+  <si>
+    <t>05/01/26 09:21 CDT</t>
+  </si>
+  <si>
+    <t>04/30/26 10:09 CDT</t>
+  </si>
+  <si>
+    <t>'1209847577969852416</t>
+  </si>
+  <si>
+    <t>50.3mi SW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.129576, -101.218704</t>
+  </si>
+  <si>
+    <t>05/01/26 09:23 CDT</t>
+  </si>
+  <si>
+    <t>04/30/26 11:09 CDT</t>
+  </si>
+  <si>
+    <t>'1209862715993128960</t>
+  </si>
+  <si>
+    <t>13.7mi NW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.586008, -100.609569</t>
+  </si>
+  <si>
+    <t>05/01/26 09:24 CDT</t>
+  </si>
+  <si>
+    <t>04/30/26 12:04 CDT</t>
+  </si>
+  <si>
+    <t>'1209876767901384704</t>
+  </si>
+  <si>
+    <t>2.2mi NE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.470902, -100.432062</t>
+  </si>
+  <si>
+    <t>04/30/26 12:46 CDT</t>
+  </si>
+  <si>
+    <t>'1209887125009498112</t>
+  </si>
+  <si>
+    <t>31.444829, -100.420379</t>
+  </si>
+  <si>
+    <t>04/30/26 13:23 CDT</t>
+  </si>
+  <si>
+    <t>'1209896539632336896</t>
+  </si>
+  <si>
+    <t>31.415262, -100.470012</t>
+  </si>
+  <si>
+    <t>05/01/26 09:25 CDT</t>
+  </si>
+  <si>
+    <t>04/30/26 13:25 CDT</t>
+  </si>
+  <si>
+    <t>'1209897055397511168</t>
+  </si>
+  <si>
+    <t>31.423580, -100.482109</t>
+  </si>
+  <si>
+    <t>04/30/26 15:32 CDT</t>
+  </si>
+  <si>
+    <t>'1209929012286226432</t>
+  </si>
+  <si>
+    <t>31.424130, -100.422893</t>
+  </si>
+  <si>
+    <t>04/30/26 15:59 CDT</t>
+  </si>
+  <si>
+    <t>'1209935767443505152</t>
+  </si>
+  <si>
+    <t>31.445194, -100.442006</t>
+  </si>
+  <si>
+    <t>05/01/26 09:26 CDT</t>
+  </si>
+  <si>
+    <t>04/30/26 16:25 CDT</t>
+  </si>
+  <si>
+    <t>'1209942283785502720</t>
+  </si>
+  <si>
+    <t>31.398824, -100.432575</t>
+  </si>
+  <si>
+    <t>04/30/26 16:55 CDT</t>
+  </si>
+  <si>
+    <t>'1209949906643615744</t>
+  </si>
+  <si>
+    <t>36mi N of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.942585, -100.277001</t>
+  </si>
+  <si>
+    <t>04/30/26 17:06 CDT</t>
+  </si>
+  <si>
+    <t>'1209952646237159424</t>
+  </si>
+  <si>
+    <t>24.3mi NE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.765526, -100.288103</t>
+  </si>
+  <si>
+    <t>04/30/26 17:16 CDT</t>
+  </si>
+  <si>
+    <t>'1209955169488502784</t>
+  </si>
+  <si>
+    <t>12.2mi NE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.600494, -100.357443</t>
+  </si>
+  <si>
+    <t>05/01/26 09:27 CDT</t>
+  </si>
+  <si>
+    <t>04/30/26 17:19 CDT</t>
+  </si>
+  <si>
+    <t>'1209955952804134912</t>
+  </si>
+  <si>
+    <t>8.6mi NE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.545774, -100.369133</t>
+  </si>
+  <si>
+    <t>04/30/26 19:52 CDT</t>
+  </si>
+  <si>
+    <t>'1209994389687009280</t>
+  </si>
+  <si>
+    <t>31.4mi SE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.227426, -99.981303</t>
+  </si>
+  <si>
+    <t>05/01/26 09:39 CDT</t>
+  </si>
+  <si>
+    <t>04/30/26 19:53 CDT</t>
+  </si>
+  <si>
+    <t>'1209994676992638976</t>
+  </si>
+  <si>
+    <t>29.9mi SE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.238792, -100.002891</t>
+  </si>
+  <si>
+    <t>05/01/26 09:30 CDT</t>
+  </si>
+  <si>
+    <t>04/30/26 22:42 CDT</t>
+  </si>
+  <si>
+    <t>'1210037089819852800</t>
+  </si>
+  <si>
+    <t>31.421456, -100.373853</t>
+  </si>
+  <si>
+    <t>05/01/26 08:37 CDT</t>
+  </si>
+  <si>
+    <t>'1210186883943006208</t>
+  </si>
+  <si>
+    <t>31.497203, -100.477131</t>
+  </si>
+  <si>
+    <t>05/01/26 10:11 CDT</t>
+  </si>
+  <si>
+    <t>'1210210545110777856</t>
+  </si>
+  <si>
+    <t>13mi SE of Lamesa TX</t>
+  </si>
+  <si>
+    <t>32.601237, -101.794628</t>
+  </si>
+  <si>
+    <t>05/04/26 08:56 CDT</t>
+  </si>
+  <si>
+    <t>05/01/26 11:35 CDT</t>
+  </si>
+  <si>
+    <t>'1210231590039486464</t>
+  </si>
+  <si>
+    <t>1.5mi SW of Wolfforth TX</t>
+  </si>
+  <si>
+    <t>33.499448, -102.026210</t>
+  </si>
+  <si>
+    <t>05/01/26 11:50 CDT</t>
+  </si>
+  <si>
+    <t>'1210235427081060352</t>
+  </si>
+  <si>
+    <t>31.469364, -100.446388</t>
+  </si>
+  <si>
+    <t>05/01/26 11:55 CDT</t>
+  </si>
+  <si>
+    <t>'1210236860757082112</t>
+  </si>
+  <si>
+    <t>31.444905, -100.441875</t>
+  </si>
+  <si>
+    <t>05/01/26 11:57 CDT</t>
+  </si>
+  <si>
+    <t>'1210237393492410368</t>
+  </si>
+  <si>
+    <t>31.466778, -100.446778</t>
+  </si>
+  <si>
+    <t>05/01/26 15:02 CDT</t>
+  </si>
+  <si>
+    <t>'1210283751721041920</t>
+  </si>
+  <si>
+    <t>38.7mi SE of Big Spring TX</t>
+  </si>
+  <si>
+    <t>31.840397, -101.016439</t>
+  </si>
+  <si>
+    <t>05/01/26 16:31 CDT</t>
+  </si>
+  <si>
+    <t>'1210306208087572480</t>
+  </si>
+  <si>
+    <t>4.4mi W of Abilene TX</t>
+  </si>
+  <si>
+    <t>32.454468, -99.814602</t>
+  </si>
+  <si>
+    <t>05/04/26 09:01 CDT</t>
+  </si>
+  <si>
+    <t>05/01/26 17:26 CDT</t>
+  </si>
+  <si>
+    <t>'1210320065006829568</t>
+  </si>
+  <si>
+    <t>31.418418, -100.400906</t>
+  </si>
+  <si>
+    <t>05/04/26 08:55 CDT</t>
+  </si>
+  <si>
+    <t>05/02/26 08:10 CDT</t>
+  </si>
+  <si>
+    <t>'1210542573811302400</t>
+  </si>
+  <si>
+    <t>31.422634, -100.423445</t>
+  </si>
+  <si>
+    <t>05/04/26 08:59 CDT</t>
+  </si>
+  <si>
+    <t>05/02/26 09:45 CDT</t>
+  </si>
+  <si>
+    <t>'1210566516106493952</t>
+  </si>
+  <si>
+    <t>31.431000, -100.431456</t>
+  </si>
+  <si>
+    <t>05/02/26 09:52 CDT</t>
+  </si>
+  <si>
+    <t>'1210568247641014272</t>
+  </si>
+  <si>
+    <t>31.450748, -100.488273</t>
+  </si>
+  <si>
+    <t>05/02/26 11:01 CDT</t>
+  </si>
+  <si>
+    <t>'1210585552265576448</t>
+  </si>
+  <si>
+    <t>31.396244, -100.433590</t>
+  </si>
+  <si>
+    <t>05/02/26 11:32 CDT</t>
+  </si>
+  <si>
+    <t>'1210593338936426496</t>
+  </si>
+  <si>
+    <t>31.475553, -100.419624</t>
+  </si>
+  <si>
+    <t>05/02/26 11:43 CDT</t>
+  </si>
+  <si>
+    <t>'1210595987500990464</t>
+  </si>
+  <si>
+    <t>31.487583, -100.381183</t>
+  </si>
+  <si>
+    <t>05/02/26 12:29 CDT</t>
+  </si>
+  <si>
+    <t>'1210607709431431168</t>
+  </si>
+  <si>
+    <t>31.436497, -100.504584</t>
+  </si>
+  <si>
+    <t>05/02/26 12:30 CDT</t>
+  </si>
+  <si>
+    <t>'1210607933419847680</t>
+  </si>
+  <si>
+    <t>18.8mi NE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.594235, -100.185593</t>
+  </si>
+  <si>
+    <t>05/04/26 08:54 CDT</t>
+  </si>
+  <si>
+    <t>05/02/26 12:33 CDT</t>
+  </si>
+  <si>
+    <t>'1210608811887460352</t>
+  </si>
+  <si>
+    <t>1.4mi NW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.459099, -100.464393</t>
+  </si>
+  <si>
+    <t>05/02/26 12:37 CDT</t>
+  </si>
+  <si>
+    <t>'1210609696944324608</t>
+  </si>
+  <si>
+    <t>31.398141, -100.432921</t>
+  </si>
+  <si>
+    <t>05/02/26 13:10 CDT</t>
+  </si>
+  <si>
+    <t>'1210617955767975936</t>
+  </si>
+  <si>
+    <t>31.443147, -100.460829</t>
+  </si>
+  <si>
+    <t>05/02/26 13:23 CDT</t>
+  </si>
+  <si>
+    <t>'1210621284820615168</t>
+  </si>
+  <si>
+    <t>31.476320, -100.413513</t>
+  </si>
+  <si>
+    <t>05/02/26 13:26 CDT</t>
+  </si>
+  <si>
+    <t>'1210622088587673600</t>
+  </si>
+  <si>
+    <t>31.470320, -100.441812</t>
+  </si>
+  <si>
+    <t>05/02/26 14:46 CDT</t>
+  </si>
+  <si>
+    <t>'1210642208529743872</t>
+  </si>
+  <si>
+    <t>31.484222, -100.462403</t>
+  </si>
+  <si>
+    <t>05/04/26 08:53 CDT</t>
+  </si>
+  <si>
+    <t>05/03/26 01:26 CDT</t>
+  </si>
+  <si>
+    <t>'1210803258986233856</t>
+  </si>
+  <si>
+    <t>31.479660, -100.447948</t>
+  </si>
+  <si>
+    <t>05/03/26 07:48 CDT</t>
+  </si>
+  <si>
+    <t>'1210899255947067392</t>
+  </si>
+  <si>
+    <t>31.470108, -100.441891</t>
+  </si>
+  <si>
+    <t>05/03/26 08:22 CDT</t>
+  </si>
+  <si>
+    <t>'1210907838193500160</t>
+  </si>
+  <si>
+    <t>31.487121, -100.457868</t>
+  </si>
+  <si>
+    <t>05/03/26 09:02 CDT</t>
+  </si>
+  <si>
+    <t>'1210917994016964608</t>
+  </si>
+  <si>
+    <t>31.484333, -100.440231</t>
+  </si>
+  <si>
+    <t>05/04/26 08:58 CDT</t>
+  </si>
+  <si>
+    <t>05/03/26 09:04 CDT</t>
+  </si>
+  <si>
+    <t>'1210918530149679104</t>
+  </si>
+  <si>
+    <t>31.485366, -100.448650</t>
+  </si>
+  <si>
+    <t>05/04/26 08:57 CDT</t>
+  </si>
+  <si>
+    <t>05/03/26 11:23 CDT</t>
+  </si>
+  <si>
+    <t>'1210953420597526528</t>
+  </si>
+  <si>
+    <t>30.2mi NW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.742987, -100.823321</t>
+  </si>
+  <si>
+    <t>05/03/26 14:05 CDT</t>
+  </si>
+  <si>
+    <t>'1211036292037640192</t>
+  </si>
+  <si>
+    <t>31.432146, -100.492495</t>
+  </si>
+  <si>
+    <t>05/03/26 18:22 CDT</t>
+  </si>
+  <si>
+    <t>'1211058818239332352</t>
+  </si>
+  <si>
+    <t>4.8mi E of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.421497, -100.373053</t>
+  </si>
+  <si>
+    <t>05/03/26 18:40 CDT</t>
+  </si>
+  <si>
+    <t>'1211063351791222784</t>
+  </si>
+  <si>
+    <t>20.6mi NE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.605560, -100.156835</t>
+  </si>
+  <si>
+    <t>05/03/26 18:50 CDT</t>
+  </si>
+  <si>
+    <t>'1211065954071642112</t>
+  </si>
+  <si>
+    <t>32.7mi NE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.700888, -99.985297</t>
+  </si>
+  <si>
+    <t>05/03/26 19:09 CDT</t>
+  </si>
+  <si>
+    <t>'1211070646428270592</t>
+  </si>
+  <si>
+    <t>31.472389, -100.386792</t>
+  </si>
+  <si>
+    <t>05/04/26 08:52 CDT</t>
+  </si>
+  <si>
+    <t>05/03/26 22:15 CDT</t>
+  </si>
+  <si>
+    <t>'1211117621857124352</t>
+  </si>
+  <si>
+    <t>35.2mi NE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.729384, -99.956738</t>
+  </si>
+  <si>
+    <t>05/03/26 22:42 CDT</t>
+  </si>
+  <si>
+    <t>'1211124411449638912</t>
+  </si>
+  <si>
+    <t>4.7mi NE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.482144, -100.386609</t>
+  </si>
+  <si>
+    <t>05/04/26 09:09 CDT</t>
+  </si>
+  <si>
+    <t>'1211282264705630208</t>
+  </si>
+  <si>
+    <t>35.9mi NE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.746977, -99.956675</t>
   </si>
 </sst>
 </file>
@@ -9351,7 +10392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N745"/>
+  <dimension ref="A1:N834"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -36637,7 +37678,9 @@
       <c r="G710" s="3" t="s">
         <v>2868</v>
       </c>
-      <c r="H710" s="3"/>
+      <c r="H710" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I710" s="3">
         <v>12</v>
       </c>
@@ -36645,22 +37688,26 @@
         <v>65</v>
       </c>
       <c r="K710" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L710" s="3"/>
-      <c r="M710" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L710" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M710" s="3" t="s">
+        <v>2869</v>
+      </c>
       <c r="N710" s="3"/>
     </row>
     <row r="711" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A711" s="3" t="s">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="B711" s="3"/>
       <c r="C711" s="3">
         <v>404</v>
       </c>
       <c r="D711" s="3" t="s">
-        <v>2870</v>
+        <v>2871</v>
       </c>
       <c r="E711" s="3" t="s">
         <v>290</v>
@@ -36669,28 +37716,34 @@
         <v>325</v>
       </c>
       <c r="G711" s="3" t="s">
-        <v>2871</v>
-      </c>
-      <c r="H711" s="3"/>
+        <v>2872</v>
+      </c>
+      <c r="H711" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I711" s="3"/>
       <c r="J711" s="3"/>
       <c r="K711" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L711" s="3"/>
-      <c r="M711" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L711" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M711" s="3" t="s">
+        <v>2873</v>
+      </c>
       <c r="N711" s="3"/>
     </row>
     <row r="712" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A712" s="3" t="s">
-        <v>2872</v>
+        <v>2874</v>
       </c>
       <c r="B712" s="3"/>
       <c r="C712" s="3">
         <v>404</v>
       </c>
       <c r="D712" s="3" t="s">
-        <v>2873</v>
+        <v>2875</v>
       </c>
       <c r="E712" s="3" t="s">
         <v>290</v>
@@ -36699,30 +37752,36 @@
         <v>1834</v>
       </c>
       <c r="G712" s="3" t="s">
-        <v>2874</v>
-      </c>
-      <c r="H712" s="3"/>
+        <v>2876</v>
+      </c>
+      <c r="H712" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I712" s="3">
         <v>19</v>
       </c>
       <c r="J712" s="3"/>
       <c r="K712" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L712" s="3"/>
-      <c r="M712" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L712" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M712" s="3" t="s">
+        <v>2873</v>
+      </c>
       <c r="N712" s="3"/>
     </row>
     <row r="713" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A713" s="3" t="s">
-        <v>2875</v>
+        <v>2877</v>
       </c>
       <c r="B713" s="3"/>
       <c r="C713" s="3">
         <v>405</v>
       </c>
       <c r="D713" s="3" t="s">
-        <v>2876</v>
+        <v>2878</v>
       </c>
       <c r="E713" s="3" t="s">
         <v>225</v>
@@ -36731,30 +37790,36 @@
         <v>2049</v>
       </c>
       <c r="G713" s="3" t="s">
-        <v>2877</v>
-      </c>
-      <c r="H713" s="3"/>
+        <v>2879</v>
+      </c>
+      <c r="H713" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I713" s="3">
         <v>38</v>
       </c>
       <c r="J713" s="3"/>
       <c r="K713" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L713" s="3"/>
-      <c r="M713" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L713" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M713" s="3" t="s">
+        <v>2873</v>
+      </c>
       <c r="N713" s="3"/>
     </row>
     <row r="714" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A714" s="3" t="s">
-        <v>2875</v>
+        <v>2877</v>
       </c>
       <c r="B714" s="3"/>
       <c r="C714" s="3">
         <v>405</v>
       </c>
       <c r="D714" s="3" t="s">
-        <v>2878</v>
+        <v>2880</v>
       </c>
       <c r="E714" s="3" t="s">
         <v>290</v>
@@ -36763,30 +37828,36 @@
         <v>1610</v>
       </c>
       <c r="G714" s="3" t="s">
-        <v>2879</v>
-      </c>
-      <c r="H714" s="3"/>
+        <v>2881</v>
+      </c>
+      <c r="H714" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I714" s="3">
         <v>10</v>
       </c>
       <c r="J714" s="3"/>
       <c r="K714" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L714" s="3"/>
-      <c r="M714" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L714" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M714" s="3" t="s">
+        <v>2873</v>
+      </c>
       <c r="N714" s="3"/>
     </row>
     <row r="715" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A715" s="3" t="s">
-        <v>2880</v>
+        <v>2882</v>
       </c>
       <c r="B715" s="3"/>
       <c r="C715" s="3">
         <v>413</v>
       </c>
       <c r="D715" s="3" t="s">
-        <v>2881</v>
+        <v>2883</v>
       </c>
       <c r="E715" s="3" t="s">
         <v>1150</v>
@@ -36795,73 +37866,89 @@
         <v>1804</v>
       </c>
       <c r="G715" s="3" t="s">
-        <v>2882</v>
-      </c>
-      <c r="H715" s="3"/>
+        <v>2884</v>
+      </c>
+      <c r="H715" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I715" s="3">
         <v>18</v>
       </c>
       <c r="J715" s="3"/>
       <c r="K715" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L715" s="3"/>
-      <c r="M715" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L715" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M715" s="3" t="s">
+        <v>2873</v>
+      </c>
       <c r="N715" s="3"/>
     </row>
     <row r="716" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A716" s="3" t="s">
-        <v>2883</v>
+        <v>2885</v>
       </c>
       <c r="B716" s="3"/>
       <c r="C716" s="3">
         <v>413</v>
       </c>
       <c r="D716" s="3" t="s">
-        <v>2884</v>
+        <v>2886</v>
       </c>
       <c r="E716" s="3" t="s">
         <v>1150</v>
       </c>
       <c r="F716" s="3" t="s">
-        <v>2885</v>
+        <v>2887</v>
       </c>
       <c r="G716" s="3" t="s">
-        <v>2886</v>
-      </c>
-      <c r="H716" s="3"/>
+        <v>2888</v>
+      </c>
+      <c r="H716" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I716" s="3">
         <v>48</v>
       </c>
       <c r="J716" s="3"/>
       <c r="K716" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L716" s="3"/>
-      <c r="M716" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L716" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M716" s="3" t="s">
+        <v>2873</v>
+      </c>
       <c r="N716" s="3"/>
     </row>
     <row r="717" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A717" s="3" t="s">
-        <v>2887</v>
-      </c>
-      <c r="B717" s="3"/>
+        <v>2889</v>
+      </c>
+      <c r="B717" s="3" t="s">
+        <v>295</v>
+      </c>
       <c r="C717" s="3">
         <v>413</v>
       </c>
       <c r="D717" s="3" t="s">
-        <v>2888</v>
+        <v>2890</v>
       </c>
       <c r="E717" s="3" t="s">
         <v>1150</v>
       </c>
       <c r="F717" s="3" t="s">
-        <v>2889</v>
+        <v>2891</v>
       </c>
       <c r="G717" s="3" t="s">
-        <v>2890</v>
-      </c>
-      <c r="H717" s="3"/>
+        <v>2892</v>
+      </c>
+      <c r="H717" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="I717" s="3">
         <v>78</v>
       </c>
@@ -36869,22 +37956,26 @@
         <v>75</v>
       </c>
       <c r="K717" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L717" s="3"/>
-      <c r="M717" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L717" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M717" s="3" t="s">
+        <v>2893</v>
+      </c>
       <c r="N717" s="3"/>
     </row>
     <row r="718" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A718" s="3" t="s">
-        <v>2891</v>
+        <v>2894</v>
       </c>
       <c r="B718" s="3"/>
       <c r="C718" s="3">
         <v>413</v>
       </c>
       <c r="D718" s="3" t="s">
-        <v>2892</v>
+        <v>2895</v>
       </c>
       <c r="E718" s="3" t="s">
         <v>1150</v>
@@ -36893,28 +37984,34 @@
         <v>1804</v>
       </c>
       <c r="G718" s="3" t="s">
-        <v>2893</v>
-      </c>
-      <c r="H718" s="3"/>
+        <v>2896</v>
+      </c>
+      <c r="H718" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I718" s="3"/>
       <c r="J718" s="3"/>
       <c r="K718" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L718" s="3"/>
-      <c r="M718" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L718" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M718" s="3" t="s">
+        <v>2897</v>
+      </c>
       <c r="N718" s="3"/>
     </row>
     <row r="719" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A719" s="3" t="s">
-        <v>2894</v>
+        <v>2898</v>
       </c>
       <c r="B719" s="3"/>
       <c r="C719" s="3">
         <v>413</v>
       </c>
       <c r="D719" s="3" t="s">
-        <v>2895</v>
+        <v>2899</v>
       </c>
       <c r="E719" s="3" t="s">
         <v>76</v>
@@ -36923,105 +38020,127 @@
         <v>28</v>
       </c>
       <c r="G719" s="3" t="s">
-        <v>2896</v>
-      </c>
-      <c r="H719" s="3"/>
+        <v>2900</v>
+      </c>
+      <c r="H719" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I719" s="3">
         <v>20</v>
       </c>
       <c r="J719" s="3"/>
       <c r="K719" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L719" s="3"/>
-      <c r="M719" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L719" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M719" s="3" t="s">
+        <v>2901</v>
+      </c>
       <c r="N719" s="3"/>
     </row>
     <row r="720" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A720" s="3" t="s">
-        <v>2897</v>
+        <v>2902</v>
       </c>
       <c r="B720" s="3"/>
       <c r="C720" s="3">
         <v>413</v>
       </c>
       <c r="D720" s="3" t="s">
-        <v>2898</v>
+        <v>2903</v>
       </c>
       <c r="E720" s="3" t="s">
         <v>290</v>
       </c>
       <c r="F720" s="3" t="s">
-        <v>2899</v>
+        <v>2904</v>
       </c>
       <c r="G720" s="3" t="s">
-        <v>2900</v>
-      </c>
-      <c r="H720" s="3"/>
+        <v>2905</v>
+      </c>
+      <c r="H720" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I720" s="3">
         <v>27</v>
       </c>
       <c r="J720" s="3"/>
       <c r="K720" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L720" s="3"/>
-      <c r="M720" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L720" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M720" s="3" t="s">
+        <v>2901</v>
+      </c>
       <c r="N720" s="3"/>
     </row>
     <row r="721" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A721" s="3" t="s">
-        <v>2901</v>
-      </c>
-      <c r="B721" s="3"/>
+        <v>2906</v>
+      </c>
+      <c r="B721" s="3" t="s">
+        <v>338</v>
+      </c>
       <c r="C721" s="3">
         <v>403</v>
       </c>
       <c r="D721" s="3" t="s">
-        <v>2902</v>
+        <v>2907</v>
       </c>
       <c r="E721" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F721" s="3" t="s">
-        <v>2903</v>
+        <v>2908</v>
       </c>
       <c r="G721" s="3" t="s">
-        <v>2904</v>
-      </c>
-      <c r="H721" s="3"/>
+        <v>2909</v>
+      </c>
+      <c r="H721" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="I721" s="3">
         <v>61</v>
       </c>
       <c r="J721" s="3"/>
       <c r="K721" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L721" s="3"/>
-      <c r="M721" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L721" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M721" s="3" t="s">
+        <v>2910</v>
+      </c>
       <c r="N721" s="3"/>
     </row>
     <row r="722" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A722" s="3" t="s">
-        <v>2905</v>
+        <v>2911</v>
       </c>
       <c r="B722" s="3"/>
       <c r="C722" s="3">
         <v>414</v>
       </c>
       <c r="D722" s="3" t="s">
-        <v>2906</v>
+        <v>2912</v>
       </c>
       <c r="E722" s="3" t="s">
         <v>211</v>
       </c>
       <c r="F722" s="3" t="s">
-        <v>2907</v>
+        <v>2913</v>
       </c>
       <c r="G722" s="3" t="s">
-        <v>2908</v>
-      </c>
-      <c r="H722" s="3"/>
+        <v>2914</v>
+      </c>
+      <c r="H722" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I722" s="3">
         <v>78</v>
       </c>
@@ -37029,86 +38148,104 @@
         <v>65</v>
       </c>
       <c r="K722" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L722" s="3"/>
-      <c r="M722" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L722" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M722" s="3" t="s">
+        <v>2910</v>
+      </c>
       <c r="N722" s="3"/>
     </row>
     <row r="723" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A723" s="3" t="s">
-        <v>2909</v>
+        <v>2915</v>
       </c>
       <c r="B723" s="3"/>
       <c r="C723" s="3">
         <v>414</v>
       </c>
       <c r="D723" s="3" t="s">
-        <v>2910</v>
+        <v>2916</v>
       </c>
       <c r="E723" s="3" t="s">
         <v>211</v>
       </c>
       <c r="F723" s="3" t="s">
-        <v>2911</v>
+        <v>2917</v>
       </c>
       <c r="G723" s="3" t="s">
-        <v>2912</v>
-      </c>
-      <c r="H723" s="3"/>
+        <v>2918</v>
+      </c>
+      <c r="H723" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I723" s="3">
         <v>60</v>
       </c>
       <c r="J723" s="3"/>
       <c r="K723" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L723" s="3"/>
-      <c r="M723" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L723" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M723" s="3" t="s">
+        <v>2910</v>
+      </c>
       <c r="N723" s="3"/>
     </row>
     <row r="724" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A724" s="3" t="s">
-        <v>2913</v>
+        <v>2919</v>
       </c>
       <c r="B724" s="3"/>
       <c r="C724" s="3">
         <v>413</v>
       </c>
       <c r="D724" s="3" t="s">
-        <v>2914</v>
+        <v>2920</v>
       </c>
       <c r="E724" s="3" t="s">
         <v>290</v>
       </c>
       <c r="F724" s="3" t="s">
-        <v>2915</v>
+        <v>2921</v>
       </c>
       <c r="G724" s="3" t="s">
-        <v>2916</v>
-      </c>
-      <c r="H724" s="3"/>
+        <v>2922</v>
+      </c>
+      <c r="H724" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I724" s="3">
         <v>16</v>
       </c>
       <c r="J724" s="3"/>
       <c r="K724" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L724" s="3"/>
-      <c r="M724" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L724" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M724" s="3" t="s">
+        <v>2901</v>
+      </c>
       <c r="N724" s="3"/>
     </row>
     <row r="725" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A725" s="3" t="s">
-        <v>2917</v>
-      </c>
-      <c r="B725" s="3"/>
+        <v>2923</v>
+      </c>
+      <c r="B725" s="3" t="s">
+        <v>295</v>
+      </c>
       <c r="C725" s="3">
         <v>413</v>
       </c>
       <c r="D725" s="3" t="s">
-        <v>2918</v>
+        <v>2924</v>
       </c>
       <c r="E725" s="3" t="s">
         <v>76</v>
@@ -37117,62 +38254,76 @@
         <v>238</v>
       </c>
       <c r="G725" s="3" t="s">
-        <v>2919</v>
-      </c>
-      <c r="H725" s="3"/>
+        <v>2925</v>
+      </c>
+      <c r="H725" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="I725" s="3">
         <v>33</v>
       </c>
       <c r="J725" s="3"/>
       <c r="K725" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L725" s="3"/>
-      <c r="M725" s="3"/>
-      <c r="N725" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L725" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M725" s="3" t="s">
+        <v>2897</v>
+      </c>
+      <c r="N725" s="3" t="s">
+        <v>2901</v>
+      </c>
     </row>
     <row r="726" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A726" s="3" t="s">
-        <v>2920</v>
+        <v>2926</v>
       </c>
       <c r="B726" s="3"/>
       <c r="C726" s="3">
         <v>403</v>
       </c>
       <c r="D726" s="3" t="s">
-        <v>2921</v>
+        <v>2927</v>
       </c>
       <c r="E726" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F726" s="3" t="s">
-        <v>2922</v>
+        <v>2928</v>
       </c>
       <c r="G726" s="3" t="s">
-        <v>2923</v>
-      </c>
-      <c r="H726" s="3"/>
+        <v>2929</v>
+      </c>
+      <c r="H726" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I726" s="3">
         <v>27</v>
       </c>
       <c r="J726" s="3"/>
       <c r="K726" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L726" s="3"/>
-      <c r="M726" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L726" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M726" s="3" t="s">
+        <v>2930</v>
+      </c>
       <c r="N726" s="3"/>
     </row>
     <row r="727" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A727" s="3" t="s">
-        <v>2924</v>
+        <v>2931</v>
       </c>
       <c r="B727" s="3"/>
       <c r="C727" s="3">
         <v>410</v>
       </c>
       <c r="D727" s="3" t="s">
-        <v>2925</v>
+        <v>2932</v>
       </c>
       <c r="E727" s="3" t="s">
         <v>225</v>
@@ -37181,39 +38332,47 @@
         <v>2619</v>
       </c>
       <c r="G727" s="3" t="s">
-        <v>2926</v>
-      </c>
-      <c r="H727" s="3"/>
+        <v>2933</v>
+      </c>
+      <c r="H727" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I727" s="3"/>
       <c r="J727" s="3"/>
       <c r="K727" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L727" s="3"/>
-      <c r="M727" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L727" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M727" s="3" t="s">
+        <v>2930</v>
+      </c>
       <c r="N727" s="3"/>
     </row>
     <row r="728" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A728" s="3" t="s">
-        <v>2927</v>
+        <v>2934</v>
       </c>
       <c r="B728" s="3"/>
       <c r="C728" s="3">
         <v>414</v>
       </c>
       <c r="D728" s="3" t="s">
-        <v>2928</v>
+        <v>2935</v>
       </c>
       <c r="E728" s="3" t="s">
         <v>1800</v>
       </c>
       <c r="F728" s="3" t="s">
-        <v>2929</v>
+        <v>2936</v>
       </c>
       <c r="G728" s="3" t="s">
-        <v>2930</v>
-      </c>
-      <c r="H728" s="3"/>
+        <v>2937</v>
+      </c>
+      <c r="H728" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I728" s="3">
         <v>77</v>
       </c>
@@ -37221,33 +38380,39 @@
         <v>75</v>
       </c>
       <c r="K728" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L728" s="3"/>
-      <c r="M728" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L728" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M728" s="3" t="s">
+        <v>2930</v>
+      </c>
       <c r="N728" s="3"/>
     </row>
     <row r="729" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A729" s="3" t="s">
-        <v>2931</v>
+        <v>2938</v>
       </c>
       <c r="B729" s="3"/>
       <c r="C729" s="3">
         <v>414</v>
       </c>
       <c r="D729" s="3" t="s">
-        <v>2932</v>
+        <v>2939</v>
       </c>
       <c r="E729" s="3" t="s">
         <v>1800</v>
       </c>
       <c r="F729" s="3" t="s">
-        <v>2933</v>
+        <v>2940</v>
       </c>
       <c r="G729" s="3" t="s">
-        <v>2934</v>
-      </c>
-      <c r="H729" s="3"/>
+        <v>2941</v>
+      </c>
+      <c r="H729" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I729" s="3">
         <v>77</v>
       </c>
@@ -37255,22 +38420,26 @@
         <v>75</v>
       </c>
       <c r="K729" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L729" s="3"/>
-      <c r="M729" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L729" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M729" s="3" t="s">
+        <v>2942</v>
+      </c>
       <c r="N729" s="3"/>
     </row>
     <row r="730" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A730" s="3" t="s">
-        <v>2935</v>
+        <v>2943</v>
       </c>
       <c r="B730" s="3"/>
       <c r="C730" s="3">
         <v>404</v>
       </c>
       <c r="D730" s="3" t="s">
-        <v>2936</v>
+        <v>2944</v>
       </c>
       <c r="E730" s="3" t="s">
         <v>290</v>
@@ -37279,73 +38448,87 @@
         <v>2545</v>
       </c>
       <c r="G730" s="3" t="s">
-        <v>2937</v>
-      </c>
-      <c r="H730" s="3"/>
+        <v>2945</v>
+      </c>
+      <c r="H730" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I730" s="3">
         <v>29</v>
       </c>
       <c r="J730" s="3"/>
       <c r="K730" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L730" s="3"/>
-      <c r="M730" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L730" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M730" s="3" t="s">
+        <v>2942</v>
+      </c>
       <c r="N730" s="3"/>
     </row>
     <row r="731" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A731" s="3" t="s">
-        <v>2938</v>
+        <v>2946</v>
       </c>
       <c r="B731" s="3"/>
       <c r="C731" s="3">
         <v>404</v>
       </c>
       <c r="D731" s="3" t="s">
-        <v>2939</v>
+        <v>2947</v>
       </c>
       <c r="E731" s="3" t="s">
         <v>290</v>
       </c>
       <c r="F731" s="3" t="s">
-        <v>2940</v>
+        <v>2948</v>
       </c>
       <c r="G731" s="3" t="s">
-        <v>2941</v>
-      </c>
-      <c r="H731" s="3"/>
+        <v>2949</v>
+      </c>
+      <c r="H731" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I731" s="3">
         <v>36</v>
       </c>
       <c r="J731" s="3"/>
       <c r="K731" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L731" s="3"/>
-      <c r="M731" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L731" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M731" s="3" t="s">
+        <v>2942</v>
+      </c>
       <c r="N731" s="3"/>
     </row>
     <row r="732" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A732" s="3" t="s">
-        <v>2942</v>
+        <v>2950</v>
       </c>
       <c r="B732" s="3"/>
       <c r="C732" s="3">
         <v>403</v>
       </c>
       <c r="D732" s="3" t="s">
-        <v>2943</v>
+        <v>2951</v>
       </c>
       <c r="E732" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F732" s="3" t="s">
-        <v>2944</v>
+        <v>2952</v>
       </c>
       <c r="G732" s="3" t="s">
-        <v>2945</v>
-      </c>
-      <c r="H732" s="3"/>
+        <v>2953</v>
+      </c>
+      <c r="H732" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I732" s="3">
         <v>59</v>
       </c>
@@ -37353,33 +38536,39 @@
         <v>70</v>
       </c>
       <c r="K732" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L732" s="3"/>
-      <c r="M732" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L732" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M732" s="3" t="s">
+        <v>2942</v>
+      </c>
       <c r="N732" s="3"/>
     </row>
     <row r="733" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A733" s="3" t="s">
-        <v>2946</v>
+        <v>2954</v>
       </c>
       <c r="B733" s="3"/>
       <c r="C733" s="3">
         <v>403</v>
       </c>
       <c r="D733" s="3" t="s">
-        <v>2947</v>
+        <v>2955</v>
       </c>
       <c r="E733" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F733" s="3" t="s">
-        <v>2948</v>
+        <v>2956</v>
       </c>
       <c r="G733" s="3" t="s">
-        <v>2949</v>
-      </c>
-      <c r="H733" s="3"/>
+        <v>2957</v>
+      </c>
+      <c r="H733" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I733" s="3">
         <v>64</v>
       </c>
@@ -37387,22 +38576,26 @@
         <v>70</v>
       </c>
       <c r="K733" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L733" s="3"/>
-      <c r="M733" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L733" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M733" s="3" t="s">
+        <v>2942</v>
+      </c>
       <c r="N733" s="3"/>
     </row>
     <row r="734" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A734" s="3" t="s">
-        <v>2950</v>
+        <v>2958</v>
       </c>
       <c r="B734" s="3"/>
       <c r="C734" s="3">
         <v>404</v>
       </c>
       <c r="D734" s="3" t="s">
-        <v>2951</v>
+        <v>2959</v>
       </c>
       <c r="E734" s="3" t="s">
         <v>290</v>
@@ -37411,30 +38604,36 @@
         <v>388</v>
       </c>
       <c r="G734" s="3" t="s">
-        <v>2952</v>
-      </c>
-      <c r="H734" s="3"/>
+        <v>2960</v>
+      </c>
+      <c r="H734" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I734" s="3">
         <v>25</v>
       </c>
       <c r="J734" s="3"/>
       <c r="K734" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L734" s="3"/>
-      <c r="M734" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L734" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M734" s="3" t="s">
+        <v>2942</v>
+      </c>
       <c r="N734" s="3"/>
     </row>
     <row r="735" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A735" s="3" t="s">
-        <v>2953</v>
+        <v>2961</v>
       </c>
       <c r="B735" s="3"/>
       <c r="C735" s="3">
         <v>404</v>
       </c>
       <c r="D735" s="3" t="s">
-        <v>2954</v>
+        <v>2962</v>
       </c>
       <c r="E735" s="3" t="s">
         <v>68</v>
@@ -37443,94 +38642,112 @@
         <v>1774</v>
       </c>
       <c r="G735" s="3" t="s">
-        <v>2955</v>
-      </c>
-      <c r="H735" s="3"/>
+        <v>2963</v>
+      </c>
+      <c r="H735" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I735" s="3">
         <v>4</v>
       </c>
       <c r="J735" s="3"/>
       <c r="K735" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L735" s="3"/>
-      <c r="M735" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L735" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M735" s="3" t="s">
+        <v>2942</v>
+      </c>
       <c r="N735" s="3"/>
     </row>
     <row r="736" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A736" s="3" t="s">
-        <v>2956</v>
+        <v>2964</v>
       </c>
       <c r="B736" s="3"/>
       <c r="C736" s="3">
         <v>403</v>
       </c>
       <c r="D736" s="3" t="s">
-        <v>2957</v>
+        <v>2965</v>
       </c>
       <c r="E736" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F736" s="3" t="s">
-        <v>2958</v>
+        <v>2966</v>
       </c>
       <c r="G736" s="3" t="s">
-        <v>2959</v>
-      </c>
-      <c r="H736" s="3"/>
+        <v>2967</v>
+      </c>
+      <c r="H736" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I736" s="3">
         <v>60</v>
       </c>
       <c r="J736" s="3"/>
       <c r="K736" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L736" s="3"/>
-      <c r="M736" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L736" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M736" s="3" t="s">
+        <v>2942</v>
+      </c>
       <c r="N736" s="3"/>
     </row>
     <row r="737" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A737" s="3" t="s">
-        <v>2960</v>
+        <v>2968</v>
       </c>
       <c r="B737" s="3"/>
       <c r="C737" s="3">
         <v>405</v>
       </c>
       <c r="D737" s="3" t="s">
-        <v>2961</v>
+        <v>2969</v>
       </c>
       <c r="E737" s="3" t="s">
         <v>145</v>
       </c>
       <c r="F737" s="3" t="s">
-        <v>2962</v>
+        <v>2970</v>
       </c>
       <c r="G737" s="3" t="s">
-        <v>2963</v>
-      </c>
-      <c r="H737" s="3"/>
+        <v>2971</v>
+      </c>
+      <c r="H737" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I737" s="3">
         <v>43</v>
       </c>
       <c r="J737" s="3"/>
       <c r="K737" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L737" s="3"/>
-      <c r="M737" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L737" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M737" s="3" t="s">
+        <v>2942</v>
+      </c>
       <c r="N737" s="3"/>
     </row>
     <row r="738" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A738" s="3" t="s">
-        <v>2964</v>
+        <v>2972</v>
       </c>
       <c r="B738" s="3"/>
       <c r="C738" s="3">
         <v>409</v>
       </c>
       <c r="D738" s="3" t="s">
-        <v>2965</v>
+        <v>2973</v>
       </c>
       <c r="E738" s="3" t="s">
         <v>1150</v>
@@ -37539,9 +38756,11 @@
         <v>1037</v>
       </c>
       <c r="G738" s="3" t="s">
-        <v>2966</v>
-      </c>
-      <c r="H738" s="3"/>
+        <v>2974</v>
+      </c>
+      <c r="H738" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I738" s="3">
         <v>57</v>
       </c>
@@ -37549,33 +38768,41 @@
         <v>65</v>
       </c>
       <c r="K738" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L738" s="3"/>
-      <c r="M738" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L738" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M738" s="3" t="s">
+        <v>2975</v>
+      </c>
       <c r="N738" s="3"/>
     </row>
     <row r="739" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A739" s="3" t="s">
-        <v>2967</v>
-      </c>
-      <c r="B739" s="3"/>
+        <v>2976</v>
+      </c>
+      <c r="B739" s="3" t="s">
+        <v>348</v>
+      </c>
       <c r="C739" s="3">
         <v>413</v>
       </c>
       <c r="D739" s="3" t="s">
-        <v>2968</v>
+        <v>2977</v>
       </c>
       <c r="E739" s="3" t="s">
         <v>211</v>
       </c>
       <c r="F739" s="3" t="s">
-        <v>2969</v>
+        <v>2978</v>
       </c>
       <c r="G739" s="3" t="s">
-        <v>2970</v>
-      </c>
-      <c r="H739" s="3"/>
+        <v>2979</v>
+      </c>
+      <c r="H739" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="I739" s="3">
         <v>73</v>
       </c>
@@ -37583,22 +38810,28 @@
         <v>65</v>
       </c>
       <c r="K739" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L739" s="3"/>
-      <c r="M739" s="3"/>
-      <c r="N739" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L739" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M739" s="3" t="s">
+        <v>2980</v>
+      </c>
+      <c r="N739" s="3" t="s">
+        <v>2901</v>
+      </c>
     </row>
     <row r="740" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A740" s="3" t="s">
-        <v>2971</v>
+        <v>2981</v>
       </c>
       <c r="B740" s="3"/>
       <c r="C740" s="3">
         <v>413</v>
       </c>
       <c r="D740" s="3" t="s">
-        <v>2972</v>
+        <v>2982</v>
       </c>
       <c r="E740" s="3" t="s">
         <v>225</v>
@@ -37607,28 +38840,34 @@
         <v>1995</v>
       </c>
       <c r="G740" s="3" t="s">
-        <v>2973</v>
-      </c>
-      <c r="H740" s="3"/>
+        <v>2983</v>
+      </c>
+      <c r="H740" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I740" s="3"/>
       <c r="J740" s="3"/>
       <c r="K740" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L740" s="3"/>
-      <c r="M740" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L740" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M740" s="3" t="s">
+        <v>2901</v>
+      </c>
       <c r="N740" s="3"/>
     </row>
     <row r="741" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A741" s="3" t="s">
-        <v>2974</v>
+        <v>2984</v>
       </c>
       <c r="B741" s="3"/>
       <c r="C741" s="3">
         <v>413</v>
       </c>
       <c r="D741" s="3" t="s">
-        <v>2975</v>
+        <v>2985</v>
       </c>
       <c r="E741" s="3" t="s">
         <v>290</v>
@@ -37637,30 +38876,36 @@
         <v>325</v>
       </c>
       <c r="G741" s="3" t="s">
-        <v>2976</v>
-      </c>
-      <c r="H741" s="3"/>
+        <v>2986</v>
+      </c>
+      <c r="H741" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I741" s="3">
         <v>30</v>
       </c>
       <c r="J741" s="3"/>
       <c r="K741" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L741" s="3"/>
-      <c r="M741" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L741" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M741" s="3" t="s">
+        <v>2901</v>
+      </c>
       <c r="N741" s="3"/>
     </row>
     <row r="742" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A742" s="3" t="s">
-        <v>2977</v>
+        <v>2987</v>
       </c>
       <c r="B742" s="3"/>
       <c r="C742" s="3">
         <v>411</v>
       </c>
       <c r="D742" s="3" t="s">
-        <v>2978</v>
+        <v>2988</v>
       </c>
       <c r="E742" s="3" t="s">
         <v>76</v>
@@ -37669,30 +38914,36 @@
         <v>2504</v>
       </c>
       <c r="G742" s="3" t="s">
-        <v>2979</v>
-      </c>
-      <c r="H742" s="3"/>
+        <v>2989</v>
+      </c>
+      <c r="H742" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I742" s="3">
         <v>29</v>
       </c>
       <c r="J742" s="3"/>
       <c r="K742" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L742" s="3"/>
-      <c r="M742" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L742" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M742" s="3" t="s">
+        <v>2975</v>
+      </c>
       <c r="N742" s="3"/>
     </row>
     <row r="743" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A743" s="3" t="s">
-        <v>2980</v>
+        <v>2990</v>
       </c>
       <c r="B743" s="3"/>
       <c r="C743" s="3">
         <v>413</v>
       </c>
       <c r="D743" s="3" t="s">
-        <v>2981</v>
+        <v>2991</v>
       </c>
       <c r="E743" s="3" t="s">
         <v>211</v>
@@ -37701,30 +38952,36 @@
         <v>796</v>
       </c>
       <c r="G743" s="3" t="s">
-        <v>2982</v>
-      </c>
-      <c r="H743" s="3"/>
+        <v>2992</v>
+      </c>
+      <c r="H743" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I743" s="3">
         <v>78</v>
       </c>
       <c r="J743" s="3"/>
       <c r="K743" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L743" s="3"/>
-      <c r="M743" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L743" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M743" s="3" t="s">
+        <v>2901</v>
+      </c>
       <c r="N743" s="3"/>
     </row>
     <row r="744" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A744" s="3" t="s">
-        <v>2983</v>
+        <v>2993</v>
       </c>
       <c r="B744" s="3"/>
       <c r="C744" s="3">
         <v>413</v>
       </c>
       <c r="D744" s="3" t="s">
-        <v>2984</v>
+        <v>2994</v>
       </c>
       <c r="E744" s="3" t="s">
         <v>211</v>
@@ -37733,39 +38990,47 @@
         <v>2165</v>
       </c>
       <c r="G744" s="3" t="s">
-        <v>2985</v>
-      </c>
-      <c r="H744" s="3"/>
+        <v>2995</v>
+      </c>
+      <c r="H744" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I744" s="3"/>
       <c r="J744" s="3"/>
       <c r="K744" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L744" s="3"/>
-      <c r="M744" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L744" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M744" s="3" t="s">
+        <v>2901</v>
+      </c>
       <c r="N744" s="3"/>
     </row>
     <row r="745" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A745" s="3" t="s">
-        <v>2986</v>
+        <v>2996</v>
       </c>
       <c r="B745" s="3"/>
       <c r="C745" s="3">
         <v>413</v>
       </c>
       <c r="D745" s="3" t="s">
-        <v>2987</v>
+        <v>2997</v>
       </c>
       <c r="E745" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F745" s="3" t="s">
-        <v>2988</v>
+        <v>2998</v>
       </c>
       <c r="G745" s="3" t="s">
-        <v>2989</v>
-      </c>
-      <c r="H745" s="3"/>
+        <v>2999</v>
+      </c>
+      <c r="H745" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I745" s="3">
         <v>49</v>
       </c>
@@ -37773,11 +39038,3447 @@
         <v>50</v>
       </c>
       <c r="K745" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L745" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M745" s="3" t="s">
+        <v>2901</v>
+      </c>
+      <c r="N745" s="3"/>
+    </row>
+    <row r="746" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A746" s="3" t="s">
+        <v>3000</v>
+      </c>
+      <c r="B746" s="3"/>
+      <c r="C746" s="3">
+        <v>409</v>
+      </c>
+      <c r="D746" s="3" t="s">
+        <v>3001</v>
+      </c>
+      <c r="E746" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F746" s="3" t="s">
+        <v>2627</v>
+      </c>
+      <c r="G746" s="3" t="s">
+        <v>3002</v>
+      </c>
+      <c r="H746" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I746" s="3">
+        <v>54</v>
+      </c>
+      <c r="J746" s="3">
+        <v>55</v>
+      </c>
+      <c r="K746" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L746" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M746" s="3" t="s">
+        <v>2975</v>
+      </c>
+      <c r="N746" s="3"/>
+    </row>
+    <row r="747" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A747" s="3" t="s">
+        <v>3003</v>
+      </c>
+      <c r="B747" s="3"/>
+      <c r="C747" s="3">
+        <v>403</v>
+      </c>
+      <c r="D747" s="3" t="s">
+        <v>3004</v>
+      </c>
+      <c r="E747" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F747" s="3" t="s">
+        <v>3005</v>
+      </c>
+      <c r="G747" s="3" t="s">
+        <v>3006</v>
+      </c>
+      <c r="H747" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I747" s="3">
+        <v>54</v>
+      </c>
+      <c r="J747" s="3"/>
+      <c r="K747" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L747" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M747" s="3" t="s">
+        <v>2975</v>
+      </c>
+      <c r="N747" s="3"/>
+    </row>
+    <row r="748" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A748" s="3" t="s">
+        <v>3007</v>
+      </c>
+      <c r="B748" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C748" s="3">
+        <v>403</v>
+      </c>
+      <c r="D748" s="3" t="s">
+        <v>3008</v>
+      </c>
+      <c r="E748" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F748" s="3" t="s">
+        <v>3009</v>
+      </c>
+      <c r="G748" s="3" t="s">
+        <v>3010</v>
+      </c>
+      <c r="H748" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I748" s="3">
+        <v>28</v>
+      </c>
+      <c r="J748" s="3"/>
+      <c r="K748" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L748" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M748" s="3" t="s">
+        <v>3011</v>
+      </c>
+      <c r="N748" s="3"/>
+    </row>
+    <row r="749" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A749" s="3" t="s">
+        <v>3012</v>
+      </c>
+      <c r="B749" s="3"/>
+      <c r="C749" s="3">
+        <v>405</v>
+      </c>
+      <c r="D749" s="3" t="s">
+        <v>3013</v>
+      </c>
+      <c r="E749" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F749" s="3" t="s">
+        <v>2009</v>
+      </c>
+      <c r="G749" s="3" t="s">
+        <v>3014</v>
+      </c>
+      <c r="H749" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I749" s="3"/>
+      <c r="J749" s="3"/>
+      <c r="K749" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L749" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M749" s="3" t="s">
+        <v>3015</v>
+      </c>
+      <c r="N749" s="3"/>
+    </row>
+    <row r="750" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A750" s="3" t="s">
+        <v>3016</v>
+      </c>
+      <c r="B750" s="3"/>
+      <c r="C750" s="3">
+        <v>410</v>
+      </c>
+      <c r="D750" s="3" t="s">
+        <v>3017</v>
+      </c>
+      <c r="E750" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F750" s="3" t="s">
+        <v>2545</v>
+      </c>
+      <c r="G750" s="3" t="s">
+        <v>3018</v>
+      </c>
+      <c r="H750" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I750" s="3">
+        <v>12</v>
+      </c>
+      <c r="J750" s="3">
+        <v>50</v>
+      </c>
+      <c r="K750" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L750" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M750" s="3" t="s">
+        <v>3015</v>
+      </c>
+      <c r="N750" s="3"/>
+    </row>
+    <row r="751" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A751" s="3" t="s">
+        <v>3019</v>
+      </c>
+      <c r="B751" s="3"/>
+      <c r="C751" s="3">
+        <v>405</v>
+      </c>
+      <c r="D751" s="3" t="s">
+        <v>3020</v>
+      </c>
+      <c r="E751" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F751" s="3" t="s">
+        <v>2545</v>
+      </c>
+      <c r="G751" s="3" t="s">
+        <v>3021</v>
+      </c>
+      <c r="H751" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I751" s="3">
+        <v>15</v>
+      </c>
+      <c r="J751" s="3"/>
+      <c r="K751" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L751" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M751" s="3" t="s">
+        <v>3015</v>
+      </c>
+      <c r="N751" s="3"/>
+    </row>
+    <row r="752" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A752" s="3" t="s">
+        <v>3022</v>
+      </c>
+      <c r="B752" s="3"/>
+      <c r="C752" s="3">
+        <v>410</v>
+      </c>
+      <c r="D752" s="3" t="s">
+        <v>3023</v>
+      </c>
+      <c r="E752" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F752" s="3" t="s">
+        <v>3024</v>
+      </c>
+      <c r="G752" s="3" t="s">
+        <v>3025</v>
+      </c>
+      <c r="H752" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I752" s="3">
+        <v>10</v>
+      </c>
+      <c r="J752" s="3"/>
+      <c r="K752" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L752" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M752" s="3" t="s">
+        <v>3026</v>
+      </c>
+      <c r="N752" s="3"/>
+    </row>
+    <row r="753" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A753" s="3" t="s">
+        <v>3027</v>
+      </c>
+      <c r="B753" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C753" s="3">
+        <v>403</v>
+      </c>
+      <c r="D753" s="3" t="s">
+        <v>3028</v>
+      </c>
+      <c r="E753" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F753" s="3" t="s">
+        <v>3029</v>
+      </c>
+      <c r="G753" s="3" t="s">
+        <v>3030</v>
+      </c>
+      <c r="H753" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I753" s="3">
+        <v>33</v>
+      </c>
+      <c r="J753" s="3">
+        <v>75</v>
+      </c>
+      <c r="K753" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L753" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M753" s="3" t="s">
+        <v>3031</v>
+      </c>
+      <c r="N753" s="3"/>
+    </row>
+    <row r="754" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A754" s="3" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B754" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C754" s="3">
+        <v>413</v>
+      </c>
+      <c r="D754" s="3" t="s">
+        <v>3033</v>
+      </c>
+      <c r="E754" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F754" s="3" t="s">
+        <v>3034</v>
+      </c>
+      <c r="G754" s="3" t="s">
+        <v>3035</v>
+      </c>
+      <c r="H754" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I754" s="3"/>
+      <c r="J754" s="3"/>
+      <c r="K754" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L754" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M754" s="3" t="s">
+        <v>3036</v>
+      </c>
+      <c r="N754" s="3" t="s">
+        <v>3037</v>
+      </c>
+    </row>
+    <row r="755" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A755" s="3" t="s">
+        <v>3038</v>
+      </c>
+      <c r="B755" s="3"/>
+      <c r="C755" s="3">
+        <v>409</v>
+      </c>
+      <c r="D755" s="3" t="s">
+        <v>3039</v>
+      </c>
+      <c r="E755" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F755" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="G755" s="3" t="s">
+        <v>3040</v>
+      </c>
+      <c r="H755" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I755" s="3">
+        <v>39</v>
+      </c>
+      <c r="J755" s="3"/>
+      <c r="K755" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L755" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M755" s="3" t="s">
+        <v>3026</v>
+      </c>
+      <c r="N755" s="3"/>
+    </row>
+    <row r="756" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A756" s="3" t="s">
+        <v>3041</v>
+      </c>
+      <c r="B756" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C756" s="3">
+        <v>400</v>
+      </c>
+      <c r="D756" s="3" t="s">
+        <v>3042</v>
+      </c>
+      <c r="E756" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F756" s="3" t="s">
+        <v>3043</v>
+      </c>
+      <c r="G756" s="3" t="s">
+        <v>3044</v>
+      </c>
+      <c r="H756" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I756" s="3">
+        <v>18</v>
+      </c>
+      <c r="J756" s="3"/>
+      <c r="K756" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L756" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M756" s="3" t="s">
+        <v>3045</v>
+      </c>
+      <c r="N756" s="3"/>
+    </row>
+    <row r="757" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A757" s="3" t="s">
+        <v>3046</v>
+      </c>
+      <c r="B757" s="3"/>
+      <c r="C757" s="3">
+        <v>403</v>
+      </c>
+      <c r="D757" s="3" t="s">
+        <v>3047</v>
+      </c>
+      <c r="E757" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F757" s="3" t="s">
+        <v>3048</v>
+      </c>
+      <c r="G757" s="3" t="s">
+        <v>3049</v>
+      </c>
+      <c r="H757" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I757" s="3">
+        <v>69</v>
+      </c>
+      <c r="J757" s="3">
+        <v>75</v>
+      </c>
+      <c r="K757" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L757" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M757" s="3" t="s">
+        <v>3026</v>
+      </c>
+      <c r="N757" s="3"/>
+    </row>
+    <row r="758" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A758" s="3" t="s">
+        <v>3050</v>
+      </c>
+      <c r="B758" s="3"/>
+      <c r="C758" s="3">
+        <v>414</v>
+      </c>
+      <c r="D758" s="3" t="s">
+        <v>3051</v>
+      </c>
+      <c r="E758" s="3" t="s">
+        <v>1800</v>
+      </c>
+      <c r="F758" s="3" t="s">
+        <v>3052</v>
+      </c>
+      <c r="G758" s="3" t="s">
+        <v>3053</v>
+      </c>
+      <c r="H758" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I758" s="3">
+        <v>78</v>
+      </c>
+      <c r="J758" s="3"/>
+      <c r="K758" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L758" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M758" s="3" t="s">
+        <v>3054</v>
+      </c>
+      <c r="N758" s="3"/>
+    </row>
+    <row r="759" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A759" s="3" t="s">
+        <v>3055</v>
+      </c>
+      <c r="B759" s="3"/>
+      <c r="C759" s="3">
+        <v>413</v>
+      </c>
+      <c r="D759" s="3" t="s">
+        <v>3056</v>
+      </c>
+      <c r="E759" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F759" s="3" t="s">
+        <v>3057</v>
+      </c>
+      <c r="G759" s="3" t="s">
+        <v>3058</v>
+      </c>
+      <c r="H759" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I759" s="3">
+        <v>13</v>
+      </c>
+      <c r="J759" s="3"/>
+      <c r="K759" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L759" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M759" s="3" t="s">
+        <v>3054</v>
+      </c>
+      <c r="N759" s="3"/>
+    </row>
+    <row r="760" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A760" s="3" t="s">
+        <v>3059</v>
+      </c>
+      <c r="B760" s="3"/>
+      <c r="C760" s="3">
+        <v>410</v>
+      </c>
+      <c r="D760" s="3" t="s">
+        <v>3060</v>
+      </c>
+      <c r="E760" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F760" s="3" t="s">
+        <v>2948</v>
+      </c>
+      <c r="G760" s="3" t="s">
+        <v>3061</v>
+      </c>
+      <c r="H760" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I760" s="3">
+        <v>34</v>
+      </c>
+      <c r="J760" s="3"/>
+      <c r="K760" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L760" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M760" s="3" t="s">
+        <v>3062</v>
+      </c>
+      <c r="N760" s="3"/>
+    </row>
+    <row r="761" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A761" s="3" t="s">
+        <v>3063</v>
+      </c>
+      <c r="B761" s="3"/>
+      <c r="C761" s="3">
+        <v>409</v>
+      </c>
+      <c r="D761" s="3" t="s">
+        <v>3064</v>
+      </c>
+      <c r="E761" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F761" s="3" t="s">
+        <v>1066</v>
+      </c>
+      <c r="G761" s="3" t="s">
+        <v>3065</v>
+      </c>
+      <c r="H761" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I761" s="3">
+        <v>46</v>
+      </c>
+      <c r="J761" s="3"/>
+      <c r="K761" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L761" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M761" s="3" t="s">
+        <v>3062</v>
+      </c>
+      <c r="N761" s="3"/>
+    </row>
+    <row r="762" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A762" s="3" t="s">
+        <v>3066</v>
+      </c>
+      <c r="B762" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C762" s="3">
+        <v>409</v>
+      </c>
+      <c r="D762" s="3" t="s">
+        <v>3067</v>
+      </c>
+      <c r="E762" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F762" s="3" t="s">
+        <v>2402</v>
+      </c>
+      <c r="G762" s="3" t="s">
+        <v>3068</v>
+      </c>
+      <c r="H762" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I762" s="3">
+        <v>64</v>
+      </c>
+      <c r="J762" s="3">
+        <v>70</v>
+      </c>
+      <c r="K762" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L762" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M762" s="3" t="s">
+        <v>3069</v>
+      </c>
+      <c r="N762" s="3"/>
+    </row>
+    <row r="763" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A763" s="3" t="s">
+        <v>3070</v>
+      </c>
+      <c r="B763" s="3"/>
+      <c r="C763" s="3">
+        <v>410</v>
+      </c>
+      <c r="D763" s="3" t="s">
+        <v>3071</v>
+      </c>
+      <c r="E763" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F763" s="3" t="s">
+        <v>1804</v>
+      </c>
+      <c r="G763" s="3" t="s">
+        <v>3072</v>
+      </c>
+      <c r="H763" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I763" s="3">
+        <v>25</v>
+      </c>
+      <c r="J763" s="3"/>
+      <c r="K763" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L763" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M763" s="3" t="s">
+        <v>3069</v>
+      </c>
+      <c r="N763" s="3"/>
+    </row>
+    <row r="764" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A764" s="3" t="s">
+        <v>3073</v>
+      </c>
+      <c r="B764" s="3"/>
+      <c r="C764" s="3">
+        <v>408</v>
+      </c>
+      <c r="D764" s="3" t="s">
+        <v>3074</v>
+      </c>
+      <c r="E764" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F764" s="3" t="s">
+        <v>3075</v>
+      </c>
+      <c r="G764" s="3" t="s">
+        <v>3076</v>
+      </c>
+      <c r="H764" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I764" s="3">
+        <v>56</v>
+      </c>
+      <c r="J764" s="3"/>
+      <c r="K764" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L764" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M764" s="3" t="s">
+        <v>3069</v>
+      </c>
+      <c r="N764" s="3"/>
+    </row>
+    <row r="765" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A765" s="3" t="s">
+        <v>3077</v>
+      </c>
+      <c r="B765" s="3"/>
+      <c r="C765" s="3">
+        <v>409</v>
+      </c>
+      <c r="D765" s="3" t="s">
+        <v>3078</v>
+      </c>
+      <c r="E765" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F765" s="3" t="s">
+        <v>1610</v>
+      </c>
+      <c r="G765" s="3" t="s">
+        <v>3079</v>
+      </c>
+      <c r="H765" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I765" s="3">
+        <v>32</v>
+      </c>
+      <c r="J765" s="3"/>
+      <c r="K765" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L765" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M765" s="3" t="s">
+        <v>3080</v>
+      </c>
+      <c r="N765" s="3"/>
+    </row>
+    <row r="766" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A766" s="3" t="s">
+        <v>3081</v>
+      </c>
+      <c r="B766" s="3"/>
+      <c r="C766" s="3">
+        <v>409</v>
+      </c>
+      <c r="D766" s="3" t="s">
+        <v>3082</v>
+      </c>
+      <c r="E766" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F766" s="3" t="s">
+        <v>3083</v>
+      </c>
+      <c r="G766" s="3" t="s">
+        <v>3084</v>
+      </c>
+      <c r="H766" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I766" s="3">
+        <v>75</v>
+      </c>
+      <c r="J766" s="3">
+        <v>75</v>
+      </c>
+      <c r="K766" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L766" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M766" s="3" t="s">
+        <v>3080</v>
+      </c>
+      <c r="N766" s="3"/>
+    </row>
+    <row r="767" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A767" s="3" t="s">
+        <v>3085</v>
+      </c>
+      <c r="B767" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C767" s="3">
+        <v>411</v>
+      </c>
+      <c r="D767" s="3" t="s">
+        <v>3086</v>
+      </c>
+      <c r="E767" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F767" s="3" t="s">
+        <v>3087</v>
+      </c>
+      <c r="G767" s="3" t="s">
+        <v>3088</v>
+      </c>
+      <c r="H767" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I767" s="3">
+        <v>57</v>
+      </c>
+      <c r="J767" s="3"/>
+      <c r="K767" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L767" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M767" s="3" t="s">
+        <v>3080</v>
+      </c>
+      <c r="N767" s="3"/>
+    </row>
+    <row r="768" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A768" s="3" t="s">
+        <v>3089</v>
+      </c>
+      <c r="B768" s="3"/>
+      <c r="C768" s="3">
+        <v>404</v>
+      </c>
+      <c r="D768" s="3" t="s">
+        <v>3090</v>
+      </c>
+      <c r="E768" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F768" s="3" t="s">
+        <v>2545</v>
+      </c>
+      <c r="G768" s="3" t="s">
+        <v>3091</v>
+      </c>
+      <c r="H768" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I768" s="3">
+        <v>21</v>
+      </c>
+      <c r="J768" s="3"/>
+      <c r="K768" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L768" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M768" s="3" t="s">
+        <v>3092</v>
+      </c>
+      <c r="N768" s="3"/>
+    </row>
+    <row r="769" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A769" s="3" t="s">
+        <v>3093</v>
+      </c>
+      <c r="B769" s="3"/>
+      <c r="C769" s="3">
+        <v>409</v>
+      </c>
+      <c r="D769" s="3" t="s">
+        <v>3094</v>
+      </c>
+      <c r="E769" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F769" s="3" t="s">
+        <v>1834</v>
+      </c>
+      <c r="G769" s="3" t="s">
+        <v>3095</v>
+      </c>
+      <c r="H769" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I769" s="3">
+        <v>4</v>
+      </c>
+      <c r="J769" s="3"/>
+      <c r="K769" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L769" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M769" s="3" t="s">
+        <v>3092</v>
+      </c>
+      <c r="N769" s="3"/>
+    </row>
+    <row r="770" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A770" s="3" t="s">
+        <v>3096</v>
+      </c>
+      <c r="B770" s="3"/>
+      <c r="C770" s="3">
+        <v>410</v>
+      </c>
+      <c r="D770" s="3" t="s">
+        <v>3097</v>
+      </c>
+      <c r="E770" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F770" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G770" s="3" t="s">
+        <v>3098</v>
+      </c>
+      <c r="H770" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I770" s="3">
+        <v>33</v>
+      </c>
+      <c r="J770" s="3"/>
+      <c r="K770" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L770" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M770" s="3" t="s">
+        <v>3092</v>
+      </c>
+      <c r="N770" s="3"/>
+    </row>
+    <row r="771" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A771" s="3" t="s">
+        <v>3099</v>
+      </c>
+      <c r="B771" s="3"/>
+      <c r="C771" s="3">
+        <v>404</v>
+      </c>
+      <c r="D771" s="3" t="s">
+        <v>3100</v>
+      </c>
+      <c r="E771" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F771" s="3" t="s">
+        <v>3101</v>
+      </c>
+      <c r="G771" s="3" t="s">
+        <v>3102</v>
+      </c>
+      <c r="H771" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I771" s="3">
+        <v>19</v>
+      </c>
+      <c r="J771" s="3"/>
+      <c r="K771" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L771" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M771" s="3" t="s">
+        <v>3092</v>
+      </c>
+      <c r="N771" s="3"/>
+    </row>
+    <row r="772" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A772" s="3" t="s">
+        <v>3103</v>
+      </c>
+      <c r="B772" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C772" s="3">
+        <v>413</v>
+      </c>
+      <c r="D772" s="3" t="s">
+        <v>3104</v>
+      </c>
+      <c r="E772" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F772" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="G772" s="3" t="s">
+        <v>3105</v>
+      </c>
+      <c r="H772" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I772" s="3"/>
+      <c r="J772" s="3"/>
+      <c r="K772" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L772" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M772" s="3" t="s">
+        <v>3106</v>
+      </c>
+      <c r="N772" s="3"/>
+    </row>
+    <row r="773" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A773" s="3" t="s">
+        <v>3107</v>
+      </c>
+      <c r="B773" s="3"/>
+      <c r="C773" s="3">
+        <v>404</v>
+      </c>
+      <c r="D773" s="3" t="s">
+        <v>3108</v>
+      </c>
+      <c r="E773" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F773" s="3" t="s">
+        <v>1045</v>
+      </c>
+      <c r="G773" s="3" t="s">
+        <v>3109</v>
+      </c>
+      <c r="H773" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I773" s="3">
+        <v>27</v>
+      </c>
+      <c r="J773" s="3"/>
+      <c r="K773" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L773" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M773" s="3" t="s">
+        <v>3106</v>
+      </c>
+      <c r="N773" s="3"/>
+    </row>
+    <row r="774" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A774" s="3" t="s">
+        <v>3110</v>
+      </c>
+      <c r="B774" s="3"/>
+      <c r="C774" s="3">
+        <v>414</v>
+      </c>
+      <c r="D774" s="3" t="s">
+        <v>3111</v>
+      </c>
+      <c r="E774" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F774" s="3" t="s">
+        <v>2921</v>
+      </c>
+      <c r="G774" s="3" t="s">
+        <v>3112</v>
+      </c>
+      <c r="H774" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I774" s="3">
+        <v>35</v>
+      </c>
+      <c r="J774" s="3"/>
+      <c r="K774" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L774" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M774" s="3" t="s">
+        <v>3106</v>
+      </c>
+      <c r="N774" s="3"/>
+    </row>
+    <row r="775" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A775" s="3" t="s">
+        <v>3113</v>
+      </c>
+      <c r="B775" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C775" s="3">
+        <v>413</v>
+      </c>
+      <c r="D775" s="3" t="s">
+        <v>3114</v>
+      </c>
+      <c r="E775" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F775" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="G775" s="3" t="s">
+        <v>3115</v>
+      </c>
+      <c r="H775" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I775" s="3"/>
+      <c r="J775" s="3"/>
+      <c r="K775" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L775" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M775" s="3" t="s">
+        <v>3116</v>
+      </c>
+      <c r="N775" s="3" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="776" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A776" s="3" t="s">
+        <v>3118</v>
+      </c>
+      <c r="B776" s="3"/>
+      <c r="C776" s="3">
+        <v>409</v>
+      </c>
+      <c r="D776" s="3" t="s">
+        <v>3119</v>
+      </c>
+      <c r="E776" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F776" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G776" s="3" t="s">
+        <v>3120</v>
+      </c>
+      <c r="H776" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I776" s="3">
+        <v>25</v>
+      </c>
+      <c r="J776" s="3"/>
+      <c r="K776" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L776" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M776" s="3" t="s">
+        <v>3106</v>
+      </c>
+      <c r="N776" s="3"/>
+    </row>
+    <row r="777" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A777" s="3" t="s">
+        <v>3121</v>
+      </c>
+      <c r="B777" s="3"/>
+      <c r="C777" s="3">
+        <v>409</v>
+      </c>
+      <c r="D777" s="3" t="s">
+        <v>3122</v>
+      </c>
+      <c r="E777" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F777" s="3" t="s">
+        <v>1804</v>
+      </c>
+      <c r="G777" s="3" t="s">
+        <v>3123</v>
+      </c>
+      <c r="H777" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I777" s="3">
+        <v>20</v>
+      </c>
+      <c r="J777" s="3"/>
+      <c r="K777" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L777" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M777" s="3" t="s">
+        <v>3124</v>
+      </c>
+      <c r="N777" s="3"/>
+    </row>
+    <row r="778" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A778" s="3" t="s">
+        <v>3125</v>
+      </c>
+      <c r="B778" s="3"/>
+      <c r="C778" s="3">
+        <v>414</v>
+      </c>
+      <c r="D778" s="3" t="s">
+        <v>3126</v>
+      </c>
+      <c r="E778" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F778" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G778" s="3" t="s">
+        <v>3127</v>
+      </c>
+      <c r="H778" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I778" s="3">
+        <v>26</v>
+      </c>
+      <c r="J778" s="3"/>
+      <c r="K778" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L778" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M778" s="3" t="s">
+        <v>3124</v>
+      </c>
+      <c r="N778" s="3"/>
+    </row>
+    <row r="779" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A779" s="3" t="s">
+        <v>3128</v>
+      </c>
+      <c r="B779" s="3"/>
+      <c r="C779" s="3">
+        <v>408</v>
+      </c>
+      <c r="D779" s="3" t="s">
+        <v>3129</v>
+      </c>
+      <c r="E779" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F779" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G779" s="3" t="s">
+        <v>3130</v>
+      </c>
+      <c r="H779" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I779" s="3"/>
+      <c r="J779" s="3"/>
+      <c r="K779" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L779" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M779" s="3" t="s">
+        <v>3124</v>
+      </c>
+      <c r="N779" s="3"/>
+    </row>
+    <row r="780" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A780" s="3" t="s">
+        <v>3131</v>
+      </c>
+      <c r="B780" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C780" s="3">
+        <v>413</v>
+      </c>
+      <c r="D780" s="3" t="s">
+        <v>3132</v>
+      </c>
+      <c r="E780" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F780" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="G780" s="3" t="s">
+        <v>3133</v>
+      </c>
+      <c r="H780" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I780" s="3">
+        <v>3</v>
+      </c>
+      <c r="J780" s="3"/>
+      <c r="K780" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L780" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M780" s="3" t="s">
+        <v>3134</v>
+      </c>
+      <c r="N780" s="3" t="s">
+        <v>3135</v>
+      </c>
+    </row>
+    <row r="781" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A781" s="3" t="s">
+        <v>3136</v>
+      </c>
+      <c r="B781" s="3"/>
+      <c r="C781" s="3">
+        <v>413</v>
+      </c>
+      <c r="D781" s="3" t="s">
+        <v>3137</v>
+      </c>
+      <c r="E781" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F781" s="3" t="s">
+        <v>2371</v>
+      </c>
+      <c r="G781" s="3" t="s">
+        <v>3138</v>
+      </c>
+      <c r="H781" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I781" s="3">
+        <v>41</v>
+      </c>
+      <c r="J781" s="3"/>
+      <c r="K781" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L781" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M781" s="3" t="s">
+        <v>3139</v>
+      </c>
+      <c r="N781" s="3"/>
+    </row>
+    <row r="782" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A782" s="3" t="s">
+        <v>3140</v>
+      </c>
+      <c r="B782" s="3" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C782" s="3">
+        <v>412</v>
+      </c>
+      <c r="D782" s="3" t="s">
+        <v>3141</v>
+      </c>
+      <c r="E782" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F782" s="3" t="s">
+        <v>3142</v>
+      </c>
+      <c r="G782" s="3" t="s">
+        <v>3143</v>
+      </c>
+      <c r="H782" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I782" s="3">
+        <v>54</v>
+      </c>
+      <c r="J782" s="3"/>
+      <c r="K782" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L782" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M782" s="3" t="s">
+        <v>3144</v>
+      </c>
+      <c r="N782" s="3"/>
+    </row>
+    <row r="783" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A783" s="3" t="s">
+        <v>3145</v>
+      </c>
+      <c r="B783" s="3"/>
+      <c r="C783" s="3">
+        <v>408</v>
+      </c>
+      <c r="D783" s="3" t="s">
+        <v>3146</v>
+      </c>
+      <c r="E783" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F783" s="3" t="s">
+        <v>3147</v>
+      </c>
+      <c r="G783" s="3" t="s">
+        <v>3148</v>
+      </c>
+      <c r="H783" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I783" s="3">
+        <v>32</v>
+      </c>
+      <c r="J783" s="3"/>
+      <c r="K783" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L783" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M783" s="3" t="s">
+        <v>3149</v>
+      </c>
+      <c r="N783" s="3"/>
+    </row>
+    <row r="784" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A784" s="3" t="s">
+        <v>3150</v>
+      </c>
+      <c r="B784" s="3"/>
+      <c r="C784" s="3">
+        <v>408</v>
+      </c>
+      <c r="D784" s="3" t="s">
+        <v>3151</v>
+      </c>
+      <c r="E784" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F784" s="3" t="s">
+        <v>3152</v>
+      </c>
+      <c r="G784" s="3" t="s">
+        <v>3153</v>
+      </c>
+      <c r="H784" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I784" s="3"/>
+      <c r="J784" s="3"/>
+      <c r="K784" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L784" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M784" s="3" t="s">
+        <v>3149</v>
+      </c>
+      <c r="N784" s="3"/>
+    </row>
+    <row r="785" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A785" s="3" t="s">
+        <v>3154</v>
+      </c>
+      <c r="B785" s="3"/>
+      <c r="C785" s="3">
+        <v>408</v>
+      </c>
+      <c r="D785" s="3" t="s">
+        <v>3155</v>
+      </c>
+      <c r="E785" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F785" s="3" t="s">
+        <v>2440</v>
+      </c>
+      <c r="G785" s="3" t="s">
+        <v>3156</v>
+      </c>
+      <c r="H785" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I785" s="3">
+        <v>17</v>
+      </c>
+      <c r="J785" s="3"/>
+      <c r="K785" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L785" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M785" s="3" t="s">
+        <v>3149</v>
+      </c>
+      <c r="N785" s="3"/>
+    </row>
+    <row r="786" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A786" s="3" t="s">
+        <v>3157</v>
+      </c>
+      <c r="B786" s="3" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C786" s="3">
+        <v>409</v>
+      </c>
+      <c r="D786" s="3" t="s">
+        <v>3158</v>
+      </c>
+      <c r="E786" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F786" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="G786" s="3" t="s">
+        <v>3159</v>
+      </c>
+      <c r="H786" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I786" s="3">
+        <v>57</v>
+      </c>
+      <c r="J786" s="3">
+        <v>65</v>
+      </c>
+      <c r="K786" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L786" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M786" s="3" t="s">
+        <v>3160</v>
+      </c>
+      <c r="N786" s="3"/>
+    </row>
+    <row r="787" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A787" s="3" t="s">
+        <v>3161</v>
+      </c>
+      <c r="B787" s="3"/>
+      <c r="C787" s="3">
+        <v>409</v>
+      </c>
+      <c r="D787" s="3" t="s">
+        <v>3162</v>
+      </c>
+      <c r="E787" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F787" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="G787" s="3" t="s">
+        <v>3163</v>
+      </c>
+      <c r="H787" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I787" s="3">
+        <v>34</v>
+      </c>
+      <c r="J787" s="3"/>
+      <c r="K787" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L787" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M787" s="3" t="s">
+        <v>3160</v>
+      </c>
+      <c r="N787" s="3"/>
+    </row>
+    <row r="788" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A788" s="3" t="s">
+        <v>3164</v>
+      </c>
+      <c r="B788" s="3"/>
+      <c r="C788" s="3">
+        <v>405</v>
+      </c>
+      <c r="D788" s="3" t="s">
+        <v>3165</v>
+      </c>
+      <c r="E788" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F788" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="G788" s="3" t="s">
+        <v>3166</v>
+      </c>
+      <c r="H788" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I788" s="3"/>
+      <c r="J788" s="3"/>
+      <c r="K788" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L788" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M788" s="3" t="s">
+        <v>3160</v>
+      </c>
+      <c r="N788" s="3"/>
+    </row>
+    <row r="789" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A789" s="3" t="s">
+        <v>3167</v>
+      </c>
+      <c r="B789" s="3"/>
+      <c r="C789" s="3">
+        <v>414</v>
+      </c>
+      <c r="D789" s="3" t="s">
+        <v>3168</v>
+      </c>
+      <c r="E789" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F789" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G789" s="3" t="s">
+        <v>3169</v>
+      </c>
+      <c r="H789" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I789" s="3">
+        <v>15</v>
+      </c>
+      <c r="J789" s="3"/>
+      <c r="K789" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L789" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M789" s="3" t="s">
+        <v>3170</v>
+      </c>
+      <c r="N789" s="3"/>
+    </row>
+    <row r="790" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A790" s="3" t="s">
+        <v>3171</v>
+      </c>
+      <c r="B790" s="3"/>
+      <c r="C790" s="3">
+        <v>413</v>
+      </c>
+      <c r="D790" s="3" t="s">
+        <v>3172</v>
+      </c>
+      <c r="E790" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F790" s="3" t="s">
+        <v>1804</v>
+      </c>
+      <c r="G790" s="3" t="s">
+        <v>3173</v>
+      </c>
+      <c r="H790" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I790" s="3">
+        <v>5</v>
+      </c>
+      <c r="J790" s="3"/>
+      <c r="K790" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L790" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M790" s="3" t="s">
+        <v>3170</v>
+      </c>
+      <c r="N790" s="3"/>
+    </row>
+    <row r="791" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A791" s="3" t="s">
+        <v>3174</v>
+      </c>
+      <c r="B791" s="3"/>
+      <c r="C791" s="3">
+        <v>409</v>
+      </c>
+      <c r="D791" s="3" t="s">
+        <v>3175</v>
+      </c>
+      <c r="E791" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F791" s="3" t="s">
+        <v>3176</v>
+      </c>
+      <c r="G791" s="3" t="s">
+        <v>3177</v>
+      </c>
+      <c r="H791" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I791" s="3">
+        <v>75</v>
+      </c>
+      <c r="J791" s="3">
+        <v>75</v>
+      </c>
+      <c r="K791" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L791" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M791" s="3" t="s">
+        <v>3170</v>
+      </c>
+      <c r="N791" s="3"/>
+    </row>
+    <row r="792" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A792" s="3" t="s">
+        <v>3178</v>
+      </c>
+      <c r="B792" s="3"/>
+      <c r="C792" s="3">
+        <v>409</v>
+      </c>
+      <c r="D792" s="3" t="s">
+        <v>3179</v>
+      </c>
+      <c r="E792" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F792" s="3" t="s">
+        <v>3180</v>
+      </c>
+      <c r="G792" s="3" t="s">
+        <v>3181</v>
+      </c>
+      <c r="H792" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I792" s="3">
+        <v>75</v>
+      </c>
+      <c r="J792" s="3">
+        <v>75</v>
+      </c>
+      <c r="K792" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L792" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M792" s="3" t="s">
+        <v>3170</v>
+      </c>
+      <c r="N792" s="3"/>
+    </row>
+    <row r="793" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A793" s="3" t="s">
+        <v>3182</v>
+      </c>
+      <c r="B793" s="3"/>
+      <c r="C793" s="3">
+        <v>409</v>
+      </c>
+      <c r="D793" s="3" t="s">
+        <v>3183</v>
+      </c>
+      <c r="E793" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F793" s="3" t="s">
+        <v>3184</v>
+      </c>
+      <c r="G793" s="3" t="s">
+        <v>3185</v>
+      </c>
+      <c r="H793" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I793" s="3">
+        <v>75</v>
+      </c>
+      <c r="J793" s="3">
+        <v>75</v>
+      </c>
+      <c r="K793" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L793" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M793" s="3" t="s">
+        <v>3186</v>
+      </c>
+      <c r="N793" s="3"/>
+    </row>
+    <row r="794" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A794" s="3" t="s">
+        <v>3187</v>
+      </c>
+      <c r="B794" s="3"/>
+      <c r="C794" s="3">
+        <v>409</v>
+      </c>
+      <c r="D794" s="3" t="s">
+        <v>3188</v>
+      </c>
+      <c r="E794" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F794" s="3" t="s">
+        <v>3189</v>
+      </c>
+      <c r="G794" s="3" t="s">
+        <v>3190</v>
+      </c>
+      <c r="H794" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I794" s="3">
+        <v>75</v>
+      </c>
+      <c r="J794" s="3"/>
+      <c r="K794" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L794" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M794" s="3" t="s">
+        <v>3186</v>
+      </c>
+      <c r="N794" s="3"/>
+    </row>
+    <row r="795" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A795" s="3" t="s">
+        <v>3191</v>
+      </c>
+      <c r="B795" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C795" s="3">
+        <v>403</v>
+      </c>
+      <c r="D795" s="3" t="s">
+        <v>3192</v>
+      </c>
+      <c r="E795" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F795" s="3" t="s">
+        <v>3193</v>
+      </c>
+      <c r="G795" s="3" t="s">
+        <v>3194</v>
+      </c>
+      <c r="H795" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I795" s="3">
+        <v>79</v>
+      </c>
+      <c r="J795" s="3">
+        <v>75</v>
+      </c>
+      <c r="K795" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L795" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M795" s="3" t="s">
+        <v>3186</v>
+      </c>
+      <c r="N795" s="3" t="s">
+        <v>3195</v>
+      </c>
+    </row>
+    <row r="796" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A796" s="3" t="s">
+        <v>3196</v>
+      </c>
+      <c r="B796" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C796" s="3">
+        <v>403</v>
+      </c>
+      <c r="D796" s="3" t="s">
+        <v>3197</v>
+      </c>
+      <c r="E796" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F796" s="3" t="s">
+        <v>3198</v>
+      </c>
+      <c r="G796" s="3" t="s">
+        <v>3199</v>
+      </c>
+      <c r="H796" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I796" s="3"/>
+      <c r="J796" s="3"/>
+      <c r="K796" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L796" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M796" s="3" t="s">
+        <v>3200</v>
+      </c>
+      <c r="N796" s="3"/>
+    </row>
+    <row r="797" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A797" s="3" t="s">
+        <v>3201</v>
+      </c>
+      <c r="B797" s="3"/>
+      <c r="C797" s="3">
+        <v>411</v>
+      </c>
+      <c r="D797" s="3" t="s">
+        <v>3202</v>
+      </c>
+      <c r="E797" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F797" s="3" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G797" s="3" t="s">
+        <v>3203</v>
+      </c>
+      <c r="H797" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I797" s="3">
         <v>22</v>
       </c>
-      <c r="L745" s="3"/>
-      <c r="M745" s="3"/>
-      <c r="N745" s="3"/>
+      <c r="J797" s="3"/>
+      <c r="K797" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L797" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M797" s="3" t="s">
+        <v>3135</v>
+      </c>
+      <c r="N797" s="3"/>
+    </row>
+    <row r="798" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A798" s="3" t="s">
+        <v>3204</v>
+      </c>
+      <c r="B798" s="3"/>
+      <c r="C798" s="3">
+        <v>406</v>
+      </c>
+      <c r="D798" s="3" t="s">
+        <v>3205</v>
+      </c>
+      <c r="E798" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F798" s="3" t="s">
+        <v>1982</v>
+      </c>
+      <c r="G798" s="3" t="s">
+        <v>3206</v>
+      </c>
+      <c r="H798" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I798" s="3">
+        <v>68</v>
+      </c>
+      <c r="J798" s="3">
+        <v>65</v>
+      </c>
+      <c r="K798" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L798" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M798" s="3" t="s">
+        <v>3135</v>
+      </c>
+      <c r="N798" s="3"/>
+    </row>
+    <row r="799" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A799" s="3" t="s">
+        <v>3207</v>
+      </c>
+      <c r="B799" s="3"/>
+      <c r="C799" s="3">
+        <v>406</v>
+      </c>
+      <c r="D799" s="3" t="s">
+        <v>3208</v>
+      </c>
+      <c r="E799" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F799" s="3" t="s">
+        <v>3209</v>
+      </c>
+      <c r="G799" s="3" t="s">
+        <v>3210</v>
+      </c>
+      <c r="H799" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I799" s="3">
+        <v>77</v>
+      </c>
+      <c r="J799" s="3">
+        <v>75</v>
+      </c>
+      <c r="K799" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L799" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M799" s="3" t="s">
+        <v>3211</v>
+      </c>
+      <c r="N799" s="3"/>
+    </row>
+    <row r="800" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A800" s="3" t="s">
+        <v>3212</v>
+      </c>
+      <c r="B800" s="3"/>
+      <c r="C800" s="3">
+        <v>406</v>
+      </c>
+      <c r="D800" s="3" t="s">
+        <v>3213</v>
+      </c>
+      <c r="E800" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F800" s="3" t="s">
+        <v>3214</v>
+      </c>
+      <c r="G800" s="3" t="s">
+        <v>3215</v>
+      </c>
+      <c r="H800" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I800" s="3">
+        <v>14</v>
+      </c>
+      <c r="J800" s="3"/>
+      <c r="K800" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L800" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M800" s="3" t="s">
+        <v>3211</v>
+      </c>
+      <c r="N800" s="3"/>
+    </row>
+    <row r="801" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A801" s="3" t="s">
+        <v>3216</v>
+      </c>
+      <c r="B801" s="3"/>
+      <c r="C801" s="3">
+        <v>413</v>
+      </c>
+      <c r="D801" s="3" t="s">
+        <v>3217</v>
+      </c>
+      <c r="E801" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F801" s="3" t="s">
+        <v>1834</v>
+      </c>
+      <c r="G801" s="3" t="s">
+        <v>3218</v>
+      </c>
+      <c r="H801" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I801" s="3">
+        <v>23</v>
+      </c>
+      <c r="J801" s="3"/>
+      <c r="K801" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L801" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M801" s="3" t="s">
+        <v>3211</v>
+      </c>
+      <c r="N801" s="3"/>
+    </row>
+    <row r="802" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A802" s="3" t="s">
+        <v>3219</v>
+      </c>
+      <c r="B802" s="3"/>
+      <c r="C802" s="3">
+        <v>413</v>
+      </c>
+      <c r="D802" s="3" t="s">
+        <v>3220</v>
+      </c>
+      <c r="E802" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F802" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G802" s="3" t="s">
+        <v>3221</v>
+      </c>
+      <c r="H802" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I802" s="3">
+        <v>35</v>
+      </c>
+      <c r="J802" s="3"/>
+      <c r="K802" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L802" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M802" s="3" t="s">
+        <v>3211</v>
+      </c>
+      <c r="N802" s="3"/>
+    </row>
+    <row r="803" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A803" s="3" t="s">
+        <v>3222</v>
+      </c>
+      <c r="B803" s="3"/>
+      <c r="C803" s="3">
+        <v>408</v>
+      </c>
+      <c r="D803" s="3" t="s">
+        <v>3223</v>
+      </c>
+      <c r="E803" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F803" s="3" t="s">
+        <v>1774</v>
+      </c>
+      <c r="G803" s="3" t="s">
+        <v>3224</v>
+      </c>
+      <c r="H803" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I803" s="3">
+        <v>18</v>
+      </c>
+      <c r="J803" s="3"/>
+      <c r="K803" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L803" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M803" s="3" t="s">
+        <v>3211</v>
+      </c>
+      <c r="N803" s="3"/>
+    </row>
+    <row r="804" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A804" s="3" t="s">
+        <v>3225</v>
+      </c>
+      <c r="B804" s="3"/>
+      <c r="C804" s="3">
+        <v>406</v>
+      </c>
+      <c r="D804" s="3" t="s">
+        <v>3226</v>
+      </c>
+      <c r="E804" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F804" s="3" t="s">
+        <v>3227</v>
+      </c>
+      <c r="G804" s="3" t="s">
+        <v>3228</v>
+      </c>
+      <c r="H804" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I804" s="3">
+        <v>77</v>
+      </c>
+      <c r="J804" s="3">
+        <v>75</v>
+      </c>
+      <c r="K804" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L804" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M804" s="3" t="s">
+        <v>3211</v>
+      </c>
+      <c r="N804" s="3"/>
+    </row>
+    <row r="805" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A805" s="3" t="s">
+        <v>3229</v>
+      </c>
+      <c r="B805" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C805" s="3">
+        <v>403</v>
+      </c>
+      <c r="D805" s="3" t="s">
+        <v>3230</v>
+      </c>
+      <c r="E805" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F805" s="3" t="s">
+        <v>3231</v>
+      </c>
+      <c r="G805" s="3" t="s">
+        <v>3232</v>
+      </c>
+      <c r="H805" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I805" s="3"/>
+      <c r="J805" s="3"/>
+      <c r="K805" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L805" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M805" s="3" t="s">
+        <v>3233</v>
+      </c>
+      <c r="N805" s="3"/>
+    </row>
+    <row r="806" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A806" s="3" t="s">
+        <v>3234</v>
+      </c>
+      <c r="B806" s="3"/>
+      <c r="C806" s="3">
+        <v>413</v>
+      </c>
+      <c r="D806" s="3" t="s">
+        <v>3235</v>
+      </c>
+      <c r="E806" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F806" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="G806" s="3" t="s">
+        <v>3236</v>
+      </c>
+      <c r="H806" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I806" s="3">
+        <v>19</v>
+      </c>
+      <c r="J806" s="3"/>
+      <c r="K806" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L806" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M806" s="3" t="s">
+        <v>3237</v>
+      </c>
+      <c r="N806" s="3"/>
+    </row>
+    <row r="807" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A807" s="3" t="s">
+        <v>3238</v>
+      </c>
+      <c r="B807" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C807" s="3">
+        <v>414</v>
+      </c>
+      <c r="D807" s="3" t="s">
+        <v>3239</v>
+      </c>
+      <c r="E807" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F807" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="G807" s="3" t="s">
+        <v>3240</v>
+      </c>
+      <c r="H807" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I807" s="3">
+        <v>45</v>
+      </c>
+      <c r="J807" s="3"/>
+      <c r="K807" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L807" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M807" s="3" t="s">
+        <v>3241</v>
+      </c>
+      <c r="N807" s="3"/>
+    </row>
+    <row r="808" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A808" s="3" t="s">
+        <v>3242</v>
+      </c>
+      <c r="B808" s="3"/>
+      <c r="C808" s="3">
+        <v>414</v>
+      </c>
+      <c r="D808" s="3" t="s">
+        <v>3243</v>
+      </c>
+      <c r="E808" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F808" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G808" s="3" t="s">
+        <v>3244</v>
+      </c>
+      <c r="H808" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I808" s="3">
+        <v>67</v>
+      </c>
+      <c r="J808" s="3"/>
+      <c r="K808" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L808" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M808" s="3" t="s">
+        <v>3237</v>
+      </c>
+      <c r="N808" s="3"/>
+    </row>
+    <row r="809" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A809" s="3" t="s">
+        <v>3245</v>
+      </c>
+      <c r="B809" s="3"/>
+      <c r="C809" s="3">
+        <v>408</v>
+      </c>
+      <c r="D809" s="3" t="s">
+        <v>3246</v>
+      </c>
+      <c r="E809" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F809" s="3" t="s">
+        <v>2921</v>
+      </c>
+      <c r="G809" s="3" t="s">
+        <v>3247</v>
+      </c>
+      <c r="H809" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I809" s="3">
+        <v>20</v>
+      </c>
+      <c r="J809" s="3"/>
+      <c r="K809" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L809" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M809" s="3" t="s">
+        <v>3237</v>
+      </c>
+      <c r="N809" s="3"/>
+    </row>
+    <row r="810" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A810" s="3" t="s">
+        <v>3248</v>
+      </c>
+      <c r="B810" s="3"/>
+      <c r="C810" s="3">
+        <v>404</v>
+      </c>
+      <c r="D810" s="3" t="s">
+        <v>3249</v>
+      </c>
+      <c r="E810" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F810" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G810" s="3" t="s">
+        <v>3250</v>
+      </c>
+      <c r="H810" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I810" s="3">
+        <v>21</v>
+      </c>
+      <c r="J810" s="3"/>
+      <c r="K810" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L810" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M810" s="3" t="s">
+        <v>3237</v>
+      </c>
+      <c r="N810" s="3"/>
+    </row>
+    <row r="811" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A811" s="3" t="s">
+        <v>3251</v>
+      </c>
+      <c r="B811" s="3"/>
+      <c r="C811" s="3">
+        <v>404</v>
+      </c>
+      <c r="D811" s="3" t="s">
+        <v>3252</v>
+      </c>
+      <c r="E811" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F811" s="3" t="s">
+        <v>2575</v>
+      </c>
+      <c r="G811" s="3" t="s">
+        <v>3253</v>
+      </c>
+      <c r="H811" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I811" s="3">
+        <v>67</v>
+      </c>
+      <c r="J811" s="3">
+        <v>65</v>
+      </c>
+      <c r="K811" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L811" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M811" s="3" t="s">
+        <v>3237</v>
+      </c>
+      <c r="N811" s="3"/>
+    </row>
+    <row r="812" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A812" s="3" t="s">
+        <v>3254</v>
+      </c>
+      <c r="B812" s="3"/>
+      <c r="C812" s="3">
+        <v>410</v>
+      </c>
+      <c r="D812" s="3" t="s">
+        <v>3255</v>
+      </c>
+      <c r="E812" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F812" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G812" s="3" t="s">
+        <v>3256</v>
+      </c>
+      <c r="H812" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I812" s="3">
+        <v>21</v>
+      </c>
+      <c r="J812" s="3"/>
+      <c r="K812" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L812" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M812" s="3" t="s">
+        <v>3237</v>
+      </c>
+      <c r="N812" s="3"/>
+    </row>
+    <row r="813" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A813" s="3" t="s">
+        <v>3257</v>
+      </c>
+      <c r="B813" s="3"/>
+      <c r="C813" s="3">
+        <v>410</v>
+      </c>
+      <c r="D813" s="3" t="s">
+        <v>3258</v>
+      </c>
+      <c r="E813" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F813" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G813" s="3" t="s">
+        <v>3259</v>
+      </c>
+      <c r="H813" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I813" s="3">
+        <v>54</v>
+      </c>
+      <c r="J813" s="3"/>
+      <c r="K813" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L813" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M813" s="3" t="s">
+        <v>3237</v>
+      </c>
+      <c r="N813" s="3"/>
+    </row>
+    <row r="814" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A814" s="3" t="s">
+        <v>3260</v>
+      </c>
+      <c r="B814" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C814" s="3">
+        <v>404</v>
+      </c>
+      <c r="D814" s="3" t="s">
+        <v>3261</v>
+      </c>
+      <c r="E814" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F814" s="3" t="s">
+        <v>3262</v>
+      </c>
+      <c r="G814" s="3" t="s">
+        <v>3263</v>
+      </c>
+      <c r="H814" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I814" s="3"/>
+      <c r="J814" s="3"/>
+      <c r="K814" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L814" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M814" s="3" t="s">
+        <v>3264</v>
+      </c>
+      <c r="N814" s="3"/>
+    </row>
+    <row r="815" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A815" s="3" t="s">
+        <v>3265</v>
+      </c>
+      <c r="B815" s="3"/>
+      <c r="C815" s="3">
+        <v>410</v>
+      </c>
+      <c r="D815" s="3" t="s">
+        <v>3266</v>
+      </c>
+      <c r="E815" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F815" s="3" t="s">
+        <v>3267</v>
+      </c>
+      <c r="G815" s="3" t="s">
+        <v>3268</v>
+      </c>
+      <c r="H815" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I815" s="3">
+        <v>67</v>
+      </c>
+      <c r="J815" s="3">
+        <v>65</v>
+      </c>
+      <c r="K815" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L815" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M815" s="3" t="s">
+        <v>3264</v>
+      </c>
+      <c r="N815" s="3"/>
+    </row>
+    <row r="816" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A816" s="3" t="s">
+        <v>3269</v>
+      </c>
+      <c r="B816" s="3"/>
+      <c r="C816" s="3">
+        <v>408</v>
+      </c>
+      <c r="D816" s="3" t="s">
+        <v>3270</v>
+      </c>
+      <c r="E816" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F816" s="3" t="s">
+        <v>1804</v>
+      </c>
+      <c r="G816" s="3" t="s">
+        <v>3271</v>
+      </c>
+      <c r="H816" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I816" s="3">
+        <v>40</v>
+      </c>
+      <c r="J816" s="3"/>
+      <c r="K816" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L816" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M816" s="3" t="s">
+        <v>3264</v>
+      </c>
+      <c r="N816" s="3"/>
+    </row>
+    <row r="817" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A817" s="3" t="s">
+        <v>3272</v>
+      </c>
+      <c r="B817" s="3"/>
+      <c r="C817" s="3">
+        <v>408</v>
+      </c>
+      <c r="D817" s="3" t="s">
+        <v>3273</v>
+      </c>
+      <c r="E817" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F817" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="G817" s="3" t="s">
+        <v>3274</v>
+      </c>
+      <c r="H817" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I817" s="3">
+        <v>25</v>
+      </c>
+      <c r="J817" s="3"/>
+      <c r="K817" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L817" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M817" s="3" t="s">
+        <v>3264</v>
+      </c>
+      <c r="N817" s="3"/>
+    </row>
+    <row r="818" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A818" s="3" t="s">
+        <v>3275</v>
+      </c>
+      <c r="B818" s="3"/>
+      <c r="C818" s="3">
+        <v>404</v>
+      </c>
+      <c r="D818" s="3" t="s">
+        <v>3276</v>
+      </c>
+      <c r="E818" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F818" s="3" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G818" s="3" t="s">
+        <v>3277</v>
+      </c>
+      <c r="H818" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I818" s="3">
+        <v>29</v>
+      </c>
+      <c r="J818" s="3"/>
+      <c r="K818" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L818" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M818" s="3" t="s">
+        <v>3264</v>
+      </c>
+      <c r="N818" s="3"/>
+    </row>
+    <row r="819" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A819" s="3" t="s">
+        <v>3278</v>
+      </c>
+      <c r="B819" s="3"/>
+      <c r="C819" s="3">
+        <v>404</v>
+      </c>
+      <c r="D819" s="3" t="s">
+        <v>3279</v>
+      </c>
+      <c r="E819" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F819" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G819" s="3" t="s">
+        <v>3280</v>
+      </c>
+      <c r="H819" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I819" s="3">
+        <v>17</v>
+      </c>
+      <c r="J819" s="3"/>
+      <c r="K819" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L819" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M819" s="3" t="s">
+        <v>3264</v>
+      </c>
+      <c r="N819" s="3"/>
+    </row>
+    <row r="820" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A820" s="3" t="s">
+        <v>3281</v>
+      </c>
+      <c r="B820" s="3"/>
+      <c r="C820" s="3">
+        <v>404</v>
+      </c>
+      <c r="D820" s="3" t="s">
+        <v>3282</v>
+      </c>
+      <c r="E820" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F820" s="3" t="s">
+        <v>2086</v>
+      </c>
+      <c r="G820" s="3" t="s">
+        <v>3283</v>
+      </c>
+      <c r="H820" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I820" s="3">
+        <v>25</v>
+      </c>
+      <c r="J820" s="3"/>
+      <c r="K820" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L820" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M820" s="3" t="s">
+        <v>3284</v>
+      </c>
+      <c r="N820" s="3"/>
+    </row>
+    <row r="821" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A821" s="3" t="s">
+        <v>3285</v>
+      </c>
+      <c r="B821" s="3"/>
+      <c r="C821" s="3">
+        <v>404</v>
+      </c>
+      <c r="D821" s="3" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E821" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F821" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="G821" s="3" t="s">
+        <v>3287</v>
+      </c>
+      <c r="H821" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I821" s="3">
+        <v>28</v>
+      </c>
+      <c r="J821" s="3"/>
+      <c r="K821" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L821" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M821" s="3" t="s">
+        <v>3284</v>
+      </c>
+      <c r="N821" s="3"/>
+    </row>
+    <row r="822" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A822" s="3" t="s">
+        <v>3288</v>
+      </c>
+      <c r="B822" s="3"/>
+      <c r="C822" s="3">
+        <v>404</v>
+      </c>
+      <c r="D822" s="3" t="s">
+        <v>3289</v>
+      </c>
+      <c r="E822" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F822" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G822" s="3" t="s">
+        <v>3290</v>
+      </c>
+      <c r="H822" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I822" s="3">
+        <v>26</v>
+      </c>
+      <c r="J822" s="3"/>
+      <c r="K822" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L822" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M822" s="3" t="s">
+        <v>3284</v>
+      </c>
+      <c r="N822" s="3"/>
+    </row>
+    <row r="823" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A823" s="3" t="s">
+        <v>3291</v>
+      </c>
+      <c r="B823" s="3"/>
+      <c r="C823" s="3">
+        <v>404</v>
+      </c>
+      <c r="D823" s="3" t="s">
+        <v>3292</v>
+      </c>
+      <c r="E823" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F823" s="3" t="s">
+        <v>1707</v>
+      </c>
+      <c r="G823" s="3" t="s">
+        <v>3293</v>
+      </c>
+      <c r="H823" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I823" s="3">
+        <v>29</v>
+      </c>
+      <c r="J823" s="3"/>
+      <c r="K823" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L823" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M823" s="3" t="s">
+        <v>3284</v>
+      </c>
+      <c r="N823" s="3"/>
+    </row>
+    <row r="824" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A824" s="3" t="s">
+        <v>3294</v>
+      </c>
+      <c r="B824" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C824" s="3">
+        <v>404</v>
+      </c>
+      <c r="D824" s="3" t="s">
+        <v>3295</v>
+      </c>
+      <c r="E824" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F824" s="3" t="s">
+        <v>2086</v>
+      </c>
+      <c r="G824" s="3" t="s">
+        <v>3296</v>
+      </c>
+      <c r="H824" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I824" s="3">
+        <v>17</v>
+      </c>
+      <c r="J824" s="3"/>
+      <c r="K824" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L824" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M824" s="3" t="s">
+        <v>3297</v>
+      </c>
+      <c r="N824" s="3"/>
+    </row>
+    <row r="825" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A825" s="3" t="s">
+        <v>3298</v>
+      </c>
+      <c r="B825" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C825" s="3">
+        <v>404</v>
+      </c>
+      <c r="D825" s="3" t="s">
+        <v>3299</v>
+      </c>
+      <c r="E825" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F825" s="3" t="s">
+        <v>2086</v>
+      </c>
+      <c r="G825" s="3" t="s">
+        <v>3300</v>
+      </c>
+      <c r="H825" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I825" s="3">
+        <v>30</v>
+      </c>
+      <c r="J825" s="3"/>
+      <c r="K825" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L825" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M825" s="3" t="s">
+        <v>3301</v>
+      </c>
+      <c r="N825" s="3"/>
+    </row>
+    <row r="826" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A826" s="3" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B826" s="3"/>
+      <c r="C826" s="3">
+        <v>404</v>
+      </c>
+      <c r="D826" s="3" t="s">
+        <v>3303</v>
+      </c>
+      <c r="E826" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F826" s="3" t="s">
+        <v>3304</v>
+      </c>
+      <c r="G826" s="3" t="s">
+        <v>3305</v>
+      </c>
+      <c r="H826" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I826" s="3">
+        <v>24</v>
+      </c>
+      <c r="J826" s="3"/>
+      <c r="K826" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L826" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M826" s="3" t="s">
+        <v>3284</v>
+      </c>
+      <c r="N826" s="3"/>
+    </row>
+    <row r="827" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A827" s="3" t="s">
+        <v>3306</v>
+      </c>
+      <c r="B827" s="3"/>
+      <c r="C827" s="3">
+        <v>409</v>
+      </c>
+      <c r="D827" s="3" t="s">
+        <v>3307</v>
+      </c>
+      <c r="E827" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F827" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="G827" s="3" t="s">
+        <v>3308</v>
+      </c>
+      <c r="H827" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I827" s="3">
+        <v>8</v>
+      </c>
+      <c r="J827" s="3"/>
+      <c r="K827" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L827" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M827" s="3" t="s">
+        <v>3284</v>
+      </c>
+      <c r="N827" s="3"/>
+    </row>
+    <row r="828" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A828" s="3" t="s">
+        <v>3309</v>
+      </c>
+      <c r="B828" s="3"/>
+      <c r="C828" s="3">
+        <v>400</v>
+      </c>
+      <c r="D828" s="3" t="s">
+        <v>3310</v>
+      </c>
+      <c r="E828" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F828" s="3" t="s">
+        <v>3311</v>
+      </c>
+      <c r="G828" s="3" t="s">
+        <v>3312</v>
+      </c>
+      <c r="H828" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I828" s="3">
+        <v>15</v>
+      </c>
+      <c r="J828" s="3"/>
+      <c r="K828" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L828" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M828" s="3" t="s">
+        <v>3284</v>
+      </c>
+      <c r="N828" s="3"/>
+    </row>
+    <row r="829" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A829" s="3" t="s">
+        <v>3313</v>
+      </c>
+      <c r="B829" s="3"/>
+      <c r="C829" s="3">
+        <v>400</v>
+      </c>
+      <c r="D829" s="3" t="s">
+        <v>3314</v>
+      </c>
+      <c r="E829" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F829" s="3" t="s">
+        <v>3315</v>
+      </c>
+      <c r="G829" s="3" t="s">
+        <v>3316</v>
+      </c>
+      <c r="H829" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I829" s="3"/>
+      <c r="J829" s="3"/>
+      <c r="K829" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L829" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M829" s="3" t="s">
+        <v>3284</v>
+      </c>
+      <c r="N829" s="3"/>
+    </row>
+    <row r="830" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A830" s="3" t="s">
+        <v>3317</v>
+      </c>
+      <c r="B830" s="3"/>
+      <c r="C830" s="3">
+        <v>400</v>
+      </c>
+      <c r="D830" s="3" t="s">
+        <v>3318</v>
+      </c>
+      <c r="E830" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F830" s="3" t="s">
+        <v>3319</v>
+      </c>
+      <c r="G830" s="3" t="s">
+        <v>3320</v>
+      </c>
+      <c r="H830" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I830" s="3">
+        <v>72</v>
+      </c>
+      <c r="J830" s="3">
+        <v>75</v>
+      </c>
+      <c r="K830" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L830" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M830" s="3" t="s">
+        <v>3284</v>
+      </c>
+      <c r="N830" s="3"/>
+    </row>
+    <row r="831" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A831" s="3" t="s">
+        <v>3321</v>
+      </c>
+      <c r="B831" s="3"/>
+      <c r="C831" s="3">
+        <v>404</v>
+      </c>
+      <c r="D831" s="3" t="s">
+        <v>3322</v>
+      </c>
+      <c r="E831" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F831" s="3" t="s">
+        <v>2237</v>
+      </c>
+      <c r="G831" s="3" t="s">
+        <v>3323</v>
+      </c>
+      <c r="H831" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I831" s="3"/>
+      <c r="J831" s="3"/>
+      <c r="K831" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L831" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M831" s="3" t="s">
+        <v>3324</v>
+      </c>
+      <c r="N831" s="3"/>
+    </row>
+    <row r="832" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A832" s="3" t="s">
+        <v>3325</v>
+      </c>
+      <c r="B832" s="3"/>
+      <c r="C832" s="3">
+        <v>400</v>
+      </c>
+      <c r="D832" s="3" t="s">
+        <v>3326</v>
+      </c>
+      <c r="E832" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F832" s="3" t="s">
+        <v>3327</v>
+      </c>
+      <c r="G832" s="3" t="s">
+        <v>3328</v>
+      </c>
+      <c r="H832" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I832" s="3">
+        <v>45</v>
+      </c>
+      <c r="J832" s="3">
+        <v>45</v>
+      </c>
+      <c r="K832" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L832" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M832" s="3" t="s">
+        <v>3324</v>
+      </c>
+      <c r="N832" s="3"/>
+    </row>
+    <row r="833" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A833" s="3" t="s">
+        <v>3329</v>
+      </c>
+      <c r="B833" s="3"/>
+      <c r="C833" s="3">
+        <v>400</v>
+      </c>
+      <c r="D833" s="3" t="s">
+        <v>3330</v>
+      </c>
+      <c r="E833" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F833" s="3" t="s">
+        <v>3331</v>
+      </c>
+      <c r="G833" s="3" t="s">
+        <v>3332</v>
+      </c>
+      <c r="H833" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I833" s="3">
+        <v>57</v>
+      </c>
+      <c r="J833" s="3"/>
+      <c r="K833" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L833" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M833" s="3" t="s">
+        <v>3324</v>
+      </c>
+      <c r="N833" s="3"/>
+    </row>
+    <row r="834" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A834" s="3" t="s">
+        <v>3333</v>
+      </c>
+      <c r="B834" s="3"/>
+      <c r="C834" s="3">
+        <v>406</v>
+      </c>
+      <c r="D834" s="3" t="s">
+        <v>3334</v>
+      </c>
+      <c r="E834" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F834" s="3" t="s">
+        <v>3335</v>
+      </c>
+      <c r="G834" s="3" t="s">
+        <v>3336</v>
+      </c>
+      <c r="H834" s="3"/>
+      <c r="I834" s="3">
+        <v>29</v>
+      </c>
+      <c r="J834" s="3"/>
+      <c r="K834" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L834" s="3"/>
+      <c r="M834" s="3"/>
+      <c r="N834" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Home Motors\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94D81608-F2CB-4BC9-9A7B-24EDBCF07EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F521A43-C883-409F-9906-AC4E3264E0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9252" uniqueCount="4004">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9955" uniqueCount="4284">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -10258,18 +10258,18 @@
     <t>05/05/26 09:42 CDT</t>
   </si>
   <si>
+    <t>'1211652737482260480</t>
+  </si>
+  <si>
+    <t>31.458058, -100.442999</t>
+  </si>
+  <si>
     <t>'1211652858001391616</t>
   </si>
   <si>
-    <t>31.458058, -100.442999</t>
-  </si>
-  <si>
     <t>05/06/26 09:15 CDT</t>
   </si>
   <si>
-    <t>'1211652737482260480</t>
-  </si>
-  <si>
     <t>05/05/26 10:17 CDT</t>
   </si>
   <si>
@@ -11812,6 +11812,9 @@
     <t>31.388503, -100.411724</t>
   </si>
   <si>
+    <t>05/18/26 08:33 CDT</t>
+  </si>
+  <si>
     <t>05/15/26 09:10 CDT</t>
   </si>
   <si>
@@ -11842,6 +11845,9 @@
     <t>31.400822, -100.226978</t>
   </si>
   <si>
+    <t>05/18/26 08:34 CDT</t>
+  </si>
+  <si>
     <t>'1215284522451632128</t>
   </si>
   <si>
@@ -11860,6 +11866,9 @@
     <t>31.667308, -100.025117</t>
   </si>
   <si>
+    <t>05/18/26 08:35 CDT</t>
+  </si>
+  <si>
     <t>05/15/26 10:20 CDT</t>
   </si>
   <si>
@@ -11962,6 +11971,9 @@
     <t>31.445089, -100.441968</t>
   </si>
   <si>
+    <t>05/18/26 08:36 CDT</t>
+  </si>
+  <si>
     <t>05/16/26 12:39 CDT</t>
   </si>
   <si>
@@ -11989,6 +12001,12 @@
     <t>31.410527, -100.457037</t>
   </si>
   <si>
+    <t>05/18/26 08:38 CDT</t>
+  </si>
+  <si>
+    <t>05/18/26 08:42 CDT</t>
+  </si>
+  <si>
     <t>05/16/26 16:28 CDT</t>
   </si>
   <si>
@@ -11998,6 +12016,9 @@
     <t>31.424365, -100.423044</t>
   </si>
   <si>
+    <t>05/18/26 08:39 CDT</t>
+  </si>
+  <si>
     <t>05/16/26 19:21 CDT</t>
   </si>
   <si>
@@ -12016,6 +12037,12 @@
     <t>31.499614, -100.446623</t>
   </si>
   <si>
+    <t>05/18/26 08:40 CDT</t>
+  </si>
+  <si>
+    <t>05/18/26 08:43 CDT</t>
+  </si>
+  <si>
     <t>05/17/26 02:43 CDT</t>
   </si>
   <si>
@@ -12032,6 +12059,819 @@
   </si>
   <si>
     <t>31.443331, -100.464632</t>
+  </si>
+  <si>
+    <t>05/17/26 08:53 CDT</t>
+  </si>
+  <si>
+    <t>'1215989139707691008</t>
+  </si>
+  <si>
+    <t>4.4mi N of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.504378, -100.464426</t>
+  </si>
+  <si>
+    <t>05/17/26 09:01 CDT</t>
+  </si>
+  <si>
+    <t>'1215991069184000000</t>
+  </si>
+  <si>
+    <t>31.443170, -100.375999</t>
+  </si>
+  <si>
+    <t>05/17/26 09:12 CDT</t>
+  </si>
+  <si>
+    <t>'1215994072481824768</t>
+  </si>
+  <si>
+    <t>18.2mi NW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.626747, -100.671114</t>
+  </si>
+  <si>
+    <t>05/17/26 09:21 CDT</t>
+  </si>
+  <si>
+    <t>'1215996252320333824</t>
+  </si>
+  <si>
+    <t>17mi NW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.613303, -100.657357</t>
+  </si>
+  <si>
+    <t>05/17/26 12:02 CDT</t>
+  </si>
+  <si>
+    <t>'1216036665190154240</t>
+  </si>
+  <si>
+    <t>31.479453, -100.448164</t>
+  </si>
+  <si>
+    <t>05/17/26 17:34 CDT</t>
+  </si>
+  <si>
+    <t>'1216120209618927616</t>
+  </si>
+  <si>
+    <t>4.3mi N of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.503704, -100.460327</t>
+  </si>
+  <si>
+    <t>05/18/26 08:41 CDT</t>
+  </si>
+  <si>
+    <t>05/17/26 17:48 CDT</t>
+  </si>
+  <si>
+    <t>'1216123859477102592</t>
+  </si>
+  <si>
+    <t>31.505985, -100.479763</t>
+  </si>
+  <si>
+    <t>'1216123865932136448</t>
+  </si>
+  <si>
+    <t>31.451062, -100.488050</t>
+  </si>
+  <si>
+    <t>05/18/26 08:03 CDT</t>
+  </si>
+  <si>
+    <t>'1216339012114087936</t>
+  </si>
+  <si>
+    <t>11.5mi SW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.368824, -100.624350</t>
+  </si>
+  <si>
+    <t>05/18/26 15:18 CDT</t>
+  </si>
+  <si>
+    <t>05/18/26 11:01 CDT</t>
+  </si>
+  <si>
+    <t>'1216383780504371200</t>
+  </si>
+  <si>
+    <t>31.432488, -100.503770</t>
+  </si>
+  <si>
+    <t>05/18/26 16:54 CDT</t>
+  </si>
+  <si>
+    <t>'1216472710440452096</t>
+  </si>
+  <si>
+    <t>32.2mi NE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.697258, -99.991778</t>
+  </si>
+  <si>
+    <t>05/19/26 07:44 CDT</t>
+  </si>
+  <si>
+    <t>05/18/26 17:08 CDT</t>
+  </si>
+  <si>
+    <t>'1216476111333130240</t>
+  </si>
+  <si>
+    <t>31.444127, -100.474763</t>
+  </si>
+  <si>
+    <t>05/18/26 17:10 CDT</t>
+  </si>
+  <si>
+    <t>'1216476507371896832</t>
+  </si>
+  <si>
+    <t>31.443346, -100.464758</t>
+  </si>
+  <si>
+    <t>05/18/26 18:34 CDT</t>
+  </si>
+  <si>
+    <t>'1216497728964689920</t>
+  </si>
+  <si>
+    <t>31.460227, -100.444171</t>
+  </si>
+  <si>
+    <t>05/18/26 18:35 CDT</t>
+  </si>
+  <si>
+    <t>'1216498075233845248</t>
+  </si>
+  <si>
+    <t>9.9mi NE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.539167, -100.326429</t>
+  </si>
+  <si>
+    <t>05/18/26 23:57 CDT</t>
+  </si>
+  <si>
+    <t>'1216579141290328064</t>
+  </si>
+  <si>
+    <t>31.497403, -100.459367</t>
+  </si>
+  <si>
+    <t>05/19/26 07:45 CDT</t>
+  </si>
+  <si>
+    <t>05/19/26 02:03 CDT</t>
+  </si>
+  <si>
+    <t>'1216610735627599872</t>
+  </si>
+  <si>
+    <t>31.480396, -100.456304</t>
+  </si>
+  <si>
+    <t>05/19/26 07:46 CDT</t>
+  </si>
+  <si>
+    <t>05/19/26 09:16 CDT</t>
+  </si>
+  <si>
+    <t>'1216719795106512896</t>
+  </si>
+  <si>
+    <t>31.482007, -100.442360</t>
+  </si>
+  <si>
+    <t>05/19/26 12:48 CDT</t>
+  </si>
+  <si>
+    <t>05/19/26 09:44 CDT</t>
+  </si>
+  <si>
+    <t>'1216726677766438912</t>
+  </si>
+  <si>
+    <t>31.476652, -100.453561</t>
+  </si>
+  <si>
+    <t>05/19/26 10:31 CDT</t>
+  </si>
+  <si>
+    <t>'1216738591087165440</t>
+  </si>
+  <si>
+    <t>31.443287, -100.462810</t>
+  </si>
+  <si>
+    <t>05/19/26 12:49 CDT</t>
+  </si>
+  <si>
+    <t>05/19/26 14:15 CDT</t>
+  </si>
+  <si>
+    <t>'1216797206196158464</t>
+  </si>
+  <si>
+    <t>0.7mi E of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.442777, -100.438911</t>
+  </si>
+  <si>
+    <t>05/20/26 07:54 CDT</t>
+  </si>
+  <si>
+    <t>05/20/26 07:55 CDT</t>
+  </si>
+  <si>
+    <t>05/19/26 14:36 CDT</t>
+  </si>
+  <si>
+    <t>'1216800290737651712</t>
+  </si>
+  <si>
+    <t>31.443311, -100.464537</t>
+  </si>
+  <si>
+    <t>05/19/26 16:19 CDT</t>
+  </si>
+  <si>
+    <t>'1216826070993633281</t>
+  </si>
+  <si>
+    <t>31.458156, -100.443004</t>
+  </si>
+  <si>
+    <t>05/20/26 07:56 CDT</t>
+  </si>
+  <si>
+    <t>05/19/26 16:22 CDT</t>
+  </si>
+  <si>
+    <t>'1216826890388668416</t>
+  </si>
+  <si>
+    <t>31.444886, -100.434897</t>
+  </si>
+  <si>
+    <t>05/19/26 19:35 CDT</t>
+  </si>
+  <si>
+    <t>'1216875507187089408</t>
+  </si>
+  <si>
+    <t>31.487176, -100.457926</t>
+  </si>
+  <si>
+    <t>05/20/26 02:43 CDT</t>
+  </si>
+  <si>
+    <t>'1216983312128704512</t>
+  </si>
+  <si>
+    <t>31.479903, -100.448204</t>
+  </si>
+  <si>
+    <t>05/21/26 09:05 CDT</t>
+  </si>
+  <si>
+    <t>05/20/26 08:48 CDT</t>
+  </si>
+  <si>
+    <t>'1217075103347671040</t>
+  </si>
+  <si>
+    <t>31.448168, -100.492450</t>
+  </si>
+  <si>
+    <t>05/21/26 09:06 CDT</t>
+  </si>
+  <si>
+    <t>05/20/26 09:07 CDT</t>
+  </si>
+  <si>
+    <t>'1217079946367893504</t>
+  </si>
+  <si>
+    <t>13.3mi NW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.583416, -100.603595</t>
+  </si>
+  <si>
+    <t>05/20/26 09:08 CDT</t>
+  </si>
+  <si>
+    <t>'1217080198076465153</t>
+  </si>
+  <si>
+    <t>14.6mi NW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.593391, -100.624059</t>
+  </si>
+  <si>
+    <t>05/21/26 09:08 CDT</t>
+  </si>
+  <si>
+    <t>05/20/26 09:16 CDT</t>
+  </si>
+  <si>
+    <t>'1217082080492683265</t>
+  </si>
+  <si>
+    <t>23.5mi NW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.678178, -100.737882</t>
+  </si>
+  <si>
+    <t>05/20/26 09:17 CDT</t>
+  </si>
+  <si>
+    <t>'1217082341965594624</t>
+  </si>
+  <si>
+    <t>24.7mi NW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.683875, -100.760232</t>
+  </si>
+  <si>
+    <t>05/20/26 10:49 CDT</t>
+  </si>
+  <si>
+    <t>'1217105485954711552</t>
+  </si>
+  <si>
+    <t>31.443305, -100.464649</t>
+  </si>
+  <si>
+    <t>05/21/26 09:09 CDT</t>
+  </si>
+  <si>
+    <t>05/20/26 11:02 CDT</t>
+  </si>
+  <si>
+    <t>'1217108792580407297</t>
+  </si>
+  <si>
+    <t>3.1mi S of Midland TX</t>
+  </si>
+  <si>
+    <t>31.979431, -102.113001</t>
+  </si>
+  <si>
+    <t>05/20/26 12:05 CDT</t>
+  </si>
+  <si>
+    <t>'1217124596621410304</t>
+  </si>
+  <si>
+    <t>31.422583, -100.423455</t>
+  </si>
+  <si>
+    <t>05/21/26 09:10 CDT</t>
+  </si>
+  <si>
+    <t>05/20/26 12:07 CDT</t>
+  </si>
+  <si>
+    <t>'1217125233694244864</t>
+  </si>
+  <si>
+    <t>31.424380, -100.423101</t>
+  </si>
+  <si>
+    <t>05/20/26 12:10 CDT</t>
+  </si>
+  <si>
+    <t>'1217125918003331072</t>
+  </si>
+  <si>
+    <t>31.445003, -100.434767</t>
+  </si>
+  <si>
+    <t>05/20/26 12:18 CDT</t>
+  </si>
+  <si>
+    <t>'1217127967197659136</t>
+  </si>
+  <si>
+    <t>27.3mi S of Big Spring TX</t>
+  </si>
+  <si>
+    <t>31.874305, -101.657691</t>
+  </si>
+  <si>
+    <t>05/20/26 12:33 CDT</t>
+  </si>
+  <si>
+    <t>'1217131642557202432</t>
+  </si>
+  <si>
+    <t>28.1mi S of Big Spring TX</t>
+  </si>
+  <si>
+    <t>31.843264, -101.367478</t>
+  </si>
+  <si>
+    <t>05/20/26 12:35 CDT</t>
+  </si>
+  <si>
+    <t>'1217132079658205184</t>
+  </si>
+  <si>
+    <t>1.6mi S of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.420844, -100.440976</t>
+  </si>
+  <si>
+    <t>'1217132144565059584</t>
+  </si>
+  <si>
+    <t>30mi S of Big Spring TX</t>
+  </si>
+  <si>
+    <t>31.822997, -101.330889</t>
+  </si>
+  <si>
+    <t>05/20/26 12:40 CDT</t>
+  </si>
+  <si>
+    <t>'1217133567121981441</t>
+  </si>
+  <si>
+    <t>33.6mi SE of Big Spring TX</t>
+  </si>
+  <si>
+    <t>31.807314, -101.215785</t>
+  </si>
+  <si>
+    <t>05/20/26 12:42 CDT</t>
+  </si>
+  <si>
+    <t>'1217133911063298048</t>
+  </si>
+  <si>
+    <t>33.3mi SE of Big Spring TX</t>
+  </si>
+  <si>
+    <t>31.823840, -101.192584</t>
+  </si>
+  <si>
+    <t>05/20/26 16:33 CDT</t>
+  </si>
+  <si>
+    <t>'1217192005654970368</t>
+  </si>
+  <si>
+    <t>31.500428, -100.371500</t>
+  </si>
+  <si>
+    <t>05/21/26 09:12 CDT</t>
+  </si>
+  <si>
+    <t>05/21/26 10:04 CDT</t>
+  </si>
+  <si>
+    <t>05/20/26 16:50 CDT</t>
+  </si>
+  <si>
+    <t>'1217196320205471744</t>
+  </si>
+  <si>
+    <t>1.1mi SW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.429820, -100.462992</t>
+  </si>
+  <si>
+    <t>05/21/26 09:14 CDT</t>
+  </si>
+  <si>
+    <t>05/21/26 09:37 CDT</t>
+  </si>
+  <si>
+    <t>05/21/26 07:57 CDT</t>
+  </si>
+  <si>
+    <t>'1217424601282412544</t>
+  </si>
+  <si>
+    <t>31.424562, -100.424074</t>
+  </si>
+  <si>
+    <t>05/22/26 07:52 CDT</t>
+  </si>
+  <si>
+    <t>05/21/26 08:15 CDT</t>
+  </si>
+  <si>
+    <t>'1217429055817809920</t>
+  </si>
+  <si>
+    <t>31.416902, -100.425672</t>
+  </si>
+  <si>
+    <t>05/22/26 07:53 CDT</t>
+  </si>
+  <si>
+    <t>05/21/26 08:43 CDT</t>
+  </si>
+  <si>
+    <t>'1217436112881090560</t>
+  </si>
+  <si>
+    <t>32.1mi W of Brady TX</t>
+  </si>
+  <si>
+    <t>31.216743, -99.904046</t>
+  </si>
+  <si>
+    <t>05/21/26 08:53 CDT</t>
+  </si>
+  <si>
+    <t>'1217438632361754624</t>
+  </si>
+  <si>
+    <t>31.120247, -99.825698</t>
+  </si>
+  <si>
+    <t>05/21/26 08:56 CDT</t>
+  </si>
+  <si>
+    <t>'1217439409725669376</t>
+  </si>
+  <si>
+    <t>27.1mi W of Brady TX</t>
+  </si>
+  <si>
+    <t>31.063693, -99.821157</t>
+  </si>
+  <si>
+    <t>05/21/26 09:20 CDT</t>
+  </si>
+  <si>
+    <t>'1217445616481894400</t>
+  </si>
+  <si>
+    <t>39.6mi SW of Brady TX</t>
+  </si>
+  <si>
+    <t>30.677854, -99.778295</t>
+  </si>
+  <si>
+    <t>05/21/26 09:22 CDT</t>
+  </si>
+  <si>
+    <t>'1217445933864878080</t>
+  </si>
+  <si>
+    <t>41.1mi SW of Brady TX</t>
+  </si>
+  <si>
+    <t>30.654861, -99.782199</t>
+  </si>
+  <si>
+    <t>05/21/26 09:39 CDT</t>
+  </si>
+  <si>
+    <t>'1217450212247896064</t>
+  </si>
+  <si>
+    <t>44mi NW of Kerrville TX</t>
+  </si>
+  <si>
+    <t>30.434849, -99.709182</t>
+  </si>
+  <si>
+    <t>05/21/26 09:45 CDT</t>
+  </si>
+  <si>
+    <t>'1217451684268244992</t>
+  </si>
+  <si>
+    <t>37.1mi NW of Kerrville TX</t>
+  </si>
+  <si>
+    <t>30.381057, -99.610629</t>
+  </si>
+  <si>
+    <t>05/21/26 15:46 CDT</t>
+  </si>
+  <si>
+    <t>'1217542616795742208</t>
+  </si>
+  <si>
+    <t>16.9mi E of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.347608, -100.186995</t>
+  </si>
+  <si>
+    <t>05/21/26 16:23 CDT</t>
+  </si>
+  <si>
+    <t>'1217551956621557761</t>
+  </si>
+  <si>
+    <t>6.3mi N of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.528662, -100.487477</t>
+  </si>
+  <si>
+    <t>05/22/26 07:55 CDT</t>
+  </si>
+  <si>
+    <t>05/21/26 16:43 CDT</t>
+  </si>
+  <si>
+    <t>'1217556882064048128</t>
+  </si>
+  <si>
+    <t>28.8mi NW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.727047, -100.807666</t>
+  </si>
+  <si>
+    <t>05/22/26 07:56 CDT</t>
+  </si>
+  <si>
+    <t>05/21/26 16:58 CDT</t>
+  </si>
+  <si>
+    <t>'1217560776395620352</t>
+  </si>
+  <si>
+    <t>31.462569, -100.436601</t>
+  </si>
+  <si>
+    <t>05/21/26 17:07 CDT</t>
+  </si>
+  <si>
+    <t>'1217563114120314880</t>
+  </si>
+  <si>
+    <t>31.440694, -100.434817</t>
+  </si>
+  <si>
+    <t>05/21/26 17:11 CDT</t>
+  </si>
+  <si>
+    <t>'1217563918680096768</t>
+  </si>
+  <si>
+    <t>31.439443, -100.442000</t>
+  </si>
+  <si>
+    <t>05/21/26 17:47 CDT</t>
+  </si>
+  <si>
+    <t>'1217573049822511104</t>
+  </si>
+  <si>
+    <t>34.9mi SE of Big Spring TX</t>
+  </si>
+  <si>
+    <t>31.856987, -101.090648</t>
+  </si>
+  <si>
+    <t>05/21/26 18:40 CDT</t>
+  </si>
+  <si>
+    <t>'1217586339659284480</t>
+  </si>
+  <si>
+    <t>1.8mi NW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.466339, -100.464384</t>
+  </si>
+  <si>
+    <t>05/22/26 07:57 CDT</t>
+  </si>
+  <si>
+    <t>05/22/26 07:59 CDT</t>
+  </si>
+  <si>
+    <t>'1217586549064105984</t>
+  </si>
+  <si>
+    <t>31.519560, -100.436561</t>
+  </si>
+  <si>
+    <t>05/22/26 07:58 CDT</t>
+  </si>
+  <si>
+    <t>05/22/26 09:35 CDT</t>
+  </si>
+  <si>
+    <t>'1217811777128136704</t>
+  </si>
+  <si>
+    <t>31.396334, -100.433629</t>
+  </si>
+  <si>
+    <t>05/22/26 13:03 CDT</t>
+  </si>
+  <si>
+    <t>'1217864023257808896</t>
+  </si>
+  <si>
+    <t>37.4mi E of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.636233, -99.857315</t>
+  </si>
+  <si>
+    <t>05/22/26 13:47 CDT</t>
+  </si>
+  <si>
+    <t>'1217875030604677120</t>
+  </si>
+  <si>
+    <t>1.7mi E of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.445186, -100.421043</t>
+  </si>
+  <si>
+    <t>05/22/26 18:33 CDT</t>
+  </si>
+  <si>
+    <t>'1217947144611332096</t>
+  </si>
+  <si>
+    <t>31.515104, -100.480431</t>
+  </si>
+  <si>
+    <t>05/22/26 18:41 CDT</t>
+  </si>
+  <si>
+    <t>'1217949188407590912</t>
+  </si>
+  <si>
+    <t>9.8mi NW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.558941, -100.545174</t>
+  </si>
+  <si>
+    <t>05/22/26 19:07 CDT</t>
+  </si>
+  <si>
+    <t>'1217955685208326144</t>
+  </si>
+  <si>
+    <t>31.520604, -100.482914</t>
+  </si>
+  <si>
+    <t>05/22/26 19:45 CDT</t>
+  </si>
+  <si>
+    <t>'1217965158362677248</t>
+  </si>
+  <si>
+    <t>1.8mi SE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.425781, -100.426767</t>
+  </si>
+  <si>
+    <t>05/23/26 03:13 CDT</t>
+  </si>
+  <si>
+    <t>'1218077812406255616</t>
+  </si>
+  <si>
+    <t>31.480995, -100.441706</t>
+  </si>
+  <si>
+    <t>05/23/26 08:18 CDT</t>
+  </si>
+  <si>
+    <t>'1218154658401517568</t>
+  </si>
+  <si>
+    <t>31.430497, -100.431034</t>
   </si>
 </sst>
 </file>
@@ -12393,7 +13233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1014"/>
+  <dimension ref="A1:N1085"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="14" width="15" customWidth="1"/>
@@ -45049,7 +45889,7 @@
         <v>3412</v>
       </c>
       <c r="E848" s="3" t="s">
-        <v>225</v>
+        <v>477</v>
       </c>
       <c r="F848" s="3" t="s">
         <v>278</v>
@@ -45071,7 +45911,7 @@
         <v>37</v>
       </c>
       <c r="M848" s="3" t="s">
-        <v>3414</v>
+        <v>3410</v>
       </c>
       <c r="N848" s="3"/>
     </row>
@@ -45084,10 +45924,10 @@
         <v>410</v>
       </c>
       <c r="D849" s="3" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="E849" s="3" t="s">
-        <v>477</v>
+        <v>225</v>
       </c>
       <c r="F849" s="3" t="s">
         <v>278</v>
@@ -45109,7 +45949,7 @@
         <v>37</v>
       </c>
       <c r="M849" s="3" t="s">
-        <v>3410</v>
+        <v>3415</v>
       </c>
       <c r="N849" s="3"/>
     </row>
@@ -45147,7 +45987,7 @@
         <v>37</v>
       </c>
       <c r="M850" s="3" t="s">
-        <v>3414</v>
+        <v>3415</v>
       </c>
       <c r="N850" s="3"/>
     </row>
@@ -45187,7 +46027,7 @@
         <v>37</v>
       </c>
       <c r="M851" s="3" t="s">
-        <v>3414</v>
+        <v>3415</v>
       </c>
       <c r="N851" s="3" t="s">
         <v>3423</v>
@@ -50521,28 +51361,34 @@
       <c r="G990" s="3" t="s">
         <v>3929</v>
       </c>
-      <c r="H990" s="3"/>
+      <c r="H990" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="I990" s="3">
         <v>71</v>
       </c>
       <c r="J990" s="3"/>
       <c r="K990" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L990" s="3"/>
-      <c r="M990" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L990" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M990" s="3" t="s">
+        <v>3930</v>
+      </c>
       <c r="N990" s="3"/>
     </row>
     <row r="991" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A991" s="3" t="s">
-        <v>3930</v>
+        <v>3931</v>
       </c>
       <c r="B991" s="3"/>
       <c r="C991" s="3">
         <v>409</v>
       </c>
       <c r="D991" s="3" t="s">
-        <v>3931</v>
+        <v>3932</v>
       </c>
       <c r="E991" s="3" t="s">
         <v>63</v>
@@ -50551,30 +51397,36 @@
         <v>405</v>
       </c>
       <c r="G991" s="3" t="s">
-        <v>3932</v>
-      </c>
-      <c r="H991" s="3"/>
+        <v>3933</v>
+      </c>
+      <c r="H991" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I991" s="3">
         <v>32</v>
       </c>
       <c r="J991" s="3"/>
       <c r="K991" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L991" s="3"/>
-      <c r="M991" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L991" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M991" s="3" t="s">
+        <v>3930</v>
+      </c>
       <c r="N991" s="3"/>
     </row>
     <row r="992" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A992" s="3" t="s">
-        <v>3933</v>
+        <v>3934</v>
       </c>
       <c r="B992" s="3"/>
       <c r="C992" s="3">
         <v>414</v>
       </c>
       <c r="D992" s="3" t="s">
-        <v>3934</v>
+        <v>3935</v>
       </c>
       <c r="E992" s="3" t="s">
         <v>290</v>
@@ -50583,135 +51435,161 @@
         <v>862</v>
       </c>
       <c r="G992" s="3" t="s">
-        <v>3935</v>
-      </c>
-      <c r="H992" s="3"/>
+        <v>3936</v>
+      </c>
+      <c r="H992" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I992" s="3">
         <v>34</v>
       </c>
       <c r="J992" s="3"/>
       <c r="K992" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L992" s="3"/>
-      <c r="M992" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L992" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M992" s="3" t="s">
+        <v>3930</v>
+      </c>
       <c r="N992" s="3"/>
     </row>
     <row r="993" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A993" s="3" t="s">
-        <v>3936</v>
+        <v>3937</v>
       </c>
       <c r="B993" s="3"/>
       <c r="C993" s="3">
         <v>405</v>
       </c>
       <c r="D993" s="3" t="s">
-        <v>3937</v>
+        <v>3938</v>
       </c>
       <c r="E993" s="3" t="s">
         <v>145</v>
       </c>
       <c r="F993" s="3" t="s">
-        <v>3938</v>
+        <v>3939</v>
       </c>
       <c r="G993" s="3" t="s">
-        <v>3939</v>
-      </c>
-      <c r="H993" s="3"/>
+        <v>3940</v>
+      </c>
+      <c r="H993" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="I993" s="3"/>
       <c r="J993" s="3"/>
       <c r="K993" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L993" s="3"/>
-      <c r="M993" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L993" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M993" s="3" t="s">
+        <v>3941</v>
+      </c>
       <c r="N993" s="3"/>
     </row>
     <row r="994" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A994" s="3" t="s">
-        <v>3936</v>
+        <v>3937</v>
       </c>
       <c r="B994" s="3"/>
       <c r="C994" s="3">
         <v>405</v>
       </c>
       <c r="D994" s="3" t="s">
-        <v>3940</v>
+        <v>3942</v>
       </c>
       <c r="E994" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F994" s="3" t="s">
-        <v>3938</v>
+        <v>3939</v>
       </c>
       <c r="G994" s="3" t="s">
-        <v>3941</v>
-      </c>
-      <c r="H994" s="3"/>
+        <v>3943</v>
+      </c>
+      <c r="H994" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I994" s="3">
         <v>38</v>
       </c>
       <c r="J994" s="3"/>
       <c r="K994" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L994" s="3"/>
-      <c r="M994" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L994" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M994" s="3" t="s">
+        <v>3941</v>
+      </c>
       <c r="N994" s="3"/>
     </row>
     <row r="995" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A995" s="3" t="s">
-        <v>3942</v>
+        <v>3944</v>
       </c>
       <c r="B995" s="3"/>
       <c r="C995" s="3">
         <v>414</v>
       </c>
       <c r="D995" s="3" t="s">
-        <v>3943</v>
+        <v>3945</v>
       </c>
       <c r="E995" s="3" t="s">
         <v>225</v>
       </c>
       <c r="F995" s="3" t="s">
-        <v>3944</v>
+        <v>3946</v>
       </c>
       <c r="G995" s="3" t="s">
-        <v>3945</v>
-      </c>
-      <c r="H995" s="3"/>
+        <v>3947</v>
+      </c>
+      <c r="H995" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I995" s="3">
         <v>8</v>
       </c>
       <c r="J995" s="3"/>
       <c r="K995" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L995" s="3"/>
-      <c r="M995" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L995" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M995" s="3" t="s">
+        <v>3948</v>
+      </c>
       <c r="N995" s="3"/>
     </row>
     <row r="996" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A996" s="3" t="s">
-        <v>3946</v>
+        <v>3949</v>
       </c>
       <c r="B996" s="3"/>
       <c r="C996" s="3">
         <v>405</v>
       </c>
       <c r="D996" s="3" t="s">
-        <v>3947</v>
+        <v>3950</v>
       </c>
       <c r="E996" s="3" t="s">
         <v>1150</v>
       </c>
       <c r="F996" s="3" t="s">
-        <v>3948</v>
+        <v>3951</v>
       </c>
       <c r="G996" s="3" t="s">
-        <v>3949</v>
-      </c>
-      <c r="H996" s="3"/>
+        <v>3952</v>
+      </c>
+      <c r="H996" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I996" s="3">
         <v>60</v>
       </c>
@@ -50719,22 +51597,26 @@
         <v>75</v>
       </c>
       <c r="K996" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L996" s="3"/>
-      <c r="M996" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L996" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M996" s="3" t="s">
+        <v>3948</v>
+      </c>
       <c r="N996" s="3"/>
     </row>
     <row r="997" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A997" s="3" t="s">
-        <v>3950</v>
+        <v>3953</v>
       </c>
       <c r="B997" s="3"/>
       <c r="C997" s="3">
         <v>412</v>
       </c>
       <c r="D997" s="3" t="s">
-        <v>3951</v>
+        <v>3954</v>
       </c>
       <c r="E997" s="3" t="s">
         <v>290</v>
@@ -50743,30 +51625,36 @@
         <v>1084</v>
       </c>
       <c r="G997" s="3" t="s">
-        <v>3952</v>
-      </c>
-      <c r="H997" s="3"/>
+        <v>3955</v>
+      </c>
+      <c r="H997" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I997" s="3">
         <v>22</v>
       </c>
       <c r="J997" s="3"/>
       <c r="K997" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L997" s="3"/>
-      <c r="M997" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L997" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M997" s="3" t="s">
+        <v>3948</v>
+      </c>
       <c r="N997" s="3"/>
     </row>
     <row r="998" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A998" s="3" t="s">
-        <v>3953</v>
+        <v>3956</v>
       </c>
       <c r="B998" s="3"/>
       <c r="C998" s="3">
         <v>405</v>
       </c>
       <c r="D998" s="3" t="s">
-        <v>3954</v>
+        <v>3957</v>
       </c>
       <c r="E998" s="3" t="s">
         <v>145</v>
@@ -50775,30 +51663,36 @@
         <v>1255</v>
       </c>
       <c r="G998" s="3" t="s">
-        <v>3955</v>
-      </c>
-      <c r="H998" s="3"/>
+        <v>3958</v>
+      </c>
+      <c r="H998" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I998" s="3">
         <v>46</v>
       </c>
       <c r="J998" s="3"/>
       <c r="K998" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L998" s="3"/>
-      <c r="M998" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L998" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M998" s="3" t="s">
+        <v>3948</v>
+      </c>
       <c r="N998" s="3"/>
     </row>
     <row r="999" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A999" s="3" t="s">
-        <v>3956</v>
+        <v>3959</v>
       </c>
       <c r="B999" s="3"/>
       <c r="C999" s="3">
         <v>414</v>
       </c>
       <c r="D999" s="3" t="s">
-        <v>3957</v>
+        <v>3960</v>
       </c>
       <c r="E999" s="3" t="s">
         <v>290</v>
@@ -50807,9 +51701,11 @@
         <v>2555</v>
       </c>
       <c r="G999" s="3" t="s">
-        <v>3958</v>
-      </c>
-      <c r="H999" s="3"/>
+        <v>3961</v>
+      </c>
+      <c r="H999" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I999" s="3">
         <v>35</v>
       </c>
@@ -50817,22 +51713,26 @@
         <v>50</v>
       </c>
       <c r="K999" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L999" s="3"/>
-      <c r="M999" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L999" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M999" s="3" t="s">
+        <v>3948</v>
+      </c>
       <c r="N999" s="3"/>
     </row>
     <row r="1000" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1000" s="3" t="s">
-        <v>3959</v>
+        <v>3962</v>
       </c>
       <c r="B1000" s="3"/>
       <c r="C1000" s="3">
         <v>408</v>
       </c>
       <c r="D1000" s="3" t="s">
-        <v>3960</v>
+        <v>3963</v>
       </c>
       <c r="E1000" s="3" t="s">
         <v>63</v>
@@ -50841,30 +51741,36 @@
         <v>72</v>
       </c>
       <c r="G1000" s="3" t="s">
-        <v>3961</v>
-      </c>
-      <c r="H1000" s="3"/>
+        <v>3964</v>
+      </c>
+      <c r="H1000" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1000" s="3">
         <v>13</v>
       </c>
       <c r="J1000" s="3"/>
       <c r="K1000" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1000" s="3"/>
-      <c r="M1000" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1000" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1000" s="3" t="s">
+        <v>3948</v>
+      </c>
       <c r="N1000" s="3"/>
     </row>
     <row r="1001" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1001" s="3" t="s">
-        <v>3962</v>
+        <v>3965</v>
       </c>
       <c r="B1001" s="3"/>
       <c r="C1001" s="3">
         <v>408</v>
       </c>
       <c r="D1001" s="3" t="s">
-        <v>3963</v>
+        <v>3966</v>
       </c>
       <c r="E1001" s="3" t="s">
         <v>63</v>
@@ -50873,30 +51779,36 @@
         <v>72</v>
       </c>
       <c r="G1001" s="3" t="s">
-        <v>3964</v>
-      </c>
-      <c r="H1001" s="3"/>
+        <v>3967</v>
+      </c>
+      <c r="H1001" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1001" s="3">
         <v>21</v>
       </c>
       <c r="J1001" s="3"/>
       <c r="K1001" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1001" s="3"/>
-      <c r="M1001" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1001" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1001" s="3" t="s">
+        <v>3948</v>
+      </c>
       <c r="N1001" s="3"/>
     </row>
     <row r="1002" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1002" s="3" t="s">
-        <v>3965</v>
+        <v>3968</v>
       </c>
       <c r="B1002" s="3"/>
       <c r="C1002" s="3">
         <v>414</v>
       </c>
       <c r="D1002" s="3" t="s">
-        <v>3966</v>
+        <v>3969</v>
       </c>
       <c r="E1002" s="3" t="s">
         <v>290</v>
@@ -50905,30 +51817,36 @@
         <v>1805</v>
       </c>
       <c r="G1002" s="3" t="s">
-        <v>3967</v>
-      </c>
-      <c r="H1002" s="3"/>
+        <v>3970</v>
+      </c>
+      <c r="H1002" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1002" s="3">
         <v>19</v>
       </c>
       <c r="J1002" s="3"/>
       <c r="K1002" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1002" s="3"/>
-      <c r="M1002" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1002" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1002" s="3" t="s">
+        <v>3948</v>
+      </c>
       <c r="N1002" s="3"/>
     </row>
     <row r="1003" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1003" s="3" t="s">
-        <v>3968</v>
+        <v>3971</v>
       </c>
       <c r="B1003" s="3"/>
       <c r="C1003" s="3">
         <v>409</v>
       </c>
       <c r="D1003" s="3" t="s">
-        <v>3969</v>
+        <v>3972</v>
       </c>
       <c r="E1003" s="3" t="s">
         <v>68</v>
@@ -50937,30 +51855,36 @@
         <v>28</v>
       </c>
       <c r="G1003" s="3" t="s">
-        <v>3970</v>
-      </c>
-      <c r="H1003" s="3"/>
+        <v>3973</v>
+      </c>
+      <c r="H1003" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1003" s="3">
         <v>4</v>
       </c>
       <c r="J1003" s="3"/>
       <c r="K1003" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1003" s="3"/>
-      <c r="M1003" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1003" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1003" s="3" t="s">
+        <v>3948</v>
+      </c>
       <c r="N1003" s="3"/>
     </row>
     <row r="1004" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1004" s="3" t="s">
-        <v>3971</v>
+        <v>3974</v>
       </c>
       <c r="B1004" s="3"/>
       <c r="C1004" s="3">
         <v>409</v>
       </c>
       <c r="D1004" s="3" t="s">
-        <v>3972</v>
+        <v>3975</v>
       </c>
       <c r="E1004" s="3" t="s">
         <v>1150</v>
@@ -50969,30 +51893,36 @@
         <v>2137</v>
       </c>
       <c r="G1004" s="3" t="s">
-        <v>3973</v>
-      </c>
-      <c r="H1004" s="3"/>
+        <v>3976</v>
+      </c>
+      <c r="H1004" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1004" s="3">
         <v>14</v>
       </c>
       <c r="J1004" s="3"/>
       <c r="K1004" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1004" s="3"/>
-      <c r="M1004" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1004" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1004" s="3" t="s">
+        <v>3948</v>
+      </c>
       <c r="N1004" s="3"/>
     </row>
     <row r="1005" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1005" s="3" t="s">
-        <v>3974</v>
+        <v>3977</v>
       </c>
       <c r="B1005" s="3"/>
       <c r="C1005" s="3">
         <v>409</v>
       </c>
       <c r="D1005" s="3" t="s">
-        <v>3975</v>
+        <v>3978</v>
       </c>
       <c r="E1005" s="3" t="s">
         <v>1150</v>
@@ -51001,30 +51931,36 @@
         <v>3450</v>
       </c>
       <c r="G1005" s="3" t="s">
-        <v>3976</v>
-      </c>
-      <c r="H1005" s="3"/>
+        <v>3979</v>
+      </c>
+      <c r="H1005" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1005" s="3">
         <v>45</v>
       </c>
       <c r="J1005" s="3"/>
       <c r="K1005" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1005" s="3"/>
-      <c r="M1005" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1005" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1005" s="3" t="s">
+        <v>3948</v>
+      </c>
       <c r="N1005" s="3"/>
     </row>
     <row r="1006" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1006" s="3" t="s">
-        <v>3977</v>
+        <v>3980</v>
       </c>
       <c r="B1006" s="3"/>
       <c r="C1006" s="3">
         <v>404</v>
       </c>
       <c r="D1006" s="3" t="s">
-        <v>3978</v>
+        <v>3981</v>
       </c>
       <c r="E1006" s="3" t="s">
         <v>290</v>
@@ -51033,30 +51969,36 @@
         <v>325</v>
       </c>
       <c r="G1006" s="3" t="s">
-        <v>3979</v>
-      </c>
-      <c r="H1006" s="3"/>
+        <v>3982</v>
+      </c>
+      <c r="H1006" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1006" s="3">
         <v>17</v>
       </c>
       <c r="J1006" s="3"/>
       <c r="K1006" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1006" s="3"/>
-      <c r="M1006" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1006" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1006" s="3" t="s">
+        <v>3983</v>
+      </c>
       <c r="N1006" s="3"/>
     </row>
     <row r="1007" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1007" s="3" t="s">
-        <v>3980</v>
+        <v>3984</v>
       </c>
       <c r="B1007" s="3"/>
       <c r="C1007" s="3">
         <v>404</v>
       </c>
       <c r="D1007" s="3" t="s">
-        <v>3981</v>
+        <v>3985</v>
       </c>
       <c r="E1007" s="3" t="s">
         <v>290</v>
@@ -51065,30 +52007,36 @@
         <v>388</v>
       </c>
       <c r="G1007" s="3" t="s">
-        <v>3982</v>
-      </c>
-      <c r="H1007" s="3"/>
+        <v>3986</v>
+      </c>
+      <c r="H1007" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1007" s="3">
         <v>8</v>
       </c>
       <c r="J1007" s="3"/>
       <c r="K1007" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1007" s="3"/>
-      <c r="M1007" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1007" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1007" s="3" t="s">
+        <v>3983</v>
+      </c>
       <c r="N1007" s="3"/>
     </row>
     <row r="1008" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1008" s="3" t="s">
-        <v>3983</v>
+        <v>3987</v>
       </c>
       <c r="B1008" s="3"/>
       <c r="C1008" s="3">
         <v>404</v>
       </c>
       <c r="D1008" s="3" t="s">
-        <v>3984</v>
+        <v>3988</v>
       </c>
       <c r="E1008" s="3" t="s">
         <v>290</v>
@@ -51097,30 +52045,38 @@
         <v>1835</v>
       </c>
       <c r="G1008" s="3" t="s">
-        <v>3985</v>
-      </c>
-      <c r="H1008" s="3"/>
+        <v>3989</v>
+      </c>
+      <c r="H1008" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1008" s="3">
         <v>23</v>
       </c>
       <c r="J1008" s="3"/>
       <c r="K1008" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1008" s="3"/>
-      <c r="M1008" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1008" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1008" s="3" t="s">
+        <v>3983</v>
+      </c>
       <c r="N1008" s="3"/>
     </row>
     <row r="1009" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1009" s="3" t="s">
-        <v>3986</v>
-      </c>
-      <c r="B1009" s="3"/>
+        <v>3990</v>
+      </c>
+      <c r="B1009" s="3" t="s">
+        <v>1026</v>
+      </c>
       <c r="C1009" s="3">
         <v>404</v>
       </c>
       <c r="D1009" s="3" t="s">
-        <v>3987</v>
+        <v>3991</v>
       </c>
       <c r="E1009" s="3" t="s">
         <v>211</v>
@@ -51129,30 +52085,38 @@
         <v>670</v>
       </c>
       <c r="G1009" s="3" t="s">
-        <v>3988</v>
-      </c>
-      <c r="H1009" s="3"/>
+        <v>3992</v>
+      </c>
+      <c r="H1009" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="I1009" s="3">
         <v>78</v>
       </c>
       <c r="J1009" s="3"/>
       <c r="K1009" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1009" s="3"/>
-      <c r="M1009" s="3"/>
-      <c r="N1009" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1009" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1009" s="3" t="s">
+        <v>3993</v>
+      </c>
+      <c r="N1009" s="3" t="s">
+        <v>3994</v>
+      </c>
     </row>
     <row r="1010" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1010" s="3" t="s">
-        <v>3989</v>
+        <v>3995</v>
       </c>
       <c r="B1010" s="3"/>
       <c r="C1010" s="3">
         <v>404</v>
       </c>
       <c r="D1010" s="3" t="s">
-        <v>3990</v>
+        <v>3996</v>
       </c>
       <c r="E1010" s="3" t="s">
         <v>290</v>
@@ -51161,9 +52125,11 @@
         <v>2555</v>
       </c>
       <c r="G1010" s="3" t="s">
-        <v>3991</v>
-      </c>
-      <c r="H1010" s="3"/>
+        <v>3997</v>
+      </c>
+      <c r="H1010" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1010" s="3">
         <v>33</v>
       </c>
@@ -51171,22 +52137,26 @@
         <v>50</v>
       </c>
       <c r="K1010" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1010" s="3"/>
-      <c r="M1010" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1010" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1010" s="3" t="s">
+        <v>3998</v>
+      </c>
       <c r="N1010" s="3"/>
     </row>
     <row r="1011" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1011" s="3" t="s">
-        <v>3992</v>
+        <v>3999</v>
       </c>
       <c r="B1011" s="3"/>
       <c r="C1011" s="3">
         <v>404</v>
       </c>
       <c r="D1011" s="3" t="s">
-        <v>3993</v>
+        <v>4000</v>
       </c>
       <c r="E1011" s="3" t="s">
         <v>290</v>
@@ -51195,30 +52165,38 @@
         <v>1049</v>
       </c>
       <c r="G1011" s="3" t="s">
-        <v>3994</v>
-      </c>
-      <c r="H1011" s="3"/>
+        <v>4001</v>
+      </c>
+      <c r="H1011" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1011" s="3">
         <v>33</v>
       </c>
       <c r="J1011" s="3"/>
       <c r="K1011" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1011" s="3"/>
-      <c r="M1011" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1011" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1011" s="3" t="s">
+        <v>3998</v>
+      </c>
       <c r="N1011" s="3"/>
     </row>
     <row r="1012" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1012" s="3" t="s">
-        <v>3995</v>
-      </c>
-      <c r="B1012" s="3"/>
+        <v>4002</v>
+      </c>
+      <c r="B1012" s="3" t="s">
+        <v>1026</v>
+      </c>
       <c r="C1012" s="3">
         <v>404</v>
       </c>
       <c r="D1012" s="3" t="s">
-        <v>3996</v>
+        <v>4003</v>
       </c>
       <c r="E1012" s="3" t="s">
         <v>63</v>
@@ -51227,30 +52205,38 @@
         <v>2257</v>
       </c>
       <c r="G1012" s="3" t="s">
-        <v>3997</v>
-      </c>
-      <c r="H1012" s="3"/>
+        <v>4004</v>
+      </c>
+      <c r="H1012" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="I1012" s="3">
         <v>16</v>
       </c>
       <c r="J1012" s="3"/>
       <c r="K1012" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1012" s="3"/>
-      <c r="M1012" s="3"/>
-      <c r="N1012" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1012" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1012" s="3" t="s">
+        <v>4005</v>
+      </c>
+      <c r="N1012" s="3" t="s">
+        <v>4006</v>
+      </c>
     </row>
     <row r="1013" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1013" s="3" t="s">
-        <v>3998</v>
+        <v>4007</v>
       </c>
       <c r="B1013" s="3"/>
       <c r="C1013" s="3">
         <v>404</v>
       </c>
       <c r="D1013" s="3" t="s">
-        <v>3999</v>
+        <v>4008</v>
       </c>
       <c r="E1013" s="3" t="s">
         <v>290</v>
@@ -51259,28 +52245,34 @@
         <v>1110</v>
       </c>
       <c r="G1013" s="3" t="s">
-        <v>4000</v>
-      </c>
-      <c r="H1013" s="3"/>
+        <v>4009</v>
+      </c>
+      <c r="H1013" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1013" s="3"/>
       <c r="J1013" s="3"/>
       <c r="K1013" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1013" s="3"/>
-      <c r="M1013" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1013" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1013" s="3" t="s">
+        <v>4005</v>
+      </c>
       <c r="N1013" s="3"/>
     </row>
     <row r="1014" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1014" s="3" t="s">
-        <v>4001</v>
+        <v>4010</v>
       </c>
       <c r="B1014" s="3"/>
       <c r="C1014" s="3">
         <v>409</v>
       </c>
       <c r="D1014" s="3" t="s">
-        <v>4002</v>
+        <v>4011</v>
       </c>
       <c r="E1014" s="3" t="s">
         <v>63</v>
@@ -51289,17 +52281,2703 @@
         <v>405</v>
       </c>
       <c r="G1014" s="3" t="s">
-        <v>4003</v>
-      </c>
-      <c r="H1014" s="3"/>
+        <v>4012</v>
+      </c>
+      <c r="H1014" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1014" s="3"/>
       <c r="J1014" s="3"/>
       <c r="K1014" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1014" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1014" s="3" t="s">
+        <v>4005</v>
+      </c>
+      <c r="N1014" s="3"/>
+    </row>
+    <row r="1015" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1015" s="3" t="s">
+        <v>4013</v>
+      </c>
+      <c r="B1015" s="3"/>
+      <c r="C1015" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1015" s="3" t="s">
+        <v>4014</v>
+      </c>
+      <c r="E1015" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1015" s="3" t="s">
+        <v>4015</v>
+      </c>
+      <c r="G1015" s="3" t="s">
+        <v>4016</v>
+      </c>
+      <c r="H1015" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1015" s="3">
+        <v>44</v>
+      </c>
+      <c r="J1015" s="3"/>
+      <c r="K1015" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1015" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1015" s="3" t="s">
+        <v>4005</v>
+      </c>
+      <c r="N1015" s="3"/>
+    </row>
+    <row r="1016" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1016" s="3" t="s">
+        <v>4017</v>
+      </c>
+      <c r="B1016" s="3"/>
+      <c r="C1016" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1016" s="3" t="s">
+        <v>4018</v>
+      </c>
+      <c r="E1016" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1016" s="3" t="s">
+        <v>1619</v>
+      </c>
+      <c r="G1016" s="3" t="s">
+        <v>4019</v>
+      </c>
+      <c r="H1016" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1016" s="3">
+        <v>27</v>
+      </c>
+      <c r="J1016" s="3"/>
+      <c r="K1016" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1016" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1016" s="3" t="s">
+        <v>4005</v>
+      </c>
+      <c r="N1016" s="3"/>
+    </row>
+    <row r="1017" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1017" s="3" t="s">
+        <v>4020</v>
+      </c>
+      <c r="B1017" s="3"/>
+      <c r="C1017" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1017" s="3" t="s">
+        <v>4021</v>
+      </c>
+      <c r="E1017" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1017" s="3" t="s">
+        <v>4022</v>
+      </c>
+      <c r="G1017" s="3" t="s">
+        <v>4023</v>
+      </c>
+      <c r="H1017" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1017" s="3"/>
+      <c r="J1017" s="3"/>
+      <c r="K1017" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1017" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1017" s="3" t="s">
+        <v>4005</v>
+      </c>
+      <c r="N1017" s="3"/>
+    </row>
+    <row r="1018" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1018" s="3" t="s">
+        <v>4024</v>
+      </c>
+      <c r="B1018" s="3"/>
+      <c r="C1018" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1018" s="3" t="s">
+        <v>4025</v>
+      </c>
+      <c r="E1018" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1018" s="3" t="s">
+        <v>4026</v>
+      </c>
+      <c r="G1018" s="3" t="s">
+        <v>4027</v>
+      </c>
+      <c r="H1018" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1018" s="3"/>
+      <c r="J1018" s="3"/>
+      <c r="K1018" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1018" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1018" s="3" t="s">
+        <v>4005</v>
+      </c>
+      <c r="N1018" s="3"/>
+    </row>
+    <row r="1019" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1019" s="3" t="s">
+        <v>4028</v>
+      </c>
+      <c r="B1019" s="3"/>
+      <c r="C1019" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1019" s="3" t="s">
+        <v>4029</v>
+      </c>
+      <c r="E1019" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1019" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="G1019" s="3" t="s">
+        <v>4030</v>
+      </c>
+      <c r="H1019" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1019" s="3">
+        <v>42</v>
+      </c>
+      <c r="J1019" s="3"/>
+      <c r="K1019" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1019" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1019" s="3" t="s">
+        <v>4005</v>
+      </c>
+      <c r="N1019" s="3"/>
+    </row>
+    <row r="1020" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1020" s="3" t="s">
+        <v>4031</v>
+      </c>
+      <c r="B1020" s="3"/>
+      <c r="C1020" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1020" s="3" t="s">
+        <v>4032</v>
+      </c>
+      <c r="E1020" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1020" s="3" t="s">
+        <v>4033</v>
+      </c>
+      <c r="G1020" s="3" t="s">
+        <v>4034</v>
+      </c>
+      <c r="H1020" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1020" s="3">
+        <v>25</v>
+      </c>
+      <c r="J1020" s="3"/>
+      <c r="K1020" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1020" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1020" s="3" t="s">
+        <v>4035</v>
+      </c>
+      <c r="N1020" s="3"/>
+    </row>
+    <row r="1021" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1021" s="3" t="s">
+        <v>4036</v>
+      </c>
+      <c r="B1021" s="3"/>
+      <c r="C1021" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1021" s="3" t="s">
+        <v>4037</v>
+      </c>
+      <c r="E1021" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1021" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="G1021" s="3" t="s">
+        <v>4038</v>
+      </c>
+      <c r="H1021" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1021" s="3"/>
+      <c r="J1021" s="3"/>
+      <c r="K1021" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1021" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1021" s="3" t="s">
+        <v>4035</v>
+      </c>
+      <c r="N1021" s="3"/>
+    </row>
+    <row r="1022" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1022" s="3" t="s">
+        <v>4036</v>
+      </c>
+      <c r="B1022" s="3"/>
+      <c r="C1022" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1022" s="3" t="s">
+        <v>4039</v>
+      </c>
+      <c r="E1022" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1022" s="3" t="s">
+        <v>2936</v>
+      </c>
+      <c r="G1022" s="3" t="s">
+        <v>4040</v>
+      </c>
+      <c r="H1022" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1022" s="3"/>
+      <c r="J1022" s="3"/>
+      <c r="K1022" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1022" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1022" s="3" t="s">
+        <v>4035</v>
+      </c>
+      <c r="N1022" s="3"/>
+    </row>
+    <row r="1023" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1023" s="3" t="s">
+        <v>4041</v>
+      </c>
+      <c r="B1023" s="3"/>
+      <c r="C1023" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1023" s="3" t="s">
+        <v>4042</v>
+      </c>
+      <c r="E1023" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1023" s="3" t="s">
+        <v>4043</v>
+      </c>
+      <c r="G1023" s="3" t="s">
+        <v>4044</v>
+      </c>
+      <c r="H1023" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1023" s="3">
+        <v>71</v>
+      </c>
+      <c r="J1023" s="3"/>
+      <c r="K1023" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1023" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1023" s="3" t="s">
+        <v>4045</v>
+      </c>
+      <c r="N1023" s="3"/>
+    </row>
+    <row r="1024" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1024" s="3" t="s">
+        <v>4046</v>
+      </c>
+      <c r="B1024" s="3"/>
+      <c r="C1024" s="3">
+        <v>410</v>
+      </c>
+      <c r="D1024" s="3" t="s">
+        <v>4047</v>
+      </c>
+      <c r="E1024" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1024" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G1024" s="3" t="s">
+        <v>4048</v>
+      </c>
+      <c r="H1024" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1024" s="3">
+        <v>19</v>
+      </c>
+      <c r="J1024" s="3"/>
+      <c r="K1024" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1024" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1024" s="3" t="s">
+        <v>4045</v>
+      </c>
+      <c r="N1024" s="3"/>
+    </row>
+    <row r="1025" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1025" s="3" t="s">
+        <v>4049</v>
+      </c>
+      <c r="B1025" s="3"/>
+      <c r="C1025" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1025" s="3" t="s">
+        <v>4050</v>
+      </c>
+      <c r="E1025" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="F1025" s="3" t="s">
+        <v>4051</v>
+      </c>
+      <c r="G1025" s="3" t="s">
+        <v>4052</v>
+      </c>
+      <c r="H1025" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1025" s="3">
+        <v>73</v>
+      </c>
+      <c r="J1025" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1025" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1025" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1025" s="3" t="s">
+        <v>4053</v>
+      </c>
+      <c r="N1025" s="3"/>
+    </row>
+    <row r="1026" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1026" s="3" t="s">
+        <v>4054</v>
+      </c>
+      <c r="B1026" s="3"/>
+      <c r="C1026" s="3">
+        <v>408</v>
+      </c>
+      <c r="D1026" s="3" t="s">
+        <v>4055</v>
+      </c>
+      <c r="E1026" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F1026" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="G1026" s="3" t="s">
+        <v>4056</v>
+      </c>
+      <c r="H1026" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1026" s="3"/>
+      <c r="J1026" s="3"/>
+      <c r="K1026" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1026" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1026" s="3" t="s">
+        <v>4053</v>
+      </c>
+      <c r="N1026" s="3"/>
+    </row>
+    <row r="1027" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1027" s="3" t="s">
+        <v>4057</v>
+      </c>
+      <c r="B1027" s="3"/>
+      <c r="C1027" s="3">
+        <v>408</v>
+      </c>
+      <c r="D1027" s="3" t="s">
+        <v>4058</v>
+      </c>
+      <c r="E1027" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1027" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="G1027" s="3" t="s">
+        <v>4059</v>
+      </c>
+      <c r="H1027" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1027" s="3">
         <v>22</v>
       </c>
-      <c r="L1014" s="3"/>
-      <c r="M1014" s="3"/>
-      <c r="N1014" s="3"/>
+      <c r="J1027" s="3"/>
+      <c r="K1027" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1027" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1027" s="3" t="s">
+        <v>4053</v>
+      </c>
+      <c r="N1027" s="3"/>
+    </row>
+    <row r="1028" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1028" s="3" t="s">
+        <v>4060</v>
+      </c>
+      <c r="B1028" s="3"/>
+      <c r="C1028" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1028" s="3" t="s">
+        <v>4061</v>
+      </c>
+      <c r="E1028" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1028" s="3" t="s">
+        <v>1110</v>
+      </c>
+      <c r="G1028" s="3" t="s">
+        <v>4062</v>
+      </c>
+      <c r="H1028" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1028" s="3">
+        <v>24</v>
+      </c>
+      <c r="J1028" s="3"/>
+      <c r="K1028" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1028" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1028" s="3" t="s">
+        <v>4053</v>
+      </c>
+      <c r="N1028" s="3"/>
+    </row>
+    <row r="1029" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1029" s="3" t="s">
+        <v>4063</v>
+      </c>
+      <c r="B1029" s="3"/>
+      <c r="C1029" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1029" s="3" t="s">
+        <v>4064</v>
+      </c>
+      <c r="E1029" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1029" s="3" t="s">
+        <v>4065</v>
+      </c>
+      <c r="G1029" s="3" t="s">
+        <v>4066</v>
+      </c>
+      <c r="H1029" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1029" s="3">
+        <v>72</v>
+      </c>
+      <c r="J1029" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1029" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1029" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1029" s="3" t="s">
+        <v>4053</v>
+      </c>
+      <c r="N1029" s="3"/>
+    </row>
+    <row r="1030" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1030" s="3" t="s">
+        <v>4067</v>
+      </c>
+      <c r="B1030" s="3" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C1030" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1030" s="3" t="s">
+        <v>4068</v>
+      </c>
+      <c r="E1030" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1030" s="3" t="s">
+        <v>1049</v>
+      </c>
+      <c r="G1030" s="3" t="s">
+        <v>4069</v>
+      </c>
+      <c r="H1030" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1030" s="3">
+        <v>10</v>
+      </c>
+      <c r="J1030" s="3"/>
+      <c r="K1030" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1030" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1030" s="3" t="s">
+        <v>4070</v>
+      </c>
+      <c r="N1030" s="3"/>
+    </row>
+    <row r="1031" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1031" s="3" t="s">
+        <v>4071</v>
+      </c>
+      <c r="B1031" s="3"/>
+      <c r="C1031" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1031" s="3" t="s">
+        <v>4072</v>
+      </c>
+      <c r="E1031" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1031" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="G1031" s="3" t="s">
+        <v>4073</v>
+      </c>
+      <c r="H1031" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1031" s="3">
+        <v>34</v>
+      </c>
+      <c r="J1031" s="3"/>
+      <c r="K1031" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1031" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1031" s="3" t="s">
+        <v>4074</v>
+      </c>
+      <c r="N1031" s="3"/>
+    </row>
+    <row r="1032" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1032" s="3" t="s">
+        <v>4075</v>
+      </c>
+      <c r="B1032" s="3"/>
+      <c r="C1032" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1032" s="3" t="s">
+        <v>4076</v>
+      </c>
+      <c r="E1032" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1032" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G1032" s="3" t="s">
+        <v>4077</v>
+      </c>
+      <c r="H1032" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1032" s="3">
+        <v>12</v>
+      </c>
+      <c r="J1032" s="3"/>
+      <c r="K1032" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1032" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1032" s="3" t="s">
+        <v>4078</v>
+      </c>
+      <c r="N1032" s="3"/>
+    </row>
+    <row r="1033" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1033" s="3" t="s">
+        <v>4079</v>
+      </c>
+      <c r="B1033" s="3"/>
+      <c r="C1033" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1033" s="3" t="s">
+        <v>4080</v>
+      </c>
+      <c r="E1033" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1033" s="3" t="s">
+        <v>2001</v>
+      </c>
+      <c r="G1033" s="3" t="s">
+        <v>4081</v>
+      </c>
+      <c r="H1033" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1033" s="3">
+        <v>18</v>
+      </c>
+      <c r="J1033" s="3"/>
+      <c r="K1033" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1033" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1033" s="3" t="s">
+        <v>4078</v>
+      </c>
+      <c r="N1033" s="3"/>
+    </row>
+    <row r="1034" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1034" s="3" t="s">
+        <v>4082</v>
+      </c>
+      <c r="B1034" s="3"/>
+      <c r="C1034" s="3">
+        <v>408</v>
+      </c>
+      <c r="D1034" s="3" t="s">
+        <v>4083</v>
+      </c>
+      <c r="E1034" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1034" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="G1034" s="3" t="s">
+        <v>4084</v>
+      </c>
+      <c r="H1034" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1034" s="3">
+        <v>23</v>
+      </c>
+      <c r="J1034" s="3"/>
+      <c r="K1034" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1034" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1034" s="3" t="s">
+        <v>4085</v>
+      </c>
+      <c r="N1034" s="3"/>
+    </row>
+    <row r="1035" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1035" s="3" t="s">
+        <v>4086</v>
+      </c>
+      <c r="B1035" s="3" t="s">
+        <v>2322</v>
+      </c>
+      <c r="C1035" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1035" s="3" t="s">
+        <v>4087</v>
+      </c>
+      <c r="E1035" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1035" s="3" t="s">
+        <v>4088</v>
+      </c>
+      <c r="G1035" s="3" t="s">
+        <v>4089</v>
+      </c>
+      <c r="H1035" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1035" s="3">
+        <v>22</v>
+      </c>
+      <c r="J1035" s="3"/>
+      <c r="K1035" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1035" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1035" s="3" t="s">
+        <v>4090</v>
+      </c>
+      <c r="N1035" s="3" t="s">
+        <v>4091</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1036" s="3" t="s">
+        <v>4092</v>
+      </c>
+      <c r="B1036" s="3"/>
+      <c r="C1036" s="3">
+        <v>408</v>
+      </c>
+      <c r="D1036" s="3" t="s">
+        <v>4093</v>
+      </c>
+      <c r="E1036" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1036" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="G1036" s="3" t="s">
+        <v>4094</v>
+      </c>
+      <c r="H1036" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1036" s="3">
+        <v>27</v>
+      </c>
+      <c r="J1036" s="3"/>
+      <c r="K1036" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1036" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1036" s="3" t="s">
+        <v>4091</v>
+      </c>
+      <c r="N1036" s="3"/>
+    </row>
+    <row r="1037" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1037" s="3" t="s">
+        <v>4095</v>
+      </c>
+      <c r="B1037" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1037" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1037" s="3" t="s">
+        <v>4096</v>
+      </c>
+      <c r="E1037" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1037" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="G1037" s="3" t="s">
+        <v>4097</v>
+      </c>
+      <c r="H1037" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1037" s="3">
+        <v>36</v>
+      </c>
+      <c r="J1037" s="3"/>
+      <c r="K1037" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1037" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1037" s="3" t="s">
+        <v>4091</v>
+      </c>
+      <c r="N1037" s="3" t="s">
+        <v>4098</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1038" s="3" t="s">
+        <v>4099</v>
+      </c>
+      <c r="B1038" s="3"/>
+      <c r="C1038" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1038" s="3" t="s">
+        <v>4100</v>
+      </c>
+      <c r="E1038" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1038" s="3" t="s">
+        <v>1610</v>
+      </c>
+      <c r="G1038" s="3" t="s">
+        <v>4101</v>
+      </c>
+      <c r="H1038" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1038" s="3">
+        <v>12</v>
+      </c>
+      <c r="J1038" s="3"/>
+      <c r="K1038" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1038" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1038" s="3" t="s">
+        <v>4098</v>
+      </c>
+      <c r="N1038" s="3"/>
+    </row>
+    <row r="1039" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1039" s="3" t="s">
+        <v>4102</v>
+      </c>
+      <c r="B1039" s="3"/>
+      <c r="C1039" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1039" s="3" t="s">
+        <v>4103</v>
+      </c>
+      <c r="E1039" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1039" s="3" t="s">
+        <v>1707</v>
+      </c>
+      <c r="G1039" s="3" t="s">
+        <v>4104</v>
+      </c>
+      <c r="H1039" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1039" s="3"/>
+      <c r="J1039" s="3"/>
+      <c r="K1039" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1039" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1039" s="3" t="s">
+        <v>4098</v>
+      </c>
+      <c r="N1039" s="3"/>
+    </row>
+    <row r="1040" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1040" s="3" t="s">
+        <v>4105</v>
+      </c>
+      <c r="B1040" s="3"/>
+      <c r="C1040" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1040" s="3" t="s">
+        <v>4106</v>
+      </c>
+      <c r="E1040" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1040" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="G1040" s="3" t="s">
+        <v>4107</v>
+      </c>
+      <c r="H1040" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1040" s="3">
+        <v>17</v>
+      </c>
+      <c r="J1040" s="3"/>
+      <c r="K1040" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1040" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1040" s="3" t="s">
+        <v>4108</v>
+      </c>
+      <c r="N1040" s="3"/>
+    </row>
+    <row r="1041" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1041" s="3" t="s">
+        <v>4109</v>
+      </c>
+      <c r="B1041" s="3"/>
+      <c r="C1041" s="3">
+        <v>410</v>
+      </c>
+      <c r="D1041" s="3" t="s">
+        <v>4110</v>
+      </c>
+      <c r="E1041" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1041" s="3" t="s">
+        <v>2112</v>
+      </c>
+      <c r="G1041" s="3" t="s">
+        <v>4111</v>
+      </c>
+      <c r="H1041" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1041" s="3"/>
+      <c r="J1041" s="3"/>
+      <c r="K1041" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1041" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1041" s="3" t="s">
+        <v>4112</v>
+      </c>
+      <c r="N1041" s="3"/>
+    </row>
+    <row r="1042" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1042" s="3" t="s">
+        <v>4113</v>
+      </c>
+      <c r="B1042" s="3"/>
+      <c r="C1042" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1042" s="3" t="s">
+        <v>4114</v>
+      </c>
+      <c r="E1042" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F1042" s="3" t="s">
+        <v>4115</v>
+      </c>
+      <c r="G1042" s="3" t="s">
+        <v>4116</v>
+      </c>
+      <c r="H1042" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1042" s="3">
+        <v>80</v>
+      </c>
+      <c r="J1042" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1042" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1042" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1042" s="3" t="s">
+        <v>4112</v>
+      </c>
+      <c r="N1042" s="3"/>
+    </row>
+    <row r="1043" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1043" s="3" t="s">
+        <v>4117</v>
+      </c>
+      <c r="B1043" s="3"/>
+      <c r="C1043" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1043" s="3" t="s">
+        <v>4118</v>
+      </c>
+      <c r="E1043" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F1043" s="3" t="s">
+        <v>4119</v>
+      </c>
+      <c r="G1043" s="3" t="s">
+        <v>4120</v>
+      </c>
+      <c r="H1043" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1043" s="3">
+        <v>84</v>
+      </c>
+      <c r="J1043" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1043" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1043" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1043" s="3" t="s">
+        <v>4121</v>
+      </c>
+      <c r="N1043" s="3"/>
+    </row>
+    <row r="1044" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1044" s="3" t="s">
+        <v>4122</v>
+      </c>
+      <c r="B1044" s="3"/>
+      <c r="C1044" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1044" s="3" t="s">
+        <v>4123</v>
+      </c>
+      <c r="E1044" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F1044" s="3" t="s">
+        <v>4124</v>
+      </c>
+      <c r="G1044" s="3" t="s">
+        <v>4125</v>
+      </c>
+      <c r="H1044" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1044" s="3"/>
+      <c r="J1044" s="3"/>
+      <c r="K1044" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1044" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1044" s="3" t="s">
+        <v>4121</v>
+      </c>
+      <c r="N1044" s="3"/>
+    </row>
+    <row r="1045" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1045" s="3" t="s">
+        <v>4126</v>
+      </c>
+      <c r="B1045" s="3"/>
+      <c r="C1045" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1045" s="3" t="s">
+        <v>4127</v>
+      </c>
+      <c r="E1045" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F1045" s="3" t="s">
+        <v>4128</v>
+      </c>
+      <c r="G1045" s="3" t="s">
+        <v>4129</v>
+      </c>
+      <c r="H1045" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1045" s="3">
+        <v>82</v>
+      </c>
+      <c r="J1045" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1045" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1045" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1045" s="3" t="s">
+        <v>4121</v>
+      </c>
+      <c r="N1045" s="3"/>
+    </row>
+    <row r="1046" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1046" s="3" t="s">
+        <v>4130</v>
+      </c>
+      <c r="B1046" s="3"/>
+      <c r="C1046" s="3">
+        <v>408</v>
+      </c>
+      <c r="D1046" s="3" t="s">
+        <v>4131</v>
+      </c>
+      <c r="E1046" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1046" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="G1046" s="3" t="s">
+        <v>4132</v>
+      </c>
+      <c r="H1046" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1046" s="3">
+        <v>34</v>
+      </c>
+      <c r="J1046" s="3"/>
+      <c r="K1046" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1046" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1046" s="3" t="s">
+        <v>4133</v>
+      </c>
+      <c r="N1046" s="3"/>
+    </row>
+    <row r="1047" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1047" s="3" t="s">
+        <v>4134</v>
+      </c>
+      <c r="B1047" s="3"/>
+      <c r="C1047" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1047" s="3" t="s">
+        <v>4135</v>
+      </c>
+      <c r="E1047" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1047" s="3" t="s">
+        <v>4136</v>
+      </c>
+      <c r="G1047" s="3" t="s">
+        <v>4137</v>
+      </c>
+      <c r="H1047" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1047" s="3"/>
+      <c r="J1047" s="3"/>
+      <c r="K1047" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1047" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1047" s="3" t="s">
+        <v>4133</v>
+      </c>
+      <c r="N1047" s="3"/>
+    </row>
+    <row r="1048" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1048" s="3" t="s">
+        <v>4138</v>
+      </c>
+      <c r="B1048" s="3"/>
+      <c r="C1048" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1048" s="3" t="s">
+        <v>4139</v>
+      </c>
+      <c r="E1048" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1048" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="G1048" s="3" t="s">
+        <v>4140</v>
+      </c>
+      <c r="H1048" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1048" s="3">
+        <v>38</v>
+      </c>
+      <c r="J1048" s="3"/>
+      <c r="K1048" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1048" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1048" s="3" t="s">
+        <v>4141</v>
+      </c>
+      <c r="N1048" s="3"/>
+    </row>
+    <row r="1049" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1049" s="3" t="s">
+        <v>4142</v>
+      </c>
+      <c r="B1049" s="3"/>
+      <c r="C1049" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1049" s="3" t="s">
+        <v>4143</v>
+      </c>
+      <c r="E1049" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1049" s="3" t="s">
+        <v>2555</v>
+      </c>
+      <c r="G1049" s="3" t="s">
+        <v>4144</v>
+      </c>
+      <c r="H1049" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1049" s="3">
+        <v>4</v>
+      </c>
+      <c r="J1049" s="3"/>
+      <c r="K1049" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1049" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1049" s="3" t="s">
+        <v>4133</v>
+      </c>
+      <c r="N1049" s="3"/>
+    </row>
+    <row r="1050" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1050" s="3" t="s">
+        <v>4145</v>
+      </c>
+      <c r="B1050" s="3"/>
+      <c r="C1050" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1050" s="3" t="s">
+        <v>4146</v>
+      </c>
+      <c r="E1050" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1050" s="3" t="s">
+        <v>1610</v>
+      </c>
+      <c r="G1050" s="3" t="s">
+        <v>4147</v>
+      </c>
+      <c r="H1050" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1050" s="3">
+        <v>24</v>
+      </c>
+      <c r="J1050" s="3"/>
+      <c r="K1050" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1050" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1050" s="3" t="s">
+        <v>4133</v>
+      </c>
+      <c r="N1050" s="3"/>
+    </row>
+    <row r="1051" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1051" s="3" t="s">
+        <v>4148</v>
+      </c>
+      <c r="B1051" s="3"/>
+      <c r="C1051" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1051" s="3" t="s">
+        <v>4149</v>
+      </c>
+      <c r="E1051" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F1051" s="3" t="s">
+        <v>4150</v>
+      </c>
+      <c r="G1051" s="3" t="s">
+        <v>4151</v>
+      </c>
+      <c r="H1051" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1051" s="3">
+        <v>83</v>
+      </c>
+      <c r="J1051" s="3"/>
+      <c r="K1051" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1051" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1051" s="3" t="s">
+        <v>4133</v>
+      </c>
+      <c r="N1051" s="3"/>
+    </row>
+    <row r="1052" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1052" s="3" t="s">
+        <v>4152</v>
+      </c>
+      <c r="B1052" s="3"/>
+      <c r="C1052" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1052" s="3" t="s">
+        <v>4153</v>
+      </c>
+      <c r="E1052" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F1052" s="3" t="s">
+        <v>4154</v>
+      </c>
+      <c r="G1052" s="3" t="s">
+        <v>4155</v>
+      </c>
+      <c r="H1052" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1052" s="3">
+        <v>80</v>
+      </c>
+      <c r="J1052" s="3"/>
+      <c r="K1052" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1052" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1052" s="3" t="s">
+        <v>4133</v>
+      </c>
+      <c r="N1052" s="3"/>
+    </row>
+    <row r="1053" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1053" s="3" t="s">
+        <v>4156</v>
+      </c>
+      <c r="B1053" s="3"/>
+      <c r="C1053" s="3">
+        <v>414</v>
+      </c>
+      <c r="D1053" s="3" t="s">
+        <v>4157</v>
+      </c>
+      <c r="E1053" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1053" s="3" t="s">
+        <v>4158</v>
+      </c>
+      <c r="G1053" s="3" t="s">
+        <v>4159</v>
+      </c>
+      <c r="H1053" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1053" s="3">
+        <v>17</v>
+      </c>
+      <c r="J1053" s="3"/>
+      <c r="K1053" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1053" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1053" s="3" t="s">
+        <v>4133</v>
+      </c>
+      <c r="N1053" s="3"/>
+    </row>
+    <row r="1054" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1054" s="3" t="s">
+        <v>4156</v>
+      </c>
+      <c r="B1054" s="3"/>
+      <c r="C1054" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1054" s="3" t="s">
+        <v>4160</v>
+      </c>
+      <c r="E1054" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F1054" s="3" t="s">
+        <v>4161</v>
+      </c>
+      <c r="G1054" s="3" t="s">
+        <v>4162</v>
+      </c>
+      <c r="H1054" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1054" s="3">
+        <v>80</v>
+      </c>
+      <c r="J1054" s="3"/>
+      <c r="K1054" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1054" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1054" s="3" t="s">
+        <v>4133</v>
+      </c>
+      <c r="N1054" s="3"/>
+    </row>
+    <row r="1055" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1055" s="3" t="s">
+        <v>4163</v>
+      </c>
+      <c r="B1055" s="3"/>
+      <c r="C1055" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1055" s="3" t="s">
+        <v>4164</v>
+      </c>
+      <c r="E1055" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F1055" s="3" t="s">
+        <v>4165</v>
+      </c>
+      <c r="G1055" s="3" t="s">
+        <v>4166</v>
+      </c>
+      <c r="H1055" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1055" s="3">
+        <v>81</v>
+      </c>
+      <c r="J1055" s="3"/>
+      <c r="K1055" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1055" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1055" s="3" t="s">
+        <v>4133</v>
+      </c>
+      <c r="N1055" s="3"/>
+    </row>
+    <row r="1056" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1056" s="3" t="s">
+        <v>4167</v>
+      </c>
+      <c r="B1056" s="3"/>
+      <c r="C1056" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1056" s="3" t="s">
+        <v>4168</v>
+      </c>
+      <c r="E1056" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F1056" s="3" t="s">
+        <v>4169</v>
+      </c>
+      <c r="G1056" s="3" t="s">
+        <v>4170</v>
+      </c>
+      <c r="H1056" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1056" s="3">
+        <v>81</v>
+      </c>
+      <c r="J1056" s="3"/>
+      <c r="K1056" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1056" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1056" s="3" t="s">
+        <v>4133</v>
+      </c>
+      <c r="N1056" s="3"/>
+    </row>
+    <row r="1057" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1057" s="3" t="s">
+        <v>4171</v>
+      </c>
+      <c r="B1057" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C1057" s="3">
+        <v>413</v>
+      </c>
+      <c r="D1057" s="3" t="s">
+        <v>4172</v>
+      </c>
+      <c r="E1057" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1057" s="3" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G1057" s="3" t="s">
+        <v>4173</v>
+      </c>
+      <c r="H1057" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1057" s="3">
+        <v>78</v>
+      </c>
+      <c r="J1057" s="3"/>
+      <c r="K1057" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1057" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1057" s="3" t="s">
+        <v>4174</v>
+      </c>
+      <c r="N1057" s="3" t="s">
+        <v>4175</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1058" s="3" t="s">
+        <v>4176</v>
+      </c>
+      <c r="B1058" s="3" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C1058" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1058" s="3" t="s">
+        <v>4177</v>
+      </c>
+      <c r="E1058" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1058" s="3" t="s">
+        <v>4178</v>
+      </c>
+      <c r="G1058" s="3" t="s">
+        <v>4179</v>
+      </c>
+      <c r="H1058" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1058" s="3">
+        <v>35</v>
+      </c>
+      <c r="J1058" s="3"/>
+      <c r="K1058" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1058" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1058" s="3" t="s">
+        <v>4180</v>
+      </c>
+      <c r="N1058" s="3" t="s">
+        <v>4181</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1059" s="3" t="s">
+        <v>4182</v>
+      </c>
+      <c r="B1059" s="3"/>
+      <c r="C1059" s="3">
+        <v>410</v>
+      </c>
+      <c r="D1059" s="3" t="s">
+        <v>4183</v>
+      </c>
+      <c r="E1059" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1059" s="3" t="s">
+        <v>2555</v>
+      </c>
+      <c r="G1059" s="3" t="s">
+        <v>4184</v>
+      </c>
+      <c r="H1059" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1059" s="3">
+        <v>43</v>
+      </c>
+      <c r="J1059" s="3">
+        <v>50</v>
+      </c>
+      <c r="K1059" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1059" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1059" s="3" t="s">
+        <v>4185</v>
+      </c>
+      <c r="N1059" s="3"/>
+    </row>
+    <row r="1060" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1060" s="3" t="s">
+        <v>4186</v>
+      </c>
+      <c r="B1060" s="3"/>
+      <c r="C1060" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1060" s="3" t="s">
+        <v>4187</v>
+      </c>
+      <c r="E1060" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1060" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1060" s="3" t="s">
+        <v>4188</v>
+      </c>
+      <c r="H1060" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1060" s="3">
+        <v>46</v>
+      </c>
+      <c r="J1060" s="3"/>
+      <c r="K1060" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1060" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1060" s="3" t="s">
+        <v>4189</v>
+      </c>
+      <c r="N1060" s="3"/>
+    </row>
+    <row r="1061" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1061" s="3" t="s">
+        <v>4190</v>
+      </c>
+      <c r="B1061" s="3"/>
+      <c r="C1061" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1061" s="3" t="s">
+        <v>4191</v>
+      </c>
+      <c r="E1061" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F1061" s="3" t="s">
+        <v>4192</v>
+      </c>
+      <c r="G1061" s="3" t="s">
+        <v>4193</v>
+      </c>
+      <c r="H1061" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1061" s="3">
+        <v>81</v>
+      </c>
+      <c r="J1061" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1061" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1061" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1061" s="3" t="s">
+        <v>4141</v>
+      </c>
+      <c r="N1061" s="3"/>
+    </row>
+    <row r="1062" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1062" s="3" t="s">
+        <v>4194</v>
+      </c>
+      <c r="B1062" s="3"/>
+      <c r="C1062" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1062" s="3" t="s">
+        <v>4195</v>
+      </c>
+      <c r="E1062" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F1062" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="G1062" s="3" t="s">
+        <v>4196</v>
+      </c>
+      <c r="H1062" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1062" s="3">
+        <v>78</v>
+      </c>
+      <c r="J1062" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1062" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1062" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1062" s="3" t="s">
+        <v>4141</v>
+      </c>
+      <c r="N1062" s="3"/>
+    </row>
+    <row r="1063" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1063" s="3" t="s">
+        <v>4197</v>
+      </c>
+      <c r="B1063" s="3"/>
+      <c r="C1063" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1063" s="3" t="s">
+        <v>4198</v>
+      </c>
+      <c r="E1063" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F1063" s="3" t="s">
+        <v>4199</v>
+      </c>
+      <c r="G1063" s="3" t="s">
+        <v>4200</v>
+      </c>
+      <c r="H1063" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1063" s="3">
+        <v>81</v>
+      </c>
+      <c r="J1063" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1063" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1063" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1063" s="3" t="s">
+        <v>4189</v>
+      </c>
+      <c r="N1063" s="3"/>
+    </row>
+    <row r="1064" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1064" s="3" t="s">
+        <v>4201</v>
+      </c>
+      <c r="B1064" s="3"/>
+      <c r="C1064" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1064" s="3" t="s">
+        <v>4202</v>
+      </c>
+      <c r="E1064" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F1064" s="3" t="s">
+        <v>4203</v>
+      </c>
+      <c r="G1064" s="3" t="s">
+        <v>4204</v>
+      </c>
+      <c r="H1064" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1064" s="3">
+        <v>78</v>
+      </c>
+      <c r="J1064" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1064" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1064" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1064" s="3" t="s">
+        <v>4189</v>
+      </c>
+      <c r="N1064" s="3"/>
+    </row>
+    <row r="1065" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1065" s="3" t="s">
+        <v>4205</v>
+      </c>
+      <c r="B1065" s="3"/>
+      <c r="C1065" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1065" s="3" t="s">
+        <v>4206</v>
+      </c>
+      <c r="E1065" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F1065" s="3" t="s">
+        <v>4207</v>
+      </c>
+      <c r="G1065" s="3" t="s">
+        <v>4208</v>
+      </c>
+      <c r="H1065" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1065" s="3">
+        <v>78</v>
+      </c>
+      <c r="J1065" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1065" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1065" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1065" s="3" t="s">
+        <v>4189</v>
+      </c>
+      <c r="N1065" s="3"/>
+    </row>
+    <row r="1066" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1066" s="3" t="s">
+        <v>4209</v>
+      </c>
+      <c r="B1066" s="3"/>
+      <c r="C1066" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1066" s="3" t="s">
+        <v>4210</v>
+      </c>
+      <c r="E1066" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F1066" s="3" t="s">
+        <v>4211</v>
+      </c>
+      <c r="G1066" s="3" t="s">
+        <v>4212</v>
+      </c>
+      <c r="H1066" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1066" s="3"/>
+      <c r="J1066" s="3"/>
+      <c r="K1066" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1066" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1066" s="3" t="s">
+        <v>4189</v>
+      </c>
+      <c r="N1066" s="3"/>
+    </row>
+    <row r="1067" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1067" s="3" t="s">
+        <v>4213</v>
+      </c>
+      <c r="B1067" s="3"/>
+      <c r="C1067" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1067" s="3" t="s">
+        <v>4214</v>
+      </c>
+      <c r="E1067" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F1067" s="3" t="s">
+        <v>4215</v>
+      </c>
+      <c r="G1067" s="3" t="s">
+        <v>4216</v>
+      </c>
+      <c r="H1067" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1067" s="3">
+        <v>81</v>
+      </c>
+      <c r="J1067" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1067" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1067" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1067" s="3" t="s">
+        <v>4189</v>
+      </c>
+      <c r="N1067" s="3"/>
+    </row>
+    <row r="1068" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1068" s="3" t="s">
+        <v>4217</v>
+      </c>
+      <c r="B1068" s="3"/>
+      <c r="C1068" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1068" s="3" t="s">
+        <v>4218</v>
+      </c>
+      <c r="E1068" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F1068" s="3" t="s">
+        <v>4219</v>
+      </c>
+      <c r="G1068" s="3" t="s">
+        <v>4220</v>
+      </c>
+      <c r="H1068" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1068" s="3">
+        <v>80</v>
+      </c>
+      <c r="J1068" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1068" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1068" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1068" s="3" t="s">
+        <v>4189</v>
+      </c>
+      <c r="N1068" s="3"/>
+    </row>
+    <row r="1069" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1069" s="3" t="s">
+        <v>4221</v>
+      </c>
+      <c r="B1069" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C1069" s="3">
+        <v>408</v>
+      </c>
+      <c r="D1069" s="3" t="s">
+        <v>4222</v>
+      </c>
+      <c r="E1069" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1069" s="3" t="s">
+        <v>4223</v>
+      </c>
+      <c r="G1069" s="3" t="s">
+        <v>4224</v>
+      </c>
+      <c r="H1069" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1069" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1069" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1069" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1069" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1069" s="3" t="s">
+        <v>4225</v>
+      </c>
+      <c r="N1069" s="3"/>
+    </row>
+    <row r="1070" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1070" s="3" t="s">
+        <v>4226</v>
+      </c>
+      <c r="B1070" s="3"/>
+      <c r="C1070" s="3">
+        <v>408</v>
+      </c>
+      <c r="D1070" s="3" t="s">
+        <v>4227</v>
+      </c>
+      <c r="E1070" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1070" s="3" t="s">
+        <v>4228</v>
+      </c>
+      <c r="G1070" s="3" t="s">
+        <v>4229</v>
+      </c>
+      <c r="H1070" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1070" s="3">
+        <v>75</v>
+      </c>
+      <c r="J1070" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1070" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1070" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1070" s="3" t="s">
+        <v>4230</v>
+      </c>
+      <c r="N1070" s="3"/>
+    </row>
+    <row r="1071" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1071" s="3" t="s">
+        <v>4231</v>
+      </c>
+      <c r="B1071" s="3"/>
+      <c r="C1071" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1071" s="3" t="s">
+        <v>4232</v>
+      </c>
+      <c r="E1071" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1071" s="3" t="s">
+        <v>3594</v>
+      </c>
+      <c r="G1071" s="3" t="s">
+        <v>4233</v>
+      </c>
+      <c r="H1071" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1071" s="3">
+        <v>13</v>
+      </c>
+      <c r="J1071" s="3"/>
+      <c r="K1071" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1071" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1071" s="3" t="s">
+        <v>4230</v>
+      </c>
+      <c r="N1071" s="3"/>
+    </row>
+    <row r="1072" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1072" s="3" t="s">
+        <v>4234</v>
+      </c>
+      <c r="B1072" s="3"/>
+      <c r="C1072" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1072" s="3" t="s">
+        <v>4235</v>
+      </c>
+      <c r="E1072" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1072" s="3" t="s">
+        <v>1610</v>
+      </c>
+      <c r="G1072" s="3" t="s">
+        <v>4236</v>
+      </c>
+      <c r="H1072" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1072" s="3">
+        <v>21</v>
+      </c>
+      <c r="J1072" s="3"/>
+      <c r="K1072" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1072" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1072" s="3" t="s">
+        <v>4230</v>
+      </c>
+      <c r="N1072" s="3"/>
+    </row>
+    <row r="1073" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1073" s="3" t="s">
+        <v>4237</v>
+      </c>
+      <c r="B1073" s="3"/>
+      <c r="C1073" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1073" s="3" t="s">
+        <v>4238</v>
+      </c>
+      <c r="E1073" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1073" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G1073" s="3" t="s">
+        <v>4239</v>
+      </c>
+      <c r="H1073" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1073" s="3">
+        <v>8</v>
+      </c>
+      <c r="J1073" s="3"/>
+      <c r="K1073" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1073" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1073" s="3" t="s">
+        <v>4230</v>
+      </c>
+      <c r="N1073" s="3"/>
+    </row>
+    <row r="1074" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1074" s="3" t="s">
+        <v>4240</v>
+      </c>
+      <c r="B1074" s="3"/>
+      <c r="C1074" s="3">
+        <v>408</v>
+      </c>
+      <c r="D1074" s="3" t="s">
+        <v>4241</v>
+      </c>
+      <c r="E1074" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1074" s="3" t="s">
+        <v>4242</v>
+      </c>
+      <c r="G1074" s="3" t="s">
+        <v>4243</v>
+      </c>
+      <c r="H1074" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1074" s="3">
+        <v>75</v>
+      </c>
+      <c r="J1074" s="3"/>
+      <c r="K1074" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1074" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1074" s="3" t="s">
+        <v>4230</v>
+      </c>
+      <c r="N1074" s="3"/>
+    </row>
+    <row r="1075" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1075" s="3" t="s">
+        <v>4244</v>
+      </c>
+      <c r="B1075" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C1075" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1075" s="3" t="s">
+        <v>4245</v>
+      </c>
+      <c r="E1075" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1075" s="3" t="s">
+        <v>4246</v>
+      </c>
+      <c r="G1075" s="3" t="s">
+        <v>4247</v>
+      </c>
+      <c r="H1075" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1075" s="3">
+        <v>14</v>
+      </c>
+      <c r="J1075" s="3"/>
+      <c r="K1075" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1075" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1075" s="3" t="s">
+        <v>4248</v>
+      </c>
+      <c r="N1075" s="3" t="s">
+        <v>4249</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1076" s="3" t="s">
+        <v>4244</v>
+      </c>
+      <c r="B1076" s="3"/>
+      <c r="C1076" s="3">
+        <v>408</v>
+      </c>
+      <c r="D1076" s="3" t="s">
+        <v>4250</v>
+      </c>
+      <c r="E1076" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1076" s="3" t="s">
+        <v>2172</v>
+      </c>
+      <c r="G1076" s="3" t="s">
+        <v>4251</v>
+      </c>
+      <c r="H1076" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1076" s="3">
+        <v>53</v>
+      </c>
+      <c r="J1076" s="3"/>
+      <c r="K1076" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1076" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1076" s="3" t="s">
+        <v>4252</v>
+      </c>
+      <c r="N1076" s="3"/>
+    </row>
+    <row r="1077" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1077" s="3" t="s">
+        <v>4253</v>
+      </c>
+      <c r="B1077" s="3"/>
+      <c r="C1077" s="3">
+        <v>410</v>
+      </c>
+      <c r="D1077" s="3" t="s">
+        <v>4254</v>
+      </c>
+      <c r="E1077" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1077" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G1077" s="3" t="s">
+        <v>4255</v>
+      </c>
+      <c r="H1077" s="3"/>
+      <c r="I1077" s="3">
+        <v>22</v>
+      </c>
+      <c r="J1077" s="3"/>
+      <c r="K1077" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1077" s="3"/>
+      <c r="M1077" s="3"/>
+      <c r="N1077" s="3"/>
+    </row>
+    <row r="1078" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1078" s="3" t="s">
+        <v>4256</v>
+      </c>
+      <c r="B1078" s="3"/>
+      <c r="C1078" s="3">
+        <v>410</v>
+      </c>
+      <c r="D1078" s="3" t="s">
+        <v>4257</v>
+      </c>
+      <c r="E1078" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1078" s="3" t="s">
+        <v>4258</v>
+      </c>
+      <c r="G1078" s="3" t="s">
+        <v>4259</v>
+      </c>
+      <c r="H1078" s="3"/>
+      <c r="I1078" s="3">
+        <v>16</v>
+      </c>
+      <c r="J1078" s="3"/>
+      <c r="K1078" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1078" s="3"/>
+      <c r="M1078" s="3"/>
+      <c r="N1078" s="3"/>
+    </row>
+    <row r="1079" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1079" s="3" t="s">
+        <v>4260</v>
+      </c>
+      <c r="B1079" s="3"/>
+      <c r="C1079" s="3">
+        <v>408</v>
+      </c>
+      <c r="D1079" s="3" t="s">
+        <v>4261</v>
+      </c>
+      <c r="E1079" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1079" s="3" t="s">
+        <v>4262</v>
+      </c>
+      <c r="G1079" s="3" t="s">
+        <v>4263</v>
+      </c>
+      <c r="H1079" s="3"/>
+      <c r="I1079" s="3"/>
+      <c r="J1079" s="3"/>
+      <c r="K1079" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1079" s="3"/>
+      <c r="M1079" s="3"/>
+      <c r="N1079" s="3"/>
+    </row>
+    <row r="1080" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1080" s="3" t="s">
+        <v>4264</v>
+      </c>
+      <c r="B1080" s="3"/>
+      <c r="C1080" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1080" s="3" t="s">
+        <v>4265</v>
+      </c>
+      <c r="E1080" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1080" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="G1080" s="3" t="s">
+        <v>4266</v>
+      </c>
+      <c r="H1080" s="3"/>
+      <c r="I1080" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1080" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1080" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1080" s="3"/>
+      <c r="M1080" s="3"/>
+      <c r="N1080" s="3"/>
+    </row>
+    <row r="1081" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1081" s="3" t="s">
+        <v>4267</v>
+      </c>
+      <c r="B1081" s="3"/>
+      <c r="C1081" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1081" s="3" t="s">
+        <v>4268</v>
+      </c>
+      <c r="E1081" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1081" s="3" t="s">
+        <v>4269</v>
+      </c>
+      <c r="G1081" s="3" t="s">
+        <v>4270</v>
+      </c>
+      <c r="H1081" s="3"/>
+      <c r="I1081" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1081" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1081" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1081" s="3"/>
+      <c r="M1081" s="3"/>
+      <c r="N1081" s="3"/>
+    </row>
+    <row r="1082" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1082" s="3" t="s">
+        <v>4271</v>
+      </c>
+      <c r="B1082" s="3"/>
+      <c r="C1082" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1082" s="3" t="s">
+        <v>4272</v>
+      </c>
+      <c r="E1082" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1082" s="3" t="s">
+        <v>1179</v>
+      </c>
+      <c r="G1082" s="3" t="s">
+        <v>4273</v>
+      </c>
+      <c r="H1082" s="3"/>
+      <c r="I1082" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1082" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1082" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1082" s="3"/>
+      <c r="M1082" s="3"/>
+      <c r="N1082" s="3"/>
+    </row>
+    <row r="1083" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1083" s="3" t="s">
+        <v>4274</v>
+      </c>
+      <c r="B1083" s="3"/>
+      <c r="C1083" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1083" s="3" t="s">
+        <v>4275</v>
+      </c>
+      <c r="E1083" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1083" s="3" t="s">
+        <v>4276</v>
+      </c>
+      <c r="G1083" s="3" t="s">
+        <v>4277</v>
+      </c>
+      <c r="H1083" s="3"/>
+      <c r="I1083" s="3"/>
+      <c r="J1083" s="3"/>
+      <c r="K1083" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1083" s="3"/>
+      <c r="M1083" s="3"/>
+      <c r="N1083" s="3"/>
+    </row>
+    <row r="1084" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1084" s="3" t="s">
+        <v>4278</v>
+      </c>
+      <c r="B1084" s="3"/>
+      <c r="C1084" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1084" s="3" t="s">
+        <v>4279</v>
+      </c>
+      <c r="E1084" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1084" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1084" s="3" t="s">
+        <v>4280</v>
+      </c>
+      <c r="H1084" s="3"/>
+      <c r="I1084" s="3">
+        <v>15</v>
+      </c>
+      <c r="J1084" s="3"/>
+      <c r="K1084" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1084" s="3"/>
+      <c r="M1084" s="3"/>
+      <c r="N1084" s="3"/>
+    </row>
+    <row r="1085" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1085" s="3" t="s">
+        <v>4281</v>
+      </c>
+      <c r="B1085" s="3"/>
+      <c r="C1085" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1085" s="3" t="s">
+        <v>4282</v>
+      </c>
+      <c r="E1085" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1085" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G1085" s="3" t="s">
+        <v>4283</v>
+      </c>
+      <c r="H1085" s="3"/>
+      <c r="I1085" s="3">
+        <v>52</v>
+      </c>
+      <c r="J1085" s="3"/>
+      <c r="K1085" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1085" s="3"/>
+      <c r="M1085" s="3"/>
+      <c r="N1085" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Home Motors- TS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Home-Motors \"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CD14735-38BA-4C85-B479-2103AA05D2BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3CCAB47-9EE2-4C75-92BD-0AC52C014C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1215" windowWidth="21930" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12616" uniqueCount="5388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13691" uniqueCount="5789">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -15703,6 +15703,9 @@
     <t>31.444728, -100.420339</t>
   </si>
   <si>
+    <t>06/15/26 08:31 CDT</t>
+  </si>
+  <si>
     <t>06/12/26 07:50 CDT</t>
   </si>
   <si>
@@ -15757,6 +15760,9 @@
     <t>31.438625, -100.434683</t>
   </si>
   <si>
+    <t>06/15/26 08:30 CDT</t>
+  </si>
+  <si>
     <t>06/12/26 15:10 CDT</t>
   </si>
   <si>
@@ -15769,6 +15775,9 @@
     <t>31.406742, -100.487266</t>
   </si>
   <si>
+    <t>06/15/26 08:29 CDT</t>
+  </si>
+  <si>
     <t>06/12/26 17:13 CDT</t>
   </si>
   <si>
@@ -15787,6 +15796,9 @@
     <t>31.487528, -100.381071</t>
   </si>
   <si>
+    <t>06/15/26 08:28 CDT</t>
+  </si>
+  <si>
     <t>06/12/26 17:56 CDT</t>
   </si>
   <si>
@@ -15811,6 +15823,9 @@
     <t>31.417181, -100.373344</t>
   </si>
   <si>
+    <t>06/15/26 08:59 CDT</t>
+  </si>
+  <si>
     <t>06/12/26 18:07 CDT</t>
   </si>
   <si>
@@ -15820,6 +15835,9 @@
     <t>31.424388, -100.423056</t>
   </si>
   <si>
+    <t>06/15/26 08:27 CDT</t>
+  </si>
+  <si>
     <t>06/12/26 18:11 CDT</t>
   </si>
   <si>
@@ -15937,6 +15955,9 @@
     <t>31.671572, -100.325674</t>
   </si>
   <si>
+    <t>06/15/26 08:26 CDT</t>
+  </si>
+  <si>
     <t>06/12/26 22:39 CDT</t>
   </si>
   <si>
@@ -15961,6 +15982,9 @@
     <t>31.615254, -100.352752</t>
   </si>
   <si>
+    <t>06/15/26 08:32 CDT</t>
+  </si>
+  <si>
     <t>06/12/26 22:43 CDT</t>
   </si>
   <si>
@@ -15973,6 +15997,9 @@
     <t>31.563549, -100.369082</t>
   </si>
   <si>
+    <t>06/15/26 08:24 CDT</t>
+  </si>
+  <si>
     <t>06/13/26 08:53 CDT</t>
   </si>
   <si>
@@ -15982,6 +16009,9 @@
     <t>31.444971, -100.434799</t>
   </si>
   <si>
+    <t>06/15/26 08:23 CDT</t>
+  </si>
+  <si>
     <t>06/13/26 09:17 CDT</t>
   </si>
   <si>
@@ -16117,6 +16147,9 @@
     <t>31.451574, -100.434446</t>
   </si>
   <si>
+    <t>06/15/26 08:22 CDT</t>
+  </si>
+  <si>
     <t>06/14/26 07:11 CDT</t>
   </si>
   <si>
@@ -16184,6 +16217,1176 @@
   </si>
   <si>
     <t>31.233292, -99.691008</t>
+  </si>
+  <si>
+    <t>06/14/26 15:24 CDT</t>
+  </si>
+  <si>
+    <t>'1226234293760720896</t>
+  </si>
+  <si>
+    <t>9.6mi NW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.552121, -100.549316</t>
+  </si>
+  <si>
+    <t>06/14/26 15:28 CDT</t>
+  </si>
+  <si>
+    <t>'1226235546624491520</t>
+  </si>
+  <si>
+    <t>7mi NW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.502020, -100.546008</t>
+  </si>
+  <si>
+    <t>06/15/26 08:21 CDT</t>
+  </si>
+  <si>
+    <t>06/14/26 15:29 CDT</t>
+  </si>
+  <si>
+    <t>'1226235788270927872</t>
+  </si>
+  <si>
+    <t>7.8mi NW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.508429, -100.557084</t>
+  </si>
+  <si>
+    <t>06/14/26 15:44 CDT</t>
+  </si>
+  <si>
+    <t>'1226239585722466304</t>
+  </si>
+  <si>
+    <t>31.420757, -100.424191</t>
+  </si>
+  <si>
+    <t>06/14/26 16:54 CDT</t>
+  </si>
+  <si>
+    <t>'1226257119142117376</t>
+  </si>
+  <si>
+    <t>31.483491, -100.452593</t>
+  </si>
+  <si>
+    <t>06/15/26 08:20 CDT</t>
+  </si>
+  <si>
+    <t>06/15/26 01:00 CDT</t>
+  </si>
+  <si>
+    <t>'1226379260080586752</t>
+  </si>
+  <si>
+    <t>31.444970, -100.434798</t>
+  </si>
+  <si>
+    <t>06/16/26 08:13 CDT</t>
+  </si>
+  <si>
+    <t>06/15/26 07:03 CDT</t>
+  </si>
+  <si>
+    <t>'1226470713880379392</t>
+  </si>
+  <si>
+    <t>31.511931, -100.370260</t>
+  </si>
+  <si>
+    <t>06/16/26 08:32 CDT</t>
+  </si>
+  <si>
+    <t>'1226470791395311616</t>
+  </si>
+  <si>
+    <t>06/16/26 08:12 CDT</t>
+  </si>
+  <si>
+    <t>06/15/26 07:08 CDT</t>
+  </si>
+  <si>
+    <t>'1226471940806574080</t>
+  </si>
+  <si>
+    <t>11.7mi NE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.592573, -100.359275</t>
+  </si>
+  <si>
+    <t>06/15/26 07:51 CDT</t>
+  </si>
+  <si>
+    <t>'1226482789185126400</t>
+  </si>
+  <si>
+    <t>31.444771, -100.420357</t>
+  </si>
+  <si>
+    <t>06/16/26 08:11 CDT</t>
+  </si>
+  <si>
+    <t>06/15/26 08:46 CDT</t>
+  </si>
+  <si>
+    <t>'1226496560397975553</t>
+  </si>
+  <si>
+    <t>31.422570, -100.423469</t>
+  </si>
+  <si>
+    <t>06/15/26 08:49 CDT</t>
+  </si>
+  <si>
+    <t>'1226497337099190272</t>
+  </si>
+  <si>
+    <t>3.7mi SE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.420893, -100.392085</t>
+  </si>
+  <si>
+    <t>06/15/26 08:52 CDT</t>
+  </si>
+  <si>
+    <t>'1226498087070105600</t>
+  </si>
+  <si>
+    <t>6mi E of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.421095, -100.352089</t>
+  </si>
+  <si>
+    <t>06/16/26 08:10 CDT</t>
+  </si>
+  <si>
+    <t>06/15/26 10:09 CDT</t>
+  </si>
+  <si>
+    <t>'1226517646544109568</t>
+  </si>
+  <si>
+    <t>31.444999, -100.478645</t>
+  </si>
+  <si>
+    <t>06/15/26 12:15 CDT</t>
+  </si>
+  <si>
+    <t>'1226549144752128000</t>
+  </si>
+  <si>
+    <t>13.7mi E of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.403575, -100.222995</t>
+  </si>
+  <si>
+    <t>06/16/26 08:09 CDT</t>
+  </si>
+  <si>
+    <t>06/15/26 12:22 CDT</t>
+  </si>
+  <si>
+    <t>'1226550955634491392</t>
+  </si>
+  <si>
+    <t>31.373142, -100.282269</t>
+  </si>
+  <si>
+    <t>06/16/26 08:08 CDT</t>
+  </si>
+  <si>
+    <t>06/15/26 12:49 CDT</t>
+  </si>
+  <si>
+    <t>'1226557794308751360</t>
+  </si>
+  <si>
+    <t>31.443320, -100.464644</t>
+  </si>
+  <si>
+    <t>06/15/26 14:38 CDT</t>
+  </si>
+  <si>
+    <t>'1226585264932159488</t>
+  </si>
+  <si>
+    <t>3.4mi S of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.396178, -100.433249</t>
+  </si>
+  <si>
+    <t>06/15/26 15:52 CDT</t>
+  </si>
+  <si>
+    <t>'1226603838497259520</t>
+  </si>
+  <si>
+    <t>31.462554, -100.436650</t>
+  </si>
+  <si>
+    <t>06/15/26 16:10 CDT</t>
+  </si>
+  <si>
+    <t>'1226608463560474624</t>
+  </si>
+  <si>
+    <t>31.453104, -100.462434</t>
+  </si>
+  <si>
+    <t>06/15/26 18:18 CDT</t>
+  </si>
+  <si>
+    <t>'1226640525512310784</t>
+  </si>
+  <si>
+    <t>31.432430, -100.503873</t>
+  </si>
+  <si>
+    <t>06/15/26 18:20 CDT</t>
+  </si>
+  <si>
+    <t>'1226641060420288512</t>
+  </si>
+  <si>
+    <t>31.427322, -100.512395</t>
+  </si>
+  <si>
+    <t>06/15/26 19:02 CDT</t>
+  </si>
+  <si>
+    <t>'1226651743430017024</t>
+  </si>
+  <si>
+    <t>31.487147, -100.457895</t>
+  </si>
+  <si>
+    <t>06/15/26 19:03 CDT</t>
+  </si>
+  <si>
+    <t>'1226651920387702785</t>
+  </si>
+  <si>
+    <t>31.482490, -100.454605</t>
+  </si>
+  <si>
+    <t>06/16/26 08:07 CDT</t>
+  </si>
+  <si>
+    <t>06/15/26 22:52 CDT</t>
+  </si>
+  <si>
+    <t>'1226709579245715456</t>
+  </si>
+  <si>
+    <t>31.481393, -100.454376</t>
+  </si>
+  <si>
+    <t>06/15/26 23:23 CDT</t>
+  </si>
+  <si>
+    <t>'1226717408400670720</t>
+  </si>
+  <si>
+    <t>31.439784, -100.441834</t>
+  </si>
+  <si>
+    <t>06/17/26 08:41 CDT</t>
+  </si>
+  <si>
+    <t>06/16/26 09:10 CDT</t>
+  </si>
+  <si>
+    <t>'1226864978527682560</t>
+  </si>
+  <si>
+    <t>31.422581, -100.423466</t>
+  </si>
+  <si>
+    <t>06/17/26 08:46 CDT</t>
+  </si>
+  <si>
+    <t>06/16/26 13:25 CDT</t>
+  </si>
+  <si>
+    <t>'1226929153211793408</t>
+  </si>
+  <si>
+    <t>6.3mi S of Lubbock TX</t>
+  </si>
+  <si>
+    <t>33.475821, -101.875613</t>
+  </si>
+  <si>
+    <t>06/17/26 08:45 CDT</t>
+  </si>
+  <si>
+    <t>06/16/26 13:56 CDT</t>
+  </si>
+  <si>
+    <t>'1226937171781517312</t>
+  </si>
+  <si>
+    <t>40.4mi S of San Angelo TX</t>
+  </si>
+  <si>
+    <t>30.869809, -100.590377</t>
+  </si>
+  <si>
+    <t>06/16/26 15:32 CDT</t>
+  </si>
+  <si>
+    <t>'1226961126332465152</t>
+  </si>
+  <si>
+    <t>33.7mi SE of Big Spring TX</t>
+  </si>
+  <si>
+    <t>31.893268, -101.074460</t>
+  </si>
+  <si>
+    <t>06/16/26 15:58 CDT</t>
+  </si>
+  <si>
+    <t>'1226967841161510912</t>
+  </si>
+  <si>
+    <t>36.8mi NW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.793821, -100.919474</t>
+  </si>
+  <si>
+    <t>06/16/26 16:20 CDT</t>
+  </si>
+  <si>
+    <t>'1226973226652041216</t>
+  </si>
+  <si>
+    <t>17.1mi S of Abilene TX</t>
+  </si>
+  <si>
+    <t>32.211748, -99.796462</t>
+  </si>
+  <si>
+    <t>06/17/26 08:43 CDT</t>
+  </si>
+  <si>
+    <t>06/16/26 17:23 CDT</t>
+  </si>
+  <si>
+    <t>'1226989170388533248</t>
+  </si>
+  <si>
+    <t>17.5mi SW of Abilene TX</t>
+  </si>
+  <si>
+    <t>32.273121, -99.946628</t>
+  </si>
+  <si>
+    <t>06/17/26 08:42 CDT</t>
+  </si>
+  <si>
+    <t>06/16/26 17:53 CDT</t>
+  </si>
+  <si>
+    <t>'1226996640854999040</t>
+  </si>
+  <si>
+    <t>31.892636, -100.288557</t>
+  </si>
+  <si>
+    <t>06/16/26 18:29 CDT</t>
+  </si>
+  <si>
+    <t>'1227005773566083072</t>
+  </si>
+  <si>
+    <t>31.396275, -100.433594</t>
+  </si>
+  <si>
+    <t>06/16/26 18:31 CDT</t>
+  </si>
+  <si>
+    <t>'1227006342489866240</t>
+  </si>
+  <si>
+    <t>31.421076, -100.439441</t>
+  </si>
+  <si>
+    <t>06/16/26 18:44 CDT</t>
+  </si>
+  <si>
+    <t>'1227009514088333312</t>
+  </si>
+  <si>
+    <t>31.444846, -100.442005</t>
+  </si>
+  <si>
+    <t>06/17/26 08:40 CDT</t>
+  </si>
+  <si>
+    <t>06/16/26 20:05 CDT</t>
+  </si>
+  <si>
+    <t>'1227029871184740352</t>
+  </si>
+  <si>
+    <t>31.455602, -100.472297</t>
+  </si>
+  <si>
+    <t>06/16/26 20:43 CDT</t>
+  </si>
+  <si>
+    <t>'1227039565961920512</t>
+  </si>
+  <si>
+    <t>31.508506, -100.556844</t>
+  </si>
+  <si>
+    <t>06/16/26 20:45 CDT</t>
+  </si>
+  <si>
+    <t>'1227040012776931328</t>
+  </si>
+  <si>
+    <t>9.1mi NW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.531937, -100.563721</t>
+  </si>
+  <si>
+    <t>06/17/26 08:39 CDT</t>
+  </si>
+  <si>
+    <t>06/17/26 07:39 CDT</t>
+  </si>
+  <si>
+    <t>'1227204613699174400</t>
+  </si>
+  <si>
+    <t>31.424201, -100.423018</t>
+  </si>
+  <si>
+    <t>06/17/26 09:57 CDT</t>
+  </si>
+  <si>
+    <t>'1227239353084968960</t>
+  </si>
+  <si>
+    <t>0.3mi E of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.442930, -100.444538</t>
+  </si>
+  <si>
+    <t>06/17/26 14:37 CDT</t>
+  </si>
+  <si>
+    <t>06/17/26 10:02 CDT</t>
+  </si>
+  <si>
+    <t>'1227240506870890496</t>
+  </si>
+  <si>
+    <t>26.4mi E of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.459780, -100.003428</t>
+  </si>
+  <si>
+    <t>06/17/26 10:03 CDT</t>
+  </si>
+  <si>
+    <t>'1227240836874534912</t>
+  </si>
+  <si>
+    <t>31.448358, -100.488268</t>
+  </si>
+  <si>
+    <t>06/17/26 11:09 CDT</t>
+  </si>
+  <si>
+    <t>'1227257456414064640</t>
+  </si>
+  <si>
+    <t>31.396235, -100.433389</t>
+  </si>
+  <si>
+    <t>06/17/26 11:14 CDT</t>
+  </si>
+  <si>
+    <t>'1227258703917514752</t>
+  </si>
+  <si>
+    <t>31.443140, -100.460850</t>
+  </si>
+  <si>
+    <t>06/17/26 14:36 CDT</t>
+  </si>
+  <si>
+    <t>06/17/26 12:03 CDT</t>
+  </si>
+  <si>
+    <t>'1227271017857187840</t>
+  </si>
+  <si>
+    <t>28.7mi E of Brady TX</t>
+  </si>
+  <si>
+    <t>31.240642, -98.900818</t>
+  </si>
+  <si>
+    <t>06/17/26 12:05 CDT</t>
+  </si>
+  <si>
+    <t>'1227271395877224448</t>
+  </si>
+  <si>
+    <t>30.1mi E of Brady TX</t>
+  </si>
+  <si>
+    <t>31.230608, -98.874769</t>
+  </si>
+  <si>
+    <t>06/18/26 08:09 CDT</t>
+  </si>
+  <si>
+    <t>06/18/26 08:14 CDT</t>
+  </si>
+  <si>
+    <t>06/17/26 12:08 CDT</t>
+  </si>
+  <si>
+    <t>'1227272189003333632</t>
+  </si>
+  <si>
+    <t>31.443300, -100.464604</t>
+  </si>
+  <si>
+    <t>06/17/26 12:52 CDT</t>
+  </si>
+  <si>
+    <t>'1227283383688790016</t>
+  </si>
+  <si>
+    <t>2.4mi E of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.446507, -100.409301</t>
+  </si>
+  <si>
+    <t>06/17/26 17:46 CDT</t>
+  </si>
+  <si>
+    <t>06/17/26 13:00 CDT</t>
+  </si>
+  <si>
+    <t>'1227285251542384640</t>
+  </si>
+  <si>
+    <t>31.476265, -100.413500</t>
+  </si>
+  <si>
+    <t>06/17/26 13:05 CDT</t>
+  </si>
+  <si>
+    <t>'1227286557405380608</t>
+  </si>
+  <si>
+    <t>31.467673, -100.447399</t>
+  </si>
+  <si>
+    <t>06/17/26 13:27 CDT</t>
+  </si>
+  <si>
+    <t>'1227292194000502784</t>
+  </si>
+  <si>
+    <t>31.484592, -100.462230</t>
+  </si>
+  <si>
+    <t>06/17/26 14:17 CDT</t>
+  </si>
+  <si>
+    <t>'1227304741051203585</t>
+  </si>
+  <si>
+    <t>31.896983, -100.286024</t>
+  </si>
+  <si>
+    <t>06/18/26 08:07 CDT</t>
+  </si>
+  <si>
+    <t>06/17/26 14:28 CDT</t>
+  </si>
+  <si>
+    <t>'1227307604020199424</t>
+  </si>
+  <si>
+    <t>0.9mi W of Belton TX</t>
+  </si>
+  <si>
+    <t>31.050611, -97.493233</t>
+  </si>
+  <si>
+    <t>06/17/26 17:45 CDT</t>
+  </si>
+  <si>
+    <t>06/17/26 14:57 CDT</t>
+  </si>
+  <si>
+    <t>'1227314681992085504</t>
+  </si>
+  <si>
+    <t>1.8mi W of Belton TX</t>
+  </si>
+  <si>
+    <t>31.055511, -97.509953</t>
+  </si>
+  <si>
+    <t>06/17/26 14:58 CDT</t>
+  </si>
+  <si>
+    <t>'1227314982895648768</t>
+  </si>
+  <si>
+    <t>3mi W of Belton TX</t>
+  </si>
+  <si>
+    <t>31.055845, -97.528977</t>
+  </si>
+  <si>
+    <t>06/17/26 15:03 CDT</t>
+  </si>
+  <si>
+    <t>'1227316274175049728</t>
+  </si>
+  <si>
+    <t>1.8mi N of Harker Heights TX</t>
+  </si>
+  <si>
+    <t>31.083221, -97.641366</t>
+  </si>
+  <si>
+    <t>06/17/26 15:08 CDT</t>
+  </si>
+  <si>
+    <t>'1227317527244341248</t>
+  </si>
+  <si>
+    <t>1.3mi N of Killeen TX</t>
+  </si>
+  <si>
+    <t>31.093684, -97.727991</t>
+  </si>
+  <si>
+    <t>06/17/26 15:09 CDT</t>
+  </si>
+  <si>
+    <t>'1227317777405214721</t>
+  </si>
+  <si>
+    <t>2.1mi N of Killeen TX</t>
+  </si>
+  <si>
+    <t>31.104291, -97.742729</t>
+  </si>
+  <si>
+    <t>06/18/26 08:08 CDT</t>
+  </si>
+  <si>
+    <t>06/17/26 15:19 CDT</t>
+  </si>
+  <si>
+    <t>'1227320290812526592</t>
+  </si>
+  <si>
+    <t>31.897612, -100.285987</t>
+  </si>
+  <si>
+    <t>06/17/26 15:35 CDT</t>
+  </si>
+  <si>
+    <t>'1227324336382312448</t>
+  </si>
+  <si>
+    <t>0.9mi E of Lampasas TX</t>
+  </si>
+  <si>
+    <t>31.064441, -98.166610</t>
+  </si>
+  <si>
+    <t>06/17/26 17:44 CDT</t>
+  </si>
+  <si>
+    <t>06/17/26 16:15 CDT</t>
+  </si>
+  <si>
+    <t>'1227334447473524736</t>
+  </si>
+  <si>
+    <t>7.2mi NW of Lampasas TX</t>
+  </si>
+  <si>
+    <t>31.128512, -98.277682</t>
+  </si>
+  <si>
+    <t>06/17/26 16:52 CDT</t>
+  </si>
+  <si>
+    <t>'1227343776247349248</t>
+  </si>
+  <si>
+    <t>27mi E of Brady TX</t>
+  </si>
+  <si>
+    <t>31.269856, -98.941959</t>
+  </si>
+  <si>
+    <t>06/17/26 17:03 CDT</t>
+  </si>
+  <si>
+    <t>'1227346554998915072</t>
+  </si>
+  <si>
+    <t>31.440816, -100.419643</t>
+  </si>
+  <si>
+    <t>06/18/26 08:06 CDT</t>
+  </si>
+  <si>
+    <t>06/17/26 17:08 CDT</t>
+  </si>
+  <si>
+    <t>'1227347836056797184</t>
+  </si>
+  <si>
+    <t>8.4mi NE of Brady TX</t>
+  </si>
+  <si>
+    <t>31.188308, -99.243802</t>
+  </si>
+  <si>
+    <t>06/17/26 17:43 CDT</t>
+  </si>
+  <si>
+    <t>06/17/26 17:14 CDT</t>
+  </si>
+  <si>
+    <t>'1227349366797402112</t>
+  </si>
+  <si>
+    <t>2.2mi E of Brady TX</t>
+  </si>
+  <si>
+    <t>31.141051, -99.335106</t>
+  </si>
+  <si>
+    <t>06/17/26 17:17 CDT</t>
+  </si>
+  <si>
+    <t>'1227350157276905472</t>
+  </si>
+  <si>
+    <t>2mi N of Brady TX</t>
+  </si>
+  <si>
+    <t>31.160731, -99.368479</t>
+  </si>
+  <si>
+    <t>06/17/26 17:57 CDT</t>
+  </si>
+  <si>
+    <t>'1227360133630296064</t>
+  </si>
+  <si>
+    <t>20mi E of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.342619, -100.132131</t>
+  </si>
+  <si>
+    <t>06/18/26 08:05 CDT</t>
+  </si>
+  <si>
+    <t>06/17/26 17:59 CDT</t>
+  </si>
+  <si>
+    <t>'1227360524598149120</t>
+  </si>
+  <si>
+    <t>18.1mi E of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.343295, -100.166377</t>
+  </si>
+  <si>
+    <t>06/17/26 18:02 CDT</t>
+  </si>
+  <si>
+    <t>'1227361412498751488</t>
+  </si>
+  <si>
+    <t>31.373218, -100.235617</t>
+  </si>
+  <si>
+    <t>06/18/26 08:04 CDT</t>
+  </si>
+  <si>
+    <t>06/17/26 18:36 CDT</t>
+  </si>
+  <si>
+    <t>'1227369985941340160</t>
+  </si>
+  <si>
+    <t>31.480400, -100.456242</t>
+  </si>
+  <si>
+    <t>06/17/26 19:18 CDT</t>
+  </si>
+  <si>
+    <t>'1227380453657444352</t>
+  </si>
+  <si>
+    <t>31.470096, -100.441907</t>
+  </si>
+  <si>
+    <t>06/17/26 23:29 CDT</t>
+  </si>
+  <si>
+    <t>'1227443596786040832</t>
+  </si>
+  <si>
+    <t>31.452832, -100.440489</t>
+  </si>
+  <si>
+    <t>06/19/26 07:53 CDT</t>
+  </si>
+  <si>
+    <t>06/18/26 08:54 CDT</t>
+  </si>
+  <si>
+    <t>'1227585838943207424</t>
+  </si>
+  <si>
+    <t>3.2mi SW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.412028, -100.491383</t>
+  </si>
+  <si>
+    <t>06/19/26 07:52 CDT</t>
+  </si>
+  <si>
+    <t>06/18/26 09:29 CDT</t>
+  </si>
+  <si>
+    <t>'1227594531998957568</t>
+  </si>
+  <si>
+    <t>31.461791, -100.442600</t>
+  </si>
+  <si>
+    <t>06/18/26 11:02 CDT</t>
+  </si>
+  <si>
+    <t>'1227617928199962624</t>
+  </si>
+  <si>
+    <t>31.444771, -100.420361</t>
+  </si>
+  <si>
+    <t>06/18/26 11:15 CDT</t>
+  </si>
+  <si>
+    <t>'1227621280707149824</t>
+  </si>
+  <si>
+    <t>31.441029, -100.408457</t>
+  </si>
+  <si>
+    <t>06/18/26 11:31 CDT</t>
+  </si>
+  <si>
+    <t>'1227625253426069504</t>
+  </si>
+  <si>
+    <t>3.5mi E of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.441415, -100.391476</t>
+  </si>
+  <si>
+    <t>06/18/26 11:51 CDT</t>
+  </si>
+  <si>
+    <t>'1227630469160534016</t>
+  </si>
+  <si>
+    <t>31.475617, -100.428746</t>
+  </si>
+  <si>
+    <t>06/18/26 12:46 CDT</t>
+  </si>
+  <si>
+    <t>'1227644280789696512</t>
+  </si>
+  <si>
+    <t>22.9mi E of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.332027, -100.084455</t>
+  </si>
+  <si>
+    <t>06/18/26 12:58 CDT</t>
+  </si>
+  <si>
+    <t>'1227647268748951552</t>
+  </si>
+  <si>
+    <t>31.444818, -100.420330</t>
+  </si>
+  <si>
+    <t>06/18/26 13:25 CDT</t>
+  </si>
+  <si>
+    <t>'1227654091996561408</t>
+  </si>
+  <si>
+    <t>31.396222, -100.433464</t>
+  </si>
+  <si>
+    <t>06/18/26 13:58 CDT</t>
+  </si>
+  <si>
+    <t>'1227662414015791104</t>
+  </si>
+  <si>
+    <t>31.475114, -100.413159</t>
+  </si>
+  <si>
+    <t>06/18/26 14:03 CDT</t>
+  </si>
+  <si>
+    <t>'1227663614115217408</t>
+  </si>
+  <si>
+    <t>31.422609, -100.423505</t>
+  </si>
+  <si>
+    <t>06/18/26 14:08 CDT</t>
+  </si>
+  <si>
+    <t>'1227664762855391233</t>
+  </si>
+  <si>
+    <t>31.388423, -100.419526</t>
+  </si>
+  <si>
+    <t>06/19/26 07:51 CDT</t>
+  </si>
+  <si>
+    <t>06/18/26 14:24 CDT</t>
+  </si>
+  <si>
+    <t>'1227668902918651904</t>
+  </si>
+  <si>
+    <t>0.6mi SE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.437546, -100.441806</t>
+  </si>
+  <si>
+    <t>06/19/26 07:50 CDT</t>
+  </si>
+  <si>
+    <t>06/18/26 16:01 CDT</t>
+  </si>
+  <si>
+    <t>'1227693263369175040</t>
+  </si>
+  <si>
+    <t>31.453106, -100.462484</t>
+  </si>
+  <si>
+    <t>06/18/26 16:16 CDT</t>
+  </si>
+  <si>
+    <t>'1227697179746009088</t>
+  </si>
+  <si>
+    <t>10.5mi SE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.372436, -100.292823</t>
+  </si>
+  <si>
+    <t>06/18/26 16:32 CDT</t>
+  </si>
+  <si>
+    <t>'1227701042641272832</t>
+  </si>
+  <si>
+    <t>31.444658, -100.434607</t>
+  </si>
+  <si>
+    <t>06/19/26 07:49 CDT</t>
+  </si>
+  <si>
+    <t>06/18/26 18:52 CDT</t>
+  </si>
+  <si>
+    <t>'1227736439677157376</t>
+  </si>
+  <si>
+    <t>31.470121, -100.441890</t>
+  </si>
+  <si>
+    <t>06/19/26 07:48 CDT</t>
+  </si>
+  <si>
+    <t>06/19/26 10:21 CDT</t>
+  </si>
+  <si>
+    <t>'1227970142990925825</t>
+  </si>
+  <si>
+    <t>31.441734, -100.440137</t>
+  </si>
+  <si>
+    <t>06/19/26 12:14 CDT</t>
+  </si>
+  <si>
+    <t>'1227998585979830272</t>
+  </si>
+  <si>
+    <t>31.444810, -100.419938</t>
+  </si>
+  <si>
+    <t>06/19/26 18:10 CDT</t>
+  </si>
+  <si>
+    <t>'1228088120726159360</t>
+  </si>
+  <si>
+    <t>31.427967, -100.441419</t>
+  </si>
+  <si>
+    <t>06/19/26 18:34 CDT</t>
+  </si>
+  <si>
+    <t>'1228094230824648704</t>
+  </si>
+  <si>
+    <t>31.487474, -100.458064</t>
+  </si>
+  <si>
+    <t>06/19/26 19:16 CDT</t>
+  </si>
+  <si>
+    <t>'1228104667595177984</t>
+  </si>
+  <si>
+    <t>31.396267, -100.433487</t>
+  </si>
+  <si>
+    <t>06/19/26 20:41 CDT</t>
+  </si>
+  <si>
+    <t>'1228126102975840256</t>
+  </si>
+  <si>
+    <t>31.439889, -100.441792</t>
+  </si>
+  <si>
+    <t>06/19/26 22:46 CDT</t>
+  </si>
+  <si>
+    <t>'1228157572087971840</t>
+  </si>
+  <si>
+    <t>31.424383, -100.423140</t>
+  </si>
+  <si>
+    <t>06/20/26 01:25 CDT</t>
+  </si>
+  <si>
+    <t>'1228197673899819008</t>
+  </si>
+  <si>
+    <t>31.396278, -100.433628</t>
+  </si>
+  <si>
+    <t>06/20/26 07:30 CDT</t>
+  </si>
+  <si>
+    <t>'1228289349121114112</t>
+  </si>
+  <si>
+    <t>31.465167, -100.438020</t>
+  </si>
+  <si>
+    <t>06/20/26 07:35 CDT</t>
+  </si>
+  <si>
+    <t>'1228290659371352064</t>
+  </si>
+  <si>
+    <t>31.429109, -100.429892</t>
+  </si>
+  <si>
+    <t>06/20/26 08:46 CDT</t>
+  </si>
+  <si>
+    <t>'1228308488225193984</t>
+  </si>
+  <si>
+    <t>10.3mi SE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.370817, -100.297439</t>
+  </si>
+  <si>
+    <t>06/20/26 08:49 CDT</t>
+  </si>
+  <si>
+    <t>'1228309381318344704</t>
+  </si>
+  <si>
+    <t>15.8mi NW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.604402, -100.640286</t>
+  </si>
+  <si>
+    <t>06/20/26 13:19 CDT</t>
+  </si>
+  <si>
+    <t>'1228377416603435008</t>
+  </si>
+  <si>
+    <t>31.432418, -100.503790</t>
+  </si>
+  <si>
+    <t>06/20/26 18:01 CDT</t>
+  </si>
+  <si>
+    <t>'1228448204320833536</t>
+  </si>
+  <si>
+    <t>31.444952, -100.441859</t>
   </si>
 </sst>
 </file>
@@ -16545,10 +17748,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1387"/>
+  <dimension ref="A1:N1492"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="14" width="15" customWidth="1"/>
+    <col min="1" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="14" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -68175,28 +69380,34 @@
       <c r="G1341" s="3" t="s">
         <v>5226</v>
       </c>
-      <c r="H1341" s="3"/>
+      <c r="H1341" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1341" s="3">
         <v>13</v>
       </c>
       <c r="J1341" s="3"/>
       <c r="K1341" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1341" s="3"/>
-      <c r="M1341" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1341" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1341" s="3" t="s">
+        <v>5227</v>
+      </c>
       <c r="N1341" s="3"/>
     </row>
     <row r="1342" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1342" s="3" t="s">
-        <v>5227</v>
+        <v>5228</v>
       </c>
       <c r="B1342" s="3"/>
       <c r="C1342" s="3">
         <v>404</v>
       </c>
       <c r="D1342" s="3" t="s">
-        <v>5228</v>
+        <v>5229</v>
       </c>
       <c r="E1342" s="3" t="s">
         <v>290</v>
@@ -68205,30 +69416,36 @@
         <v>2448</v>
       </c>
       <c r="G1342" s="3" t="s">
-        <v>5229</v>
-      </c>
-      <c r="H1342" s="3"/>
+        <v>5230</v>
+      </c>
+      <c r="H1342" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1342" s="3">
         <v>6</v>
       </c>
       <c r="J1342" s="3"/>
       <c r="K1342" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1342" s="3"/>
-      <c r="M1342" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1342" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1342" s="3" t="s">
+        <v>5227</v>
+      </c>
       <c r="N1342" s="3"/>
     </row>
     <row r="1343" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1343" s="3" t="s">
-        <v>5230</v>
+        <v>5231</v>
       </c>
       <c r="B1343" s="3"/>
       <c r="C1343" s="3">
         <v>410</v>
       </c>
       <c r="D1343" s="3" t="s">
-        <v>5231</v>
+        <v>5232</v>
       </c>
       <c r="E1343" s="3" t="s">
         <v>225</v>
@@ -68237,28 +69454,34 @@
         <v>4984</v>
       </c>
       <c r="G1343" s="3" t="s">
-        <v>5232</v>
-      </c>
-      <c r="H1343" s="3"/>
+        <v>5233</v>
+      </c>
+      <c r="H1343" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1343" s="3"/>
       <c r="J1343" s="3"/>
       <c r="K1343" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1343" s="3"/>
-      <c r="M1343" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1343" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1343" s="3" t="s">
+        <v>5227</v>
+      </c>
       <c r="N1343" s="3"/>
     </row>
     <row r="1344" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1344" s="3" t="s">
-        <v>5233</v>
+        <v>5234</v>
       </c>
       <c r="B1344" s="3"/>
       <c r="C1344" s="3">
         <v>413</v>
       </c>
       <c r="D1344" s="3" t="s">
-        <v>5234</v>
+        <v>5235</v>
       </c>
       <c r="E1344" s="3" t="s">
         <v>290</v>
@@ -68267,30 +69490,38 @@
         <v>4088</v>
       </c>
       <c r="G1344" s="3" t="s">
-        <v>5235</v>
-      </c>
-      <c r="H1344" s="3"/>
+        <v>5236</v>
+      </c>
+      <c r="H1344" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1344" s="3">
         <v>17</v>
       </c>
       <c r="J1344" s="3"/>
       <c r="K1344" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1344" s="3"/>
-      <c r="M1344" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1344" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1344" s="3" t="s">
+        <v>5227</v>
+      </c>
       <c r="N1344" s="3"/>
     </row>
     <row r="1345" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1345" s="3" t="s">
-        <v>5236</v>
-      </c>
-      <c r="B1345" s="3"/>
+        <v>5237</v>
+      </c>
+      <c r="B1345" s="3" t="s">
+        <v>295</v>
+      </c>
       <c r="C1345" s="3">
         <v>411</v>
       </c>
       <c r="D1345" s="3" t="s">
-        <v>5237</v>
+        <v>5238</v>
       </c>
       <c r="E1345" s="3" t="s">
         <v>76</v>
@@ -68299,30 +69530,36 @@
         <v>415</v>
       </c>
       <c r="G1345" s="3" t="s">
-        <v>5238</v>
-      </c>
-      <c r="H1345" s="3"/>
+        <v>5239</v>
+      </c>
+      <c r="H1345" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1345" s="3">
         <v>36</v>
       </c>
       <c r="J1345" s="3"/>
       <c r="K1345" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1345" s="3"/>
-      <c r="M1345" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1345" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1345" s="3" t="s">
+        <v>5227</v>
+      </c>
       <c r="N1345" s="3"/>
     </row>
     <row r="1346" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1346" s="3" t="s">
-        <v>5239</v>
+        <v>5240</v>
       </c>
       <c r="B1346" s="3"/>
       <c r="C1346" s="3">
         <v>404</v>
       </c>
       <c r="D1346" s="3" t="s">
-        <v>5240</v>
+        <v>5241</v>
       </c>
       <c r="E1346" s="3" t="s">
         <v>290</v>
@@ -68331,30 +69568,36 @@
         <v>2555</v>
       </c>
       <c r="G1346" s="3" t="s">
-        <v>5241</v>
-      </c>
-      <c r="H1346" s="3"/>
+        <v>5242</v>
+      </c>
+      <c r="H1346" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1346" s="3">
         <v>37</v>
       </c>
       <c r="J1346" s="3"/>
       <c r="K1346" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1346" s="3"/>
-      <c r="M1346" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1346" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1346" s="3" t="s">
+        <v>5227</v>
+      </c>
       <c r="N1346" s="3"/>
     </row>
     <row r="1347" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1347" s="3" t="s">
-        <v>5242</v>
+        <v>5243</v>
       </c>
       <c r="B1347" s="3"/>
       <c r="C1347" s="3">
         <v>405</v>
       </c>
       <c r="D1347" s="3" t="s">
-        <v>5243</v>
+        <v>5244</v>
       </c>
       <c r="E1347" s="3" t="s">
         <v>145</v>
@@ -68363,62 +69606,76 @@
         <v>2055</v>
       </c>
       <c r="G1347" s="3" t="s">
-        <v>5244</v>
-      </c>
-      <c r="H1347" s="3"/>
+        <v>5245</v>
+      </c>
+      <c r="H1347" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="I1347" s="3">
         <v>39</v>
       </c>
       <c r="J1347" s="3"/>
       <c r="K1347" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1347" s="3"/>
-      <c r="M1347" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1347" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1347" s="3" t="s">
+        <v>5246</v>
+      </c>
       <c r="N1347" s="3"/>
     </row>
     <row r="1348" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1348" s="3" t="s">
-        <v>5245</v>
+        <v>5247</v>
       </c>
       <c r="B1348" s="3"/>
       <c r="C1348" s="3">
         <v>414</v>
       </c>
       <c r="D1348" s="3" t="s">
-        <v>5246</v>
+        <v>5248</v>
       </c>
       <c r="E1348" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F1348" s="3" t="s">
-        <v>5247</v>
+        <v>5249</v>
       </c>
       <c r="G1348" s="3" t="s">
-        <v>5248</v>
-      </c>
-      <c r="H1348" s="3"/>
+        <v>5250</v>
+      </c>
+      <c r="H1348" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1348" s="3">
         <v>21</v>
       </c>
       <c r="J1348" s="3"/>
       <c r="K1348" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1348" s="3"/>
-      <c r="M1348" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1348" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1348" s="3" t="s">
+        <v>5251</v>
+      </c>
       <c r="N1348" s="3"/>
     </row>
     <row r="1349" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1349" s="3" t="s">
-        <v>5249</v>
-      </c>
-      <c r="B1349" s="3"/>
+        <v>5252</v>
+      </c>
+      <c r="B1349" s="3" t="s">
+        <v>1026</v>
+      </c>
       <c r="C1349" s="3">
         <v>408</v>
       </c>
       <c r="D1349" s="3" t="s">
-        <v>5250</v>
+        <v>5253</v>
       </c>
       <c r="E1349" s="3" t="s">
         <v>211</v>
@@ -68427,9 +69684,11 @@
         <v>2551</v>
       </c>
       <c r="G1349" s="3" t="s">
-        <v>5251</v>
-      </c>
-      <c r="H1349" s="3"/>
+        <v>5254</v>
+      </c>
+      <c r="H1349" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="I1349" s="3">
         <v>76</v>
       </c>
@@ -68437,22 +69696,26 @@
         <v>65</v>
       </c>
       <c r="K1349" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1349" s="3"/>
-      <c r="M1349" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1349" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1349" s="3" t="s">
+        <v>5251</v>
+      </c>
       <c r="N1349" s="3"/>
     </row>
     <row r="1350" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1350" s="3" t="s">
-        <v>5252</v>
+        <v>5255</v>
       </c>
       <c r="B1350" s="3"/>
       <c r="C1350" s="3">
         <v>400</v>
       </c>
       <c r="D1350" s="3" t="s">
-        <v>5253</v>
+        <v>5256</v>
       </c>
       <c r="E1350" s="3" t="s">
         <v>63</v>
@@ -68461,90 +69724,112 @@
         <v>72</v>
       </c>
       <c r="G1350" s="3" t="s">
-        <v>5254</v>
-      </c>
-      <c r="H1350" s="3"/>
+        <v>5257</v>
+      </c>
+      <c r="H1350" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1350" s="3"/>
       <c r="J1350" s="3"/>
       <c r="K1350" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1350" s="3"/>
-      <c r="M1350" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1350" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1350" s="3" t="s">
+        <v>5258</v>
+      </c>
       <c r="N1350" s="3"/>
     </row>
     <row r="1351" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1351" s="3" t="s">
-        <v>5255</v>
+        <v>5259</v>
       </c>
       <c r="B1351" s="3"/>
       <c r="C1351" s="3">
         <v>404</v>
       </c>
       <c r="D1351" s="3" t="s">
-        <v>5256</v>
+        <v>5260</v>
       </c>
       <c r="E1351" s="3" t="s">
         <v>290</v>
       </c>
       <c r="F1351" s="3" t="s">
-        <v>5257</v>
+        <v>5261</v>
       </c>
       <c r="G1351" s="3" t="s">
-        <v>5258</v>
-      </c>
-      <c r="H1351" s="3"/>
+        <v>5262</v>
+      </c>
+      <c r="H1351" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1351" s="3"/>
       <c r="J1351" s="3"/>
       <c r="K1351" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1351" s="3"/>
-      <c r="M1351" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1351" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1351" s="3" t="s">
+        <v>5258</v>
+      </c>
       <c r="N1351" s="3"/>
     </row>
     <row r="1352" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1352" s="3" t="s">
-        <v>5259</v>
-      </c>
-      <c r="B1352" s="3"/>
+        <v>5263</v>
+      </c>
+      <c r="B1352" s="3" t="s">
+        <v>1026</v>
+      </c>
       <c r="C1352" s="3">
         <v>404</v>
       </c>
       <c r="D1352" s="3" t="s">
-        <v>5260</v>
+        <v>5264</v>
       </c>
       <c r="E1352" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F1352" s="3" t="s">
-        <v>5261</v>
+        <v>5265</v>
       </c>
       <c r="G1352" s="3" t="s">
-        <v>5262</v>
-      </c>
-      <c r="H1352" s="3"/>
+        <v>5266</v>
+      </c>
+      <c r="H1352" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="I1352" s="3">
         <v>47</v>
       </c>
       <c r="J1352" s="3"/>
       <c r="K1352" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1352" s="3"/>
-      <c r="M1352" s="3"/>
-      <c r="N1352" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1352" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1352" s="3" t="s">
+        <v>5258</v>
+      </c>
+      <c r="N1352" s="3" t="s">
+        <v>5267</v>
+      </c>
     </row>
     <row r="1353" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1353" s="3" t="s">
-        <v>5263</v>
+        <v>5268</v>
       </c>
       <c r="B1353" s="3"/>
       <c r="C1353" s="3">
         <v>413</v>
       </c>
       <c r="D1353" s="3" t="s">
-        <v>5264</v>
+        <v>5269</v>
       </c>
       <c r="E1353" s="3" t="s">
         <v>290</v>
@@ -68553,30 +69838,36 @@
         <v>2555</v>
       </c>
       <c r="G1353" s="3" t="s">
-        <v>5265</v>
-      </c>
-      <c r="H1353" s="3"/>
+        <v>5270</v>
+      </c>
+      <c r="H1353" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1353" s="3">
         <v>19</v>
       </c>
       <c r="J1353" s="3"/>
       <c r="K1353" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1353" s="3"/>
-      <c r="M1353" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1353" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1353" s="3" t="s">
+        <v>5271</v>
+      </c>
       <c r="N1353" s="3"/>
     </row>
     <row r="1354" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1354" s="3" t="s">
-        <v>5266</v>
+        <v>5272</v>
       </c>
       <c r="B1354" s="3"/>
       <c r="C1354" s="3">
         <v>408</v>
       </c>
       <c r="D1354" s="3" t="s">
-        <v>5267</v>
+        <v>5273</v>
       </c>
       <c r="E1354" s="3" t="s">
         <v>63</v>
@@ -68585,30 +69876,36 @@
         <v>2859</v>
       </c>
       <c r="G1354" s="3" t="s">
-        <v>5268</v>
-      </c>
-      <c r="H1354" s="3"/>
+        <v>5274</v>
+      </c>
+      <c r="H1354" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1354" s="3">
         <v>21</v>
       </c>
       <c r="J1354" s="3"/>
       <c r="K1354" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1354" s="3"/>
-      <c r="M1354" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1354" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1354" s="3" t="s">
+        <v>5271</v>
+      </c>
       <c r="N1354" s="3"/>
     </row>
     <row r="1355" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1355" s="3" t="s">
-        <v>5269</v>
+        <v>5275</v>
       </c>
       <c r="B1355" s="3"/>
       <c r="C1355" s="3">
         <v>404</v>
       </c>
       <c r="D1355" s="3" t="s">
-        <v>5270</v>
+        <v>5276</v>
       </c>
       <c r="E1355" s="3" t="s">
         <v>290</v>
@@ -68617,30 +69914,36 @@
         <v>875</v>
       </c>
       <c r="G1355" s="3" t="s">
-        <v>5271</v>
-      </c>
-      <c r="H1355" s="3"/>
+        <v>5277</v>
+      </c>
+      <c r="H1355" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1355" s="3">
         <v>14</v>
       </c>
       <c r="J1355" s="3"/>
       <c r="K1355" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1355" s="3"/>
-      <c r="M1355" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1355" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1355" s="3" t="s">
+        <v>5271</v>
+      </c>
       <c r="N1355" s="3"/>
     </row>
     <row r="1356" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1356" s="3" t="s">
-        <v>5272</v>
+        <v>5278</v>
       </c>
       <c r="B1356" s="3"/>
       <c r="C1356" s="3">
         <v>404</v>
       </c>
       <c r="D1356" s="3" t="s">
-        <v>5273</v>
+        <v>5279</v>
       </c>
       <c r="E1356" s="3" t="s">
         <v>290</v>
@@ -68649,30 +69952,36 @@
         <v>388</v>
       </c>
       <c r="G1356" s="3" t="s">
-        <v>5274</v>
-      </c>
-      <c r="H1356" s="3"/>
+        <v>5280</v>
+      </c>
+      <c r="H1356" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1356" s="3">
         <v>31</v>
       </c>
       <c r="J1356" s="3"/>
       <c r="K1356" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1356" s="3"/>
-      <c r="M1356" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1356" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1356" s="3" t="s">
+        <v>5271</v>
+      </c>
       <c r="N1356" s="3"/>
     </row>
     <row r="1357" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1357" s="3" t="s">
-        <v>5275</v>
+        <v>5281</v>
       </c>
       <c r="B1357" s="3"/>
       <c r="C1357" s="3">
         <v>404</v>
       </c>
       <c r="D1357" s="3" t="s">
-        <v>5276</v>
+        <v>5282</v>
       </c>
       <c r="E1357" s="3" t="s">
         <v>290</v>
@@ -68681,41 +69990,49 @@
         <v>1003</v>
       </c>
       <c r="G1357" s="3" t="s">
-        <v>5277</v>
-      </c>
-      <c r="H1357" s="3"/>
+        <v>5283</v>
+      </c>
+      <c r="H1357" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1357" s="3">
         <v>35</v>
       </c>
       <c r="J1357" s="3"/>
       <c r="K1357" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1357" s="3"/>
-      <c r="M1357" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1357" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1357" s="3" t="s">
+        <v>5271</v>
+      </c>
       <c r="N1357" s="3"/>
     </row>
     <row r="1358" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1358" s="3" t="s">
-        <v>5278</v>
+        <v>5284</v>
       </c>
       <c r="B1358" s="3"/>
       <c r="C1358" s="3">
         <v>408</v>
       </c>
       <c r="D1358" s="3" t="s">
-        <v>5279</v>
+        <v>5285</v>
       </c>
       <c r="E1358" s="3" t="s">
         <v>434</v>
       </c>
       <c r="F1358" s="3" t="s">
-        <v>5280</v>
+        <v>5286</v>
       </c>
       <c r="G1358" s="3" t="s">
-        <v>5281</v>
-      </c>
-      <c r="H1358" s="3"/>
+        <v>5287</v>
+      </c>
+      <c r="H1358" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1358" s="3">
         <v>80</v>
       </c>
@@ -68723,174 +70040,208 @@
         <v>75</v>
       </c>
       <c r="K1358" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1358" s="3"/>
-      <c r="M1358" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1358" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1358" s="3" t="s">
+        <v>5271</v>
+      </c>
       <c r="N1358" s="3"/>
     </row>
     <row r="1359" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1359" s="3" t="s">
-        <v>5282</v>
+        <v>5288</v>
       </c>
       <c r="B1359" s="3"/>
       <c r="C1359" s="3">
         <v>408</v>
       </c>
       <c r="D1359" s="3" t="s">
-        <v>5283</v>
+        <v>5289</v>
       </c>
       <c r="E1359" s="3" t="s">
         <v>434</v>
       </c>
       <c r="F1359" s="3" t="s">
-        <v>5284</v>
+        <v>5290</v>
       </c>
       <c r="G1359" s="3" t="s">
-        <v>5285</v>
-      </c>
-      <c r="H1359" s="3"/>
+        <v>5291</v>
+      </c>
+      <c r="H1359" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1359" s="3"/>
       <c r="J1359" s="3"/>
       <c r="K1359" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1359" s="3"/>
-      <c r="M1359" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1359" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1359" s="3" t="s">
+        <v>5271</v>
+      </c>
       <c r="N1359" s="3"/>
     </row>
     <row r="1360" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1360" s="3" t="s">
-        <v>5286</v>
+        <v>5292</v>
       </c>
       <c r="B1360" s="3"/>
       <c r="C1360" s="3">
         <v>408</v>
       </c>
       <c r="D1360" s="3" t="s">
-        <v>5287</v>
+        <v>5293</v>
       </c>
       <c r="E1360" s="3" t="s">
         <v>434</v>
       </c>
       <c r="F1360" s="3" t="s">
-        <v>5288</v>
+        <v>5294</v>
       </c>
       <c r="G1360" s="3" t="s">
-        <v>5289</v>
-      </c>
-      <c r="H1360" s="3"/>
+        <v>5295</v>
+      </c>
+      <c r="H1360" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1360" s="3"/>
       <c r="J1360" s="3"/>
       <c r="K1360" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1360" s="3"/>
-      <c r="M1360" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1360" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1360" s="3" t="s">
+        <v>5271</v>
+      </c>
       <c r="N1360" s="3"/>
     </row>
     <row r="1361" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1361" s="3" t="s">
-        <v>5290</v>
+        <v>5296</v>
       </c>
       <c r="B1361" s="3"/>
       <c r="C1361" s="3">
         <v>408</v>
       </c>
       <c r="D1361" s="3" t="s">
-        <v>5291</v>
+        <v>5297</v>
       </c>
       <c r="E1361" s="3" t="s">
         <v>434</v>
       </c>
       <c r="F1361" s="3" t="s">
-        <v>5292</v>
+        <v>5298</v>
       </c>
       <c r="G1361" s="3" t="s">
-        <v>5293</v>
-      </c>
-      <c r="H1361" s="3"/>
+        <v>5299</v>
+      </c>
+      <c r="H1361" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1361" s="3"/>
       <c r="J1361" s="3"/>
       <c r="K1361" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1361" s="3"/>
-      <c r="M1361" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1361" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1361" s="3" t="s">
+        <v>5271</v>
+      </c>
       <c r="N1361" s="3"/>
     </row>
     <row r="1362" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1362" s="3" t="s">
-        <v>5294</v>
+        <v>5300</v>
       </c>
       <c r="B1362" s="3"/>
       <c r="C1362" s="3">
         <v>408</v>
       </c>
       <c r="D1362" s="3" t="s">
-        <v>5295</v>
+        <v>5301</v>
       </c>
       <c r="E1362" s="3" t="s">
         <v>434</v>
       </c>
       <c r="F1362" s="3" t="s">
-        <v>5296</v>
+        <v>5302</v>
       </c>
       <c r="G1362" s="3" t="s">
-        <v>5297</v>
-      </c>
-      <c r="H1362" s="3"/>
+        <v>5303</v>
+      </c>
+      <c r="H1362" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1362" s="3"/>
       <c r="J1362" s="3"/>
       <c r="K1362" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1362" s="3"/>
-      <c r="M1362" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1362" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1362" s="3" t="s">
+        <v>5271</v>
+      </c>
       <c r="N1362" s="3"/>
     </row>
     <row r="1363" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1363" s="3" t="s">
-        <v>5298</v>
+        <v>5304</v>
       </c>
       <c r="B1363" s="3"/>
       <c r="C1363" s="3">
         <v>408</v>
       </c>
       <c r="D1363" s="3" t="s">
-        <v>5299</v>
+        <v>5305</v>
       </c>
       <c r="E1363" s="3" t="s">
         <v>434</v>
       </c>
       <c r="F1363" s="3" t="s">
-        <v>5300</v>
+        <v>5306</v>
       </c>
       <c r="G1363" s="3" t="s">
-        <v>5301</v>
-      </c>
-      <c r="H1363" s="3"/>
+        <v>5307</v>
+      </c>
+      <c r="H1363" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1363" s="3">
         <v>82</v>
       </c>
       <c r="J1363" s="3"/>
       <c r="K1363" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1363" s="3"/>
-      <c r="M1363" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1363" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1363" s="3" t="s">
+        <v>5271</v>
+      </c>
       <c r="N1363" s="3"/>
     </row>
     <row r="1364" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1364" s="3" t="s">
-        <v>5302</v>
+        <v>5308</v>
       </c>
       <c r="B1364" s="3"/>
       <c r="C1364" s="3">
         <v>408</v>
       </c>
       <c r="D1364" s="3" t="s">
-        <v>5303</v>
+        <v>5309</v>
       </c>
       <c r="E1364" s="3" t="s">
         <v>434</v>
@@ -68899,122 +70250,150 @@
         <v>2696</v>
       </c>
       <c r="G1364" s="3" t="s">
-        <v>5304</v>
-      </c>
-      <c r="H1364" s="3"/>
+        <v>5310</v>
+      </c>
+      <c r="H1364" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1364" s="3">
         <v>83</v>
       </c>
       <c r="J1364" s="3"/>
       <c r="K1364" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1364" s="3"/>
-      <c r="M1364" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1364" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1364" s="3" t="s">
+        <v>5311</v>
+      </c>
       <c r="N1364" s="3"/>
     </row>
     <row r="1365" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1365" s="3" t="s">
-        <v>5305</v>
+        <v>5312</v>
       </c>
       <c r="B1365" s="3"/>
       <c r="C1365" s="3">
         <v>408</v>
       </c>
       <c r="D1365" s="3" t="s">
-        <v>5306</v>
+        <v>5313</v>
       </c>
       <c r="E1365" s="3" t="s">
         <v>434</v>
       </c>
       <c r="F1365" s="3" t="s">
-        <v>5307</v>
+        <v>5314</v>
       </c>
       <c r="G1365" s="3" t="s">
-        <v>5308</v>
-      </c>
-      <c r="H1365" s="3"/>
+        <v>5315</v>
+      </c>
+      <c r="H1365" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1365" s="3">
         <v>82</v>
       </c>
       <c r="J1365" s="3"/>
       <c r="K1365" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1365" s="3"/>
-      <c r="M1365" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1365" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1365" s="3" t="s">
+        <v>5311</v>
+      </c>
       <c r="N1365" s="3"/>
     </row>
     <row r="1366" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1366" s="3" t="s">
-        <v>5309</v>
-      </c>
-      <c r="B1366" s="3"/>
+        <v>5316</v>
+      </c>
+      <c r="B1366" s="3" t="s">
+        <v>348</v>
+      </c>
       <c r="C1366" s="3">
         <v>408</v>
       </c>
       <c r="D1366" s="3" t="s">
-        <v>5310</v>
+        <v>5317</v>
       </c>
       <c r="E1366" s="3" t="s">
         <v>434</v>
       </c>
       <c r="F1366" s="3" t="s">
-        <v>5311</v>
+        <v>5318</v>
       </c>
       <c r="G1366" s="3" t="s">
-        <v>5312</v>
-      </c>
-      <c r="H1366" s="3"/>
+        <v>5319</v>
+      </c>
+      <c r="H1366" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="I1366" s="3"/>
       <c r="J1366" s="3"/>
       <c r="K1366" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1366" s="3"/>
-      <c r="M1366" s="3"/>
-      <c r="N1366" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1366" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1366" s="3" t="s">
+        <v>5311</v>
+      </c>
+      <c r="N1366" s="3" t="s">
+        <v>5320</v>
+      </c>
     </row>
     <row r="1367" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1367" s="3" t="s">
-        <v>5313</v>
+        <v>5321</v>
       </c>
       <c r="B1367" s="3"/>
       <c r="C1367" s="3">
         <v>408</v>
       </c>
       <c r="D1367" s="3" t="s">
-        <v>5314</v>
+        <v>5322</v>
       </c>
       <c r="E1367" s="3" t="s">
         <v>434</v>
       </c>
       <c r="F1367" s="3" t="s">
-        <v>5315</v>
+        <v>5323</v>
       </c>
       <c r="G1367" s="3" t="s">
-        <v>5316</v>
-      </c>
-      <c r="H1367" s="3"/>
+        <v>5324</v>
+      </c>
+      <c r="H1367" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1367" s="3"/>
       <c r="J1367" s="3"/>
       <c r="K1367" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1367" s="3"/>
-      <c r="M1367" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1367" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1367" s="3" t="s">
+        <v>5325</v>
+      </c>
       <c r="N1367" s="3"/>
     </row>
     <row r="1368" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1368" s="3" t="s">
-        <v>5317</v>
+        <v>5326</v>
       </c>
       <c r="B1368" s="3"/>
       <c r="C1368" s="3">
         <v>404</v>
       </c>
       <c r="D1368" s="3" t="s">
-        <v>5318</v>
+        <v>5327</v>
       </c>
       <c r="E1368" s="3" t="s">
         <v>290</v>
@@ -69023,30 +70402,36 @@
         <v>1610</v>
       </c>
       <c r="G1368" s="3" t="s">
-        <v>5319</v>
-      </c>
-      <c r="H1368" s="3"/>
+        <v>5328</v>
+      </c>
+      <c r="H1368" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1368" s="3">
         <v>16</v>
       </c>
       <c r="J1368" s="3"/>
       <c r="K1368" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1368" s="3"/>
-      <c r="M1368" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1368" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1368" s="3" t="s">
+        <v>5329</v>
+      </c>
       <c r="N1368" s="3"/>
     </row>
     <row r="1369" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1369" s="3" t="s">
-        <v>5320</v>
+        <v>5330</v>
       </c>
       <c r="B1369" s="3"/>
       <c r="C1369" s="3">
         <v>404</v>
       </c>
       <c r="D1369" s="3" t="s">
-        <v>5321</v>
+        <v>5331</v>
       </c>
       <c r="E1369" s="3" t="s">
         <v>290</v>
@@ -69055,28 +70440,34 @@
         <v>325</v>
       </c>
       <c r="G1369" s="3" t="s">
-        <v>5322</v>
-      </c>
-      <c r="H1369" s="3"/>
+        <v>5332</v>
+      </c>
+      <c r="H1369" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1369" s="3"/>
       <c r="J1369" s="3"/>
       <c r="K1369" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1369" s="3"/>
-      <c r="M1369" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1369" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1369" s="3" t="s">
+        <v>5329</v>
+      </c>
       <c r="N1369" s="3"/>
     </row>
     <row r="1370" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1370" s="3" t="s">
-        <v>5323</v>
+        <v>5333</v>
       </c>
       <c r="B1370" s="3"/>
       <c r="C1370" s="3">
         <v>404</v>
       </c>
       <c r="D1370" s="3" t="s">
-        <v>5324</v>
+        <v>5334</v>
       </c>
       <c r="E1370" s="3" t="s">
         <v>290</v>
@@ -69085,30 +70476,36 @@
         <v>1610</v>
       </c>
       <c r="G1370" s="3" t="s">
-        <v>5325</v>
-      </c>
-      <c r="H1370" s="3"/>
+        <v>5335</v>
+      </c>
+      <c r="H1370" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1370" s="3">
         <v>11</v>
       </c>
       <c r="J1370" s="3"/>
       <c r="K1370" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1370" s="3"/>
-      <c r="M1370" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1370" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1370" s="3" t="s">
+        <v>5329</v>
+      </c>
       <c r="N1370" s="3"/>
     </row>
     <row r="1371" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1371" s="3" t="s">
-        <v>5326</v>
+        <v>5336</v>
       </c>
       <c r="B1371" s="3"/>
       <c r="C1371" s="3">
         <v>405</v>
       </c>
       <c r="D1371" s="3" t="s">
-        <v>5327</v>
+        <v>5337</v>
       </c>
       <c r="E1371" s="3" t="s">
         <v>290</v>
@@ -69117,30 +70514,36 @@
         <v>1084</v>
       </c>
       <c r="G1371" s="3" t="s">
-        <v>5328</v>
-      </c>
-      <c r="H1371" s="3"/>
+        <v>5338</v>
+      </c>
+      <c r="H1371" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1371" s="3">
         <v>39</v>
       </c>
       <c r="J1371" s="3"/>
       <c r="K1371" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1371" s="3"/>
-      <c r="M1371" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1371" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1371" s="3" t="s">
+        <v>5329</v>
+      </c>
       <c r="N1371" s="3"/>
     </row>
     <row r="1372" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1372" s="3" t="s">
-        <v>5329</v>
+        <v>5339</v>
       </c>
       <c r="B1372" s="3"/>
       <c r="C1372" s="3">
         <v>404</v>
       </c>
       <c r="D1372" s="3" t="s">
-        <v>5330</v>
+        <v>5340</v>
       </c>
       <c r="E1372" s="3" t="s">
         <v>290</v>
@@ -69149,41 +70552,49 @@
         <v>226</v>
       </c>
       <c r="G1372" s="3" t="s">
-        <v>5331</v>
-      </c>
-      <c r="H1372" s="3"/>
+        <v>5341</v>
+      </c>
+      <c r="H1372" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1372" s="3">
         <v>22</v>
       </c>
       <c r="J1372" s="3"/>
       <c r="K1372" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1372" s="3"/>
-      <c r="M1372" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1372" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1372" s="3" t="s">
+        <v>5329</v>
+      </c>
       <c r="N1372" s="3"/>
     </row>
     <row r="1373" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1373" s="3" t="s">
-        <v>5332</v>
+        <v>5342</v>
       </c>
       <c r="B1373" s="3"/>
       <c r="C1373" s="3">
         <v>404</v>
       </c>
       <c r="D1373" s="3" t="s">
-        <v>5333</v>
+        <v>5343</v>
       </c>
       <c r="E1373" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F1373" s="3" t="s">
-        <v>5334</v>
+        <v>5344</v>
       </c>
       <c r="G1373" s="3" t="s">
-        <v>5335</v>
-      </c>
-      <c r="H1373" s="3"/>
+        <v>5345</v>
+      </c>
+      <c r="H1373" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1373" s="3">
         <v>69</v>
       </c>
@@ -69191,52 +70602,62 @@
         <v>65</v>
       </c>
       <c r="K1373" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1373" s="3"/>
-      <c r="M1373" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1373" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1373" s="3" t="s">
+        <v>5329</v>
+      </c>
       <c r="N1373" s="3"/>
     </row>
     <row r="1374" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1374" s="3" t="s">
-        <v>5336</v>
+        <v>5346</v>
       </c>
       <c r="B1374" s="3"/>
       <c r="C1374" s="3">
         <v>404</v>
       </c>
       <c r="D1374" s="3" t="s">
-        <v>5337</v>
+        <v>5347</v>
       </c>
       <c r="E1374" s="3" t="s">
         <v>290</v>
       </c>
       <c r="F1374" s="3" t="s">
-        <v>5338</v>
+        <v>5348</v>
       </c>
       <c r="G1374" s="3" t="s">
-        <v>5339</v>
-      </c>
-      <c r="H1374" s="3"/>
+        <v>5349</v>
+      </c>
+      <c r="H1374" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1374" s="3"/>
       <c r="J1374" s="3"/>
       <c r="K1374" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1374" s="3"/>
-      <c r="M1374" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1374" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1374" s="3" t="s">
+        <v>5329</v>
+      </c>
       <c r="N1374" s="3"/>
     </row>
     <row r="1375" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1375" s="3" t="s">
-        <v>5340</v>
+        <v>5350</v>
       </c>
       <c r="B1375" s="3"/>
       <c r="C1375" s="3">
         <v>404</v>
       </c>
       <c r="D1375" s="3" t="s">
-        <v>5341</v>
+        <v>5351</v>
       </c>
       <c r="E1375" s="3" t="s">
         <v>290</v>
@@ -69245,103 +70666,123 @@
         <v>1003</v>
       </c>
       <c r="G1375" s="3" t="s">
-        <v>5342</v>
-      </c>
-      <c r="H1375" s="3"/>
+        <v>5352</v>
+      </c>
+      <c r="H1375" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1375" s="3">
         <v>34</v>
       </c>
       <c r="J1375" s="3"/>
       <c r="K1375" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1375" s="3"/>
-      <c r="M1375" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1375" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1375" s="3" t="s">
+        <v>5329</v>
+      </c>
       <c r="N1375" s="3"/>
     </row>
     <row r="1376" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1376" s="3" t="s">
-        <v>5343</v>
+        <v>5353</v>
       </c>
       <c r="B1376" s="3"/>
       <c r="C1376" s="3">
         <v>403</v>
       </c>
       <c r="D1376" s="3" t="s">
-        <v>5344</v>
+        <v>5354</v>
       </c>
       <c r="E1376" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F1376" s="3" t="s">
-        <v>5345</v>
+        <v>5355</v>
       </c>
       <c r="G1376" s="3" t="s">
-        <v>5346</v>
-      </c>
-      <c r="H1376" s="3"/>
+        <v>5356</v>
+      </c>
+      <c r="H1376" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1376" s="3"/>
       <c r="J1376" s="3"/>
       <c r="K1376" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1376" s="3"/>
-      <c r="M1376" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1376" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1376" s="3" t="s">
+        <v>5329</v>
+      </c>
       <c r="N1376" s="3"/>
     </row>
     <row r="1377" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1377" s="3" t="s">
-        <v>5347</v>
+        <v>5357</v>
       </c>
       <c r="B1377" s="3"/>
       <c r="C1377" s="3">
         <v>404</v>
       </c>
       <c r="D1377" s="3" t="s">
-        <v>5348</v>
+        <v>5358</v>
       </c>
       <c r="E1377" s="3" t="s">
         <v>290</v>
       </c>
       <c r="F1377" s="3" t="s">
-        <v>5349</v>
+        <v>5359</v>
       </c>
       <c r="G1377" s="3" t="s">
-        <v>5350</v>
-      </c>
-      <c r="H1377" s="3"/>
+        <v>5360</v>
+      </c>
+      <c r="H1377" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1377" s="3">
         <v>37</v>
       </c>
       <c r="J1377" s="3"/>
       <c r="K1377" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1377" s="3"/>
-      <c r="M1377" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1377" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1377" s="3" t="s">
+        <v>5329</v>
+      </c>
       <c r="N1377" s="3"/>
     </row>
     <row r="1378" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1378" s="3" t="s">
-        <v>5351</v>
+        <v>5361</v>
       </c>
       <c r="B1378" s="3"/>
       <c r="C1378" s="3">
         <v>404</v>
       </c>
       <c r="D1378" s="3" t="s">
-        <v>5352</v>
+        <v>5362</v>
       </c>
       <c r="E1378" s="3" t="s">
         <v>194</v>
       </c>
       <c r="F1378" s="3" t="s">
-        <v>5353</v>
+        <v>5363</v>
       </c>
       <c r="G1378" s="3" t="s">
-        <v>5354</v>
-      </c>
-      <c r="H1378" s="3"/>
+        <v>5364</v>
+      </c>
+      <c r="H1378" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1378" s="3">
         <v>76</v>
       </c>
@@ -69349,22 +70790,26 @@
         <v>75</v>
       </c>
       <c r="K1378" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1378" s="3"/>
-      <c r="M1378" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1378" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1378" s="3" t="s">
+        <v>5329</v>
+      </c>
       <c r="N1378" s="3"/>
     </row>
     <row r="1379" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1379" s="3" t="s">
-        <v>5355</v>
+        <v>5365</v>
       </c>
       <c r="B1379" s="3"/>
       <c r="C1379" s="3">
         <v>404</v>
       </c>
       <c r="D1379" s="3" t="s">
-        <v>5356</v>
+        <v>5366</v>
       </c>
       <c r="E1379" s="3" t="s">
         <v>290</v>
@@ -69373,60 +70818,72 @@
         <v>3594</v>
       </c>
       <c r="G1379" s="3" t="s">
-        <v>5357</v>
-      </c>
-      <c r="H1379" s="3"/>
+        <v>5367</v>
+      </c>
+      <c r="H1379" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1379" s="3"/>
       <c r="J1379" s="3"/>
       <c r="K1379" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1379" s="3"/>
-      <c r="M1379" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1379" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1379" s="3" t="s">
+        <v>5329</v>
+      </c>
       <c r="N1379" s="3"/>
     </row>
     <row r="1380" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1380" s="3" t="s">
-        <v>5358</v>
+        <v>5368</v>
       </c>
       <c r="B1380" s="3"/>
       <c r="C1380" s="3">
         <v>404</v>
       </c>
       <c r="D1380" s="3" t="s">
-        <v>5359</v>
+        <v>5369</v>
       </c>
       <c r="E1380" s="3" t="s">
         <v>290</v>
       </c>
       <c r="F1380" s="3" t="s">
-        <v>5360</v>
+        <v>5370</v>
       </c>
       <c r="G1380" s="3" t="s">
-        <v>5361</v>
-      </c>
-      <c r="H1380" s="3"/>
+        <v>5371</v>
+      </c>
+      <c r="H1380" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1380" s="3">
         <v>21</v>
       </c>
       <c r="J1380" s="3"/>
       <c r="K1380" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1380" s="3"/>
-      <c r="M1380" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1380" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1380" s="3" t="s">
+        <v>5329</v>
+      </c>
       <c r="N1380" s="3"/>
     </row>
     <row r="1381" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1381" s="3" t="s">
-        <v>5362</v>
+        <v>5372</v>
       </c>
       <c r="B1381" s="3"/>
       <c r="C1381" s="3">
         <v>404</v>
       </c>
       <c r="D1381" s="3" t="s">
-        <v>5363</v>
+        <v>5373</v>
       </c>
       <c r="E1381" s="3" t="s">
         <v>290</v>
@@ -69435,103 +70892,123 @@
         <v>2306</v>
       </c>
       <c r="G1381" s="3" t="s">
-        <v>5364</v>
-      </c>
-      <c r="H1381" s="3"/>
+        <v>5374</v>
+      </c>
+      <c r="H1381" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1381" s="3">
         <v>34</v>
       </c>
       <c r="J1381" s="3"/>
       <c r="K1381" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1381" s="3"/>
-      <c r="M1381" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1381" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1381" s="3" t="s">
+        <v>5375</v>
+      </c>
       <c r="N1381" s="3"/>
     </row>
     <row r="1382" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1382" s="3" t="s">
-        <v>5365</v>
+        <v>5376</v>
       </c>
       <c r="B1382" s="3"/>
       <c r="C1382" s="3">
         <v>403</v>
       </c>
       <c r="D1382" s="3" t="s">
-        <v>5366</v>
+        <v>5377</v>
       </c>
       <c r="E1382" s="3" t="s">
         <v>1150</v>
       </c>
       <c r="F1382" s="3" t="s">
-        <v>5367</v>
+        <v>5378</v>
       </c>
       <c r="G1382" s="3" t="s">
-        <v>5368</v>
-      </c>
-      <c r="H1382" s="3"/>
+        <v>5379</v>
+      </c>
+      <c r="H1382" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1382" s="3">
         <v>74</v>
       </c>
       <c r="J1382" s="3"/>
       <c r="K1382" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1382" s="3"/>
-      <c r="M1382" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1382" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1382" s="3" t="s">
+        <v>5375</v>
+      </c>
       <c r="N1382" s="3"/>
     </row>
     <row r="1383" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1383" s="3" t="s">
-        <v>5369</v>
+        <v>5380</v>
       </c>
       <c r="B1383" s="3"/>
       <c r="C1383" s="3">
         <v>403</v>
       </c>
       <c r="D1383" s="3" t="s">
-        <v>5370</v>
+        <v>5381</v>
       </c>
       <c r="E1383" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F1383" s="3" t="s">
-        <v>5371</v>
+        <v>5382</v>
       </c>
       <c r="G1383" s="3" t="s">
-        <v>5372</v>
-      </c>
-      <c r="H1383" s="3"/>
+        <v>5383</v>
+      </c>
+      <c r="H1383" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1383" s="3"/>
       <c r="J1383" s="3"/>
       <c r="K1383" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1383" s="3"/>
-      <c r="M1383" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1383" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1383" s="3" t="s">
+        <v>5375</v>
+      </c>
       <c r="N1383" s="3"/>
     </row>
     <row r="1384" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1384" s="3" t="s">
-        <v>5373</v>
+        <v>5384</v>
       </c>
       <c r="B1384" s="3"/>
       <c r="C1384" s="3">
         <v>403</v>
       </c>
       <c r="D1384" s="3" t="s">
-        <v>5374</v>
+        <v>5385</v>
       </c>
       <c r="E1384" s="3" t="s">
         <v>211</v>
       </c>
       <c r="F1384" s="3" t="s">
-        <v>5375</v>
+        <v>5386</v>
       </c>
       <c r="G1384" s="3" t="s">
-        <v>5376</v>
-      </c>
-      <c r="H1384" s="3"/>
+        <v>5387</v>
+      </c>
+      <c r="H1384" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1384" s="3">
         <v>74</v>
       </c>
@@ -69539,22 +71016,26 @@
         <v>60</v>
       </c>
       <c r="K1384" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1384" s="3"/>
-      <c r="M1384" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1384" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1384" s="3" t="s">
+        <v>5375</v>
+      </c>
       <c r="N1384" s="3"/>
     </row>
     <row r="1385" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1385" s="3" t="s">
-        <v>5377</v>
+        <v>5388</v>
       </c>
       <c r="B1385" s="3"/>
       <c r="C1385" s="3">
         <v>404</v>
       </c>
       <c r="D1385" s="3" t="s">
-        <v>5378</v>
+        <v>5389</v>
       </c>
       <c r="E1385" s="3" t="s">
         <v>290</v>
@@ -69563,41 +71044,49 @@
         <v>2555</v>
       </c>
       <c r="G1385" s="3" t="s">
-        <v>5379</v>
-      </c>
-      <c r="H1385" s="3"/>
+        <v>5390</v>
+      </c>
+      <c r="H1385" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1385" s="3">
         <v>35</v>
       </c>
       <c r="J1385" s="3"/>
       <c r="K1385" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1385" s="3"/>
-      <c r="M1385" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1385" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1385" s="3" t="s">
+        <v>5375</v>
+      </c>
       <c r="N1385" s="3"/>
     </row>
     <row r="1386" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1386" s="3" t="s">
-        <v>5380</v>
+        <v>5391</v>
       </c>
       <c r="B1386" s="3"/>
       <c r="C1386" s="3">
         <v>403</v>
       </c>
       <c r="D1386" s="3" t="s">
-        <v>5381</v>
+        <v>5392</v>
       </c>
       <c r="E1386" s="3" t="s">
         <v>211</v>
       </c>
       <c r="F1386" s="3" t="s">
-        <v>5382</v>
+        <v>5393</v>
       </c>
       <c r="G1386" s="3" t="s">
-        <v>5383</v>
-      </c>
-      <c r="H1386" s="3"/>
+        <v>5394</v>
+      </c>
+      <c r="H1386" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1386" s="3">
         <v>57</v>
       </c>
@@ -69605,43 +71094,3989 @@
         <v>45</v>
       </c>
       <c r="K1386" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1386" s="3"/>
-      <c r="M1386" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1386" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1386" s="3" t="s">
+        <v>5375</v>
+      </c>
       <c r="N1386" s="3"/>
     </row>
     <row r="1387" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1387" s="3" t="s">
-        <v>5384</v>
+        <v>5395</v>
       </c>
       <c r="B1387" s="3"/>
       <c r="C1387" s="3">
         <v>403</v>
       </c>
       <c r="D1387" s="3" t="s">
-        <v>5385</v>
+        <v>5396</v>
       </c>
       <c r="E1387" s="3" t="s">
         <v>194</v>
       </c>
       <c r="F1387" s="3" t="s">
-        <v>5386</v>
+        <v>5397</v>
       </c>
       <c r="G1387" s="3" t="s">
-        <v>5387</v>
-      </c>
-      <c r="H1387" s="3"/>
+        <v>5398</v>
+      </c>
+      <c r="H1387" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1387" s="3">
         <v>74</v>
       </c>
       <c r="J1387" s="3"/>
       <c r="K1387" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1387" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1387" s="3" t="s">
+        <v>5375</v>
+      </c>
+      <c r="N1387" s="3"/>
+    </row>
+    <row r="1388" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1388" s="3" t="s">
+        <v>5399</v>
+      </c>
+      <c r="B1388" s="3"/>
+      <c r="C1388" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1388" s="3" t="s">
+        <v>5400</v>
+      </c>
+      <c r="E1388" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1388" s="3" t="s">
+        <v>5401</v>
+      </c>
+      <c r="G1388" s="3" t="s">
+        <v>5402</v>
+      </c>
+      <c r="H1388" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1388" s="3">
+        <v>63</v>
+      </c>
+      <c r="J1388" s="3">
+        <v>45</v>
+      </c>
+      <c r="K1388" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1388" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1388" s="3" t="s">
+        <v>5375</v>
+      </c>
+      <c r="N1388" s="3"/>
+    </row>
+    <row r="1389" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1389" s="3" t="s">
+        <v>5403</v>
+      </c>
+      <c r="B1389" s="3"/>
+      <c r="C1389" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1389" s="3" t="s">
+        <v>5404</v>
+      </c>
+      <c r="E1389" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1389" s="3" t="s">
+        <v>5405</v>
+      </c>
+      <c r="G1389" s="3" t="s">
+        <v>5406</v>
+      </c>
+      <c r="H1389" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1389" s="3">
+        <v>2</v>
+      </c>
+      <c r="J1389" s="3"/>
+      <c r="K1389" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1389" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1389" s="3" t="s">
+        <v>5407</v>
+      </c>
+      <c r="N1389" s="3"/>
+    </row>
+    <row r="1390" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1390" s="3" t="s">
+        <v>5408</v>
+      </c>
+      <c r="B1390" s="3"/>
+      <c r="C1390" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1390" s="3" t="s">
+        <v>5409</v>
+      </c>
+      <c r="E1390" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1390" s="3" t="s">
+        <v>5410</v>
+      </c>
+      <c r="G1390" s="3" t="s">
+        <v>5411</v>
+      </c>
+      <c r="H1390" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1390" s="3">
+        <v>27</v>
+      </c>
+      <c r="J1390" s="3"/>
+      <c r="K1390" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1390" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1390" s="3" t="s">
+        <v>5407</v>
+      </c>
+      <c r="N1390" s="3"/>
+    </row>
+    <row r="1391" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1391" s="3" t="s">
+        <v>5412</v>
+      </c>
+      <c r="B1391" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1391" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1391" s="3" t="s">
+        <v>5413</v>
+      </c>
+      <c r="E1391" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1391" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1391" s="3" t="s">
+        <v>5414</v>
+      </c>
+      <c r="H1391" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1391" s="3">
+        <v>13</v>
+      </c>
+      <c r="J1391" s="3"/>
+      <c r="K1391" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1391" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1391" s="3" t="s">
+        <v>5407</v>
+      </c>
+      <c r="N1391" s="3" t="s">
+        <v>5375</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1392" s="3" t="s">
+        <v>5415</v>
+      </c>
+      <c r="B1392" s="3"/>
+      <c r="C1392" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1392" s="3" t="s">
+        <v>5416</v>
+      </c>
+      <c r="E1392" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1392" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G1392" s="3" t="s">
+        <v>5417</v>
+      </c>
+      <c r="H1392" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1392" s="3">
+        <v>13</v>
+      </c>
+      <c r="J1392" s="3"/>
+      <c r="K1392" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1392" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1392" s="3" t="s">
+        <v>5418</v>
+      </c>
+      <c r="N1392" s="3"/>
+    </row>
+    <row r="1393" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1393" s="3" t="s">
+        <v>5419</v>
+      </c>
+      <c r="B1393" s="3"/>
+      <c r="C1393" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1393" s="3" t="s">
+        <v>5420</v>
+      </c>
+      <c r="E1393" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1393" s="3" t="s">
+        <v>1610</v>
+      </c>
+      <c r="G1393" s="3" t="s">
+        <v>5421</v>
+      </c>
+      <c r="H1393" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1393" s="3">
         <v>22</v>
       </c>
-      <c r="L1387" s="3"/>
-      <c r="M1387" s="3"/>
-      <c r="N1387" s="3"/>
+      <c r="J1393" s="3"/>
+      <c r="K1393" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1393" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1393" s="3" t="s">
+        <v>5422</v>
+      </c>
+      <c r="N1393" s="3"/>
+    </row>
+    <row r="1394" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1394" s="3" t="s">
+        <v>5423</v>
+      </c>
+      <c r="B1394" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C1394" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1394" s="3" t="s">
+        <v>5424</v>
+      </c>
+      <c r="E1394" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1394" s="3" t="s">
+        <v>1870</v>
+      </c>
+      <c r="G1394" s="3" t="s">
+        <v>5425</v>
+      </c>
+      <c r="H1394" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1394" s="3"/>
+      <c r="J1394" s="3"/>
+      <c r="K1394" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1394" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1394" s="3" t="s">
+        <v>5422</v>
+      </c>
+      <c r="N1394" s="3" t="s">
+        <v>5426</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1395" s="3" t="s">
+        <v>5423</v>
+      </c>
+      <c r="B1395" s="3"/>
+      <c r="C1395" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1395" s="3" t="s">
+        <v>5427</v>
+      </c>
+      <c r="E1395" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1395" s="3" t="s">
+        <v>1870</v>
+      </c>
+      <c r="G1395" s="3" t="s">
+        <v>5425</v>
+      </c>
+      <c r="H1395" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1395" s="3"/>
+      <c r="J1395" s="3"/>
+      <c r="K1395" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1395" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1395" s="3" t="s">
+        <v>5428</v>
+      </c>
+      <c r="N1395" s="3"/>
+    </row>
+    <row r="1396" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1396" s="3" t="s">
+        <v>5429</v>
+      </c>
+      <c r="B1396" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C1396" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1396" s="3" t="s">
+        <v>5430</v>
+      </c>
+      <c r="E1396" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1396" s="3" t="s">
+        <v>5431</v>
+      </c>
+      <c r="G1396" s="3" t="s">
+        <v>5432</v>
+      </c>
+      <c r="H1396" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1396" s="3">
+        <v>78</v>
+      </c>
+      <c r="J1396" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1396" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1396" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1396" s="3" t="s">
+        <v>5428</v>
+      </c>
+      <c r="N1396" s="3"/>
+    </row>
+    <row r="1397" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1397" s="3" t="s">
+        <v>5433</v>
+      </c>
+      <c r="B1397" s="3"/>
+      <c r="C1397" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1397" s="3" t="s">
+        <v>5434</v>
+      </c>
+      <c r="E1397" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1397" s="3" t="s">
+        <v>2448</v>
+      </c>
+      <c r="G1397" s="3" t="s">
+        <v>5435</v>
+      </c>
+      <c r="H1397" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1397" s="3">
+        <v>14</v>
+      </c>
+      <c r="J1397" s="3"/>
+      <c r="K1397" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1397" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1397" s="3" t="s">
+        <v>5436</v>
+      </c>
+      <c r="N1397" s="3"/>
+    </row>
+    <row r="1398" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1398" s="3" t="s">
+        <v>5437</v>
+      </c>
+      <c r="B1398" s="3"/>
+      <c r="C1398" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1398" s="3" t="s">
+        <v>5438</v>
+      </c>
+      <c r="E1398" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1398" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="G1398" s="3" t="s">
+        <v>5439</v>
+      </c>
+      <c r="H1398" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1398" s="3">
+        <v>36</v>
+      </c>
+      <c r="J1398" s="3"/>
+      <c r="K1398" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1398" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1398" s="3" t="s">
+        <v>5436</v>
+      </c>
+      <c r="N1398" s="3"/>
+    </row>
+    <row r="1399" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1399" s="3" t="s">
+        <v>5440</v>
+      </c>
+      <c r="B1399" s="3"/>
+      <c r="C1399" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1399" s="3" t="s">
+        <v>5441</v>
+      </c>
+      <c r="E1399" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1399" s="3" t="s">
+        <v>5442</v>
+      </c>
+      <c r="G1399" s="3" t="s">
+        <v>5443</v>
+      </c>
+      <c r="H1399" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1399" s="3"/>
+      <c r="J1399" s="3"/>
+      <c r="K1399" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1399" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1399" s="3" t="s">
+        <v>5436</v>
+      </c>
+      <c r="N1399" s="3"/>
+    </row>
+    <row r="1400" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1400" s="3" t="s">
+        <v>5444</v>
+      </c>
+      <c r="B1400" s="3"/>
+      <c r="C1400" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1400" s="3" t="s">
+        <v>5445</v>
+      </c>
+      <c r="E1400" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1400" s="3" t="s">
+        <v>5446</v>
+      </c>
+      <c r="G1400" s="3" t="s">
+        <v>5447</v>
+      </c>
+      <c r="H1400" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1400" s="3">
+        <v>62</v>
+      </c>
+      <c r="J1400" s="3"/>
+      <c r="K1400" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1400" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1400" s="3" t="s">
+        <v>5448</v>
+      </c>
+      <c r="N1400" s="3"/>
+    </row>
+    <row r="1401" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1401" s="3" t="s">
+        <v>5449</v>
+      </c>
+      <c r="B1401" s="3"/>
+      <c r="C1401" s="3">
+        <v>410</v>
+      </c>
+      <c r="D1401" s="3" t="s">
+        <v>5450</v>
+      </c>
+      <c r="E1401" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F1401" s="3" t="s">
+        <v>2338</v>
+      </c>
+      <c r="G1401" s="3" t="s">
+        <v>5451</v>
+      </c>
+      <c r="H1401" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1401" s="3">
+        <v>29</v>
+      </c>
+      <c r="J1401" s="3"/>
+      <c r="K1401" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1401" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1401" s="3" t="s">
+        <v>5448</v>
+      </c>
+      <c r="N1401" s="3"/>
+    </row>
+    <row r="1402" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1402" s="3" t="s">
+        <v>5452</v>
+      </c>
+      <c r="B1402" s="3"/>
+      <c r="C1402" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1402" s="3" t="s">
+        <v>5453</v>
+      </c>
+      <c r="E1402" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1402" s="3" t="s">
+        <v>5454</v>
+      </c>
+      <c r="G1402" s="3" t="s">
+        <v>5455</v>
+      </c>
+      <c r="H1402" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1402" s="3">
+        <v>34</v>
+      </c>
+      <c r="J1402" s="3"/>
+      <c r="K1402" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1402" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1402" s="3" t="s">
+        <v>5456</v>
+      </c>
+      <c r="N1402" s="3"/>
+    </row>
+    <row r="1403" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1403" s="3" t="s">
+        <v>5457</v>
+      </c>
+      <c r="B1403" s="3"/>
+      <c r="C1403" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1403" s="3" t="s">
+        <v>5458</v>
+      </c>
+      <c r="E1403" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1403" s="3" t="s">
+        <v>4793</v>
+      </c>
+      <c r="G1403" s="3" t="s">
+        <v>5459</v>
+      </c>
+      <c r="H1403" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1403" s="3"/>
+      <c r="J1403" s="3"/>
+      <c r="K1403" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1403" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1403" s="3" t="s">
+        <v>5460</v>
+      </c>
+      <c r="N1403" s="3"/>
+    </row>
+    <row r="1404" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1404" s="3" t="s">
+        <v>5461</v>
+      </c>
+      <c r="B1404" s="3"/>
+      <c r="C1404" s="3">
+        <v>408</v>
+      </c>
+      <c r="D1404" s="3" t="s">
+        <v>5462</v>
+      </c>
+      <c r="E1404" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1404" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="G1404" s="3" t="s">
+        <v>5463</v>
+      </c>
+      <c r="H1404" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1404" s="3"/>
+      <c r="J1404" s="3"/>
+      <c r="K1404" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1404" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1404" s="3" t="s">
+        <v>5460</v>
+      </c>
+      <c r="N1404" s="3"/>
+    </row>
+    <row r="1405" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1405" s="3" t="s">
+        <v>5464</v>
+      </c>
+      <c r="B1405" s="3"/>
+      <c r="C1405" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1405" s="3" t="s">
+        <v>5465</v>
+      </c>
+      <c r="E1405" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1405" s="3" t="s">
+        <v>5466</v>
+      </c>
+      <c r="G1405" s="3" t="s">
+        <v>5467</v>
+      </c>
+      <c r="H1405" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1405" s="3">
+        <v>35</v>
+      </c>
+      <c r="J1405" s="3"/>
+      <c r="K1405" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1405" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1405" s="3" t="s">
+        <v>5460</v>
+      </c>
+      <c r="N1405" s="3"/>
+    </row>
+    <row r="1406" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1406" s="3" t="s">
+        <v>5468</v>
+      </c>
+      <c r="B1406" s="3"/>
+      <c r="C1406" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1406" s="3" t="s">
+        <v>5469</v>
+      </c>
+      <c r="E1406" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1406" s="3" t="s">
+        <v>3594</v>
+      </c>
+      <c r="G1406" s="3" t="s">
+        <v>5470</v>
+      </c>
+      <c r="H1406" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1406" s="3">
+        <v>20</v>
+      </c>
+      <c r="J1406" s="3"/>
+      <c r="K1406" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1406" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1406" s="3" t="s">
+        <v>5460</v>
+      </c>
+      <c r="N1406" s="3"/>
+    </row>
+    <row r="1407" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1407" s="3" t="s">
+        <v>5471</v>
+      </c>
+      <c r="B1407" s="3"/>
+      <c r="C1407" s="3">
+        <v>408</v>
+      </c>
+      <c r="D1407" s="3" t="s">
+        <v>5472</v>
+      </c>
+      <c r="E1407" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1407" s="3" t="s">
+        <v>1088</v>
+      </c>
+      <c r="G1407" s="3" t="s">
+        <v>5473</v>
+      </c>
+      <c r="H1407" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1407" s="3">
+        <v>34</v>
+      </c>
+      <c r="J1407" s="3"/>
+      <c r="K1407" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1407" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1407" s="3" t="s">
+        <v>5460</v>
+      </c>
+      <c r="N1407" s="3"/>
+    </row>
+    <row r="1408" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1408" s="3" t="s">
+        <v>5474</v>
+      </c>
+      <c r="B1408" s="3"/>
+      <c r="C1408" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1408" s="3" t="s">
+        <v>5475</v>
+      </c>
+      <c r="E1408" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1408" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G1408" s="3" t="s">
+        <v>5476</v>
+      </c>
+      <c r="H1408" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1408" s="3">
+        <v>16</v>
+      </c>
+      <c r="J1408" s="3"/>
+      <c r="K1408" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1408" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1408" s="3" t="s">
+        <v>5460</v>
+      </c>
+      <c r="N1408" s="3"/>
+    </row>
+    <row r="1409" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1409" s="3" t="s">
+        <v>5477</v>
+      </c>
+      <c r="B1409" s="3"/>
+      <c r="C1409" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1409" s="3" t="s">
+        <v>5478</v>
+      </c>
+      <c r="E1409" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1409" s="3" t="s">
+        <v>3751</v>
+      </c>
+      <c r="G1409" s="3" t="s">
+        <v>5479</v>
+      </c>
+      <c r="H1409" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1409" s="3">
+        <v>9</v>
+      </c>
+      <c r="J1409" s="3"/>
+      <c r="K1409" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1409" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1409" s="3" t="s">
+        <v>5460</v>
+      </c>
+      <c r="N1409" s="3"/>
+    </row>
+    <row r="1410" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1410" s="3" t="s">
+        <v>5480</v>
+      </c>
+      <c r="B1410" s="3"/>
+      <c r="C1410" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1410" s="3" t="s">
+        <v>5481</v>
+      </c>
+      <c r="E1410" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1410" s="3" t="s">
+        <v>1707</v>
+      </c>
+      <c r="G1410" s="3" t="s">
+        <v>5482</v>
+      </c>
+      <c r="H1410" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1410" s="3">
+        <v>12</v>
+      </c>
+      <c r="J1410" s="3"/>
+      <c r="K1410" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1410" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1410" s="3" t="s">
+        <v>5460</v>
+      </c>
+      <c r="N1410" s="3"/>
+    </row>
+    <row r="1411" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1411" s="3" t="s">
+        <v>5483</v>
+      </c>
+      <c r="B1411" s="3"/>
+      <c r="C1411" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1411" s="3" t="s">
+        <v>5484</v>
+      </c>
+      <c r="E1411" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1411" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G1411" s="3" t="s">
+        <v>5485</v>
+      </c>
+      <c r="H1411" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1411" s="3">
+        <v>19</v>
+      </c>
+      <c r="J1411" s="3"/>
+      <c r="K1411" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1411" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1411" s="3" t="s">
+        <v>5486</v>
+      </c>
+      <c r="N1411" s="3"/>
+    </row>
+    <row r="1412" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1412" s="3" t="s">
+        <v>5487</v>
+      </c>
+      <c r="B1412" s="3"/>
+      <c r="C1412" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1412" s="3" t="s">
+        <v>5488</v>
+      </c>
+      <c r="E1412" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1412" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1412" s="3" t="s">
+        <v>5489</v>
+      </c>
+      <c r="H1412" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1412" s="3">
+        <v>24</v>
+      </c>
+      <c r="J1412" s="3"/>
+      <c r="K1412" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1412" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1412" s="3" t="s">
+        <v>5486</v>
+      </c>
+      <c r="N1412" s="3"/>
+    </row>
+    <row r="1413" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1413" s="3" t="s">
+        <v>5490</v>
+      </c>
+      <c r="B1413" s="3"/>
+      <c r="C1413" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1413" s="3" t="s">
+        <v>5491</v>
+      </c>
+      <c r="E1413" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1413" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G1413" s="3" t="s">
+        <v>5492</v>
+      </c>
+      <c r="H1413" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1413" s="3">
+        <v>16</v>
+      </c>
+      <c r="J1413" s="3"/>
+      <c r="K1413" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1413" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1413" s="3" t="s">
+        <v>5493</v>
+      </c>
+      <c r="N1413" s="3"/>
+    </row>
+    <row r="1414" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1414" s="3" t="s">
+        <v>5494</v>
+      </c>
+      <c r="B1414" s="3"/>
+      <c r="C1414" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1414" s="3" t="s">
+        <v>5495</v>
+      </c>
+      <c r="E1414" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1414" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="G1414" s="3" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1414" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1414" s="3"/>
+      <c r="J1414" s="3"/>
+      <c r="K1414" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1414" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1414" s="3" t="s">
+        <v>5497</v>
+      </c>
+      <c r="N1414" s="3"/>
+    </row>
+    <row r="1415" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1415" s="3" t="s">
+        <v>5498</v>
+      </c>
+      <c r="B1415" s="3"/>
+      <c r="C1415" s="3">
+        <v>414</v>
+      </c>
+      <c r="D1415" s="3" t="s">
+        <v>5499</v>
+      </c>
+      <c r="E1415" s="3" t="s">
+        <v>1801</v>
+      </c>
+      <c r="F1415" s="3" t="s">
+        <v>5500</v>
+      </c>
+      <c r="G1415" s="3" t="s">
+        <v>5501</v>
+      </c>
+      <c r="H1415" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1415" s="3">
+        <v>62</v>
+      </c>
+      <c r="J1415" s="3"/>
+      <c r="K1415" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1415" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1415" s="3" t="s">
+        <v>5502</v>
+      </c>
+      <c r="N1415" s="3"/>
+    </row>
+    <row r="1416" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1416" s="3" t="s">
+        <v>5503</v>
+      </c>
+      <c r="B1416" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1416" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1416" s="3" t="s">
+        <v>5504</v>
+      </c>
+      <c r="E1416" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1416" s="3" t="s">
+        <v>5505</v>
+      </c>
+      <c r="G1416" s="3" t="s">
+        <v>5506</v>
+      </c>
+      <c r="H1416" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1416" s="3">
+        <v>30</v>
+      </c>
+      <c r="J1416" s="3"/>
+      <c r="K1416" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1416" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1416" s="3" t="s">
+        <v>5502</v>
+      </c>
+      <c r="N1416" s="3" t="s">
+        <v>5497</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1417" s="3" t="s">
+        <v>5507</v>
+      </c>
+      <c r="B1417" s="3"/>
+      <c r="C1417" s="3">
+        <v>414</v>
+      </c>
+      <c r="D1417" s="3" t="s">
+        <v>5508</v>
+      </c>
+      <c r="E1417" s="3" t="s">
+        <v>1801</v>
+      </c>
+      <c r="F1417" s="3" t="s">
+        <v>5509</v>
+      </c>
+      <c r="G1417" s="3" t="s">
+        <v>5510</v>
+      </c>
+      <c r="H1417" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1417" s="3"/>
+      <c r="J1417" s="3"/>
+      <c r="K1417" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1417" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1417" s="3" t="s">
+        <v>5502</v>
+      </c>
+      <c r="N1417" s="3"/>
+    </row>
+    <row r="1418" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1418" s="3" t="s">
+        <v>5511</v>
+      </c>
+      <c r="B1418" s="3"/>
+      <c r="C1418" s="3">
+        <v>414</v>
+      </c>
+      <c r="D1418" s="3" t="s">
+        <v>5512</v>
+      </c>
+      <c r="E1418" s="3" t="s">
+        <v>1801</v>
+      </c>
+      <c r="F1418" s="3" t="s">
+        <v>5513</v>
+      </c>
+      <c r="G1418" s="3" t="s">
+        <v>5514</v>
+      </c>
+      <c r="H1418" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1418" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1418" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1418" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1418" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1418" s="3" t="s">
+        <v>5502</v>
+      </c>
+      <c r="N1418" s="3"/>
+    </row>
+    <row r="1419" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1419" s="3" t="s">
+        <v>5515</v>
+      </c>
+      <c r="B1419" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1419" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1419" s="3" t="s">
+        <v>5516</v>
+      </c>
+      <c r="E1419" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1419" s="3" t="s">
+        <v>5517</v>
+      </c>
+      <c r="G1419" s="3" t="s">
+        <v>5518</v>
+      </c>
+      <c r="H1419" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1419" s="3">
+        <v>14</v>
+      </c>
+      <c r="J1419" s="3"/>
+      <c r="K1419" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1419" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1419" s="3" t="s">
+        <v>5519</v>
+      </c>
+      <c r="N1419" s="3" t="s">
+        <v>5502</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1420" s="3" t="s">
+        <v>5520</v>
+      </c>
+      <c r="B1420" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1420" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1420" s="3" t="s">
+        <v>5521</v>
+      </c>
+      <c r="E1420" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1420" s="3" t="s">
+        <v>5522</v>
+      </c>
+      <c r="G1420" s="3" t="s">
+        <v>5523</v>
+      </c>
+      <c r="H1420" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1420" s="3">
+        <v>76</v>
+      </c>
+      <c r="J1420" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1420" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1420" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1420" s="3" t="s">
+        <v>5524</v>
+      </c>
+      <c r="N1420" s="3" t="s">
+        <v>5519</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1421" s="3" t="s">
+        <v>5525</v>
+      </c>
+      <c r="B1421" s="3"/>
+      <c r="C1421" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1421" s="3" t="s">
+        <v>5526</v>
+      </c>
+      <c r="E1421" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1421" s="3" t="s">
+        <v>2106</v>
+      </c>
+      <c r="G1421" s="3" t="s">
+        <v>5527</v>
+      </c>
+      <c r="H1421" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1421" s="3">
+        <v>64</v>
+      </c>
+      <c r="J1421" s="3"/>
+      <c r="K1421" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1421" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1421" s="3" t="s">
+        <v>5493</v>
+      </c>
+      <c r="N1421" s="3"/>
+    </row>
+    <row r="1422" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1422" s="3" t="s">
+        <v>5528</v>
+      </c>
+      <c r="B1422" s="3"/>
+      <c r="C1422" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1422" s="3" t="s">
+        <v>5529</v>
+      </c>
+      <c r="E1422" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1422" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G1422" s="3" t="s">
+        <v>5530</v>
+      </c>
+      <c r="H1422" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1422" s="3">
+        <v>45</v>
+      </c>
+      <c r="J1422" s="3"/>
+      <c r="K1422" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1422" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1422" s="3" t="s">
+        <v>5493</v>
+      </c>
+      <c r="N1422" s="3"/>
+    </row>
+    <row r="1423" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1423" s="3" t="s">
+        <v>5531</v>
+      </c>
+      <c r="B1423" s="3"/>
+      <c r="C1423" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1423" s="3" t="s">
+        <v>5532</v>
+      </c>
+      <c r="E1423" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1423" s="3" t="s">
+        <v>2615</v>
+      </c>
+      <c r="G1423" s="3" t="s">
+        <v>5533</v>
+      </c>
+      <c r="H1423" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1423" s="3">
+        <v>15</v>
+      </c>
+      <c r="J1423" s="3"/>
+      <c r="K1423" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1423" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1423" s="3" t="s">
+        <v>5493</v>
+      </c>
+      <c r="N1423" s="3"/>
+    </row>
+    <row r="1424" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1424" s="3" t="s">
+        <v>5534</v>
+      </c>
+      <c r="B1424" s="3"/>
+      <c r="C1424" s="3">
+        <v>408</v>
+      </c>
+      <c r="D1424" s="3" t="s">
+        <v>5535</v>
+      </c>
+      <c r="E1424" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F1424" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G1424" s="3" t="s">
+        <v>5536</v>
+      </c>
+      <c r="H1424" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1424" s="3"/>
+      <c r="J1424" s="3"/>
+      <c r="K1424" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1424" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1424" s="3" t="s">
+        <v>5537</v>
+      </c>
+      <c r="N1424" s="3"/>
+    </row>
+    <row r="1425" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1425" s="3" t="s">
+        <v>5538</v>
+      </c>
+      <c r="B1425" s="3"/>
+      <c r="C1425" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1425" s="3" t="s">
+        <v>5539</v>
+      </c>
+      <c r="E1425" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1425" s="3" t="s">
+        <v>2197</v>
+      </c>
+      <c r="G1425" s="3" t="s">
+        <v>5540</v>
+      </c>
+      <c r="H1425" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1425" s="3"/>
+      <c r="J1425" s="3"/>
+      <c r="K1425" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1425" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1425" s="3" t="s">
+        <v>5537</v>
+      </c>
+      <c r="N1425" s="3"/>
+    </row>
+    <row r="1426" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1426" s="3" t="s">
+        <v>5541</v>
+      </c>
+      <c r="B1426" s="3"/>
+      <c r="C1426" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1426" s="3" t="s">
+        <v>5542</v>
+      </c>
+      <c r="E1426" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1426" s="3" t="s">
+        <v>5410</v>
+      </c>
+      <c r="G1426" s="3" t="s">
+        <v>5543</v>
+      </c>
+      <c r="H1426" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1426" s="3"/>
+      <c r="J1426" s="3"/>
+      <c r="K1426" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1426" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1426" s="3" t="s">
+        <v>5537</v>
+      </c>
+      <c r="N1426" s="3"/>
+    </row>
+    <row r="1427" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1427" s="3" t="s">
+        <v>5544</v>
+      </c>
+      <c r="B1427" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C1427" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1427" s="3" t="s">
+        <v>5545</v>
+      </c>
+      <c r="E1427" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1427" s="3" t="s">
+        <v>5546</v>
+      </c>
+      <c r="G1427" s="3" t="s">
+        <v>5547</v>
+      </c>
+      <c r="H1427" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1427" s="3">
+        <v>77</v>
+      </c>
+      <c r="J1427" s="3"/>
+      <c r="K1427" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1427" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1427" s="3" t="s">
+        <v>5548</v>
+      </c>
+      <c r="N1427" s="3" t="s">
+        <v>5493</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1428" s="3" t="s">
+        <v>5549</v>
+      </c>
+      <c r="B1428" s="3"/>
+      <c r="C1428" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1428" s="3" t="s">
+        <v>5550</v>
+      </c>
+      <c r="E1428" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1428" s="3" t="s">
+        <v>2555</v>
+      </c>
+      <c r="G1428" s="3" t="s">
+        <v>5551</v>
+      </c>
+      <c r="H1428" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1428" s="3">
+        <v>31</v>
+      </c>
+      <c r="J1428" s="3"/>
+      <c r="K1428" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1428" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1428" s="3" t="s">
+        <v>5537</v>
+      </c>
+      <c r="N1428" s="3"/>
+    </row>
+    <row r="1429" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1429" s="3" t="s">
+        <v>5552</v>
+      </c>
+      <c r="B1429" s="3"/>
+      <c r="C1429" s="3">
+        <v>413</v>
+      </c>
+      <c r="D1429" s="3" t="s">
+        <v>5553</v>
+      </c>
+      <c r="E1429" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F1429" s="3" t="s">
+        <v>5554</v>
+      </c>
+      <c r="G1429" s="3" t="s">
+        <v>5555</v>
+      </c>
+      <c r="H1429" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1429" s="3">
+        <v>35</v>
+      </c>
+      <c r="J1429" s="3"/>
+      <c r="K1429" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1429" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1429" s="3" t="s">
+        <v>5556</v>
+      </c>
+      <c r="N1429" s="3"/>
+    </row>
+    <row r="1430" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1430" s="3" t="s">
+        <v>5557</v>
+      </c>
+      <c r="B1430" s="3"/>
+      <c r="C1430" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1430" s="3" t="s">
+        <v>5558</v>
+      </c>
+      <c r="E1430" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1430" s="3" t="s">
+        <v>5559</v>
+      </c>
+      <c r="G1430" s="3" t="s">
+        <v>5560</v>
+      </c>
+      <c r="H1430" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1430" s="3">
+        <v>27</v>
+      </c>
+      <c r="J1430" s="3"/>
+      <c r="K1430" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1430" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1430" s="3" t="s">
+        <v>5556</v>
+      </c>
+      <c r="N1430" s="3"/>
+    </row>
+    <row r="1431" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1431" s="3" t="s">
+        <v>5561</v>
+      </c>
+      <c r="B1431" s="3"/>
+      <c r="C1431" s="3">
+        <v>413</v>
+      </c>
+      <c r="D1431" s="3" t="s">
+        <v>5562</v>
+      </c>
+      <c r="E1431" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1431" s="3" t="s">
+        <v>2936</v>
+      </c>
+      <c r="G1431" s="3" t="s">
+        <v>5563</v>
+      </c>
+      <c r="H1431" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1431" s="3">
+        <v>17</v>
+      </c>
+      <c r="J1431" s="3"/>
+      <c r="K1431" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1431" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1431" s="3" t="s">
+        <v>5556</v>
+      </c>
+      <c r="N1431" s="3"/>
+    </row>
+    <row r="1432" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1432" s="3" t="s">
+        <v>5564</v>
+      </c>
+      <c r="B1432" s="3"/>
+      <c r="C1432" s="3">
+        <v>413</v>
+      </c>
+      <c r="D1432" s="3" t="s">
+        <v>5565</v>
+      </c>
+      <c r="E1432" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1432" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G1432" s="3" t="s">
+        <v>5566</v>
+      </c>
+      <c r="H1432" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1432" s="3">
+        <v>24</v>
+      </c>
+      <c r="J1432" s="3"/>
+      <c r="K1432" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1432" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1432" s="3" t="s">
+        <v>5556</v>
+      </c>
+      <c r="N1432" s="3"/>
+    </row>
+    <row r="1433" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1433" s="3" t="s">
+        <v>5567</v>
+      </c>
+      <c r="B1433" s="3"/>
+      <c r="C1433" s="3">
+        <v>410</v>
+      </c>
+      <c r="D1433" s="3" t="s">
+        <v>5568</v>
+      </c>
+      <c r="E1433" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1433" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="G1433" s="3" t="s">
+        <v>5569</v>
+      </c>
+      <c r="H1433" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1433" s="3"/>
+      <c r="J1433" s="3"/>
+      <c r="K1433" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1433" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1433" s="3" t="s">
+        <v>5570</v>
+      </c>
+      <c r="N1433" s="3"/>
+    </row>
+    <row r="1434" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1434" s="3" t="s">
+        <v>5571</v>
+      </c>
+      <c r="B1434" s="3"/>
+      <c r="C1434" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1434" s="3" t="s">
+        <v>5572</v>
+      </c>
+      <c r="E1434" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1434" s="3" t="s">
+        <v>5573</v>
+      </c>
+      <c r="G1434" s="3" t="s">
+        <v>5574</v>
+      </c>
+      <c r="H1434" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1434" s="3">
+        <v>57</v>
+      </c>
+      <c r="J1434" s="3"/>
+      <c r="K1434" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1434" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1434" s="3" t="s">
+        <v>5570</v>
+      </c>
+      <c r="N1434" s="3"/>
+    </row>
+    <row r="1435" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1435" s="3" t="s">
+        <v>5575</v>
+      </c>
+      <c r="B1435" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1435" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1435" s="3" t="s">
+        <v>5576</v>
+      </c>
+      <c r="E1435" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1435" s="3" t="s">
+        <v>5577</v>
+      </c>
+      <c r="G1435" s="3" t="s">
+        <v>5578</v>
+      </c>
+      <c r="H1435" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1435" s="3">
+        <v>62</v>
+      </c>
+      <c r="J1435" s="3"/>
+      <c r="K1435" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1435" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1435" s="3" t="s">
+        <v>5579</v>
+      </c>
+      <c r="N1435" s="3" t="s">
+        <v>5580</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1436" s="3" t="s">
+        <v>5581</v>
+      </c>
+      <c r="B1436" s="3"/>
+      <c r="C1436" s="3">
+        <v>410</v>
+      </c>
+      <c r="D1436" s="3" t="s">
+        <v>5582</v>
+      </c>
+      <c r="E1436" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1436" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="G1436" s="3" t="s">
+        <v>5583</v>
+      </c>
+      <c r="H1436" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1436" s="3">
+        <v>31</v>
+      </c>
+      <c r="J1436" s="3"/>
+      <c r="K1436" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1436" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1436" s="3" t="s">
+        <v>5570</v>
+      </c>
+      <c r="N1436" s="3"/>
+    </row>
+    <row r="1437" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1437" s="3" t="s">
+        <v>5584</v>
+      </c>
+      <c r="B1437" s="3"/>
+      <c r="C1437" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1437" s="3" t="s">
+        <v>5585</v>
+      </c>
+      <c r="E1437" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1437" s="3" t="s">
+        <v>5586</v>
+      </c>
+      <c r="G1437" s="3" t="s">
+        <v>5587</v>
+      </c>
+      <c r="H1437" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1437" s="3">
+        <v>28</v>
+      </c>
+      <c r="J1437" s="3"/>
+      <c r="K1437" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1437" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1437" s="3" t="s">
+        <v>5588</v>
+      </c>
+      <c r="N1437" s="3"/>
+    </row>
+    <row r="1438" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1438" s="3" t="s">
+        <v>5589</v>
+      </c>
+      <c r="B1438" s="3"/>
+      <c r="C1438" s="3">
+        <v>413</v>
+      </c>
+      <c r="D1438" s="3" t="s">
+        <v>5590</v>
+      </c>
+      <c r="E1438" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1438" s="3" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G1438" s="3" t="s">
+        <v>5591</v>
+      </c>
+      <c r="H1438" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1438" s="3">
+        <v>20</v>
+      </c>
+      <c r="J1438" s="3"/>
+      <c r="K1438" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1438" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1438" s="3" t="s">
+        <v>5570</v>
+      </c>
+      <c r="N1438" s="3"/>
+    </row>
+    <row r="1439" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1439" s="3" t="s">
+        <v>5592</v>
+      </c>
+      <c r="B1439" s="3"/>
+      <c r="C1439" s="3">
+        <v>400</v>
+      </c>
+      <c r="D1439" s="3" t="s">
+        <v>5593</v>
+      </c>
+      <c r="E1439" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1439" s="3" t="s">
+        <v>3699</v>
+      </c>
+      <c r="G1439" s="3" t="s">
+        <v>5594</v>
+      </c>
+      <c r="H1439" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1439" s="3">
+        <v>31</v>
+      </c>
+      <c r="J1439" s="3"/>
+      <c r="K1439" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1439" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1439" s="3" t="s">
+        <v>5570</v>
+      </c>
+      <c r="N1439" s="3"/>
+    </row>
+    <row r="1440" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1440" s="3" t="s">
+        <v>5595</v>
+      </c>
+      <c r="B1440" s="3"/>
+      <c r="C1440" s="3">
+        <v>413</v>
+      </c>
+      <c r="D1440" s="3" t="s">
+        <v>5596</v>
+      </c>
+      <c r="E1440" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F1440" s="3" t="s">
+        <v>2092</v>
+      </c>
+      <c r="G1440" s="3" t="s">
+        <v>5597</v>
+      </c>
+      <c r="H1440" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1440" s="3"/>
+      <c r="J1440" s="3"/>
+      <c r="K1440" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1440" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1440" s="3" t="s">
+        <v>5570</v>
+      </c>
+      <c r="N1440" s="3"/>
+    </row>
+    <row r="1441" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1441" s="3" t="s">
+        <v>5598</v>
+      </c>
+      <c r="B1441" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C1441" s="3">
+        <v>413</v>
+      </c>
+      <c r="D1441" s="3" t="s">
+        <v>5599</v>
+      </c>
+      <c r="E1441" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1441" s="3" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G1441" s="3" t="s">
+        <v>5600</v>
+      </c>
+      <c r="H1441" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1441" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1441" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1441" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1441" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1441" s="3" t="s">
+        <v>5601</v>
+      </c>
+      <c r="N1441" s="3"/>
+    </row>
+    <row r="1442" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1442" s="3" t="s">
+        <v>5602</v>
+      </c>
+      <c r="B1442" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1442" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1442" s="3" t="s">
+        <v>5603</v>
+      </c>
+      <c r="E1442" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1442" s="3" t="s">
+        <v>5604</v>
+      </c>
+      <c r="G1442" s="3" t="s">
+        <v>5605</v>
+      </c>
+      <c r="H1442" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1442" s="3">
+        <v>30</v>
+      </c>
+      <c r="J1442" s="3"/>
+      <c r="K1442" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1442" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1442" s="3" t="s">
+        <v>5606</v>
+      </c>
+      <c r="N1442" s="3"/>
+    </row>
+    <row r="1443" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1443" s="3" t="s">
+        <v>5607</v>
+      </c>
+      <c r="B1443" s="3"/>
+      <c r="C1443" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1443" s="3" t="s">
+        <v>5608</v>
+      </c>
+      <c r="E1443" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1443" s="3" t="s">
+        <v>5609</v>
+      </c>
+      <c r="G1443" s="3" t="s">
+        <v>5610</v>
+      </c>
+      <c r="H1443" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1443" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1443" s="3"/>
+      <c r="K1443" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1443" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1443" s="3" t="s">
+        <v>5606</v>
+      </c>
+      <c r="N1443" s="3"/>
+    </row>
+    <row r="1444" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1444" s="3" t="s">
+        <v>5611</v>
+      </c>
+      <c r="B1444" s="3"/>
+      <c r="C1444" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1444" s="3" t="s">
+        <v>5612</v>
+      </c>
+      <c r="E1444" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1444" s="3" t="s">
+        <v>5613</v>
+      </c>
+      <c r="G1444" s="3" t="s">
+        <v>5614</v>
+      </c>
+      <c r="H1444" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1444" s="3">
+        <v>77</v>
+      </c>
+      <c r="J1444" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1444" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1444" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1444" s="3" t="s">
+        <v>5606</v>
+      </c>
+      <c r="N1444" s="3"/>
+    </row>
+    <row r="1445" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1445" s="3" t="s">
+        <v>5615</v>
+      </c>
+      <c r="B1445" s="3"/>
+      <c r="C1445" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1445" s="3" t="s">
+        <v>5616</v>
+      </c>
+      <c r="E1445" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1445" s="3" t="s">
+        <v>5617</v>
+      </c>
+      <c r="G1445" s="3" t="s">
+        <v>5618</v>
+      </c>
+      <c r="H1445" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1445" s="3">
+        <v>78</v>
+      </c>
+      <c r="J1445" s="3"/>
+      <c r="K1445" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1445" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1445" s="3" t="s">
+        <v>5606</v>
+      </c>
+      <c r="N1445" s="3"/>
+    </row>
+    <row r="1446" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1446" s="3" t="s">
+        <v>5619</v>
+      </c>
+      <c r="B1446" s="3"/>
+      <c r="C1446" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1446" s="3" t="s">
+        <v>5620</v>
+      </c>
+      <c r="E1446" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1446" s="3" t="s">
+        <v>5621</v>
+      </c>
+      <c r="G1446" s="3" t="s">
+        <v>5622</v>
+      </c>
+      <c r="H1446" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1446" s="3">
+        <v>71</v>
+      </c>
+      <c r="J1446" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1446" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1446" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1446" s="3" t="s">
+        <v>5606</v>
+      </c>
+      <c r="N1446" s="3"/>
+    </row>
+    <row r="1447" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1447" s="3" t="s">
+        <v>5623</v>
+      </c>
+      <c r="B1447" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1447" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1447" s="3" t="s">
+        <v>5624</v>
+      </c>
+      <c r="E1447" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1447" s="3" t="s">
+        <v>5625</v>
+      </c>
+      <c r="G1447" s="3" t="s">
+        <v>5626</v>
+      </c>
+      <c r="H1447" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1447" s="3">
+        <v>71</v>
+      </c>
+      <c r="J1447" s="3"/>
+      <c r="K1447" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1447" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1447" s="3" t="s">
+        <v>5627</v>
+      </c>
+      <c r="N1447" s="3" t="s">
+        <v>5580</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1448" s="3" t="s">
+        <v>5628</v>
+      </c>
+      <c r="B1448" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C1448" s="3">
+        <v>413</v>
+      </c>
+      <c r="D1448" s="3" t="s">
+        <v>5629</v>
+      </c>
+      <c r="E1448" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1448" s="3" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G1448" s="3" t="s">
+        <v>5630</v>
+      </c>
+      <c r="H1448" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1448" s="3">
+        <v>77</v>
+      </c>
+      <c r="J1448" s="3">
+        <v>55</v>
+      </c>
+      <c r="K1448" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1448" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1448" s="3" t="s">
+        <v>5601</v>
+      </c>
+      <c r="N1448" s="3" t="s">
+        <v>5627</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1449" s="3" t="s">
+        <v>5631</v>
+      </c>
+      <c r="B1449" s="3"/>
+      <c r="C1449" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1449" s="3" t="s">
+        <v>5632</v>
+      </c>
+      <c r="E1449" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1449" s="3" t="s">
+        <v>5633</v>
+      </c>
+      <c r="G1449" s="3" t="s">
+        <v>5634</v>
+      </c>
+      <c r="H1449" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1449" s="3">
+        <v>42</v>
+      </c>
+      <c r="J1449" s="3"/>
+      <c r="K1449" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1449" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1449" s="3" t="s">
+        <v>5635</v>
+      </c>
+      <c r="N1449" s="3"/>
+    </row>
+    <row r="1450" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1450" s="3" t="s">
+        <v>5636</v>
+      </c>
+      <c r="B1450" s="3"/>
+      <c r="C1450" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1450" s="3" t="s">
+        <v>5637</v>
+      </c>
+      <c r="E1450" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1450" s="3" t="s">
+        <v>5638</v>
+      </c>
+      <c r="G1450" s="3" t="s">
+        <v>5639</v>
+      </c>
+      <c r="H1450" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1450" s="3">
+        <v>76</v>
+      </c>
+      <c r="J1450" s="3"/>
+      <c r="K1450" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1450" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1450" s="3" t="s">
+        <v>5635</v>
+      </c>
+      <c r="N1450" s="3"/>
+    </row>
+    <row r="1451" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1451" s="3" t="s">
+        <v>5640</v>
+      </c>
+      <c r="B1451" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1451" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1451" s="3" t="s">
+        <v>5641</v>
+      </c>
+      <c r="E1451" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1451" s="3" t="s">
+        <v>5642</v>
+      </c>
+      <c r="G1451" s="3" t="s">
+        <v>5643</v>
+      </c>
+      <c r="H1451" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1451" s="3">
+        <v>43</v>
+      </c>
+      <c r="J1451" s="3"/>
+      <c r="K1451" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1451" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1451" s="3" t="s">
+        <v>5588</v>
+      </c>
+      <c r="N1451" s="3"/>
+    </row>
+    <row r="1452" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1452" s="3" t="s">
+        <v>5644</v>
+      </c>
+      <c r="B1452" s="3"/>
+      <c r="C1452" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1452" s="3" t="s">
+        <v>5645</v>
+      </c>
+      <c r="E1452" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1452" s="3" t="s">
+        <v>2448</v>
+      </c>
+      <c r="G1452" s="3" t="s">
+        <v>5646</v>
+      </c>
+      <c r="H1452" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1452" s="3">
+        <v>37</v>
+      </c>
+      <c r="J1452" s="3"/>
+      <c r="K1452" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1452" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1452" s="3" t="s">
+        <v>5647</v>
+      </c>
+      <c r="N1452" s="3"/>
+    </row>
+    <row r="1453" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1453" s="3" t="s">
+        <v>5648</v>
+      </c>
+      <c r="B1453" s="3"/>
+      <c r="C1453" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1453" s="3" t="s">
+        <v>5649</v>
+      </c>
+      <c r="E1453" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1453" s="3" t="s">
+        <v>5650</v>
+      </c>
+      <c r="G1453" s="3" t="s">
+        <v>5651</v>
+      </c>
+      <c r="H1453" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1453" s="3">
+        <v>78</v>
+      </c>
+      <c r="J1453" s="3"/>
+      <c r="K1453" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1453" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1453" s="3" t="s">
+        <v>5652</v>
+      </c>
+      <c r="N1453" s="3"/>
+    </row>
+    <row r="1454" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1454" s="3" t="s">
+        <v>5653</v>
+      </c>
+      <c r="B1454" s="3"/>
+      <c r="C1454" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1454" s="3" t="s">
+        <v>5654</v>
+      </c>
+      <c r="E1454" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1454" s="3" t="s">
+        <v>5655</v>
+      </c>
+      <c r="G1454" s="3" t="s">
+        <v>5656</v>
+      </c>
+      <c r="H1454" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1454" s="3">
+        <v>33</v>
+      </c>
+      <c r="J1454" s="3"/>
+      <c r="K1454" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1454" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1454" s="3" t="s">
+        <v>5652</v>
+      </c>
+      <c r="N1454" s="3"/>
+    </row>
+    <row r="1455" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1455" s="3" t="s">
+        <v>5657</v>
+      </c>
+      <c r="B1455" s="3"/>
+      <c r="C1455" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1455" s="3" t="s">
+        <v>5658</v>
+      </c>
+      <c r="E1455" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1455" s="3" t="s">
+        <v>5659</v>
+      </c>
+      <c r="G1455" s="3" t="s">
+        <v>5660</v>
+      </c>
+      <c r="H1455" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1455" s="3">
+        <v>79</v>
+      </c>
+      <c r="J1455" s="3"/>
+      <c r="K1455" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1455" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1455" s="3" t="s">
+        <v>5588</v>
+      </c>
+      <c r="N1455" s="3"/>
+    </row>
+    <row r="1456" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1456" s="3" t="s">
+        <v>5661</v>
+      </c>
+      <c r="B1456" s="3"/>
+      <c r="C1456" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1456" s="3" t="s">
+        <v>5662</v>
+      </c>
+      <c r="E1456" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1456" s="3" t="s">
+        <v>5663</v>
+      </c>
+      <c r="G1456" s="3" t="s">
+        <v>5664</v>
+      </c>
+      <c r="H1456" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1456" s="3"/>
+      <c r="J1456" s="3"/>
+      <c r="K1456" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1456" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1456" s="3" t="s">
+        <v>5665</v>
+      </c>
+      <c r="N1456" s="3"/>
+    </row>
+    <row r="1457" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1457" s="3" t="s">
+        <v>5666</v>
+      </c>
+      <c r="B1457" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1457" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1457" s="3" t="s">
+        <v>5667</v>
+      </c>
+      <c r="E1457" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1457" s="3" t="s">
+        <v>5668</v>
+      </c>
+      <c r="G1457" s="3" t="s">
+        <v>5669</v>
+      </c>
+      <c r="H1457" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1457" s="3"/>
+      <c r="J1457" s="3"/>
+      <c r="K1457" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1457" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1457" s="3" t="s">
+        <v>5665</v>
+      </c>
+      <c r="N1457" s="3"/>
+    </row>
+    <row r="1458" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1458" s="3" t="s">
+        <v>5670</v>
+      </c>
+      <c r="B1458" s="3"/>
+      <c r="C1458" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1458" s="3" t="s">
+        <v>5671</v>
+      </c>
+      <c r="E1458" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1458" s="3" t="s">
+        <v>3939</v>
+      </c>
+      <c r="G1458" s="3" t="s">
+        <v>5672</v>
+      </c>
+      <c r="H1458" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1458" s="3"/>
+      <c r="J1458" s="3"/>
+      <c r="K1458" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1458" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1458" s="3" t="s">
+        <v>5673</v>
+      </c>
+      <c r="N1458" s="3"/>
+    </row>
+    <row r="1459" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1459" s="3" t="s">
+        <v>5674</v>
+      </c>
+      <c r="B1459" s="3"/>
+      <c r="C1459" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1459" s="3" t="s">
+        <v>5675</v>
+      </c>
+      <c r="E1459" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1459" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="G1459" s="3" t="s">
+        <v>5676</v>
+      </c>
+      <c r="H1459" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1459" s="3">
+        <v>18</v>
+      </c>
+      <c r="J1459" s="3"/>
+      <c r="K1459" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1459" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1459" s="3" t="s">
+        <v>5673</v>
+      </c>
+      <c r="N1459" s="3"/>
+    </row>
+    <row r="1460" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1460" s="3" t="s">
+        <v>5677</v>
+      </c>
+      <c r="B1460" s="3"/>
+      <c r="C1460" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1460" s="3" t="s">
+        <v>5678</v>
+      </c>
+      <c r="E1460" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1460" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G1460" s="3" t="s">
+        <v>5679</v>
+      </c>
+      <c r="H1460" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1460" s="3">
+        <v>22</v>
+      </c>
+      <c r="J1460" s="3"/>
+      <c r="K1460" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1460" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1460" s="3" t="s">
+        <v>5673</v>
+      </c>
+      <c r="N1460" s="3"/>
+    </row>
+    <row r="1461" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1461" s="3" t="s">
+        <v>5680</v>
+      </c>
+      <c r="B1461" s="3"/>
+      <c r="C1461" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1461" s="3" t="s">
+        <v>5681</v>
+      </c>
+      <c r="E1461" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1461" s="3" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G1461" s="3" t="s">
+        <v>5682</v>
+      </c>
+      <c r="H1461" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1461" s="3">
+        <v>48</v>
+      </c>
+      <c r="J1461" s="3"/>
+      <c r="K1461" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1461" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1461" s="3" t="s">
+        <v>5683</v>
+      </c>
+      <c r="N1461" s="3"/>
+    </row>
+    <row r="1462" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1462" s="3" t="s">
+        <v>5684</v>
+      </c>
+      <c r="B1462" s="3"/>
+      <c r="C1462" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1462" s="3" t="s">
+        <v>5685</v>
+      </c>
+      <c r="E1462" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1462" s="3" t="s">
+        <v>5686</v>
+      </c>
+      <c r="G1462" s="3" t="s">
+        <v>5687</v>
+      </c>
+      <c r="H1462" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1462" s="3">
+        <v>6</v>
+      </c>
+      <c r="J1462" s="3"/>
+      <c r="K1462" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1462" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1462" s="3" t="s">
+        <v>5688</v>
+      </c>
+      <c r="N1462" s="3"/>
+    </row>
+    <row r="1463" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1463" s="3" t="s">
+        <v>5689</v>
+      </c>
+      <c r="B1463" s="3"/>
+      <c r="C1463" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1463" s="3" t="s">
+        <v>5690</v>
+      </c>
+      <c r="E1463" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1463" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G1463" s="3" t="s">
+        <v>5691</v>
+      </c>
+      <c r="H1463" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1463" s="3"/>
+      <c r="J1463" s="3"/>
+      <c r="K1463" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1463" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1463" s="3" t="s">
+        <v>5688</v>
+      </c>
+      <c r="N1463" s="3"/>
+    </row>
+    <row r="1464" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1464" s="3" t="s">
+        <v>5692</v>
+      </c>
+      <c r="B1464" s="3"/>
+      <c r="C1464" s="3">
+        <v>413</v>
+      </c>
+      <c r="D1464" s="3" t="s">
+        <v>5693</v>
+      </c>
+      <c r="E1464" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1464" s="3" t="s">
+        <v>2448</v>
+      </c>
+      <c r="G1464" s="3" t="s">
+        <v>5694</v>
+      </c>
+      <c r="H1464" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1464" s="3">
+        <v>13</v>
+      </c>
+      <c r="J1464" s="3"/>
+      <c r="K1464" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1464" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1464" s="3" t="s">
+        <v>5688</v>
+      </c>
+      <c r="N1464" s="3"/>
+    </row>
+    <row r="1465" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1465" s="3" t="s">
+        <v>5695</v>
+      </c>
+      <c r="B1465" s="3"/>
+      <c r="C1465" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1465" s="3" t="s">
+        <v>5696</v>
+      </c>
+      <c r="E1465" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1465" s="3" t="s">
+        <v>3818</v>
+      </c>
+      <c r="G1465" s="3" t="s">
+        <v>5697</v>
+      </c>
+      <c r="H1465" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1465" s="3">
+        <v>35</v>
+      </c>
+      <c r="J1465" s="3"/>
+      <c r="K1465" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1465" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1465" s="3" t="s">
+        <v>5688</v>
+      </c>
+      <c r="N1465" s="3"/>
+    </row>
+    <row r="1466" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1466" s="3" t="s">
+        <v>5698</v>
+      </c>
+      <c r="B1466" s="3"/>
+      <c r="C1466" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1466" s="3" t="s">
+        <v>5699</v>
+      </c>
+      <c r="E1466" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1466" s="3" t="s">
+        <v>5700</v>
+      </c>
+      <c r="G1466" s="3" t="s">
+        <v>5701</v>
+      </c>
+      <c r="H1466" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1466" s="3">
+        <v>42</v>
+      </c>
+      <c r="J1466" s="3"/>
+      <c r="K1466" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1466" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1466" s="3" t="s">
+        <v>5688</v>
+      </c>
+      <c r="N1466" s="3"/>
+    </row>
+    <row r="1467" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1467" s="3" t="s">
+        <v>5702</v>
+      </c>
+      <c r="B1467" s="3"/>
+      <c r="C1467" s="3">
+        <v>408</v>
+      </c>
+      <c r="D1467" s="3" t="s">
+        <v>5703</v>
+      </c>
+      <c r="E1467" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1467" s="3" t="s">
+        <v>3463</v>
+      </c>
+      <c r="G1467" s="3" t="s">
+        <v>5704</v>
+      </c>
+      <c r="H1467" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1467" s="3">
+        <v>61</v>
+      </c>
+      <c r="J1467" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1467" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1467" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1467" s="3" t="s">
+        <v>5688</v>
+      </c>
+      <c r="N1467" s="3"/>
+    </row>
+    <row r="1468" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1468" s="3" t="s">
+        <v>5705</v>
+      </c>
+      <c r="B1468" s="3"/>
+      <c r="C1468" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1468" s="3" t="s">
+        <v>5706</v>
+      </c>
+      <c r="E1468" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1468" s="3" t="s">
+        <v>5707</v>
+      </c>
+      <c r="G1468" s="3" t="s">
+        <v>5708</v>
+      </c>
+      <c r="H1468" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1468" s="3">
+        <v>79</v>
+      </c>
+      <c r="J1468" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1468" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1468" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1468" s="3" t="s">
+        <v>5688</v>
+      </c>
+      <c r="N1468" s="3"/>
+    </row>
+    <row r="1469" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1469" s="3" t="s">
+        <v>5709</v>
+      </c>
+      <c r="B1469" s="3"/>
+      <c r="C1469" s="3">
+        <v>408</v>
+      </c>
+      <c r="D1469" s="3" t="s">
+        <v>5710</v>
+      </c>
+      <c r="E1469" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1469" s="3" t="s">
+        <v>2448</v>
+      </c>
+      <c r="G1469" s="3" t="s">
+        <v>5711</v>
+      </c>
+      <c r="H1469" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1469" s="3">
+        <v>19</v>
+      </c>
+      <c r="J1469" s="3"/>
+      <c r="K1469" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1469" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1469" s="3" t="s">
+        <v>5688</v>
+      </c>
+      <c r="N1469" s="3"/>
+    </row>
+    <row r="1470" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1470" s="3" t="s">
+        <v>5712</v>
+      </c>
+      <c r="B1470" s="3"/>
+      <c r="C1470" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1470" s="3" t="s">
+        <v>5713</v>
+      </c>
+      <c r="E1470" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1470" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G1470" s="3" t="s">
+        <v>5714</v>
+      </c>
+      <c r="H1470" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1470" s="3">
+        <v>35</v>
+      </c>
+      <c r="J1470" s="3"/>
+      <c r="K1470" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1470" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1470" s="3" t="s">
+        <v>5688</v>
+      </c>
+      <c r="N1470" s="3"/>
+    </row>
+    <row r="1471" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1471" s="3" t="s">
+        <v>5715</v>
+      </c>
+      <c r="B1471" s="3"/>
+      <c r="C1471" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1471" s="3" t="s">
+        <v>5716</v>
+      </c>
+      <c r="E1471" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1471" s="3" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G1471" s="3" t="s">
+        <v>5717</v>
+      </c>
+      <c r="H1471" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1471" s="3">
+        <v>47</v>
+      </c>
+      <c r="J1471" s="3"/>
+      <c r="K1471" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1471" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1471" s="3" t="s">
+        <v>5688</v>
+      </c>
+      <c r="N1471" s="3"/>
+    </row>
+    <row r="1472" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1472" s="3" t="s">
+        <v>5718</v>
+      </c>
+      <c r="B1472" s="3"/>
+      <c r="C1472" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1472" s="3" t="s">
+        <v>5719</v>
+      </c>
+      <c r="E1472" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1472" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="G1472" s="3" t="s">
+        <v>5720</v>
+      </c>
+      <c r="H1472" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1472" s="3">
+        <v>32</v>
+      </c>
+      <c r="J1472" s="3"/>
+      <c r="K1472" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1472" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1472" s="3" t="s">
+        <v>5688</v>
+      </c>
+      <c r="N1472" s="3"/>
+    </row>
+    <row r="1473" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1473" s="3" t="s">
+        <v>5721</v>
+      </c>
+      <c r="B1473" s="3"/>
+      <c r="C1473" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1473" s="3" t="s">
+        <v>5722</v>
+      </c>
+      <c r="E1473" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1473" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="G1473" s="3" t="s">
+        <v>5723</v>
+      </c>
+      <c r="H1473" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1473" s="3"/>
+      <c r="J1473" s="3"/>
+      <c r="K1473" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1473" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1473" s="3" t="s">
+        <v>5724</v>
+      </c>
+      <c r="N1473" s="3"/>
+    </row>
+    <row r="1474" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1474" s="3" t="s">
+        <v>5725</v>
+      </c>
+      <c r="B1474" s="3"/>
+      <c r="C1474" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1474" s="3" t="s">
+        <v>5726</v>
+      </c>
+      <c r="E1474" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1474" s="3" t="s">
+        <v>5727</v>
+      </c>
+      <c r="G1474" s="3" t="s">
+        <v>5728</v>
+      </c>
+      <c r="H1474" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1474" s="3">
+        <v>11</v>
+      </c>
+      <c r="J1474" s="3"/>
+      <c r="K1474" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1474" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1474" s="3" t="s">
+        <v>5729</v>
+      </c>
+      <c r="N1474" s="3"/>
+    </row>
+    <row r="1475" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1475" s="3" t="s">
+        <v>5730</v>
+      </c>
+      <c r="B1475" s="3"/>
+      <c r="C1475" s="3">
+        <v>410</v>
+      </c>
+      <c r="D1475" s="3" t="s">
+        <v>5731</v>
+      </c>
+      <c r="E1475" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1475" s="3" t="s">
+        <v>1088</v>
+      </c>
+      <c r="G1475" s="3" t="s">
+        <v>5732</v>
+      </c>
+      <c r="H1475" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1475" s="3">
+        <v>32</v>
+      </c>
+      <c r="J1475" s="3"/>
+      <c r="K1475" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1475" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1475" s="3" t="s">
+        <v>5729</v>
+      </c>
+      <c r="N1475" s="3"/>
+    </row>
+    <row r="1476" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1476" s="3" t="s">
+        <v>5733</v>
+      </c>
+      <c r="B1476" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1476" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1476" s="3" t="s">
+        <v>5734</v>
+      </c>
+      <c r="E1476" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1476" s="3" t="s">
+        <v>5735</v>
+      </c>
+      <c r="G1476" s="3" t="s">
+        <v>5736</v>
+      </c>
+      <c r="H1476" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1476" s="3">
+        <v>47</v>
+      </c>
+      <c r="J1476" s="3"/>
+      <c r="K1476" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1476" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1476" s="3" t="s">
+        <v>5729</v>
+      </c>
+      <c r="N1476" s="3" t="s">
+        <v>5724</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1477" s="3" t="s">
+        <v>5737</v>
+      </c>
+      <c r="B1477" s="3"/>
+      <c r="C1477" s="3">
+        <v>408</v>
+      </c>
+      <c r="D1477" s="3" t="s">
+        <v>5738</v>
+      </c>
+      <c r="E1477" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1477" s="3" t="s">
+        <v>1610</v>
+      </c>
+      <c r="G1477" s="3" t="s">
+        <v>5739</v>
+      </c>
+      <c r="H1477" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1477" s="3">
+        <v>24</v>
+      </c>
+      <c r="J1477" s="3"/>
+      <c r="K1477" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1477" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1477" s="3" t="s">
+        <v>5740</v>
+      </c>
+      <c r="N1477" s="3"/>
+    </row>
+    <row r="1478" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1478" s="3" t="s">
+        <v>5741</v>
+      </c>
+      <c r="B1478" s="3"/>
+      <c r="C1478" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1478" s="3" t="s">
+        <v>5742</v>
+      </c>
+      <c r="E1478" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1478" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G1478" s="3" t="s">
+        <v>5743</v>
+      </c>
+      <c r="H1478" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1478" s="3">
+        <v>31</v>
+      </c>
+      <c r="J1478" s="3"/>
+      <c r="K1478" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1478" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1478" s="3" t="s">
+        <v>5744</v>
+      </c>
+      <c r="N1478" s="3"/>
+    </row>
+    <row r="1479" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1479" s="3" t="s">
+        <v>5745</v>
+      </c>
+      <c r="B1479" s="3"/>
+      <c r="C1479" s="3">
+        <v>413</v>
+      </c>
+      <c r="D1479" s="3" t="s">
+        <v>5746</v>
+      </c>
+      <c r="E1479" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1479" s="3" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G1479" s="3" t="s">
+        <v>5747</v>
+      </c>
+      <c r="H1479" s="3"/>
+      <c r="I1479" s="3">
+        <v>14</v>
+      </c>
+      <c r="J1479" s="3"/>
+      <c r="K1479" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1479" s="3"/>
+      <c r="M1479" s="3"/>
+      <c r="N1479" s="3"/>
+    </row>
+    <row r="1480" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1480" s="3" t="s">
+        <v>5748</v>
+      </c>
+      <c r="B1480" s="3"/>
+      <c r="C1480" s="3">
+        <v>408</v>
+      </c>
+      <c r="D1480" s="3" t="s">
+        <v>5749</v>
+      </c>
+      <c r="E1480" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1480" s="3" t="s">
+        <v>2448</v>
+      </c>
+      <c r="G1480" s="3" t="s">
+        <v>5750</v>
+      </c>
+      <c r="H1480" s="3"/>
+      <c r="I1480" s="3">
+        <v>36</v>
+      </c>
+      <c r="J1480" s="3"/>
+      <c r="K1480" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1480" s="3"/>
+      <c r="M1480" s="3"/>
+      <c r="N1480" s="3"/>
+    </row>
+    <row r="1481" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1481" s="3" t="s">
+        <v>5751</v>
+      </c>
+      <c r="B1481" s="3"/>
+      <c r="C1481" s="3">
+        <v>408</v>
+      </c>
+      <c r="D1481" s="3" t="s">
+        <v>5752</v>
+      </c>
+      <c r="E1481" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1481" s="3" t="s">
+        <v>3014</v>
+      </c>
+      <c r="G1481" s="3" t="s">
+        <v>5753</v>
+      </c>
+      <c r="H1481" s="3"/>
+      <c r="I1481" s="3">
+        <v>44</v>
+      </c>
+      <c r="J1481" s="3"/>
+      <c r="K1481" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1481" s="3"/>
+      <c r="M1481" s="3"/>
+      <c r="N1481" s="3"/>
+    </row>
+    <row r="1482" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1482" s="3" t="s">
+        <v>5754</v>
+      </c>
+      <c r="B1482" s="3"/>
+      <c r="C1482" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1482" s="3" t="s">
+        <v>5755</v>
+      </c>
+      <c r="E1482" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1482" s="3" t="s">
+        <v>1707</v>
+      </c>
+      <c r="G1482" s="3" t="s">
+        <v>5756</v>
+      </c>
+      <c r="H1482" s="3"/>
+      <c r="I1482" s="3">
+        <v>23</v>
+      </c>
+      <c r="J1482" s="3"/>
+      <c r="K1482" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1482" s="3"/>
+      <c r="M1482" s="3"/>
+      <c r="N1482" s="3"/>
+    </row>
+    <row r="1483" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1483" s="3" t="s">
+        <v>5757</v>
+      </c>
+      <c r="B1483" s="3"/>
+      <c r="C1483" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1483" s="3" t="s">
+        <v>5758</v>
+      </c>
+      <c r="E1483" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1483" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G1483" s="3" t="s">
+        <v>5759</v>
+      </c>
+      <c r="H1483" s="3"/>
+      <c r="I1483" s="3">
+        <v>17</v>
+      </c>
+      <c r="J1483" s="3"/>
+      <c r="K1483" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1483" s="3"/>
+      <c r="M1483" s="3"/>
+      <c r="N1483" s="3"/>
+    </row>
+    <row r="1484" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1484" s="3" t="s">
+        <v>5760</v>
+      </c>
+      <c r="B1484" s="3"/>
+      <c r="C1484" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1484" s="3" t="s">
+        <v>5761</v>
+      </c>
+      <c r="E1484" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1484" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G1484" s="3" t="s">
+        <v>5762</v>
+      </c>
+      <c r="H1484" s="3"/>
+      <c r="I1484" s="3">
+        <v>28</v>
+      </c>
+      <c r="J1484" s="3"/>
+      <c r="K1484" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1484" s="3"/>
+      <c r="M1484" s="3"/>
+      <c r="N1484" s="3"/>
+    </row>
+    <row r="1485" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1485" s="3" t="s">
+        <v>5763</v>
+      </c>
+      <c r="B1485" s="3"/>
+      <c r="C1485" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1485" s="3" t="s">
+        <v>5764</v>
+      </c>
+      <c r="E1485" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1485" s="3" t="s">
+        <v>2555</v>
+      </c>
+      <c r="G1485" s="3" t="s">
+        <v>5765</v>
+      </c>
+      <c r="H1485" s="3"/>
+      <c r="I1485" s="3"/>
+      <c r="J1485" s="3"/>
+      <c r="K1485" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1485" s="3"/>
+      <c r="M1485" s="3"/>
+      <c r="N1485" s="3"/>
+    </row>
+    <row r="1486" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1486" s="3" t="s">
+        <v>5766</v>
+      </c>
+      <c r="B1486" s="3"/>
+      <c r="C1486" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1486" s="3" t="s">
+        <v>5767</v>
+      </c>
+      <c r="E1486" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1486" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G1486" s="3" t="s">
+        <v>5768</v>
+      </c>
+      <c r="H1486" s="3"/>
+      <c r="I1486" s="3">
+        <v>16</v>
+      </c>
+      <c r="J1486" s="3"/>
+      <c r="K1486" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1486" s="3"/>
+      <c r="M1486" s="3"/>
+      <c r="N1486" s="3"/>
+    </row>
+    <row r="1487" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1487" s="3" t="s">
+        <v>5769</v>
+      </c>
+      <c r="B1487" s="3"/>
+      <c r="C1487" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1487" s="3" t="s">
+        <v>5770</v>
+      </c>
+      <c r="E1487" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1487" s="3" t="s">
+        <v>4648</v>
+      </c>
+      <c r="G1487" s="3" t="s">
+        <v>5771</v>
+      </c>
+      <c r="H1487" s="3"/>
+      <c r="I1487" s="3">
+        <v>32</v>
+      </c>
+      <c r="J1487" s="3"/>
+      <c r="K1487" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1487" s="3"/>
+      <c r="M1487" s="3"/>
+      <c r="N1487" s="3"/>
+    </row>
+    <row r="1488" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1488" s="3" t="s">
+        <v>5772</v>
+      </c>
+      <c r="B1488" s="3"/>
+      <c r="C1488" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1488" s="3" t="s">
+        <v>5773</v>
+      </c>
+      <c r="E1488" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1488" s="3" t="s">
+        <v>3772</v>
+      </c>
+      <c r="G1488" s="3" t="s">
+        <v>5774</v>
+      </c>
+      <c r="H1488" s="3"/>
+      <c r="I1488" s="3"/>
+      <c r="J1488" s="3"/>
+      <c r="K1488" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1488" s="3"/>
+      <c r="M1488" s="3"/>
+      <c r="N1488" s="3"/>
+    </row>
+    <row r="1489" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1489" s="3" t="s">
+        <v>5775</v>
+      </c>
+      <c r="B1489" s="3"/>
+      <c r="C1489" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1489" s="3" t="s">
+        <v>5776</v>
+      </c>
+      <c r="E1489" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1489" s="3" t="s">
+        <v>5777</v>
+      </c>
+      <c r="G1489" s="3" t="s">
+        <v>5778</v>
+      </c>
+      <c r="H1489" s="3"/>
+      <c r="I1489" s="3">
+        <v>46</v>
+      </c>
+      <c r="J1489" s="3"/>
+      <c r="K1489" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1489" s="3"/>
+      <c r="M1489" s="3"/>
+      <c r="N1489" s="3"/>
+    </row>
+    <row r="1490" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1490" s="3" t="s">
+        <v>5779</v>
+      </c>
+      <c r="B1490" s="3"/>
+      <c r="C1490" s="3">
+        <v>410</v>
+      </c>
+      <c r="D1490" s="3" t="s">
+        <v>5780</v>
+      </c>
+      <c r="E1490" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1490" s="3" t="s">
+        <v>5781</v>
+      </c>
+      <c r="G1490" s="3" t="s">
+        <v>5782</v>
+      </c>
+      <c r="H1490" s="3"/>
+      <c r="I1490" s="3">
+        <v>26</v>
+      </c>
+      <c r="J1490" s="3"/>
+      <c r="K1490" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1490" s="3"/>
+      <c r="M1490" s="3"/>
+      <c r="N1490" s="3"/>
+    </row>
+    <row r="1491" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1491" s="3" t="s">
+        <v>5783</v>
+      </c>
+      <c r="B1491" s="3"/>
+      <c r="C1491" s="3">
+        <v>408</v>
+      </c>
+      <c r="D1491" s="3" t="s">
+        <v>5784</v>
+      </c>
+      <c r="E1491" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F1491" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G1491" s="3" t="s">
+        <v>5785</v>
+      </c>
+      <c r="H1491" s="3"/>
+      <c r="I1491" s="3"/>
+      <c r="J1491" s="3"/>
+      <c r="K1491" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1491" s="3"/>
+      <c r="M1491" s="3"/>
+      <c r="N1491" s="3"/>
+    </row>
+    <row r="1492" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1492" s="3" t="s">
+        <v>5786</v>
+      </c>
+      <c r="B1492" s="3"/>
+      <c r="C1492" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1492" s="3" t="s">
+        <v>5787</v>
+      </c>
+      <c r="E1492" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1492" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G1492" s="3" t="s">
+        <v>5788</v>
+      </c>
+      <c r="H1492" s="3"/>
+      <c r="I1492" s="3">
+        <v>3</v>
+      </c>
+      <c r="J1492" s="3"/>
+      <c r="K1492" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1492" s="3"/>
+      <c r="M1492" s="3"/>
+      <c r="N1492" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Home-Motors \"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3CCAB47-9EE2-4C75-92BD-0AC52C014C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D64175F1-DB2C-42DF-AFBE-AAB093BD125E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13691" uniqueCount="5789">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14810" uniqueCount="6270">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -10258,18 +10258,18 @@
     <t>05/05/26 09:42 CDT</t>
   </si>
   <si>
+    <t>'1211652737482260480</t>
+  </si>
+  <si>
+    <t>31.458058, -100.442999</t>
+  </si>
+  <si>
     <t>'1211652858001391616</t>
   </si>
   <si>
-    <t>31.458058, -100.442999</t>
-  </si>
-  <si>
     <t>05/06/26 09:15 CDT</t>
   </si>
   <si>
-    <t>'1211652737482260480</t>
-  </si>
-  <si>
     <t>05/05/26 10:17 CDT</t>
   </si>
   <si>
@@ -16294,21 +16294,21 @@
     <t>06/15/26 07:03 CDT</t>
   </si>
   <si>
+    <t>'1226470791395311616</t>
+  </si>
+  <si>
+    <t>31.511931, -100.370260</t>
+  </si>
+  <si>
+    <t>06/16/26 08:12 CDT</t>
+  </si>
+  <si>
     <t>'1226470713880379392</t>
   </si>
   <si>
-    <t>31.511931, -100.370260</t>
-  </si>
-  <si>
     <t>06/16/26 08:32 CDT</t>
   </si>
   <si>
-    <t>'1226470791395311616</t>
-  </si>
-  <si>
-    <t>06/16/26 08:12 CDT</t>
-  </si>
-  <si>
     <t>06/15/26 07:08 CDT</t>
   </si>
   <si>
@@ -17266,6 +17266,9 @@
     <t>31.441734, -100.440137</t>
   </si>
   <si>
+    <t>06/21/26 18:20 CDT</t>
+  </si>
+  <si>
     <t>06/19/26 12:14 CDT</t>
   </si>
   <si>
@@ -17359,6 +17362,9 @@
     <t>31.370817, -100.297439</t>
   </si>
   <si>
+    <t>06/21/26 18:19 CDT</t>
+  </si>
+  <si>
     <t>06/20/26 08:49 CDT</t>
   </si>
   <si>
@@ -17387,6 +17393,1443 @@
   </si>
   <si>
     <t>31.444952, -100.441859</t>
+  </si>
+  <si>
+    <t>06/21/26 11:49 CDT</t>
+  </si>
+  <si>
+    <t>'1228716918450585600</t>
+  </si>
+  <si>
+    <t>31.388314, -100.420578</t>
+  </si>
+  <si>
+    <t>06/21/26 12:28 CDT</t>
+  </si>
+  <si>
+    <t>'1228726846376542208</t>
+  </si>
+  <si>
+    <t>7mi SE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.374551, -100.362777</t>
+  </si>
+  <si>
+    <t>06/21/26 13:00 CDT</t>
+  </si>
+  <si>
+    <t>'1228734821849792512</t>
+  </si>
+  <si>
+    <t>6mi SE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.386274, -100.373686</t>
+  </si>
+  <si>
+    <t>06/21/26 14:33 CDT</t>
+  </si>
+  <si>
+    <t>'1228758313177612288</t>
+  </si>
+  <si>
+    <t>8.7mi SE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.374546, -100.326728</t>
+  </si>
+  <si>
+    <t>06/22/26 09:53 CDT</t>
+  </si>
+  <si>
+    <t>06/21/26 17:43 CDT</t>
+  </si>
+  <si>
+    <t>'1228806022232178688</t>
+  </si>
+  <si>
+    <t>31.596737, -100.179023</t>
+  </si>
+  <si>
+    <t>06/21/26 17:55 CDT</t>
+  </si>
+  <si>
+    <t>'1228809094169788416</t>
+  </si>
+  <si>
+    <t>31.490281, -100.379237</t>
+  </si>
+  <si>
+    <t>06/21/26 20:19 CDT</t>
+  </si>
+  <si>
+    <t>'1228845352820572160</t>
+  </si>
+  <si>
+    <t>31.443265, -100.375531</t>
+  </si>
+  <si>
+    <t>06/22/26 09:51 CDT</t>
+  </si>
+  <si>
+    <t>06/22/26 11:56 CDT</t>
+  </si>
+  <si>
+    <t>06/22/26 08:36 CDT</t>
+  </si>
+  <si>
+    <t>'1229030855209549824</t>
+  </si>
+  <si>
+    <t>31.430897, -100.431289</t>
+  </si>
+  <si>
+    <t>06/23/26 11:18 CDT</t>
+  </si>
+  <si>
+    <t>06/22/26 13:24 CDT</t>
+  </si>
+  <si>
+    <t>'1229103294518034432</t>
+  </si>
+  <si>
+    <t>15.2mi NW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.598163, -100.632159</t>
+  </si>
+  <si>
+    <t>06/22/26 14:25 CDT</t>
+  </si>
+  <si>
+    <t>'1229118581040644096</t>
+  </si>
+  <si>
+    <t>31.396324, -100.433661</t>
+  </si>
+  <si>
+    <t>06/22/26 14:45 CDT</t>
+  </si>
+  <si>
+    <t>06/22/26 14:35 CDT</t>
+  </si>
+  <si>
+    <t>'1229121170671042560</t>
+  </si>
+  <si>
+    <t>9.5mi NW of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.550991, -100.549773</t>
+  </si>
+  <si>
+    <t>'1229123656370782208</t>
+  </si>
+  <si>
+    <t>31.458717, -100.465322</t>
+  </si>
+  <si>
+    <t>06/23/26 09:59 CDT</t>
+  </si>
+  <si>
+    <t>06/22/26 15:04 CDT</t>
+  </si>
+  <si>
+    <t>'1229128470026682369</t>
+  </si>
+  <si>
+    <t>31.467584, -100.447541</t>
+  </si>
+  <si>
+    <t>06/22/26 17:14 CDT</t>
+  </si>
+  <si>
+    <t>'1229161305060048896</t>
+  </si>
+  <si>
+    <t>31.414001, -100.466944</t>
+  </si>
+  <si>
+    <t>06/22/26 17:35 CDT</t>
+  </si>
+  <si>
+    <t>'1229166576486481920</t>
+  </si>
+  <si>
+    <t>31.414297, -100.438837</t>
+  </si>
+  <si>
+    <t>06/23/26 09:58 CDT</t>
+  </si>
+  <si>
+    <t>06/23/26 03:42 CDT</t>
+  </si>
+  <si>
+    <t>'1229319222396616704</t>
+  </si>
+  <si>
+    <t>31.439718, -100.442280</t>
+  </si>
+  <si>
+    <t>06/23/26 06:44 CDT</t>
+  </si>
+  <si>
+    <t>'1229365006387281920</t>
+  </si>
+  <si>
+    <t>31.420850, -100.440973</t>
+  </si>
+  <si>
+    <t>06/23/26 07:08 CDT</t>
+  </si>
+  <si>
+    <t>'1229371082373496832</t>
+  </si>
+  <si>
+    <t>17.2mi E of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.345376, -100.182378</t>
+  </si>
+  <si>
+    <t>06/23/26 18:52 CDT</t>
+  </si>
+  <si>
+    <t>06/23/26 09:21 CDT</t>
+  </si>
+  <si>
+    <t>'1229404627007602688</t>
+  </si>
+  <si>
+    <t>20.8mi NW of Lampasas TX</t>
+  </si>
+  <si>
+    <t>31.224628, -98.479652</t>
+  </si>
+  <si>
+    <t>06/23/26 09:47 CDT</t>
+  </si>
+  <si>
+    <t>'1229411212698222592</t>
+  </si>
+  <si>
+    <t>5.1mi NE of Lampasas TX</t>
+  </si>
+  <si>
+    <t>31.098416, -98.105240</t>
+  </si>
+  <si>
+    <t>06/23/26 09:51 CDT</t>
+  </si>
+  <si>
+    <t>'1229412033934557184</t>
+  </si>
+  <si>
+    <t>31.406992, -100.446352</t>
+  </si>
+  <si>
+    <t>06/23/26 09:53 CDT</t>
+  </si>
+  <si>
+    <t>'1229412543492161536</t>
+  </si>
+  <si>
+    <t>31.417485, -100.472570</t>
+  </si>
+  <si>
+    <t>06/23/26 10:12 CDT</t>
+  </si>
+  <si>
+    <t>'1229417510131105792</t>
+  </si>
+  <si>
+    <t>2.5mi SE of Fort Hood TX</t>
+  </si>
+  <si>
+    <t>31.110909, -97.752281</t>
+  </si>
+  <si>
+    <t>06/23/26 10:13 CDT</t>
+  </si>
+  <si>
+    <t>'1229417773306904576</t>
+  </si>
+  <si>
+    <t>1.6mi N of Killeen TX</t>
+  </si>
+  <si>
+    <t>31.097884, -97.738645</t>
+  </si>
+  <si>
+    <t>06/23/26 10:15 CDT</t>
+  </si>
+  <si>
+    <t>'1229418023346143232</t>
+  </si>
+  <si>
+    <t>1.2mi NE of Killeen TX</t>
+  </si>
+  <si>
+    <t>31.090646, -97.719515</t>
+  </si>
+  <si>
+    <t>06/23/26 10:16 CDT</t>
+  </si>
+  <si>
+    <t>'1229418279311933440</t>
+  </si>
+  <si>
+    <t>1.7mi E of Killeen TX</t>
+  </si>
+  <si>
+    <t>31.082059, -97.702123</t>
+  </si>
+  <si>
+    <t>06/23/26 10:27 CDT</t>
+  </si>
+  <si>
+    <t>'1229421174602235904</t>
+  </si>
+  <si>
+    <t>0.3mi SW of Belton TX</t>
+  </si>
+  <si>
+    <t>31.049323, -97.483077</t>
+  </si>
+  <si>
+    <t>06/23/26 18:51 CDT</t>
+  </si>
+  <si>
+    <t>06/23/26 10:41 CDT</t>
+  </si>
+  <si>
+    <t>'1229424620654985216</t>
+  </si>
+  <si>
+    <t>31.423811, -100.418287</t>
+  </si>
+  <si>
+    <t>06/23/26 10:42 CDT</t>
+  </si>
+  <si>
+    <t>'1229424893867753472</t>
+  </si>
+  <si>
+    <t>4.5mi E of Temple TX</t>
+  </si>
+  <si>
+    <t>31.090527, -97.315224</t>
+  </si>
+  <si>
+    <t>06/23/26 10:44 CDT</t>
+  </si>
+  <si>
+    <t>'1229425536527400960</t>
+  </si>
+  <si>
+    <t>7.1mi E of Temple TX</t>
+  </si>
+  <si>
+    <t>31.074489, -97.274710</t>
+  </si>
+  <si>
+    <t>06/23/26 10:49 CDT</t>
+  </si>
+  <si>
+    <t>'1229426792956329984</t>
+  </si>
+  <si>
+    <t>13mi E of Temple TX</t>
+  </si>
+  <si>
+    <t>31.048887, -97.179352</t>
+  </si>
+  <si>
+    <t>06/23/26 10:54 CDT</t>
+  </si>
+  <si>
+    <t>'1229427964903587840</t>
+  </si>
+  <si>
+    <t>31.526258, -100.373129</t>
+  </si>
+  <si>
+    <t>06/23/26 10:59 CDT</t>
+  </si>
+  <si>
+    <t>'1229429217477951488</t>
+  </si>
+  <si>
+    <t>8.4mi NW of Cameron TX</t>
+  </si>
+  <si>
+    <t>30.948826, -97.073523</t>
+  </si>
+  <si>
+    <t>06/23/26 11:00 CDT</t>
+  </si>
+  <si>
+    <t>'1229429480175599617</t>
+  </si>
+  <si>
+    <t>7.3mi NW of Cameron TX</t>
+  </si>
+  <si>
+    <t>30.943136, -97.053882</t>
+  </si>
+  <si>
+    <t>06/23/26 11:07 CDT</t>
+  </si>
+  <si>
+    <t>'1229431247160377344</t>
+  </si>
+  <si>
+    <t>14.4mi N of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.650112, -100.428710</t>
+  </si>
+  <si>
+    <t>06/23/26 11:08 CDT</t>
+  </si>
+  <si>
+    <t>'1229431375665463296</t>
+  </si>
+  <si>
+    <t>31.439610, -100.441630</t>
+  </si>
+  <si>
+    <t>06/23/26 11:10 CDT</t>
+  </si>
+  <si>
+    <t>'1229432107441487872</t>
+  </si>
+  <si>
+    <t>5.9mi NE of Cameron TX</t>
+  </si>
+  <si>
+    <t>30.903801, -96.890003</t>
+  </si>
+  <si>
+    <t>06/23/26 11:27 CDT</t>
+  </si>
+  <si>
+    <t>'1229436211270156288</t>
+  </si>
+  <si>
+    <t>33.9mi N of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.929786, -100.508090</t>
+  </si>
+  <si>
+    <t>06/23/26 18:50 CDT</t>
+  </si>
+  <si>
+    <t>06/23/26 11:37 CDT</t>
+  </si>
+  <si>
+    <t>'1229438823184891904</t>
+  </si>
+  <si>
+    <t>30.9mi SW of Sweetwater TX</t>
+  </si>
+  <si>
+    <t>32.060531, -100.621945</t>
+  </si>
+  <si>
+    <t>06/23/26 11:47 CDT</t>
+  </si>
+  <si>
+    <t>'1229441421858209792</t>
+  </si>
+  <si>
+    <t>28.8mi SW of Sweetwater TX</t>
+  </si>
+  <si>
+    <t>32.176489, -100.759761</t>
+  </si>
+  <si>
+    <t>06/23/26 12:01 CDT</t>
+  </si>
+  <si>
+    <t>'1229444913654038528</t>
+  </si>
+  <si>
+    <t>22.8mi S of Snyder TX</t>
+  </si>
+  <si>
+    <t>32.389207, -100.838618</t>
+  </si>
+  <si>
+    <t>06/23/26 12:08 CDT</t>
+  </si>
+  <si>
+    <t>'1229446610212257792</t>
+  </si>
+  <si>
+    <t>21.9mi S of Snyder TX</t>
+  </si>
+  <si>
+    <t>32.396069, -100.900093</t>
+  </si>
+  <si>
+    <t>06/23/26 12:09 CDT</t>
+  </si>
+  <si>
+    <t>'1229447217048354816</t>
+  </si>
+  <si>
+    <t>22.1mi S of Snyder TX</t>
+  </si>
+  <si>
+    <t>32.392931, -100.918594</t>
+  </si>
+  <si>
+    <t>06/23/26 12:54 CDT</t>
+  </si>
+  <si>
+    <t>'1229458063216508928</t>
+  </si>
+  <si>
+    <t>22.4mi S of Snyder TX</t>
+  </si>
+  <si>
+    <t>32.389929, -100.926702</t>
+  </si>
+  <si>
+    <t>06/23/26 13:07 CDT</t>
+  </si>
+  <si>
+    <t>'1229461560368463872</t>
+  </si>
+  <si>
+    <t>26.2mi SW of Sweetwater TX</t>
+  </si>
+  <si>
+    <t>32.316413, -100.819982</t>
+  </si>
+  <si>
+    <t>06/23/26 13:08 CDT</t>
+  </si>
+  <si>
+    <t>'1229461874693799936</t>
+  </si>
+  <si>
+    <t>26.3mi SW of Sweetwater TX</t>
+  </si>
+  <si>
+    <t>32.309542, -100.818169</t>
+  </si>
+  <si>
+    <t>06/23/26 18:49 CDT</t>
+  </si>
+  <si>
+    <t>06/23/26 13:10 CDT</t>
+  </si>
+  <si>
+    <t>'1229462240441303040</t>
+  </si>
+  <si>
+    <t>26.9mi SW of Sweetwater TX</t>
+  </si>
+  <si>
+    <t>32.273407, -100.807366</t>
+  </si>
+  <si>
+    <t>06/23/26 13:18 CDT</t>
+  </si>
+  <si>
+    <t>'1229464806671679488</t>
+  </si>
+  <si>
+    <t>29.8mi SW of Sweetwater TX</t>
+  </si>
+  <si>
+    <t>32.142671, -100.743191</t>
+  </si>
+  <si>
+    <t>06/23/26 13:29 CDT</t>
+  </si>
+  <si>
+    <t>'1229467154919882752</t>
+  </si>
+  <si>
+    <t>31.6mi S of Sweetwater TX</t>
+  </si>
+  <si>
+    <t>32.033087, -100.572348</t>
+  </si>
+  <si>
+    <t>06/23/26 13:41 CDT</t>
+  </si>
+  <si>
+    <t>'1229470016794165248</t>
+  </si>
+  <si>
+    <t>30.1mi N of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.877830, -100.478522</t>
+  </si>
+  <si>
+    <t>06/23/26 13:53 CDT</t>
+  </si>
+  <si>
+    <t>'1229473107736166400</t>
+  </si>
+  <si>
+    <t>15.9mi N of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.672725, -100.435808</t>
+  </si>
+  <si>
+    <t>06/23/26 14:04 CDT</t>
+  </si>
+  <si>
+    <t>'1229475763561070592</t>
+  </si>
+  <si>
+    <t>31.526351, -100.411886</t>
+  </si>
+  <si>
+    <t>06/23/26 14:10 CDT</t>
+  </si>
+  <si>
+    <t>'1229477388136644608</t>
+  </si>
+  <si>
+    <t>31.476993, -100.387310</t>
+  </si>
+  <si>
+    <t>06/23/26 14:18 CDT</t>
+  </si>
+  <si>
+    <t>'1229479244325879808</t>
+  </si>
+  <si>
+    <t>31.423744, -100.406799</t>
+  </si>
+  <si>
+    <t>06/23/26 18:48 CDT</t>
+  </si>
+  <si>
+    <t>06/23/26 14:30 CDT</t>
+  </si>
+  <si>
+    <t>'1229482450200199168</t>
+  </si>
+  <si>
+    <t>12.1mi SW of Mexia TX</t>
+  </si>
+  <si>
+    <t>31.526536, -96.579441</t>
+  </si>
+  <si>
+    <t>06/23/26 18:44 CDT</t>
+  </si>
+  <si>
+    <t>06/23/26 18:47 CDT</t>
+  </si>
+  <si>
+    <t>06/23/26 14:39 CDT</t>
+  </si>
+  <si>
+    <t>'1229484554457350144</t>
+  </si>
+  <si>
+    <t>31.421888, -100.423818</t>
+  </si>
+  <si>
+    <t>06/23/26 14:47 CDT</t>
+  </si>
+  <si>
+    <t>'1229486628481957888</t>
+  </si>
+  <si>
+    <t>31.396300, -100.433690</t>
+  </si>
+  <si>
+    <t>06/23/26 15:00 CDT</t>
+  </si>
+  <si>
+    <t>'1229489819198062592</t>
+  </si>
+  <si>
+    <t>5.4mi N of Robinson TX</t>
+  </si>
+  <si>
+    <t>31.522867, -97.085544</t>
+  </si>
+  <si>
+    <t>06/23/26 15:01 CDT</t>
+  </si>
+  <si>
+    <t>'1229490220488097792</t>
+  </si>
+  <si>
+    <t>31.416943, -100.471891</t>
+  </si>
+  <si>
+    <t>06/23/26 18:43 CDT</t>
+  </si>
+  <si>
+    <t>06/23/26 15:30 CDT</t>
+  </si>
+  <si>
+    <t>'1229497511983611904</t>
+  </si>
+  <si>
+    <t>7.5mi E of Gatesville TX</t>
+  </si>
+  <si>
+    <t>31.422874, -97.606614</t>
+  </si>
+  <si>
+    <t>06/23/26 15:31 CDT</t>
+  </si>
+  <si>
+    <t>'1229497772038848512</t>
+  </si>
+  <si>
+    <t>6.3mi E of Gatesville TX</t>
+  </si>
+  <si>
+    <t>31.424735, -97.628128</t>
+  </si>
+  <si>
+    <t>06/23/26 18:42 CDT</t>
+  </si>
+  <si>
+    <t>06/23/26 16:04 CDT</t>
+  </si>
+  <si>
+    <t>'1229505978349813760</t>
+  </si>
+  <si>
+    <t>31.443145, -100.460755</t>
+  </si>
+  <si>
+    <t>06/23/26 18:41 CDT</t>
+  </si>
+  <si>
+    <t>06/23/26 16:54 CDT</t>
+  </si>
+  <si>
+    <t>'1229518481674895360</t>
+  </si>
+  <si>
+    <t>31.442106, -100.498271</t>
+  </si>
+  <si>
+    <t>06/23/26 18:40 CDT</t>
+  </si>
+  <si>
+    <t>'1229518641817616384</t>
+  </si>
+  <si>
+    <t>2.7mi W of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.444696, -100.495769</t>
+  </si>
+  <si>
+    <t>06/23/26 18:33 CDT</t>
+  </si>
+  <si>
+    <t>06/23/26 17:58 CDT</t>
+  </si>
+  <si>
+    <t>'1229534656811139072</t>
+  </si>
+  <si>
+    <t>31.527280, -100.486104</t>
+  </si>
+  <si>
+    <t>06/23/26 18:32 CDT</t>
+  </si>
+  <si>
+    <t>06/23/26 18:13 CDT</t>
+  </si>
+  <si>
+    <t>'1229538560479232000</t>
+  </si>
+  <si>
+    <t>31.424212, -100.422755</t>
+  </si>
+  <si>
+    <t>06/24/26 10:00 CDT</t>
+  </si>
+  <si>
+    <t>'1229776716570984448</t>
+  </si>
+  <si>
+    <t>31.487483, -100.381119</t>
+  </si>
+  <si>
+    <t>06/25/26 08:11 CDT</t>
+  </si>
+  <si>
+    <t>06/24/26 11:05 CDT</t>
+  </si>
+  <si>
+    <t>'1229793168770367488</t>
+  </si>
+  <si>
+    <t>4.8mi NE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.476523, -100.380242</t>
+  </si>
+  <si>
+    <t>06/25/26 08:29 CDT</t>
+  </si>
+  <si>
+    <t>06/24/26 11:14 CDT</t>
+  </si>
+  <si>
+    <t>'1229795453776855040</t>
+  </si>
+  <si>
+    <t>16.7mi N of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.684014, -100.438986</t>
+  </si>
+  <si>
+    <t>06/25/26 08:06 CDT</t>
+  </si>
+  <si>
+    <t>06/24/26 12:07 CDT</t>
+  </si>
+  <si>
+    <t>'1229808829198401536</t>
+  </si>
+  <si>
+    <t>31.516893, -100.370279</t>
+  </si>
+  <si>
+    <t>06/25/26 08:09 CDT</t>
+  </si>
+  <si>
+    <t>06/24/26 14:32 CDT</t>
+  </si>
+  <si>
+    <t>'1229845262990737408</t>
+  </si>
+  <si>
+    <t>31.574876, -100.238804</t>
+  </si>
+  <si>
+    <t>06/24/26 15:24 CDT</t>
+  </si>
+  <si>
+    <t>'1229858246639124480</t>
+  </si>
+  <si>
+    <t>31.408301, -100.450150</t>
+  </si>
+  <si>
+    <t>06/24/26 16:01 CDT</t>
+  </si>
+  <si>
+    <t>'1229867645042589696</t>
+  </si>
+  <si>
+    <t>31.443379, -100.465361</t>
+  </si>
+  <si>
+    <t>06/25/26 07:55 CDT</t>
+  </si>
+  <si>
+    <t>06/24/26 16:06 CDT</t>
+  </si>
+  <si>
+    <t>'1229868906143973376</t>
+  </si>
+  <si>
+    <t>31.431136, -100.431569</t>
+  </si>
+  <si>
+    <t>06/24/26 16:07 CDT</t>
+  </si>
+  <si>
+    <t>'1229869109873901568</t>
+  </si>
+  <si>
+    <t>31.424351, -100.423454</t>
+  </si>
+  <si>
+    <t>06/25/26 08:08 CDT</t>
+  </si>
+  <si>
+    <t>06/24/26 16:18 CDT</t>
+  </si>
+  <si>
+    <t>'1229871930811777024</t>
+  </si>
+  <si>
+    <t>31.443292, -100.462739</t>
+  </si>
+  <si>
+    <t>06/25/26 07:54 CDT</t>
+  </si>
+  <si>
+    <t>06/24/26 19:56 CDT</t>
+  </si>
+  <si>
+    <t>'1229926622757552128</t>
+  </si>
+  <si>
+    <t>31.500418, -100.371566</t>
+  </si>
+  <si>
+    <t>06/24/26 19:57 CDT</t>
+  </si>
+  <si>
+    <t>'1229926978883321856</t>
+  </si>
+  <si>
+    <t>31.482434, -100.385129</t>
+  </si>
+  <si>
+    <t>06/25/26 08:05 CDT</t>
+  </si>
+  <si>
+    <t>06/24/26 20:44 CDT</t>
+  </si>
+  <si>
+    <t>'1229938806820601856</t>
+  </si>
+  <si>
+    <t>31.396278, -100.433470</t>
+  </si>
+  <si>
+    <t>06/25/26 07:53 CDT</t>
+  </si>
+  <si>
+    <t>06/24/26 20:52 CDT</t>
+  </si>
+  <si>
+    <t>'1229940757201321984</t>
+  </si>
+  <si>
+    <t>23.5mi NE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.621021, -100.111089</t>
+  </si>
+  <si>
+    <t>06/25/26 08:03 CDT</t>
+  </si>
+  <si>
+    <t>06/25/26 10:14 CDT</t>
+  </si>
+  <si>
+    <t>'1230142633255534592</t>
+  </si>
+  <si>
+    <t>31.418117, -100.425308</t>
+  </si>
+  <si>
+    <t>06/25/26 16:28 CDT</t>
+  </si>
+  <si>
+    <t>06/25/26 10:28 CDT</t>
+  </si>
+  <si>
+    <t>'1230146205368090624</t>
+  </si>
+  <si>
+    <t>31.442465, -100.434616</t>
+  </si>
+  <si>
+    <t>06/25/26 17:46 CDT</t>
+  </si>
+  <si>
+    <t>06/25/26 12:17 CDT</t>
+  </si>
+  <si>
+    <t>'1230173605602689024</t>
+  </si>
+  <si>
+    <t>45.8mi SW of Brady TX</t>
+  </si>
+  <si>
+    <t>30.569274, -99.776974</t>
+  </si>
+  <si>
+    <t>06/25/26 16:26 CDT</t>
+  </si>
+  <si>
+    <t>06/25/26 13:05 CDT</t>
+  </si>
+  <si>
+    <t>'1230185798020792320</t>
+  </si>
+  <si>
+    <t>46.2mi NW of Kerrville TX</t>
+  </si>
+  <si>
+    <t>30.463920, -99.730455</t>
+  </si>
+  <si>
+    <t>06/25/26 13:07 CDT</t>
+  </si>
+  <si>
+    <t>'1230186287735144449</t>
+  </si>
+  <si>
+    <t>30.434783, -99.709014</t>
+  </si>
+  <si>
+    <t>06/25/26 15:33 CDT</t>
+  </si>
+  <si>
+    <t>06/25/26 13:38 CDT</t>
+  </si>
+  <si>
+    <t>'1230194079590154240</t>
+  </si>
+  <si>
+    <t>6.8mi NW of Kerrville TX</t>
+  </si>
+  <si>
+    <t>30.116683, -99.201637</t>
+  </si>
+  <si>
+    <t>06/25/26 17:44 CDT</t>
+  </si>
+  <si>
+    <t>06/25/26 13:41 CDT</t>
+  </si>
+  <si>
+    <t>'1230194688955416576</t>
+  </si>
+  <si>
+    <t>4.1mi NW of Kerrville TX</t>
+  </si>
+  <si>
+    <t>30.093082, -99.162718</t>
+  </si>
+  <si>
+    <t>06/25/26 15:32 CDT</t>
+  </si>
+  <si>
+    <t>06/25/26 13:57 CDT</t>
+  </si>
+  <si>
+    <t>'1230198809250922496</t>
+  </si>
+  <si>
+    <t>11.1mi E of Kerrville TX</t>
+  </si>
+  <si>
+    <t>30.007717, -98.950624</t>
+  </si>
+  <si>
+    <t>06/25/26 17:42 CDT</t>
+  </si>
+  <si>
+    <t>06/25/26 14:27 CDT</t>
+  </si>
+  <si>
+    <t>'1230206308037328896</t>
+  </si>
+  <si>
+    <t>31.424065, -100.423051</t>
+  </si>
+  <si>
+    <t>06/25/26 15:31 CDT</t>
+  </si>
+  <si>
+    <t>06/25/26 14:54 CDT</t>
+  </si>
+  <si>
+    <t>'1230213135034646528</t>
+  </si>
+  <si>
+    <t>31.403808, -100.241278</t>
+  </si>
+  <si>
+    <t>06/25/26 14:56 CDT</t>
+  </si>
+  <si>
+    <t>'1230213606545719296</t>
+  </si>
+  <si>
+    <t>13.9mi E of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.402639, -100.219669</t>
+  </si>
+  <si>
+    <t>06/25/26 15:13 CDT</t>
+  </si>
+  <si>
+    <t>'1230217885553688576</t>
+  </si>
+  <si>
+    <t>31.443317, -100.464666</t>
+  </si>
+  <si>
+    <t>06/25/26 15:40 CDT</t>
+  </si>
+  <si>
+    <t>'1230224691206193152</t>
+  </si>
+  <si>
+    <t>12.1mi E of Kerrville TX</t>
+  </si>
+  <si>
+    <t>29.996590, -98.936384</t>
+  </si>
+  <si>
+    <t>06/25/26 17:41 CDT</t>
+  </si>
+  <si>
+    <t>06/25/26 17:05 CDT</t>
+  </si>
+  <si>
+    <t>'1230246073226919936</t>
+  </si>
+  <si>
+    <t>31.388819, -100.424678</t>
+  </si>
+  <si>
+    <t>06/25/26 17:19 CDT</t>
+  </si>
+  <si>
+    <t>'1230249571750412288</t>
+  </si>
+  <si>
+    <t>31.176064, -99.836593</t>
+  </si>
+  <si>
+    <t>06/25/26 18:57 CDT</t>
+  </si>
+  <si>
+    <t>'1230274348888260608</t>
+  </si>
+  <si>
+    <t>31.447393, -100.413364</t>
+  </si>
+  <si>
+    <t>06/26/26 08:04 CDT</t>
+  </si>
+  <si>
+    <t>'1230472423426654208</t>
+  </si>
+  <si>
+    <t>31.424487, -100.423216</t>
+  </si>
+  <si>
+    <t>06/26/26 09:05 CDT</t>
+  </si>
+  <si>
+    <t>'1230487770078806016</t>
+  </si>
+  <si>
+    <t>11.7mi N of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.610568, -100.429170</t>
+  </si>
+  <si>
+    <t>06/26/26 09:12 CDT</t>
+  </si>
+  <si>
+    <t>'1230489423611854848</t>
+  </si>
+  <si>
+    <t>31.480057, -100.456452</t>
+  </si>
+  <si>
+    <t>06/26/26 09:59 CDT</t>
+  </si>
+  <si>
+    <t>'1230501331735838720</t>
+  </si>
+  <si>
+    <t>29.1mi SW of Sweetwater TX</t>
+  </si>
+  <si>
+    <t>32.164702, -100.753948</t>
+  </si>
+  <si>
+    <t>06/26/26 10:00 CDT</t>
+  </si>
+  <si>
+    <t>'1230501640751185920</t>
+  </si>
+  <si>
+    <t>28.6mi SW of Sweetwater TX</t>
+  </si>
+  <si>
+    <t>32.183214, -100.763052</t>
+  </si>
+  <si>
+    <t>06/26/26 10:22 CDT</t>
+  </si>
+  <si>
+    <t>'1230507034999422976</t>
+  </si>
+  <si>
+    <t>31.392548, -100.431673</t>
+  </si>
+  <si>
+    <t>06/26/26 10:29 CDT</t>
+  </si>
+  <si>
+    <t>'1230508892052684800</t>
+  </si>
+  <si>
+    <t>7.6mi SE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.376410, -100.347477</t>
+  </si>
+  <si>
+    <t>06/26/26 10:31 CDT</t>
+  </si>
+  <si>
+    <t>'1230509428298645505</t>
+  </si>
+  <si>
+    <t>9.9mi SE of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.369741, -100.305607</t>
+  </si>
+  <si>
+    <t>06/26/26 11:03 CDT</t>
+  </si>
+  <si>
+    <t>'1230517302211018752</t>
+  </si>
+  <si>
+    <t>31.424393, -100.423194</t>
+  </si>
+  <si>
+    <t>06/26/26 13:08 CDT</t>
+  </si>
+  <si>
+    <t>'1230548874612080640</t>
+  </si>
+  <si>
+    <t>31.465732, -100.413343</t>
+  </si>
+  <si>
+    <t>06/26/26 13:23 CDT</t>
+  </si>
+  <si>
+    <t>'1230552647224950784</t>
+  </si>
+  <si>
+    <t>31.398150, -100.432983</t>
+  </si>
+  <si>
+    <t>06/26/26 16:12 CDT</t>
+  </si>
+  <si>
+    <t>'1230595285198209024</t>
+  </si>
+  <si>
+    <t>31.442517, -100.413302</t>
+  </si>
+  <si>
+    <t>06/26/26 17:34 CDT</t>
+  </si>
+  <si>
+    <t>'1230615802684801024</t>
+  </si>
+  <si>
+    <t>31.442404, -100.413566</t>
+  </si>
+  <si>
+    <t>06/26/26 18:16 CDT</t>
+  </si>
+  <si>
+    <t>'1230626327103700992</t>
+  </si>
+  <si>
+    <t>31.432130, -100.432258</t>
+  </si>
+  <si>
+    <t>06/26/26 18:25 CDT</t>
+  </si>
+  <si>
+    <t>'1230628719954132992</t>
+  </si>
+  <si>
+    <t>31.409789, -100.428493</t>
+  </si>
+  <si>
+    <t>06/27/26 07:52 CDT</t>
+  </si>
+  <si>
+    <t>'1230831791666003968</t>
+  </si>
+  <si>
+    <t>31.444726, -100.420344</t>
+  </si>
+  <si>
+    <t>06/27/26 08:33 CDT</t>
+  </si>
+  <si>
+    <t>'1230841913368805376</t>
+  </si>
+  <si>
+    <t>31.431269, -100.431622</t>
+  </si>
+  <si>
+    <t>06/27/26 08:37 CDT</t>
+  </si>
+  <si>
+    <t>'1230843001748750336</t>
+  </si>
+  <si>
+    <t>31.463376, -100.443698</t>
+  </si>
+  <si>
+    <t>06/27/26 09:03 CDT</t>
+  </si>
+  <si>
+    <t>'1230849634549792768</t>
+  </si>
+  <si>
+    <t>31.444908, -100.441870</t>
+  </si>
+  <si>
+    <t>06/27/26 09:07 CDT</t>
+  </si>
+  <si>
+    <t>'1230850493392257024</t>
+  </si>
+  <si>
+    <t>31.420207, -100.424471</t>
+  </si>
+  <si>
+    <t>06/27/26 09:51 CDT</t>
+  </si>
+  <si>
+    <t>'1230861743723544576</t>
+  </si>
+  <si>
+    <t>31.450375, -100.431733</t>
+  </si>
+  <si>
+    <t>06/27/26 11:51 CDT</t>
+  </si>
+  <si>
+    <t>'1230922872986435585</t>
+  </si>
+  <si>
+    <t>31.483685, -100.452365</t>
+  </si>
+  <si>
+    <t>06/27/26 12:12 CDT</t>
+  </si>
+  <si>
+    <t>'1230897069166854144</t>
+  </si>
+  <si>
+    <t>31.456541, -100.470378</t>
+  </si>
+  <si>
+    <t>06/27/26 12:16 CDT</t>
+  </si>
+  <si>
+    <t>'1230898159534899200</t>
+  </si>
+  <si>
+    <t>31.432326, -100.503700</t>
+  </si>
+  <si>
+    <t>06/27/26 14:32 CDT</t>
+  </si>
+  <si>
+    <t>'1230932507919286272</t>
+  </si>
+  <si>
+    <t>1.6mi W of San Angelo TX</t>
+  </si>
+  <si>
+    <t>31.444304, -100.476674</t>
+  </si>
+  <si>
+    <t>06/27/26 15:56 CDT</t>
+  </si>
+  <si>
+    <t>'1230953407863488512</t>
+  </si>
+  <si>
+    <t>31.480404, -100.456241</t>
+  </si>
+  <si>
+    <t>06/27/26 17:17 CDT</t>
+  </si>
+  <si>
+    <t>'1230973962691969024</t>
+  </si>
+  <si>
+    <t>31.479281, -100.447796</t>
+  </si>
+  <si>
+    <t>06/27/26 17:25 CDT</t>
+  </si>
+  <si>
+    <t>'1230975813218893824</t>
+  </si>
+  <si>
+    <t>31.432269, -100.503801</t>
+  </si>
+  <si>
+    <t>06/27/26 17:26 CDT</t>
+  </si>
+  <si>
+    <t>'1230976210490785792</t>
+  </si>
+  <si>
+    <t>31.436668, -100.493498</t>
+  </si>
+  <si>
+    <t>06/27/26 17:27 CDT</t>
+  </si>
+  <si>
+    <t>'1230976500153614336</t>
+  </si>
+  <si>
+    <t>31.424397, -100.423205</t>
+  </si>
+  <si>
+    <t>06/27/26 17:53 CDT</t>
+  </si>
+  <si>
+    <t>'1230983065447333888</t>
+  </si>
+  <si>
+    <t>31.464305, -100.439540</t>
+  </si>
+  <si>
+    <t>06/27/26 20:03 CDT</t>
+  </si>
+  <si>
+    <t>'1231015597173800960</t>
+  </si>
+  <si>
+    <t>31.489925, -100.470606</t>
+  </si>
+  <si>
+    <t>06/28/26 06:33 CDT</t>
+  </si>
+  <si>
+    <t>'1231174161464983552</t>
+  </si>
+  <si>
+    <t>31.396289, -100.433631</t>
   </si>
 </sst>
 </file>
@@ -17748,12 +19191,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1492"/>
+  <dimension ref="A1:N1621"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="32.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="14" width="15" customWidth="1"/>
+    <col min="1" max="14" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -50406,7 +51847,7 @@
         <v>3412</v>
       </c>
       <c r="E848" s="3" t="s">
-        <v>225</v>
+        <v>477</v>
       </c>
       <c r="F848" s="3" t="s">
         <v>278</v>
@@ -50428,7 +51869,7 @@
         <v>37</v>
       </c>
       <c r="M848" s="3" t="s">
-        <v>3414</v>
+        <v>3410</v>
       </c>
       <c r="N848" s="3"/>
     </row>
@@ -50441,10 +51882,10 @@
         <v>410</v>
       </c>
       <c r="D849" s="3" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="E849" s="3" t="s">
-        <v>477</v>
+        <v>225</v>
       </c>
       <c r="F849" s="3" t="s">
         <v>278</v>
@@ -50466,7 +51907,7 @@
         <v>37</v>
       </c>
       <c r="M849" s="3" t="s">
-        <v>3410</v>
+        <v>3415</v>
       </c>
       <c r="N849" s="3"/>
     </row>
@@ -50504,7 +51945,7 @@
         <v>37</v>
       </c>
       <c r="M850" s="3" t="s">
-        <v>3414</v>
+        <v>3415</v>
       </c>
       <c r="N850" s="3"/>
     </row>
@@ -50544,7 +51985,7 @@
         <v>37</v>
       </c>
       <c r="M851" s="3" t="s">
-        <v>3414</v>
+        <v>3415</v>
       </c>
       <c r="N851" s="3" t="s">
         <v>3423</v>
@@ -71380,9 +72821,7 @@
       <c r="A1394" s="3" t="s">
         <v>5423</v>
       </c>
-      <c r="B1394" s="3" t="s">
-        <v>1026</v>
-      </c>
+      <c r="B1394" s="3"/>
       <c r="C1394" s="3">
         <v>404</v>
       </c>
@@ -71390,7 +72829,7 @@
         <v>5424</v>
       </c>
       <c r="E1394" s="3" t="s">
-        <v>63</v>
+        <v>290</v>
       </c>
       <c r="F1394" s="3" t="s">
         <v>1870</v>
@@ -71399,7 +72838,7 @@
         <v>5425</v>
       </c>
       <c r="H1394" s="3" t="s">
-        <v>299</v>
+        <v>35</v>
       </c>
       <c r="I1394" s="3"/>
       <c r="J1394" s="3"/>
@@ -71410,17 +72849,17 @@
         <v>37</v>
       </c>
       <c r="M1394" s="3" t="s">
-        <v>5422</v>
-      </c>
-      <c r="N1394" s="3" t="s">
         <v>5426</v>
       </c>
+      <c r="N1394" s="3"/>
     </row>
     <row r="1395" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1395" s="3" t="s">
         <v>5423</v>
       </c>
-      <c r="B1395" s="3"/>
+      <c r="B1395" s="3" t="s">
+        <v>1026</v>
+      </c>
       <c r="C1395" s="3">
         <v>404</v>
       </c>
@@ -71428,7 +72867,7 @@
         <v>5427</v>
       </c>
       <c r="E1395" s="3" t="s">
-        <v>290</v>
+        <v>63</v>
       </c>
       <c r="F1395" s="3" t="s">
         <v>1870</v>
@@ -71437,7 +72876,7 @@
         <v>5425</v>
       </c>
       <c r="H1395" s="3" t="s">
-        <v>35</v>
+        <v>299</v>
       </c>
       <c r="I1395" s="3"/>
       <c r="J1395" s="3"/>
@@ -71448,9 +72887,11 @@
         <v>37</v>
       </c>
       <c r="M1395" s="3" t="s">
+        <v>5422</v>
+      </c>
+      <c r="N1395" s="3" t="s">
         <v>5428</v>
       </c>
-      <c r="N1395" s="3"/>
     </row>
     <row r="1396" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1396" s="3" t="s">
@@ -71490,7 +72931,7 @@
         <v>37</v>
       </c>
       <c r="M1396" s="3" t="s">
-        <v>5428</v>
+        <v>5426</v>
       </c>
       <c r="N1396" s="3"/>
     </row>
@@ -74656,28 +76097,34 @@
       <c r="G1479" s="3" t="s">
         <v>5747</v>
       </c>
-      <c r="H1479" s="3"/>
+      <c r="H1479" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1479" s="3">
         <v>14</v>
       </c>
       <c r="J1479" s="3"/>
       <c r="K1479" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1479" s="3"/>
-      <c r="M1479" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1479" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1479" s="3" t="s">
+        <v>5748</v>
+      </c>
       <c r="N1479" s="3"/>
     </row>
     <row r="1480" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1480" s="3" t="s">
-        <v>5748</v>
+        <v>5749</v>
       </c>
       <c r="B1480" s="3"/>
       <c r="C1480" s="3">
         <v>408</v>
       </c>
       <c r="D1480" s="3" t="s">
-        <v>5749</v>
+        <v>5750</v>
       </c>
       <c r="E1480" s="3" t="s">
         <v>290</v>
@@ -74686,30 +76133,36 @@
         <v>2448</v>
       </c>
       <c r="G1480" s="3" t="s">
-        <v>5750</v>
-      </c>
-      <c r="H1480" s="3"/>
+        <v>5751</v>
+      </c>
+      <c r="H1480" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1480" s="3">
         <v>36</v>
       </c>
       <c r="J1480" s="3"/>
       <c r="K1480" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1480" s="3"/>
-      <c r="M1480" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1480" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1480" s="3" t="s">
+        <v>5748</v>
+      </c>
       <c r="N1480" s="3"/>
     </row>
     <row r="1481" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1481" s="3" t="s">
-        <v>5751</v>
+        <v>5752</v>
       </c>
       <c r="B1481" s="3"/>
       <c r="C1481" s="3">
         <v>408</v>
       </c>
       <c r="D1481" s="3" t="s">
-        <v>5752</v>
+        <v>5753</v>
       </c>
       <c r="E1481" s="3" t="s">
         <v>290</v>
@@ -74718,30 +76171,36 @@
         <v>3014</v>
       </c>
       <c r="G1481" s="3" t="s">
-        <v>5753</v>
-      </c>
-      <c r="H1481" s="3"/>
+        <v>5754</v>
+      </c>
+      <c r="H1481" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1481" s="3">
         <v>44</v>
       </c>
       <c r="J1481" s="3"/>
       <c r="K1481" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1481" s="3"/>
-      <c r="M1481" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1481" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1481" s="3" t="s">
+        <v>5748</v>
+      </c>
       <c r="N1481" s="3"/>
     </row>
     <row r="1482" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1482" s="3" t="s">
-        <v>5754</v>
+        <v>5755</v>
       </c>
       <c r="B1482" s="3"/>
       <c r="C1482" s="3">
         <v>409</v>
       </c>
       <c r="D1482" s="3" t="s">
-        <v>5755</v>
+        <v>5756</v>
       </c>
       <c r="E1482" s="3" t="s">
         <v>290</v>
@@ -74750,30 +76209,36 @@
         <v>1707</v>
       </c>
       <c r="G1482" s="3" t="s">
-        <v>5756</v>
-      </c>
-      <c r="H1482" s="3"/>
+        <v>5757</v>
+      </c>
+      <c r="H1482" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1482" s="3">
         <v>23</v>
       </c>
       <c r="J1482" s="3"/>
       <c r="K1482" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1482" s="3"/>
-      <c r="M1482" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1482" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1482" s="3" t="s">
+        <v>5748</v>
+      </c>
       <c r="N1482" s="3"/>
     </row>
     <row r="1483" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1483" s="3" t="s">
-        <v>5757</v>
+        <v>5758</v>
       </c>
       <c r="B1483" s="3"/>
       <c r="C1483" s="3">
         <v>405</v>
       </c>
       <c r="D1483" s="3" t="s">
-        <v>5758</v>
+        <v>5759</v>
       </c>
       <c r="E1483" s="3" t="s">
         <v>290</v>
@@ -74782,30 +76247,36 @@
         <v>1084</v>
       </c>
       <c r="G1483" s="3" t="s">
-        <v>5759</v>
-      </c>
-      <c r="H1483" s="3"/>
+        <v>5760</v>
+      </c>
+      <c r="H1483" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1483" s="3">
         <v>17</v>
       </c>
       <c r="J1483" s="3"/>
       <c r="K1483" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1483" s="3"/>
-      <c r="M1483" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1483" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1483" s="3" t="s">
+        <v>5748</v>
+      </c>
       <c r="N1483" s="3"/>
     </row>
     <row r="1484" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1484" s="3" t="s">
-        <v>5760</v>
+        <v>5761</v>
       </c>
       <c r="B1484" s="3"/>
       <c r="C1484" s="3">
         <v>405</v>
       </c>
       <c r="D1484" s="3" t="s">
-        <v>5761</v>
+        <v>5762</v>
       </c>
       <c r="E1484" s="3" t="s">
         <v>290</v>
@@ -74814,30 +76285,36 @@
         <v>325</v>
       </c>
       <c r="G1484" s="3" t="s">
-        <v>5762</v>
-      </c>
-      <c r="H1484" s="3"/>
+        <v>5763</v>
+      </c>
+      <c r="H1484" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1484" s="3">
         <v>28</v>
       </c>
       <c r="J1484" s="3"/>
       <c r="K1484" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1484" s="3"/>
-      <c r="M1484" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1484" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1484" s="3" t="s">
+        <v>5748</v>
+      </c>
       <c r="N1484" s="3"/>
     </row>
     <row r="1485" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1485" s="3" t="s">
-        <v>5763</v>
+        <v>5764</v>
       </c>
       <c r="B1485" s="3"/>
       <c r="C1485" s="3">
         <v>404</v>
       </c>
       <c r="D1485" s="3" t="s">
-        <v>5764</v>
+        <v>5765</v>
       </c>
       <c r="E1485" s="3" t="s">
         <v>290</v>
@@ -74846,28 +76323,34 @@
         <v>2555</v>
       </c>
       <c r="G1485" s="3" t="s">
-        <v>5765</v>
-      </c>
-      <c r="H1485" s="3"/>
+        <v>5766</v>
+      </c>
+      <c r="H1485" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1485" s="3"/>
       <c r="J1485" s="3"/>
       <c r="K1485" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1485" s="3"/>
-      <c r="M1485" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1485" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1485" s="3" t="s">
+        <v>5748</v>
+      </c>
       <c r="N1485" s="3"/>
     </row>
     <row r="1486" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1486" s="3" t="s">
-        <v>5766</v>
+        <v>5767</v>
       </c>
       <c r="B1486" s="3"/>
       <c r="C1486" s="3">
         <v>404</v>
       </c>
       <c r="D1486" s="3" t="s">
-        <v>5767</v>
+        <v>5768</v>
       </c>
       <c r="E1486" s="3" t="s">
         <v>290</v>
@@ -74876,30 +76359,36 @@
         <v>1084</v>
       </c>
       <c r="G1486" s="3" t="s">
-        <v>5768</v>
-      </c>
-      <c r="H1486" s="3"/>
+        <v>5769</v>
+      </c>
+      <c r="H1486" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1486" s="3">
         <v>16</v>
       </c>
       <c r="J1486" s="3"/>
       <c r="K1486" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1486" s="3"/>
-      <c r="M1486" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1486" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1486" s="3" t="s">
+        <v>5748</v>
+      </c>
       <c r="N1486" s="3"/>
     </row>
     <row r="1487" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1487" s="3" t="s">
-        <v>5769</v>
+        <v>5770</v>
       </c>
       <c r="B1487" s="3"/>
       <c r="C1487" s="3">
         <v>404</v>
       </c>
       <c r="D1487" s="3" t="s">
-        <v>5770</v>
+        <v>5771</v>
       </c>
       <c r="E1487" s="3" t="s">
         <v>290</v>
@@ -74908,30 +76397,36 @@
         <v>4648</v>
       </c>
       <c r="G1487" s="3" t="s">
-        <v>5771</v>
-      </c>
-      <c r="H1487" s="3"/>
+        <v>5772</v>
+      </c>
+      <c r="H1487" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1487" s="3">
         <v>32</v>
       </c>
       <c r="J1487" s="3"/>
       <c r="K1487" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1487" s="3"/>
-      <c r="M1487" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1487" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1487" s="3" t="s">
+        <v>5748</v>
+      </c>
       <c r="N1487" s="3"/>
     </row>
     <row r="1488" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1488" s="3" t="s">
-        <v>5772</v>
+        <v>5773</v>
       </c>
       <c r="B1488" s="3"/>
       <c r="C1488" s="3">
         <v>404</v>
       </c>
       <c r="D1488" s="3" t="s">
-        <v>5773</v>
+        <v>5774</v>
       </c>
       <c r="E1488" s="3" t="s">
         <v>211</v>
@@ -74940,92 +76435,110 @@
         <v>3772</v>
       </c>
       <c r="G1488" s="3" t="s">
-        <v>5774</v>
-      </c>
-      <c r="H1488" s="3"/>
+        <v>5775</v>
+      </c>
+      <c r="H1488" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1488" s="3"/>
       <c r="J1488" s="3"/>
       <c r="K1488" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1488" s="3"/>
-      <c r="M1488" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1488" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1488" s="3" t="s">
+        <v>5748</v>
+      </c>
       <c r="N1488" s="3"/>
     </row>
     <row r="1489" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1489" s="3" t="s">
-        <v>5775</v>
+        <v>5776</v>
       </c>
       <c r="B1489" s="3"/>
       <c r="C1489" s="3">
         <v>404</v>
       </c>
       <c r="D1489" s="3" t="s">
-        <v>5776</v>
+        <v>5777</v>
       </c>
       <c r="E1489" s="3" t="s">
         <v>1150</v>
       </c>
       <c r="F1489" s="3" t="s">
-        <v>5777</v>
+        <v>5778</v>
       </c>
       <c r="G1489" s="3" t="s">
-        <v>5778</v>
-      </c>
-      <c r="H1489" s="3"/>
+        <v>5779</v>
+      </c>
+      <c r="H1489" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1489" s="3">
         <v>46</v>
       </c>
       <c r="J1489" s="3"/>
       <c r="K1489" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1489" s="3"/>
-      <c r="M1489" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1489" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1489" s="3" t="s">
+        <v>5780</v>
+      </c>
       <c r="N1489" s="3"/>
     </row>
     <row r="1490" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1490" s="3" t="s">
-        <v>5779</v>
+        <v>5781</v>
       </c>
       <c r="B1490" s="3"/>
       <c r="C1490" s="3">
         <v>410</v>
       </c>
       <c r="D1490" s="3" t="s">
-        <v>5780</v>
+        <v>5782</v>
       </c>
       <c r="E1490" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F1490" s="3" t="s">
-        <v>5781</v>
+        <v>5783</v>
       </c>
       <c r="G1490" s="3" t="s">
-        <v>5782</v>
-      </c>
-      <c r="H1490" s="3"/>
+        <v>5784</v>
+      </c>
+      <c r="H1490" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1490" s="3">
         <v>26</v>
       </c>
       <c r="J1490" s="3"/>
       <c r="K1490" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1490" s="3"/>
-      <c r="M1490" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1490" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1490" s="3" t="s">
+        <v>5780</v>
+      </c>
       <c r="N1490" s="3"/>
     </row>
     <row r="1491" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1491" s="3" t="s">
-        <v>5783</v>
+        <v>5785</v>
       </c>
       <c r="B1491" s="3"/>
       <c r="C1491" s="3">
         <v>408</v>
       </c>
       <c r="D1491" s="3" t="s">
-        <v>5784</v>
+        <v>5786</v>
       </c>
       <c r="E1491" s="3" t="s">
         <v>225</v>
@@ -75034,28 +76547,34 @@
         <v>291</v>
       </c>
       <c r="G1491" s="3" t="s">
-        <v>5785</v>
-      </c>
-      <c r="H1491" s="3"/>
+        <v>5787</v>
+      </c>
+      <c r="H1491" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1491" s="3"/>
       <c r="J1491" s="3"/>
       <c r="K1491" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1491" s="3"/>
-      <c r="M1491" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="L1491" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1491" s="3" t="s">
+        <v>5780</v>
+      </c>
       <c r="N1491" s="3"/>
     </row>
     <row r="1492" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1492" s="3" t="s">
-        <v>5786</v>
+        <v>5788</v>
       </c>
       <c r="B1492" s="3"/>
       <c r="C1492" s="3">
         <v>404</v>
       </c>
       <c r="D1492" s="3" t="s">
-        <v>5787</v>
+        <v>5789</v>
       </c>
       <c r="E1492" s="3" t="s">
         <v>290</v>
@@ -75064,19 +76583,4811 @@
         <v>325</v>
       </c>
       <c r="G1492" s="3" t="s">
-        <v>5788</v>
-      </c>
-      <c r="H1492" s="3"/>
+        <v>5790</v>
+      </c>
+      <c r="H1492" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="I1492" s="3">
         <v>3</v>
       </c>
       <c r="J1492" s="3"/>
       <c r="K1492" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1492" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1492" s="3" t="s">
+        <v>5780</v>
+      </c>
+      <c r="N1492" s="3"/>
+    </row>
+    <row r="1493" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1493" s="3" t="s">
+        <v>5791</v>
+      </c>
+      <c r="B1493" s="3"/>
+      <c r="C1493" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1493" s="3" t="s">
+        <v>5792</v>
+      </c>
+      <c r="E1493" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1493" s="3" t="s">
+        <v>1746</v>
+      </c>
+      <c r="G1493" s="3" t="s">
+        <v>5793</v>
+      </c>
+      <c r="H1493" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1493" s="3">
+        <v>27</v>
+      </c>
+      <c r="J1493" s="3"/>
+      <c r="K1493" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1493" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1493" s="3" t="s">
+        <v>5780</v>
+      </c>
+      <c r="N1493" s="3"/>
+    </row>
+    <row r="1494" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1494" s="3" t="s">
+        <v>5794</v>
+      </c>
+      <c r="B1494" s="3"/>
+      <c r="C1494" s="3">
+        <v>408</v>
+      </c>
+      <c r="D1494" s="3" t="s">
+        <v>5795</v>
+      </c>
+      <c r="E1494" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F1494" s="3" t="s">
+        <v>5796</v>
+      </c>
+      <c r="G1494" s="3" t="s">
+        <v>5797</v>
+      </c>
+      <c r="H1494" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1494" s="3">
         <v>22</v>
       </c>
-      <c r="L1492" s="3"/>
-      <c r="M1492" s="3"/>
-      <c r="N1492" s="3"/>
+      <c r="J1494" s="3"/>
+      <c r="K1494" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1494" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1494" s="3" t="s">
+        <v>5780</v>
+      </c>
+      <c r="N1494" s="3"/>
+    </row>
+    <row r="1495" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1495" s="3" t="s">
+        <v>5798</v>
+      </c>
+      <c r="B1495" s="3"/>
+      <c r="C1495" s="3">
+        <v>408</v>
+      </c>
+      <c r="D1495" s="3" t="s">
+        <v>5799</v>
+      </c>
+      <c r="E1495" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F1495" s="3" t="s">
+        <v>5800</v>
+      </c>
+      <c r="G1495" s="3" t="s">
+        <v>5801</v>
+      </c>
+      <c r="H1495" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1495" s="3">
+        <v>36</v>
+      </c>
+      <c r="J1495" s="3"/>
+      <c r="K1495" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1495" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1495" s="3" t="s">
+        <v>5780</v>
+      </c>
+      <c r="N1495" s="3"/>
+    </row>
+    <row r="1496" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1496" s="3" t="s">
+        <v>5802</v>
+      </c>
+      <c r="B1496" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C1496" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1496" s="3" t="s">
+        <v>5803</v>
+      </c>
+      <c r="E1496" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1496" s="3" t="s">
+        <v>5804</v>
+      </c>
+      <c r="G1496" s="3" t="s">
+        <v>5805</v>
+      </c>
+      <c r="H1496" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1496" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1496" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1496" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1496" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1496" s="3" t="s">
+        <v>5806</v>
+      </c>
+      <c r="N1496" s="3"/>
+    </row>
+    <row r="1497" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1497" s="3" t="s">
+        <v>5807</v>
+      </c>
+      <c r="B1497" s="3"/>
+      <c r="C1497" s="3">
+        <v>400</v>
+      </c>
+      <c r="D1497" s="3" t="s">
+        <v>5808</v>
+      </c>
+      <c r="E1497" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1497" s="3" t="s">
+        <v>3076</v>
+      </c>
+      <c r="G1497" s="3" t="s">
+        <v>5809</v>
+      </c>
+      <c r="H1497" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1497" s="3">
+        <v>50</v>
+      </c>
+      <c r="J1497" s="3"/>
+      <c r="K1497" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1497" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1497" s="3" t="s">
+        <v>5780</v>
+      </c>
+      <c r="N1497" s="3"/>
+    </row>
+    <row r="1498" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1498" s="3" t="s">
+        <v>5810</v>
+      </c>
+      <c r="B1498" s="3"/>
+      <c r="C1498" s="3">
+        <v>400</v>
+      </c>
+      <c r="D1498" s="3" t="s">
+        <v>5811</v>
+      </c>
+      <c r="E1498" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1498" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G1498" s="3" t="s">
+        <v>5812</v>
+      </c>
+      <c r="H1498" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1498" s="3">
+        <v>68</v>
+      </c>
+      <c r="J1498" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1498" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1498" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1498" s="3" t="s">
+        <v>5780</v>
+      </c>
+      <c r="N1498" s="3"/>
+    </row>
+    <row r="1499" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1499" s="3" t="s">
+        <v>5813</v>
+      </c>
+      <c r="B1499" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C1499" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1499" s="3" t="s">
+        <v>5814</v>
+      </c>
+      <c r="E1499" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1499" s="3" t="s">
+        <v>1619</v>
+      </c>
+      <c r="G1499" s="3" t="s">
+        <v>5815</v>
+      </c>
+      <c r="H1499" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1499" s="3">
+        <v>14</v>
+      </c>
+      <c r="J1499" s="3"/>
+      <c r="K1499" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1499" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1499" s="3" t="s">
+        <v>5816</v>
+      </c>
+      <c r="N1499" s="3" t="s">
+        <v>5817</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1500" s="3" t="s">
+        <v>5818</v>
+      </c>
+      <c r="B1500" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C1500" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1500" s="3" t="s">
+        <v>5819</v>
+      </c>
+      <c r="E1500" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1500" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G1500" s="3" t="s">
+        <v>5820</v>
+      </c>
+      <c r="H1500" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1500" s="3"/>
+      <c r="J1500" s="3"/>
+      <c r="K1500" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1500" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1500" s="3" t="s">
+        <v>5821</v>
+      </c>
+      <c r="N1500" s="3"/>
+    </row>
+    <row r="1501" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1501" s="3" t="s">
+        <v>5822</v>
+      </c>
+      <c r="B1501" s="3"/>
+      <c r="C1501" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1501" s="3" t="s">
+        <v>5823</v>
+      </c>
+      <c r="E1501" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1501" s="3" t="s">
+        <v>5824</v>
+      </c>
+      <c r="G1501" s="3" t="s">
+        <v>5825</v>
+      </c>
+      <c r="H1501" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1501" s="3">
+        <v>62</v>
+      </c>
+      <c r="J1501" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1501" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1501" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1501" s="3" t="s">
+        <v>5821</v>
+      </c>
+      <c r="N1501" s="3"/>
+    </row>
+    <row r="1502" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1502" s="3" t="s">
+        <v>5826</v>
+      </c>
+      <c r="B1502" s="3"/>
+      <c r="C1502" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1502" s="3" t="s">
+        <v>5827</v>
+      </c>
+      <c r="E1502" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1502" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G1502" s="3" t="s">
+        <v>5828</v>
+      </c>
+      <c r="H1502" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1502" s="3">
+        <v>19</v>
+      </c>
+      <c r="J1502" s="3"/>
+      <c r="K1502" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1502" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1502" s="3" t="s">
+        <v>5829</v>
+      </c>
+      <c r="N1502" s="3"/>
+    </row>
+    <row r="1503" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1503" s="3" t="s">
+        <v>5830</v>
+      </c>
+      <c r="B1503" s="3"/>
+      <c r="C1503" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1503" s="3" t="s">
+        <v>5831</v>
+      </c>
+      <c r="E1503" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1503" s="3" t="s">
+        <v>5832</v>
+      </c>
+      <c r="G1503" s="3" t="s">
+        <v>5833</v>
+      </c>
+      <c r="H1503" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1503" s="3">
+        <v>61</v>
+      </c>
+      <c r="J1503" s="3"/>
+      <c r="K1503" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1503" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1503" s="3" t="s">
+        <v>5821</v>
+      </c>
+      <c r="N1503" s="3"/>
+    </row>
+    <row r="1504" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1504" s="3" t="s">
+        <v>5829</v>
+      </c>
+      <c r="B1504" s="3"/>
+      <c r="C1504" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1504" s="3" t="s">
+        <v>5834</v>
+      </c>
+      <c r="E1504" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1504" s="3" t="s">
+        <v>3289</v>
+      </c>
+      <c r="G1504" s="3" t="s">
+        <v>5835</v>
+      </c>
+      <c r="H1504" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1504" s="3">
+        <v>73</v>
+      </c>
+      <c r="J1504" s="3"/>
+      <c r="K1504" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1504" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1504" s="3" t="s">
+        <v>5836</v>
+      </c>
+      <c r="N1504" s="3"/>
+    </row>
+    <row r="1505" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1505" s="3" t="s">
+        <v>5837</v>
+      </c>
+      <c r="B1505" s="3"/>
+      <c r="C1505" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1505" s="3" t="s">
+        <v>5838</v>
+      </c>
+      <c r="E1505" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1505" s="3" t="s">
+        <v>1775</v>
+      </c>
+      <c r="G1505" s="3" t="s">
+        <v>5839</v>
+      </c>
+      <c r="H1505" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1505" s="3">
+        <v>25</v>
+      </c>
+      <c r="J1505" s="3">
+        <v>40</v>
+      </c>
+      <c r="K1505" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1505" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1505" s="3" t="s">
+        <v>5836</v>
+      </c>
+      <c r="N1505" s="3"/>
+    </row>
+    <row r="1506" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1506" s="3" t="s">
+        <v>5840</v>
+      </c>
+      <c r="B1506" s="3"/>
+      <c r="C1506" s="3">
+        <v>408</v>
+      </c>
+      <c r="D1506" s="3" t="s">
+        <v>5841</v>
+      </c>
+      <c r="E1506" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1506" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="G1506" s="3" t="s">
+        <v>5842</v>
+      </c>
+      <c r="H1506" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1506" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1506" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1506" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1506" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1506" s="3" t="s">
+        <v>5836</v>
+      </c>
+      <c r="N1506" s="3"/>
+    </row>
+    <row r="1507" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1507" s="3" t="s">
+        <v>5843</v>
+      </c>
+      <c r="B1507" s="3"/>
+      <c r="C1507" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1507" s="3" t="s">
+        <v>5844</v>
+      </c>
+      <c r="E1507" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1507" s="3" t="s">
+        <v>2700</v>
+      </c>
+      <c r="G1507" s="3" t="s">
+        <v>5845</v>
+      </c>
+      <c r="H1507" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1507" s="3">
+        <v>15</v>
+      </c>
+      <c r="J1507" s="3"/>
+      <c r="K1507" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1507" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1507" s="3" t="s">
+        <v>5846</v>
+      </c>
+      <c r="N1507" s="3"/>
+    </row>
+    <row r="1508" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1508" s="3" t="s">
+        <v>5847</v>
+      </c>
+      <c r="B1508" s="3"/>
+      <c r="C1508" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1508" s="3" t="s">
+        <v>5848</v>
+      </c>
+      <c r="E1508" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1508" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G1508" s="3" t="s">
+        <v>5849</v>
+      </c>
+      <c r="H1508" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1508" s="3">
+        <v>31</v>
+      </c>
+      <c r="J1508" s="3"/>
+      <c r="K1508" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1508" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1508" s="3" t="s">
+        <v>5846</v>
+      </c>
+      <c r="N1508" s="3"/>
+    </row>
+    <row r="1509" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1509" s="3" t="s">
+        <v>5850</v>
+      </c>
+      <c r="B1509" s="3"/>
+      <c r="C1509" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1509" s="3" t="s">
+        <v>5851</v>
+      </c>
+      <c r="E1509" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1509" s="3" t="s">
+        <v>4158</v>
+      </c>
+      <c r="G1509" s="3" t="s">
+        <v>5852</v>
+      </c>
+      <c r="H1509" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1509" s="3">
+        <v>29</v>
+      </c>
+      <c r="J1509" s="3"/>
+      <c r="K1509" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1509" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1509" s="3" t="s">
+        <v>5846</v>
+      </c>
+      <c r="N1509" s="3"/>
+    </row>
+    <row r="1510" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1510" s="3" t="s">
+        <v>5853</v>
+      </c>
+      <c r="B1510" s="3"/>
+      <c r="C1510" s="3">
+        <v>406</v>
+      </c>
+      <c r="D1510" s="3" t="s">
+        <v>5854</v>
+      </c>
+      <c r="E1510" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1510" s="3" t="s">
+        <v>5855</v>
+      </c>
+      <c r="G1510" s="3" t="s">
+        <v>5856</v>
+      </c>
+      <c r="H1510" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1510" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1510" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1510" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1510" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1510" s="3" t="s">
+        <v>5857</v>
+      </c>
+      <c r="N1510" s="3"/>
+    </row>
+    <row r="1511" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1511" s="3" t="s">
+        <v>5858</v>
+      </c>
+      <c r="B1511" s="3"/>
+      <c r="C1511" s="3">
+        <v>406</v>
+      </c>
+      <c r="D1511" s="3" t="s">
+        <v>5859</v>
+      </c>
+      <c r="E1511" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1511" s="3" t="s">
+        <v>5860</v>
+      </c>
+      <c r="G1511" s="3" t="s">
+        <v>5861</v>
+      </c>
+      <c r="H1511" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1511" s="3">
+        <v>75</v>
+      </c>
+      <c r="J1511" s="3"/>
+      <c r="K1511" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1511" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1511" s="3" t="s">
+        <v>5857</v>
+      </c>
+      <c r="N1511" s="3"/>
+    </row>
+    <row r="1512" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1512" s="3" t="s">
+        <v>5862</v>
+      </c>
+      <c r="B1512" s="3"/>
+      <c r="C1512" s="3">
+        <v>406</v>
+      </c>
+      <c r="D1512" s="3" t="s">
+        <v>5863</v>
+      </c>
+      <c r="E1512" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1512" s="3" t="s">
+        <v>5864</v>
+      </c>
+      <c r="G1512" s="3" t="s">
+        <v>5865</v>
+      </c>
+      <c r="H1512" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1512" s="3">
+        <v>75</v>
+      </c>
+      <c r="J1512" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1512" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1512" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1512" s="3" t="s">
+        <v>5857</v>
+      </c>
+      <c r="N1512" s="3"/>
+    </row>
+    <row r="1513" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1513" s="3" t="s">
+        <v>5866</v>
+      </c>
+      <c r="B1513" s="3"/>
+      <c r="C1513" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1513" s="3" t="s">
+        <v>5867</v>
+      </c>
+      <c r="E1513" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1513" s="3" t="s">
+        <v>1032</v>
+      </c>
+      <c r="G1513" s="3" t="s">
+        <v>5868</v>
+      </c>
+      <c r="H1513" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1513" s="3">
+        <v>68</v>
+      </c>
+      <c r="J1513" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1513" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1513" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1513" s="3" t="s">
+        <v>5857</v>
+      </c>
+      <c r="N1513" s="3"/>
+    </row>
+    <row r="1514" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1514" s="3" t="s">
+        <v>5869</v>
+      </c>
+      <c r="B1514" s="3"/>
+      <c r="C1514" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1514" s="3" t="s">
+        <v>5870</v>
+      </c>
+      <c r="E1514" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1514" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="G1514" s="3" t="s">
+        <v>5871</v>
+      </c>
+      <c r="H1514" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1514" s="3"/>
+      <c r="J1514" s="3"/>
+      <c r="K1514" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1514" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1514" s="3" t="s">
+        <v>5857</v>
+      </c>
+      <c r="N1514" s="3"/>
+    </row>
+    <row r="1515" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1515" s="3" t="s">
+        <v>5872</v>
+      </c>
+      <c r="B1515" s="3"/>
+      <c r="C1515" s="3">
+        <v>406</v>
+      </c>
+      <c r="D1515" s="3" t="s">
+        <v>5873</v>
+      </c>
+      <c r="E1515" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1515" s="3" t="s">
+        <v>5874</v>
+      </c>
+      <c r="G1515" s="3" t="s">
+        <v>5875</v>
+      </c>
+      <c r="H1515" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1515" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1515" s="3"/>
+      <c r="K1515" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1515" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1515" s="3" t="s">
+        <v>5857</v>
+      </c>
+      <c r="N1515" s="3"/>
+    </row>
+    <row r="1516" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1516" s="3" t="s">
+        <v>5876</v>
+      </c>
+      <c r="B1516" s="3"/>
+      <c r="C1516" s="3">
+        <v>406</v>
+      </c>
+      <c r="D1516" s="3" t="s">
+        <v>5877</v>
+      </c>
+      <c r="E1516" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1516" s="3" t="s">
+        <v>5878</v>
+      </c>
+      <c r="G1516" s="3" t="s">
+        <v>5879</v>
+      </c>
+      <c r="H1516" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1516" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1516" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1516" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1516" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1516" s="3" t="s">
+        <v>5857</v>
+      </c>
+      <c r="N1516" s="3"/>
+    </row>
+    <row r="1517" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1517" s="3" t="s">
+        <v>5880</v>
+      </c>
+      <c r="B1517" s="3"/>
+      <c r="C1517" s="3">
+        <v>406</v>
+      </c>
+      <c r="D1517" s="3" t="s">
+        <v>5881</v>
+      </c>
+      <c r="E1517" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1517" s="3" t="s">
+        <v>5882</v>
+      </c>
+      <c r="G1517" s="3" t="s">
+        <v>5883</v>
+      </c>
+      <c r="H1517" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1517" s="3">
+        <v>75</v>
+      </c>
+      <c r="J1517" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1517" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1517" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1517" s="3" t="s">
+        <v>5857</v>
+      </c>
+      <c r="N1517" s="3"/>
+    </row>
+    <row r="1518" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1518" s="3" t="s">
+        <v>5884</v>
+      </c>
+      <c r="B1518" s="3"/>
+      <c r="C1518" s="3">
+        <v>406</v>
+      </c>
+      <c r="D1518" s="3" t="s">
+        <v>5885</v>
+      </c>
+      <c r="E1518" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1518" s="3" t="s">
+        <v>5886</v>
+      </c>
+      <c r="G1518" s="3" t="s">
+        <v>5887</v>
+      </c>
+      <c r="H1518" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1518" s="3">
+        <v>69</v>
+      </c>
+      <c r="J1518" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1518" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1518" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1518" s="3" t="s">
+        <v>5857</v>
+      </c>
+      <c r="N1518" s="3"/>
+    </row>
+    <row r="1519" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1519" s="3" t="s">
+        <v>5888</v>
+      </c>
+      <c r="B1519" s="3"/>
+      <c r="C1519" s="3">
+        <v>406</v>
+      </c>
+      <c r="D1519" s="3" t="s">
+        <v>5889</v>
+      </c>
+      <c r="E1519" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1519" s="3" t="s">
+        <v>5890</v>
+      </c>
+      <c r="G1519" s="3" t="s">
+        <v>5891</v>
+      </c>
+      <c r="H1519" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1519" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1519" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1519" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1519" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1519" s="3" t="s">
+        <v>5892</v>
+      </c>
+      <c r="N1519" s="3"/>
+    </row>
+    <row r="1520" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1520" s="3" t="s">
+        <v>5893</v>
+      </c>
+      <c r="B1520" s="3"/>
+      <c r="C1520" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1520" s="3" t="s">
+        <v>5894</v>
+      </c>
+      <c r="E1520" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1520" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1520" s="3" t="s">
+        <v>5895</v>
+      </c>
+      <c r="H1520" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1520" s="3">
+        <v>34</v>
+      </c>
+      <c r="J1520" s="3"/>
+      <c r="K1520" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1520" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1520" s="3" t="s">
+        <v>5892</v>
+      </c>
+      <c r="N1520" s="3"/>
+    </row>
+    <row r="1521" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1521" s="3" t="s">
+        <v>5896</v>
+      </c>
+      <c r="B1521" s="3"/>
+      <c r="C1521" s="3">
+        <v>406</v>
+      </c>
+      <c r="D1521" s="3" t="s">
+        <v>5897</v>
+      </c>
+      <c r="E1521" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1521" s="3" t="s">
+        <v>5898</v>
+      </c>
+      <c r="G1521" s="3" t="s">
+        <v>5899</v>
+      </c>
+      <c r="H1521" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1521" s="3">
+        <v>50</v>
+      </c>
+      <c r="J1521" s="3">
+        <v>40</v>
+      </c>
+      <c r="K1521" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1521" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1521" s="3" t="s">
+        <v>5892</v>
+      </c>
+      <c r="N1521" s="3"/>
+    </row>
+    <row r="1522" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1522" s="3" t="s">
+        <v>5900</v>
+      </c>
+      <c r="B1522" s="3"/>
+      <c r="C1522" s="3">
+        <v>406</v>
+      </c>
+      <c r="D1522" s="3" t="s">
+        <v>5901</v>
+      </c>
+      <c r="E1522" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1522" s="3" t="s">
+        <v>5902</v>
+      </c>
+      <c r="G1522" s="3" t="s">
+        <v>5903</v>
+      </c>
+      <c r="H1522" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1522" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1522" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1522" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1522" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1522" s="3" t="s">
+        <v>5892</v>
+      </c>
+      <c r="N1522" s="3"/>
+    </row>
+    <row r="1523" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1523" s="3" t="s">
+        <v>5904</v>
+      </c>
+      <c r="B1523" s="3"/>
+      <c r="C1523" s="3">
+        <v>406</v>
+      </c>
+      <c r="D1523" s="3" t="s">
+        <v>5905</v>
+      </c>
+      <c r="E1523" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1523" s="3" t="s">
+        <v>5906</v>
+      </c>
+      <c r="G1523" s="3" t="s">
+        <v>5907</v>
+      </c>
+      <c r="H1523" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1523" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1523" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1523" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1523" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1523" s="3" t="s">
+        <v>5892</v>
+      </c>
+      <c r="N1523" s="3"/>
+    </row>
+    <row r="1524" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1524" s="3" t="s">
+        <v>5908</v>
+      </c>
+      <c r="B1524" s="3"/>
+      <c r="C1524" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1524" s="3" t="s">
+        <v>5909</v>
+      </c>
+      <c r="E1524" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1524" s="3" t="s">
+        <v>2379</v>
+      </c>
+      <c r="G1524" s="3" t="s">
+        <v>5910</v>
+      </c>
+      <c r="H1524" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1524" s="3"/>
+      <c r="J1524" s="3"/>
+      <c r="K1524" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1524" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1524" s="3" t="s">
+        <v>5892</v>
+      </c>
+      <c r="N1524" s="3"/>
+    </row>
+    <row r="1525" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1525" s="3" t="s">
+        <v>5911</v>
+      </c>
+      <c r="B1525" s="3"/>
+      <c r="C1525" s="3">
+        <v>406</v>
+      </c>
+      <c r="D1525" s="3" t="s">
+        <v>5912</v>
+      </c>
+      <c r="E1525" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1525" s="3" t="s">
+        <v>5913</v>
+      </c>
+      <c r="G1525" s="3" t="s">
+        <v>5914</v>
+      </c>
+      <c r="H1525" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1525" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1525" s="3"/>
+      <c r="K1525" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1525" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1525" s="3" t="s">
+        <v>5892</v>
+      </c>
+      <c r="N1525" s="3"/>
+    </row>
+    <row r="1526" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1526" s="3" t="s">
+        <v>5915</v>
+      </c>
+      <c r="B1526" s="3"/>
+      <c r="C1526" s="3">
+        <v>406</v>
+      </c>
+      <c r="D1526" s="3" t="s">
+        <v>5916</v>
+      </c>
+      <c r="E1526" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1526" s="3" t="s">
+        <v>5917</v>
+      </c>
+      <c r="G1526" s="3" t="s">
+        <v>5918</v>
+      </c>
+      <c r="H1526" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1526" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1526" s="3"/>
+      <c r="K1526" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1526" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1526" s="3" t="s">
+        <v>5892</v>
+      </c>
+      <c r="N1526" s="3"/>
+    </row>
+    <row r="1527" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1527" s="3" t="s">
+        <v>5919</v>
+      </c>
+      <c r="B1527" s="3"/>
+      <c r="C1527" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1527" s="3" t="s">
+        <v>5920</v>
+      </c>
+      <c r="E1527" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1527" s="3" t="s">
+        <v>5921</v>
+      </c>
+      <c r="G1527" s="3" t="s">
+        <v>5922</v>
+      </c>
+      <c r="H1527" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1527" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1527" s="3"/>
+      <c r="K1527" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1527" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1527" s="3" t="s">
+        <v>5892</v>
+      </c>
+      <c r="N1527" s="3"/>
+    </row>
+    <row r="1528" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1528" s="3" t="s">
+        <v>5923</v>
+      </c>
+      <c r="B1528" s="3"/>
+      <c r="C1528" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1528" s="3" t="s">
+        <v>5924</v>
+      </c>
+      <c r="E1528" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1528" s="3" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G1528" s="3" t="s">
+        <v>5925</v>
+      </c>
+      <c r="H1528" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1528" s="3">
+        <v>21</v>
+      </c>
+      <c r="J1528" s="3"/>
+      <c r="K1528" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1528" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1528" s="3" t="s">
+        <v>5892</v>
+      </c>
+      <c r="N1528" s="3"/>
+    </row>
+    <row r="1529" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1529" s="3" t="s">
+        <v>5926</v>
+      </c>
+      <c r="B1529" s="3"/>
+      <c r="C1529" s="3">
+        <v>406</v>
+      </c>
+      <c r="D1529" s="3" t="s">
+        <v>5927</v>
+      </c>
+      <c r="E1529" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1529" s="3" t="s">
+        <v>5928</v>
+      </c>
+      <c r="G1529" s="3" t="s">
+        <v>5929</v>
+      </c>
+      <c r="H1529" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1529" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1529" s="3"/>
+      <c r="K1529" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1529" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1529" s="3" t="s">
+        <v>5892</v>
+      </c>
+      <c r="N1529" s="3"/>
+    </row>
+    <row r="1530" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1530" s="3" t="s">
+        <v>5930</v>
+      </c>
+      <c r="B1530" s="3"/>
+      <c r="C1530" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1530" s="3" t="s">
+        <v>5931</v>
+      </c>
+      <c r="E1530" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1530" s="3" t="s">
+        <v>5932</v>
+      </c>
+      <c r="G1530" s="3" t="s">
+        <v>5933</v>
+      </c>
+      <c r="H1530" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1530" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1530" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1530" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1530" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1530" s="3" t="s">
+        <v>5934</v>
+      </c>
+      <c r="N1530" s="3"/>
+    </row>
+    <row r="1531" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1531" s="3" t="s">
+        <v>5935</v>
+      </c>
+      <c r="B1531" s="3"/>
+      <c r="C1531" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1531" s="3" t="s">
+        <v>5936</v>
+      </c>
+      <c r="E1531" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1531" s="3" t="s">
+        <v>5937</v>
+      </c>
+      <c r="G1531" s="3" t="s">
+        <v>5938</v>
+      </c>
+      <c r="H1531" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1531" s="3">
+        <v>73</v>
+      </c>
+      <c r="J1531" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1531" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1531" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1531" s="3" t="s">
+        <v>5934</v>
+      </c>
+      <c r="N1531" s="3"/>
+    </row>
+    <row r="1532" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1532" s="3" t="s">
+        <v>5939</v>
+      </c>
+      <c r="B1532" s="3"/>
+      <c r="C1532" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1532" s="3" t="s">
+        <v>5940</v>
+      </c>
+      <c r="E1532" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1532" s="3" t="s">
+        <v>5941</v>
+      </c>
+      <c r="G1532" s="3" t="s">
+        <v>5942</v>
+      </c>
+      <c r="H1532" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1532" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1532" s="3"/>
+      <c r="K1532" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1532" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1532" s="3" t="s">
+        <v>5934</v>
+      </c>
+      <c r="N1532" s="3"/>
+    </row>
+    <row r="1533" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1533" s="3" t="s">
+        <v>5943</v>
+      </c>
+      <c r="B1533" s="3"/>
+      <c r="C1533" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1533" s="3" t="s">
+        <v>5944</v>
+      </c>
+      <c r="E1533" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1533" s="3" t="s">
+        <v>5945</v>
+      </c>
+      <c r="G1533" s="3" t="s">
+        <v>5946</v>
+      </c>
+      <c r="H1533" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1533" s="3">
+        <v>31</v>
+      </c>
+      <c r="J1533" s="3">
+        <v>40</v>
+      </c>
+      <c r="K1533" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1533" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1533" s="3" t="s">
+        <v>5934</v>
+      </c>
+      <c r="N1533" s="3"/>
+    </row>
+    <row r="1534" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1534" s="3" t="s">
+        <v>5947</v>
+      </c>
+      <c r="B1534" s="3"/>
+      <c r="C1534" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1534" s="3" t="s">
+        <v>5948</v>
+      </c>
+      <c r="E1534" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1534" s="3" t="s">
+        <v>5949</v>
+      </c>
+      <c r="G1534" s="3" t="s">
+        <v>5950</v>
+      </c>
+      <c r="H1534" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1534" s="3">
+        <v>60</v>
+      </c>
+      <c r="J1534" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1534" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1534" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1534" s="3" t="s">
+        <v>5934</v>
+      </c>
+      <c r="N1534" s="3"/>
+    </row>
+    <row r="1535" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1535" s="3" t="s">
+        <v>5951</v>
+      </c>
+      <c r="B1535" s="3"/>
+      <c r="C1535" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1535" s="3" t="s">
+        <v>5952</v>
+      </c>
+      <c r="E1535" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1535" s="3" t="s">
+        <v>5953</v>
+      </c>
+      <c r="G1535" s="3" t="s">
+        <v>5954</v>
+      </c>
+      <c r="H1535" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1535" s="3">
+        <v>60</v>
+      </c>
+      <c r="J1535" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1535" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1535" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1535" s="3" t="s">
+        <v>5934</v>
+      </c>
+      <c r="N1535" s="3"/>
+    </row>
+    <row r="1536" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1536" s="3" t="s">
+        <v>5955</v>
+      </c>
+      <c r="B1536" s="3"/>
+      <c r="C1536" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1536" s="3" t="s">
+        <v>5956</v>
+      </c>
+      <c r="E1536" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1536" s="3" t="s">
+        <v>5957</v>
+      </c>
+      <c r="G1536" s="3" t="s">
+        <v>5958</v>
+      </c>
+      <c r="H1536" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1536" s="3">
+        <v>29</v>
+      </c>
+      <c r="J1536" s="3"/>
+      <c r="K1536" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1536" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1536" s="3" t="s">
+        <v>5934</v>
+      </c>
+      <c r="N1536" s="3"/>
+    </row>
+    <row r="1537" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1537" s="3" t="s">
+        <v>5959</v>
+      </c>
+      <c r="B1537" s="3"/>
+      <c r="C1537" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1537" s="3" t="s">
+        <v>5960</v>
+      </c>
+      <c r="E1537" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1537" s="3" t="s">
+        <v>5961</v>
+      </c>
+      <c r="G1537" s="3" t="s">
+        <v>5962</v>
+      </c>
+      <c r="H1537" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1537" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1537" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1537" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1537" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1537" s="3" t="s">
+        <v>5934</v>
+      </c>
+      <c r="N1537" s="3"/>
+    </row>
+    <row r="1538" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1538" s="3" t="s">
+        <v>5963</v>
+      </c>
+      <c r="B1538" s="3"/>
+      <c r="C1538" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1538" s="3" t="s">
+        <v>5964</v>
+      </c>
+      <c r="E1538" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1538" s="3" t="s">
+        <v>5965</v>
+      </c>
+      <c r="G1538" s="3" t="s">
+        <v>5966</v>
+      </c>
+      <c r="H1538" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1538" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1538" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1538" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1538" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1538" s="3" t="s">
+        <v>5967</v>
+      </c>
+      <c r="N1538" s="3"/>
+    </row>
+    <row r="1539" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1539" s="3" t="s">
+        <v>5968</v>
+      </c>
+      <c r="B1539" s="3"/>
+      <c r="C1539" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1539" s="3" t="s">
+        <v>5969</v>
+      </c>
+      <c r="E1539" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1539" s="3" t="s">
+        <v>5970</v>
+      </c>
+      <c r="G1539" s="3" t="s">
+        <v>5971</v>
+      </c>
+      <c r="H1539" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1539" s="3">
+        <v>69</v>
+      </c>
+      <c r="J1539" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1539" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1539" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1539" s="3" t="s">
+        <v>5967</v>
+      </c>
+      <c r="N1539" s="3"/>
+    </row>
+    <row r="1540" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1540" s="3" t="s">
+        <v>5972</v>
+      </c>
+      <c r="B1540" s="3"/>
+      <c r="C1540" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1540" s="3" t="s">
+        <v>5973</v>
+      </c>
+      <c r="E1540" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1540" s="3" t="s">
+        <v>5974</v>
+      </c>
+      <c r="G1540" s="3" t="s">
+        <v>5975</v>
+      </c>
+      <c r="H1540" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1540" s="3">
+        <v>73</v>
+      </c>
+      <c r="J1540" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1540" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1540" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1540" s="3" t="s">
+        <v>5967</v>
+      </c>
+      <c r="N1540" s="3"/>
+    </row>
+    <row r="1541" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1541" s="3" t="s">
+        <v>5976</v>
+      </c>
+      <c r="B1541" s="3"/>
+      <c r="C1541" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1541" s="3" t="s">
+        <v>5977</v>
+      </c>
+      <c r="E1541" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1541" s="3" t="s">
+        <v>5978</v>
+      </c>
+      <c r="G1541" s="3" t="s">
+        <v>5979</v>
+      </c>
+      <c r="H1541" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1541" s="3">
+        <v>72</v>
+      </c>
+      <c r="J1541" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1541" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1541" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1541" s="3" t="s">
+        <v>5967</v>
+      </c>
+      <c r="N1541" s="3"/>
+    </row>
+    <row r="1542" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1542" s="3" t="s">
+        <v>5980</v>
+      </c>
+      <c r="B1542" s="3"/>
+      <c r="C1542" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1542" s="3" t="s">
+        <v>5981</v>
+      </c>
+      <c r="E1542" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1542" s="3" t="s">
+        <v>5982</v>
+      </c>
+      <c r="G1542" s="3" t="s">
+        <v>5983</v>
+      </c>
+      <c r="H1542" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1542" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1542" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1542" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1542" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1542" s="3" t="s">
+        <v>5967</v>
+      </c>
+      <c r="N1542" s="3"/>
+    </row>
+    <row r="1543" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1543" s="3" t="s">
+        <v>5984</v>
+      </c>
+      <c r="B1543" s="3"/>
+      <c r="C1543" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1543" s="3" t="s">
+        <v>5985</v>
+      </c>
+      <c r="E1543" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1543" s="3" t="s">
+        <v>5986</v>
+      </c>
+      <c r="G1543" s="3" t="s">
+        <v>5987</v>
+      </c>
+      <c r="H1543" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1543" s="3">
+        <v>75</v>
+      </c>
+      <c r="J1543" s="3"/>
+      <c r="K1543" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1543" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1543" s="3" t="s">
+        <v>5967</v>
+      </c>
+      <c r="N1543" s="3"/>
+    </row>
+    <row r="1544" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1544" s="3" t="s">
+        <v>5988</v>
+      </c>
+      <c r="B1544" s="3"/>
+      <c r="C1544" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1544" s="3" t="s">
+        <v>5989</v>
+      </c>
+      <c r="E1544" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1544" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="G1544" s="3" t="s">
+        <v>5990</v>
+      </c>
+      <c r="H1544" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1544" s="3"/>
+      <c r="J1544" s="3"/>
+      <c r="K1544" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1544" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1544" s="3" t="s">
+        <v>5967</v>
+      </c>
+      <c r="N1544" s="3"/>
+    </row>
+    <row r="1545" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1545" s="3" t="s">
+        <v>5991</v>
+      </c>
+      <c r="B1545" s="3"/>
+      <c r="C1545" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1545" s="3" t="s">
+        <v>5992</v>
+      </c>
+      <c r="E1545" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1545" s="3" t="s">
+        <v>4487</v>
+      </c>
+      <c r="G1545" s="3" t="s">
+        <v>5993</v>
+      </c>
+      <c r="H1545" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1545" s="3"/>
+      <c r="J1545" s="3"/>
+      <c r="K1545" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1545" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1545" s="3" t="s">
+        <v>5967</v>
+      </c>
+      <c r="N1545" s="3"/>
+    </row>
+    <row r="1546" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1546" s="3" t="s">
+        <v>5994</v>
+      </c>
+      <c r="B1546" s="3"/>
+      <c r="C1546" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1546" s="3" t="s">
+        <v>5995</v>
+      </c>
+      <c r="E1546" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1546" s="3" t="s">
+        <v>3675</v>
+      </c>
+      <c r="G1546" s="3" t="s">
+        <v>5996</v>
+      </c>
+      <c r="H1546" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1546" s="3"/>
+      <c r="J1546" s="3"/>
+      <c r="K1546" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1546" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1546" s="3" t="s">
+        <v>5997</v>
+      </c>
+      <c r="N1546" s="3"/>
+    </row>
+    <row r="1547" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1547" s="3" t="s">
+        <v>5998</v>
+      </c>
+      <c r="B1547" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1547" s="3">
+        <v>406</v>
+      </c>
+      <c r="D1547" s="3" t="s">
+        <v>5999</v>
+      </c>
+      <c r="E1547" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1547" s="3" t="s">
+        <v>6000</v>
+      </c>
+      <c r="G1547" s="3" t="s">
+        <v>6001</v>
+      </c>
+      <c r="H1547" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1547" s="3">
+        <v>64</v>
+      </c>
+      <c r="J1547" s="3"/>
+      <c r="K1547" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1547" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1547" s="3" t="s">
+        <v>6002</v>
+      </c>
+      <c r="N1547" s="3" t="s">
+        <v>6003</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1548" s="3" t="s">
+        <v>6004</v>
+      </c>
+      <c r="B1548" s="3"/>
+      <c r="C1548" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1548" s="3" t="s">
+        <v>6005</v>
+      </c>
+      <c r="E1548" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1548" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="G1548" s="3" t="s">
+        <v>6006</v>
+      </c>
+      <c r="H1548" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1548" s="3">
+        <v>34</v>
+      </c>
+      <c r="J1548" s="3"/>
+      <c r="K1548" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1548" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1548" s="3" t="s">
+        <v>6002</v>
+      </c>
+      <c r="N1548" s="3"/>
+    </row>
+    <row r="1549" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1549" s="3" t="s">
+        <v>6007</v>
+      </c>
+      <c r="B1549" s="3"/>
+      <c r="C1549" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1549" s="3" t="s">
+        <v>6008</v>
+      </c>
+      <c r="E1549" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1549" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G1549" s="3" t="s">
+        <v>6009</v>
+      </c>
+      <c r="H1549" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1549" s="3">
+        <v>34</v>
+      </c>
+      <c r="J1549" s="3"/>
+      <c r="K1549" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1549" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1549" s="3" t="s">
+        <v>6002</v>
+      </c>
+      <c r="N1549" s="3"/>
+    </row>
+    <row r="1550" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1550" s="3" t="s">
+        <v>6010</v>
+      </c>
+      <c r="B1550" s="3"/>
+      <c r="C1550" s="3">
+        <v>406</v>
+      </c>
+      <c r="D1550" s="3" t="s">
+        <v>6011</v>
+      </c>
+      <c r="E1550" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1550" s="3" t="s">
+        <v>6012</v>
+      </c>
+      <c r="G1550" s="3" t="s">
+        <v>6013</v>
+      </c>
+      <c r="H1550" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1550" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1550" s="3"/>
+      <c r="K1550" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1550" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1550" s="3" t="s">
+        <v>6002</v>
+      </c>
+      <c r="N1550" s="3"/>
+    </row>
+    <row r="1551" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1551" s="3" t="s">
+        <v>6014</v>
+      </c>
+      <c r="B1551" s="3"/>
+      <c r="C1551" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1551" s="3" t="s">
+        <v>6015</v>
+      </c>
+      <c r="E1551" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1551" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="G1551" s="3" t="s">
+        <v>6016</v>
+      </c>
+      <c r="H1551" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1551" s="3">
+        <v>28</v>
+      </c>
+      <c r="J1551" s="3"/>
+      <c r="K1551" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1551" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1551" s="3" t="s">
+        <v>6017</v>
+      </c>
+      <c r="N1551" s="3"/>
+    </row>
+    <row r="1552" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1552" s="3" t="s">
+        <v>6018</v>
+      </c>
+      <c r="B1552" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1552" s="3">
+        <v>406</v>
+      </c>
+      <c r="D1552" s="3" t="s">
+        <v>6019</v>
+      </c>
+      <c r="E1552" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1552" s="3" t="s">
+        <v>6020</v>
+      </c>
+      <c r="G1552" s="3" t="s">
+        <v>6021</v>
+      </c>
+      <c r="H1552" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1552" s="3">
+        <v>75</v>
+      </c>
+      <c r="J1552" s="3">
+        <v>60</v>
+      </c>
+      <c r="K1552" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1552" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1552" s="3" t="s">
+        <v>6017</v>
+      </c>
+      <c r="N1552" s="3" t="s">
+        <v>6003</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1553" s="3" t="s">
+        <v>6022</v>
+      </c>
+      <c r="B1553" s="3"/>
+      <c r="C1553" s="3">
+        <v>406</v>
+      </c>
+      <c r="D1553" s="3" t="s">
+        <v>6023</v>
+      </c>
+      <c r="E1553" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1553" s="3" t="s">
+        <v>6024</v>
+      </c>
+      <c r="G1553" s="3" t="s">
+        <v>6025</v>
+      </c>
+      <c r="H1553" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1553" s="3"/>
+      <c r="J1553" s="3"/>
+      <c r="K1553" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1553" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1553" s="3" t="s">
+        <v>6026</v>
+      </c>
+      <c r="N1553" s="3"/>
+    </row>
+    <row r="1554" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1554" s="3" t="s">
+        <v>6027</v>
+      </c>
+      <c r="B1554" s="3"/>
+      <c r="C1554" s="3">
+        <v>408</v>
+      </c>
+      <c r="D1554" s="3" t="s">
+        <v>6028</v>
+      </c>
+      <c r="E1554" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1554" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="G1554" s="3" t="s">
+        <v>6029</v>
+      </c>
+      <c r="H1554" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1554" s="3">
+        <v>30</v>
+      </c>
+      <c r="J1554" s="3"/>
+      <c r="K1554" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1554" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1554" s="3" t="s">
+        <v>6030</v>
+      </c>
+      <c r="N1554" s="3"/>
+    </row>
+    <row r="1555" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1555" s="3" t="s">
+        <v>6031</v>
+      </c>
+      <c r="B1555" s="3" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C1555" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1555" s="3" t="s">
+        <v>6032</v>
+      </c>
+      <c r="E1555" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1555" s="3" t="s">
+        <v>1652</v>
+      </c>
+      <c r="G1555" s="3" t="s">
+        <v>6033</v>
+      </c>
+      <c r="H1555" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1555" s="3">
+        <v>62</v>
+      </c>
+      <c r="J1555" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1555" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1555" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1555" s="3" t="s">
+        <v>6034</v>
+      </c>
+      <c r="N1555" s="3"/>
+    </row>
+    <row r="1556" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1556" s="3" t="s">
+        <v>6031</v>
+      </c>
+      <c r="B1556" s="3"/>
+      <c r="C1556" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1556" s="3" t="s">
+        <v>6035</v>
+      </c>
+      <c r="E1556" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1556" s="3" t="s">
+        <v>6036</v>
+      </c>
+      <c r="G1556" s="3" t="s">
+        <v>6037</v>
+      </c>
+      <c r="H1556" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1556" s="3">
+        <v>53</v>
+      </c>
+      <c r="J1556" s="3"/>
+      <c r="K1556" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1556" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1556" s="3" t="s">
+        <v>6038</v>
+      </c>
+      <c r="N1556" s="3"/>
+    </row>
+    <row r="1557" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1557" s="3" t="s">
+        <v>6039</v>
+      </c>
+      <c r="B1557" s="3"/>
+      <c r="C1557" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1557" s="3" t="s">
+        <v>6040</v>
+      </c>
+      <c r="E1557" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1557" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="G1557" s="3" t="s">
+        <v>6041</v>
+      </c>
+      <c r="H1557" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1557" s="3">
+        <v>25</v>
+      </c>
+      <c r="J1557" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1557" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1557" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1557" s="3" t="s">
+        <v>6042</v>
+      </c>
+      <c r="N1557" s="3"/>
+    </row>
+    <row r="1558" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1558" s="3" t="s">
+        <v>6043</v>
+      </c>
+      <c r="B1558" s="3"/>
+      <c r="C1558" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1558" s="3" t="s">
+        <v>6044</v>
+      </c>
+      <c r="E1558" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1558" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="G1558" s="3" t="s">
+        <v>6045</v>
+      </c>
+      <c r="H1558" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1558" s="3">
+        <v>13</v>
+      </c>
+      <c r="J1558" s="3"/>
+      <c r="K1558" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1558" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1558" s="3" t="s">
+        <v>6042</v>
+      </c>
+      <c r="N1558" s="3"/>
+    </row>
+    <row r="1559" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1559" s="3" t="s">
+        <v>6046</v>
+      </c>
+      <c r="B1559" s="3"/>
+      <c r="C1559" s="3">
+        <v>410</v>
+      </c>
+      <c r="D1559" s="3" t="s">
+        <v>6047</v>
+      </c>
+      <c r="E1559" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1559" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1559" s="3" t="s">
+        <v>6048</v>
+      </c>
+      <c r="H1559" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1559" s="3">
+        <v>14</v>
+      </c>
+      <c r="J1559" s="3"/>
+      <c r="K1559" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1559" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1559" s="3" t="s">
+        <v>6049</v>
+      </c>
+      <c r="N1559" s="3"/>
+    </row>
+    <row r="1560" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1560" s="3" t="s">
+        <v>6050</v>
+      </c>
+      <c r="B1560" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C1560" s="3">
+        <v>408</v>
+      </c>
+      <c r="D1560" s="3" t="s">
+        <v>6051</v>
+      </c>
+      <c r="E1560" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1560" s="3" t="s">
+        <v>6052</v>
+      </c>
+      <c r="G1560" s="3" t="s">
+        <v>6053</v>
+      </c>
+      <c r="H1560" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1560" s="3">
+        <v>41</v>
+      </c>
+      <c r="J1560" s="3"/>
+      <c r="K1560" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1560" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1560" s="3" t="s">
+        <v>6049</v>
+      </c>
+      <c r="N1560" s="3" t="s">
+        <v>6054</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1561" s="3" t="s">
+        <v>6055</v>
+      </c>
+      <c r="B1561" s="3"/>
+      <c r="C1561" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1561" s="3" t="s">
+        <v>6056</v>
+      </c>
+      <c r="E1561" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1561" s="3" t="s">
+        <v>6057</v>
+      </c>
+      <c r="G1561" s="3" t="s">
+        <v>6058</v>
+      </c>
+      <c r="H1561" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1561" s="3">
+        <v>60</v>
+      </c>
+      <c r="J1561" s="3"/>
+      <c r="K1561" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1561" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1561" s="3" t="s">
+        <v>6059</v>
+      </c>
+      <c r="N1561" s="3"/>
+    </row>
+    <row r="1562" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1562" s="3" t="s">
+        <v>6060</v>
+      </c>
+      <c r="B1562" s="3"/>
+      <c r="C1562" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1562" s="3" t="s">
+        <v>6061</v>
+      </c>
+      <c r="E1562" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1562" s="3" t="s">
+        <v>2358</v>
+      </c>
+      <c r="G1562" s="3" t="s">
+        <v>6062</v>
+      </c>
+      <c r="H1562" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1562" s="3">
+        <v>70</v>
+      </c>
+      <c r="J1562" s="3"/>
+      <c r="K1562" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1562" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1562" s="3" t="s">
+        <v>6063</v>
+      </c>
+      <c r="N1562" s="3"/>
+    </row>
+    <row r="1563" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1563" s="3" t="s">
+        <v>6064</v>
+      </c>
+      <c r="B1563" s="3"/>
+      <c r="C1563" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1563" s="3" t="s">
+        <v>6065</v>
+      </c>
+      <c r="E1563" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1563" s="3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="G1563" s="3" t="s">
+        <v>6066</v>
+      </c>
+      <c r="H1563" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1563" s="3"/>
+      <c r="J1563" s="3"/>
+      <c r="K1563" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1563" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1563" s="3" t="s">
+        <v>6063</v>
+      </c>
+      <c r="N1563" s="3"/>
+    </row>
+    <row r="1564" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1564" s="3" t="s">
+        <v>6067</v>
+      </c>
+      <c r="B1564" s="3"/>
+      <c r="C1564" s="3">
+        <v>414</v>
+      </c>
+      <c r="D1564" s="3" t="s">
+        <v>6068</v>
+      </c>
+      <c r="E1564" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1564" s="3" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G1564" s="3" t="s">
+        <v>6069</v>
+      </c>
+      <c r="H1564" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1564" s="3">
+        <v>66</v>
+      </c>
+      <c r="J1564" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1564" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1564" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1564" s="3" t="s">
+        <v>6063</v>
+      </c>
+      <c r="N1564" s="3"/>
+    </row>
+    <row r="1565" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1565" s="3" t="s">
+        <v>6070</v>
+      </c>
+      <c r="B1565" s="3"/>
+      <c r="C1565" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1565" s="3" t="s">
+        <v>6071</v>
+      </c>
+      <c r="E1565" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1565" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="G1565" s="3" t="s">
+        <v>6072</v>
+      </c>
+      <c r="H1565" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1565" s="3">
+        <v>32</v>
+      </c>
+      <c r="J1565" s="3"/>
+      <c r="K1565" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1565" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1565" s="3" t="s">
+        <v>6073</v>
+      </c>
+      <c r="N1565" s="3"/>
+    </row>
+    <row r="1566" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1566" s="3" t="s">
+        <v>6074</v>
+      </c>
+      <c r="B1566" s="3"/>
+      <c r="C1566" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1566" s="3" t="s">
+        <v>6075</v>
+      </c>
+      <c r="E1566" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1566" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G1566" s="3" t="s">
+        <v>6076</v>
+      </c>
+      <c r="H1566" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1566" s="3">
+        <v>64</v>
+      </c>
+      <c r="J1566" s="3"/>
+      <c r="K1566" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1566" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1566" s="3" t="s">
+        <v>6063</v>
+      </c>
+      <c r="N1566" s="3"/>
+    </row>
+    <row r="1567" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1567" s="3" t="s">
+        <v>6077</v>
+      </c>
+      <c r="B1567" s="3"/>
+      <c r="C1567" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1567" s="3" t="s">
+        <v>6078</v>
+      </c>
+      <c r="E1567" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1567" s="3" t="s">
+        <v>2555</v>
+      </c>
+      <c r="G1567" s="3" t="s">
+        <v>6079</v>
+      </c>
+      <c r="H1567" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1567" s="3">
+        <v>45</v>
+      </c>
+      <c r="J1567" s="3"/>
+      <c r="K1567" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1567" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1567" s="3" t="s">
+        <v>6080</v>
+      </c>
+      <c r="N1567" s="3"/>
+    </row>
+    <row r="1568" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1568" s="3" t="s">
+        <v>6081</v>
+      </c>
+      <c r="B1568" s="3"/>
+      <c r="C1568" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1568" s="3" t="s">
+        <v>6082</v>
+      </c>
+      <c r="E1568" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1568" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="G1568" s="3" t="s">
+        <v>6083</v>
+      </c>
+      <c r="H1568" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1568" s="3">
+        <v>28</v>
+      </c>
+      <c r="J1568" s="3"/>
+      <c r="K1568" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1568" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1568" s="3" t="s">
+        <v>6084</v>
+      </c>
+      <c r="N1568" s="3"/>
+    </row>
+    <row r="1569" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1569" s="3" t="s">
+        <v>6085</v>
+      </c>
+      <c r="B1569" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C1569" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1569" s="3" t="s">
+        <v>6086</v>
+      </c>
+      <c r="E1569" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1569" s="3" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G1569" s="3" t="s">
+        <v>6087</v>
+      </c>
+      <c r="H1569" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1569" s="3"/>
+      <c r="J1569" s="3"/>
+      <c r="K1569" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1569" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1569" s="3" t="s">
+        <v>6059</v>
+      </c>
+      <c r="N1569" s="3" t="s">
+        <v>6059</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1570" s="3" t="s">
+        <v>6088</v>
+      </c>
+      <c r="B1570" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C1570" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1570" s="3" t="s">
+        <v>6089</v>
+      </c>
+      <c r="E1570" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1570" s="3" t="s">
+        <v>3363</v>
+      </c>
+      <c r="G1570" s="3" t="s">
+        <v>6090</v>
+      </c>
+      <c r="H1570" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1570" s="3">
+        <v>65</v>
+      </c>
+      <c r="J1570" s="3"/>
+      <c r="K1570" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1570" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1570" s="3" t="s">
+        <v>6091</v>
+      </c>
+      <c r="N1570" s="3"/>
+    </row>
+    <row r="1571" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1571" s="3" t="s">
+        <v>6092</v>
+      </c>
+      <c r="B1571" s="3"/>
+      <c r="C1571" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1571" s="3" t="s">
+        <v>6093</v>
+      </c>
+      <c r="E1571" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1571" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G1571" s="3" t="s">
+        <v>6094</v>
+      </c>
+      <c r="H1571" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1571" s="3"/>
+      <c r="J1571" s="3"/>
+      <c r="K1571" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1571" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1571" s="3" t="s">
+        <v>6095</v>
+      </c>
+      <c r="N1571" s="3"/>
+    </row>
+    <row r="1572" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1572" s="3" t="s">
+        <v>6096</v>
+      </c>
+      <c r="B1572" s="3"/>
+      <c r="C1572" s="3">
+        <v>403</v>
+      </c>
+      <c r="D1572" s="3" t="s">
+        <v>6097</v>
+      </c>
+      <c r="E1572" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1572" s="3" t="s">
+        <v>6098</v>
+      </c>
+      <c r="G1572" s="3" t="s">
+        <v>6099</v>
+      </c>
+      <c r="H1572" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1572" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1572" s="3"/>
+      <c r="K1572" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1572" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1572" s="3" t="s">
+        <v>6100</v>
+      </c>
+      <c r="N1572" s="3"/>
+    </row>
+    <row r="1573" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1573" s="3" t="s">
+        <v>6101</v>
+      </c>
+      <c r="B1573" s="3"/>
+      <c r="C1573" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1573" s="3" t="s">
+        <v>6102</v>
+      </c>
+      <c r="E1573" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F1573" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1573" s="3" t="s">
+        <v>6103</v>
+      </c>
+      <c r="H1573" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1573" s="3">
+        <v>28</v>
+      </c>
+      <c r="J1573" s="3"/>
+      <c r="K1573" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1573" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1573" s="3" t="s">
+        <v>6104</v>
+      </c>
+      <c r="N1573" s="3"/>
+    </row>
+    <row r="1574" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1574" s="3" t="s">
+        <v>6105</v>
+      </c>
+      <c r="B1574" s="3" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C1574" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1574" s="3" t="s">
+        <v>6106</v>
+      </c>
+      <c r="E1574" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1574" s="3" t="s">
+        <v>1610</v>
+      </c>
+      <c r="G1574" s="3" t="s">
+        <v>6107</v>
+      </c>
+      <c r="H1574" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1574" s="3">
+        <v>3</v>
+      </c>
+      <c r="J1574" s="3"/>
+      <c r="K1574" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1574" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1574" s="3" t="s">
+        <v>6108</v>
+      </c>
+      <c r="N1574" s="3"/>
+    </row>
+    <row r="1575" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1575" s="3" t="s">
+        <v>6109</v>
+      </c>
+      <c r="B1575" s="3"/>
+      <c r="C1575" s="3">
+        <v>414</v>
+      </c>
+      <c r="D1575" s="3" t="s">
+        <v>6110</v>
+      </c>
+      <c r="E1575" s="3" t="s">
+        <v>1801</v>
+      </c>
+      <c r="F1575" s="3" t="s">
+        <v>6111</v>
+      </c>
+      <c r="G1575" s="3" t="s">
+        <v>6112</v>
+      </c>
+      <c r="H1575" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1575" s="3">
+        <v>77</v>
+      </c>
+      <c r="J1575" s="3"/>
+      <c r="K1575" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1575" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1575" s="3" t="s">
+        <v>6113</v>
+      </c>
+      <c r="N1575" s="3"/>
+    </row>
+    <row r="1576" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1576" s="3" t="s">
+        <v>6114</v>
+      </c>
+      <c r="B1576" s="3"/>
+      <c r="C1576" s="3">
+        <v>414</v>
+      </c>
+      <c r="D1576" s="3" t="s">
+        <v>6115</v>
+      </c>
+      <c r="E1576" s="3" t="s">
+        <v>1801</v>
+      </c>
+      <c r="F1576" s="3" t="s">
+        <v>6116</v>
+      </c>
+      <c r="G1576" s="3" t="s">
+        <v>6117</v>
+      </c>
+      <c r="H1576" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1576" s="3">
+        <v>64</v>
+      </c>
+      <c r="J1576" s="3">
+        <v>80</v>
+      </c>
+      <c r="K1576" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1576" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1576" s="3" t="s">
+        <v>6113</v>
+      </c>
+      <c r="N1576" s="3"/>
+    </row>
+    <row r="1577" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1577" s="3" t="s">
+        <v>6118</v>
+      </c>
+      <c r="B1577" s="3"/>
+      <c r="C1577" s="3">
+        <v>414</v>
+      </c>
+      <c r="D1577" s="3" t="s">
+        <v>6119</v>
+      </c>
+      <c r="E1577" s="3" t="s">
+        <v>1801</v>
+      </c>
+      <c r="F1577" s="3" t="s">
+        <v>4211</v>
+      </c>
+      <c r="G1577" s="3" t="s">
+        <v>6120</v>
+      </c>
+      <c r="H1577" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1577" s="3"/>
+      <c r="J1577" s="3"/>
+      <c r="K1577" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1577" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1577" s="3" t="s">
+        <v>6121</v>
+      </c>
+      <c r="N1577" s="3"/>
+    </row>
+    <row r="1578" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1578" s="3" t="s">
+        <v>6122</v>
+      </c>
+      <c r="B1578" s="3" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C1578" s="3">
+        <v>414</v>
+      </c>
+      <c r="D1578" s="3" t="s">
+        <v>6123</v>
+      </c>
+      <c r="E1578" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F1578" s="3" t="s">
+        <v>6124</v>
+      </c>
+      <c r="G1578" s="3" t="s">
+        <v>6125</v>
+      </c>
+      <c r="H1578" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1578" s="3">
+        <v>82</v>
+      </c>
+      <c r="J1578" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1578" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1578" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1578" s="3" t="s">
+        <v>6126</v>
+      </c>
+      <c r="N1578" s="3"/>
+    </row>
+    <row r="1579" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1579" s="3" t="s">
+        <v>6127</v>
+      </c>
+      <c r="B1579" s="3"/>
+      <c r="C1579" s="3">
+        <v>414</v>
+      </c>
+      <c r="D1579" s="3" t="s">
+        <v>6128</v>
+      </c>
+      <c r="E1579" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F1579" s="3" t="s">
+        <v>6129</v>
+      </c>
+      <c r="G1579" s="3" t="s">
+        <v>6130</v>
+      </c>
+      <c r="H1579" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1579" s="3">
+        <v>83</v>
+      </c>
+      <c r="J1579" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1579" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1579" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1579" s="3" t="s">
+        <v>6131</v>
+      </c>
+      <c r="N1579" s="3"/>
+    </row>
+    <row r="1580" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1580" s="3" t="s">
+        <v>6132</v>
+      </c>
+      <c r="B1580" s="3" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C1580" s="3">
+        <v>414</v>
+      </c>
+      <c r="D1580" s="3" t="s">
+        <v>6133</v>
+      </c>
+      <c r="E1580" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1580" s="3" t="s">
+        <v>6134</v>
+      </c>
+      <c r="G1580" s="3" t="s">
+        <v>6135</v>
+      </c>
+      <c r="H1580" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1580" s="3">
+        <v>76</v>
+      </c>
+      <c r="J1580" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1580" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1580" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1580" s="3" t="s">
+        <v>6136</v>
+      </c>
+      <c r="N1580" s="3"/>
+    </row>
+    <row r="1581" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1581" s="3" t="s">
+        <v>6137</v>
+      </c>
+      <c r="B1581" s="3"/>
+      <c r="C1581" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1581" s="3" t="s">
+        <v>6138</v>
+      </c>
+      <c r="E1581" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1581" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="G1581" s="3" t="s">
+        <v>6139</v>
+      </c>
+      <c r="H1581" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1581" s="3">
+        <v>28</v>
+      </c>
+      <c r="J1581" s="3"/>
+      <c r="K1581" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1581" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1581" s="3" t="s">
+        <v>6140</v>
+      </c>
+      <c r="N1581" s="3"/>
+    </row>
+    <row r="1582" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1582" s="3" t="s">
+        <v>6141</v>
+      </c>
+      <c r="B1582" s="3"/>
+      <c r="C1582" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1582" s="3" t="s">
+        <v>6142</v>
+      </c>
+      <c r="E1582" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1582" s="3" t="s">
+        <v>1689</v>
+      </c>
+      <c r="G1582" s="3" t="s">
+        <v>6143</v>
+      </c>
+      <c r="H1582" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1582" s="3">
+        <v>49</v>
+      </c>
+      <c r="J1582" s="3"/>
+      <c r="K1582" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1582" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1582" s="3" t="s">
+        <v>6140</v>
+      </c>
+      <c r="N1582" s="3"/>
+    </row>
+    <row r="1583" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1583" s="3" t="s">
+        <v>6144</v>
+      </c>
+      <c r="B1583" s="3"/>
+      <c r="C1583" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1583" s="3" t="s">
+        <v>6145</v>
+      </c>
+      <c r="E1583" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1583" s="3" t="s">
+        <v>6146</v>
+      </c>
+      <c r="G1583" s="3" t="s">
+        <v>6147</v>
+      </c>
+      <c r="H1583" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1583" s="3">
+        <v>14</v>
+      </c>
+      <c r="J1583" s="3"/>
+      <c r="K1583" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1583" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1583" s="3" t="s">
+        <v>6140</v>
+      </c>
+      <c r="N1583" s="3"/>
+    </row>
+    <row r="1584" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1584" s="3" t="s">
+        <v>6148</v>
+      </c>
+      <c r="B1584" s="3"/>
+      <c r="C1584" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1584" s="3" t="s">
+        <v>6149</v>
+      </c>
+      <c r="E1584" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1584" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="G1584" s="3" t="s">
+        <v>6150</v>
+      </c>
+      <c r="H1584" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1584" s="3">
+        <v>31</v>
+      </c>
+      <c r="J1584" s="3"/>
+      <c r="K1584" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1584" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1584" s="3" t="s">
+        <v>6140</v>
+      </c>
+      <c r="N1584" s="3"/>
+    </row>
+    <row r="1585" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1585" s="3" t="s">
+        <v>6151</v>
+      </c>
+      <c r="B1585" s="3"/>
+      <c r="C1585" s="3">
+        <v>414</v>
+      </c>
+      <c r="D1585" s="3" t="s">
+        <v>6152</v>
+      </c>
+      <c r="E1585" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1585" s="3" t="s">
+        <v>6153</v>
+      </c>
+      <c r="G1585" s="3" t="s">
+        <v>6154</v>
+      </c>
+      <c r="H1585" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1585" s="3">
+        <v>78</v>
+      </c>
+      <c r="J1585" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1585" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1585" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1585" s="3" t="s">
+        <v>6155</v>
+      </c>
+      <c r="N1585" s="3"/>
+    </row>
+    <row r="1586" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1586" s="3" t="s">
+        <v>6156</v>
+      </c>
+      <c r="B1586" s="3"/>
+      <c r="C1586" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1586" s="3" t="s">
+        <v>6157</v>
+      </c>
+      <c r="E1586" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1586" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="G1586" s="3" t="s">
+        <v>6158</v>
+      </c>
+      <c r="H1586" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1586" s="3">
+        <v>33</v>
+      </c>
+      <c r="J1586" s="3"/>
+      <c r="K1586" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1586" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1586" s="3" t="s">
+        <v>6155</v>
+      </c>
+      <c r="N1586" s="3"/>
+    </row>
+    <row r="1587" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1587" s="3" t="s">
+        <v>6159</v>
+      </c>
+      <c r="B1587" s="3" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C1587" s="3">
+        <v>414</v>
+      </c>
+      <c r="D1587" s="3" t="s">
+        <v>6160</v>
+      </c>
+      <c r="E1587" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1587" s="3" t="s">
+        <v>1322</v>
+      </c>
+      <c r="G1587" s="3" t="s">
+        <v>6161</v>
+      </c>
+      <c r="H1587" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="I1587" s="3">
+        <v>74</v>
+      </c>
+      <c r="J1587" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1587" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1587" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1587" s="3" t="s">
+        <v>6155</v>
+      </c>
+      <c r="N1587" s="3"/>
+    </row>
+    <row r="1588" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1588" s="3" t="s">
+        <v>6162</v>
+      </c>
+      <c r="B1588" s="3"/>
+      <c r="C1588" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1588" s="3" t="s">
+        <v>6163</v>
+      </c>
+      <c r="E1588" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1588" s="3" t="s">
+        <v>2918</v>
+      </c>
+      <c r="G1588" s="3" t="s">
+        <v>6164</v>
+      </c>
+      <c r="H1588" s="3"/>
+      <c r="I1588" s="3">
+        <v>27</v>
+      </c>
+      <c r="J1588" s="3"/>
+      <c r="K1588" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1588" s="3"/>
+      <c r="M1588" s="3"/>
+      <c r="N1588" s="3"/>
+    </row>
+    <row r="1589" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1589" s="3" t="s">
+        <v>6165</v>
+      </c>
+      <c r="B1589" s="3"/>
+      <c r="C1589" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1589" s="3" t="s">
+        <v>6166</v>
+      </c>
+      <c r="E1589" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1589" s="3" t="s">
+        <v>2555</v>
+      </c>
+      <c r="G1589" s="3" t="s">
+        <v>6167</v>
+      </c>
+      <c r="H1589" s="3"/>
+      <c r="I1589" s="3">
+        <v>35</v>
+      </c>
+      <c r="J1589" s="3"/>
+      <c r="K1589" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1589" s="3"/>
+      <c r="M1589" s="3"/>
+      <c r="N1589" s="3"/>
+    </row>
+    <row r="1590" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1590" s="3" t="s">
+        <v>6168</v>
+      </c>
+      <c r="B1590" s="3"/>
+      <c r="C1590" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1590" s="3" t="s">
+        <v>6169</v>
+      </c>
+      <c r="E1590" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1590" s="3" t="s">
+        <v>6170</v>
+      </c>
+      <c r="G1590" s="3" t="s">
+        <v>6171</v>
+      </c>
+      <c r="H1590" s="3"/>
+      <c r="I1590" s="3">
+        <v>79</v>
+      </c>
+      <c r="J1590" s="3"/>
+      <c r="K1590" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1590" s="3"/>
+      <c r="M1590" s="3"/>
+      <c r="N1590" s="3"/>
+    </row>
+    <row r="1591" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1591" s="3" t="s">
+        <v>6172</v>
+      </c>
+      <c r="B1591" s="3"/>
+      <c r="C1591" s="3">
+        <v>408</v>
+      </c>
+      <c r="D1591" s="3" t="s">
+        <v>6173</v>
+      </c>
+      <c r="E1591" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1591" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="G1591" s="3" t="s">
+        <v>6174</v>
+      </c>
+      <c r="H1591" s="3"/>
+      <c r="I1591" s="3">
+        <v>8</v>
+      </c>
+      <c r="J1591" s="3"/>
+      <c r="K1591" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1591" s="3"/>
+      <c r="M1591" s="3"/>
+      <c r="N1591" s="3"/>
+    </row>
+    <row r="1592" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1592" s="3" t="s">
+        <v>6175</v>
+      </c>
+      <c r="B1592" s="3"/>
+      <c r="C1592" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1592" s="3" t="s">
+        <v>6176</v>
+      </c>
+      <c r="E1592" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1592" s="3" t="s">
+        <v>6177</v>
+      </c>
+      <c r="G1592" s="3" t="s">
+        <v>6178</v>
+      </c>
+      <c r="H1592" s="3"/>
+      <c r="I1592" s="3">
+        <v>77</v>
+      </c>
+      <c r="J1592" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1592" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1592" s="3"/>
+      <c r="M1592" s="3"/>
+      <c r="N1592" s="3"/>
+    </row>
+    <row r="1593" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1593" s="3" t="s">
+        <v>6179</v>
+      </c>
+      <c r="B1593" s="3"/>
+      <c r="C1593" s="3">
+        <v>411</v>
+      </c>
+      <c r="D1593" s="3" t="s">
+        <v>6180</v>
+      </c>
+      <c r="E1593" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1593" s="3" t="s">
+        <v>6181</v>
+      </c>
+      <c r="G1593" s="3" t="s">
+        <v>6182</v>
+      </c>
+      <c r="H1593" s="3"/>
+      <c r="I1593" s="3">
+        <v>76</v>
+      </c>
+      <c r="J1593" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1593" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1593" s="3"/>
+      <c r="M1593" s="3"/>
+      <c r="N1593" s="3"/>
+    </row>
+    <row r="1594" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1594" s="3" t="s">
+        <v>6183</v>
+      </c>
+      <c r="B1594" s="3"/>
+      <c r="C1594" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1594" s="3" t="s">
+        <v>6184</v>
+      </c>
+      <c r="E1594" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F1594" s="3" t="s">
+        <v>1572</v>
+      </c>
+      <c r="G1594" s="3" t="s">
+        <v>6185</v>
+      </c>
+      <c r="H1594" s="3"/>
+      <c r="I1594" s="3">
+        <v>3</v>
+      </c>
+      <c r="J1594" s="3"/>
+      <c r="K1594" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1594" s="3"/>
+      <c r="M1594" s="3"/>
+      <c r="N1594" s="3"/>
+    </row>
+    <row r="1595" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1595" s="3" t="s">
+        <v>6186</v>
+      </c>
+      <c r="B1595" s="3"/>
+      <c r="C1595" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1595" s="3" t="s">
+        <v>6187</v>
+      </c>
+      <c r="E1595" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1595" s="3" t="s">
+        <v>6188</v>
+      </c>
+      <c r="G1595" s="3" t="s">
+        <v>6189</v>
+      </c>
+      <c r="H1595" s="3"/>
+      <c r="I1595" s="3">
+        <v>67</v>
+      </c>
+      <c r="J1595" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1595" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1595" s="3"/>
+      <c r="M1595" s="3"/>
+      <c r="N1595" s="3"/>
+    </row>
+    <row r="1596" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1596" s="3" t="s">
+        <v>6190</v>
+      </c>
+      <c r="B1596" s="3"/>
+      <c r="C1596" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1596" s="3" t="s">
+        <v>6191</v>
+      </c>
+      <c r="E1596" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1596" s="3" t="s">
+        <v>6192</v>
+      </c>
+      <c r="G1596" s="3" t="s">
+        <v>6193</v>
+      </c>
+      <c r="H1596" s="3"/>
+      <c r="I1596" s="3">
+        <v>69</v>
+      </c>
+      <c r="J1596" s="3">
+        <v>75</v>
+      </c>
+      <c r="K1596" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1596" s="3"/>
+      <c r="M1596" s="3"/>
+      <c r="N1596" s="3"/>
+    </row>
+    <row r="1597" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1597" s="3" t="s">
+        <v>6194</v>
+      </c>
+      <c r="B1597" s="3"/>
+      <c r="C1597" s="3">
+        <v>410</v>
+      </c>
+      <c r="D1597" s="3" t="s">
+        <v>6195</v>
+      </c>
+      <c r="E1597" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1597" s="3" t="s">
+        <v>2555</v>
+      </c>
+      <c r="G1597" s="3" t="s">
+        <v>6196</v>
+      </c>
+      <c r="H1597" s="3"/>
+      <c r="I1597" s="3">
+        <v>19</v>
+      </c>
+      <c r="J1597" s="3"/>
+      <c r="K1597" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1597" s="3"/>
+      <c r="M1597" s="3"/>
+      <c r="N1597" s="3"/>
+    </row>
+    <row r="1598" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1598" s="3" t="s">
+        <v>6197</v>
+      </c>
+      <c r="B1598" s="3"/>
+      <c r="C1598" s="3">
+        <v>410</v>
+      </c>
+      <c r="D1598" s="3" t="s">
+        <v>6198</v>
+      </c>
+      <c r="E1598" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="F1598" s="3" t="s">
+        <v>4313</v>
+      </c>
+      <c r="G1598" s="3" t="s">
+        <v>6199</v>
+      </c>
+      <c r="H1598" s="3"/>
+      <c r="I1598" s="3">
+        <v>10</v>
+      </c>
+      <c r="J1598" s="3"/>
+      <c r="K1598" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1598" s="3"/>
+      <c r="M1598" s="3"/>
+      <c r="N1598" s="3"/>
+    </row>
+    <row r="1599" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1599" s="3" t="s">
+        <v>6200</v>
+      </c>
+      <c r="B1599" s="3"/>
+      <c r="C1599" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1599" s="3" t="s">
+        <v>6201</v>
+      </c>
+      <c r="E1599" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1599" s="3" t="s">
+        <v>1805</v>
+      </c>
+      <c r="G1599" s="3" t="s">
+        <v>6202</v>
+      </c>
+      <c r="H1599" s="3"/>
+      <c r="I1599" s="3"/>
+      <c r="J1599" s="3"/>
+      <c r="K1599" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1599" s="3"/>
+      <c r="M1599" s="3"/>
+      <c r="N1599" s="3"/>
+    </row>
+    <row r="1600" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1600" s="3" t="s">
+        <v>6203</v>
+      </c>
+      <c r="B1600" s="3"/>
+      <c r="C1600" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1600" s="3" t="s">
+        <v>6204</v>
+      </c>
+      <c r="E1600" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1600" s="3" t="s">
+        <v>2918</v>
+      </c>
+      <c r="G1600" s="3" t="s">
+        <v>6205</v>
+      </c>
+      <c r="H1600" s="3"/>
+      <c r="I1600" s="3">
+        <v>26</v>
+      </c>
+      <c r="J1600" s="3"/>
+      <c r="K1600" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1600" s="3"/>
+      <c r="M1600" s="3"/>
+      <c r="N1600" s="3"/>
+    </row>
+    <row r="1601" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1601" s="3" t="s">
+        <v>6206</v>
+      </c>
+      <c r="B1601" s="3"/>
+      <c r="C1601" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1601" s="3" t="s">
+        <v>6207</v>
+      </c>
+      <c r="E1601" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1601" s="3" t="s">
+        <v>2918</v>
+      </c>
+      <c r="G1601" s="3" t="s">
+        <v>6208</v>
+      </c>
+      <c r="H1601" s="3"/>
+      <c r="I1601" s="3">
+        <v>29</v>
+      </c>
+      <c r="J1601" s="3"/>
+      <c r="K1601" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1601" s="3"/>
+      <c r="M1601" s="3"/>
+      <c r="N1601" s="3"/>
+    </row>
+    <row r="1602" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1602" s="3" t="s">
+        <v>6209</v>
+      </c>
+      <c r="B1602" s="3"/>
+      <c r="C1602" s="3">
+        <v>414</v>
+      </c>
+      <c r="D1602" s="3" t="s">
+        <v>6210</v>
+      </c>
+      <c r="E1602" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1602" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="G1602" s="3" t="s">
+        <v>6211</v>
+      </c>
+      <c r="H1602" s="3"/>
+      <c r="I1602" s="3"/>
+      <c r="J1602" s="3"/>
+      <c r="K1602" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1602" s="3"/>
+      <c r="M1602" s="3"/>
+      <c r="N1602" s="3"/>
+    </row>
+    <row r="1603" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1603" s="3" t="s">
+        <v>6212</v>
+      </c>
+      <c r="B1603" s="3"/>
+      <c r="C1603" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1603" s="3" t="s">
+        <v>6213</v>
+      </c>
+      <c r="E1603" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1603" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="G1603" s="3" t="s">
+        <v>6214</v>
+      </c>
+      <c r="H1603" s="3"/>
+      <c r="I1603" s="3">
+        <v>45</v>
+      </c>
+      <c r="J1603" s="3"/>
+      <c r="K1603" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1603" s="3"/>
+      <c r="M1603" s="3"/>
+      <c r="N1603" s="3"/>
+    </row>
+    <row r="1604" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1604" s="3" t="s">
+        <v>6215</v>
+      </c>
+      <c r="B1604" s="3"/>
+      <c r="C1604" s="3">
+        <v>410</v>
+      </c>
+      <c r="D1604" s="3" t="s">
+        <v>6216</v>
+      </c>
+      <c r="E1604" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1604" s="3" t="s">
+        <v>2448</v>
+      </c>
+      <c r="G1604" s="3" t="s">
+        <v>6217</v>
+      </c>
+      <c r="H1604" s="3"/>
+      <c r="I1604" s="3">
+        <v>10</v>
+      </c>
+      <c r="J1604" s="3"/>
+      <c r="K1604" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1604" s="3"/>
+      <c r="M1604" s="3"/>
+      <c r="N1604" s="3"/>
+    </row>
+    <row r="1605" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1605" s="3" t="s">
+        <v>6218</v>
+      </c>
+      <c r="B1605" s="3"/>
+      <c r="C1605" s="3">
+        <v>410</v>
+      </c>
+      <c r="D1605" s="3" t="s">
+        <v>6219</v>
+      </c>
+      <c r="E1605" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1605" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="G1605" s="3" t="s">
+        <v>6220</v>
+      </c>
+      <c r="H1605" s="3"/>
+      <c r="I1605" s="3">
+        <v>62</v>
+      </c>
+      <c r="J1605" s="3"/>
+      <c r="K1605" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1605" s="3"/>
+      <c r="M1605" s="3"/>
+      <c r="N1605" s="3"/>
+    </row>
+    <row r="1606" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1606" s="3" t="s">
+        <v>6221</v>
+      </c>
+      <c r="B1606" s="3"/>
+      <c r="C1606" s="3">
+        <v>410</v>
+      </c>
+      <c r="D1606" s="3" t="s">
+        <v>6222</v>
+      </c>
+      <c r="E1606" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1606" s="3" t="s">
+        <v>2786</v>
+      </c>
+      <c r="G1606" s="3" t="s">
+        <v>6223</v>
+      </c>
+      <c r="H1606" s="3"/>
+      <c r="I1606" s="3"/>
+      <c r="J1606" s="3"/>
+      <c r="K1606" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1606" s="3"/>
+      <c r="M1606" s="3"/>
+      <c r="N1606" s="3"/>
+    </row>
+    <row r="1607" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1607" s="3" t="s">
+        <v>6224</v>
+      </c>
+      <c r="B1607" s="3"/>
+      <c r="C1607" s="3">
+        <v>410</v>
+      </c>
+      <c r="D1607" s="3" t="s">
+        <v>6225</v>
+      </c>
+      <c r="E1607" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1607" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G1607" s="3" t="s">
+        <v>6226</v>
+      </c>
+      <c r="H1607" s="3"/>
+      <c r="I1607" s="3">
+        <v>46</v>
+      </c>
+      <c r="J1607" s="3"/>
+      <c r="K1607" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1607" s="3"/>
+      <c r="M1607" s="3"/>
+      <c r="N1607" s="3"/>
+    </row>
+    <row r="1608" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1608" s="3" t="s">
+        <v>6227</v>
+      </c>
+      <c r="B1608" s="3"/>
+      <c r="C1608" s="3">
+        <v>410</v>
+      </c>
+      <c r="D1608" s="3" t="s">
+        <v>6228</v>
+      </c>
+      <c r="E1608" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1608" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1608" s="3" t="s">
+        <v>6229</v>
+      </c>
+      <c r="H1608" s="3"/>
+      <c r="I1608" s="3">
+        <v>41</v>
+      </c>
+      <c r="J1608" s="3"/>
+      <c r="K1608" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1608" s="3"/>
+      <c r="M1608" s="3"/>
+      <c r="N1608" s="3"/>
+    </row>
+    <row r="1609" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1609" s="3" t="s">
+        <v>6230</v>
+      </c>
+      <c r="B1609" s="3"/>
+      <c r="C1609" s="3">
+        <v>414</v>
+      </c>
+      <c r="D1609" s="3" t="s">
+        <v>6231</v>
+      </c>
+      <c r="E1609" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1609" s="3" t="s">
+        <v>2842</v>
+      </c>
+      <c r="G1609" s="3" t="s">
+        <v>6232</v>
+      </c>
+      <c r="H1609" s="3"/>
+      <c r="I1609" s="3">
+        <v>30</v>
+      </c>
+      <c r="J1609" s="3"/>
+      <c r="K1609" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1609" s="3"/>
+      <c r="M1609" s="3"/>
+      <c r="N1609" s="3"/>
+    </row>
+    <row r="1610" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1610" s="3" t="s">
+        <v>6233</v>
+      </c>
+      <c r="B1610" s="3"/>
+      <c r="C1610" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1610" s="3" t="s">
+        <v>6234</v>
+      </c>
+      <c r="E1610" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1610" s="3" t="s">
+        <v>2878</v>
+      </c>
+      <c r="G1610" s="3" t="s">
+        <v>6235</v>
+      </c>
+      <c r="H1610" s="3"/>
+      <c r="I1610" s="3">
+        <v>4</v>
+      </c>
+      <c r="J1610" s="3"/>
+      <c r="K1610" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1610" s="3"/>
+      <c r="M1610" s="3"/>
+      <c r="N1610" s="3"/>
+    </row>
+    <row r="1611" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1611" s="3" t="s">
+        <v>6236</v>
+      </c>
+      <c r="B1611" s="3"/>
+      <c r="C1611" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1611" s="3" t="s">
+        <v>6237</v>
+      </c>
+      <c r="E1611" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1611" s="3" t="s">
+        <v>1890</v>
+      </c>
+      <c r="G1611" s="3" t="s">
+        <v>6238</v>
+      </c>
+      <c r="H1611" s="3"/>
+      <c r="I1611" s="3">
+        <v>63</v>
+      </c>
+      <c r="J1611" s="3">
+        <v>65</v>
+      </c>
+      <c r="K1611" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1611" s="3"/>
+      <c r="M1611" s="3"/>
+      <c r="N1611" s="3"/>
+    </row>
+    <row r="1612" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1612" s="3" t="s">
+        <v>6239</v>
+      </c>
+      <c r="B1612" s="3"/>
+      <c r="C1612" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1612" s="3" t="s">
+        <v>6240</v>
+      </c>
+      <c r="E1612" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F1612" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G1612" s="3" t="s">
+        <v>6241</v>
+      </c>
+      <c r="H1612" s="3"/>
+      <c r="I1612" s="3">
+        <v>28</v>
+      </c>
+      <c r="J1612" s="3"/>
+      <c r="K1612" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1612" s="3"/>
+      <c r="M1612" s="3"/>
+      <c r="N1612" s="3"/>
+    </row>
+    <row r="1613" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1613" s="3" t="s">
+        <v>6242</v>
+      </c>
+      <c r="B1613" s="3"/>
+      <c r="C1613" s="3">
+        <v>405</v>
+      </c>
+      <c r="D1613" s="3" t="s">
+        <v>6243</v>
+      </c>
+      <c r="E1613" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1613" s="3" t="s">
+        <v>6244</v>
+      </c>
+      <c r="G1613" s="3" t="s">
+        <v>6245</v>
+      </c>
+      <c r="H1613" s="3"/>
+      <c r="I1613" s="3">
+        <v>36</v>
+      </c>
+      <c r="J1613" s="3"/>
+      <c r="K1613" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1613" s="3"/>
+      <c r="M1613" s="3"/>
+      <c r="N1613" s="3"/>
+    </row>
+    <row r="1614" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1614" s="3" t="s">
+        <v>6246</v>
+      </c>
+      <c r="B1614" s="3"/>
+      <c r="C1614" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1614" s="3" t="s">
+        <v>6247</v>
+      </c>
+      <c r="E1614" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1614" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="G1614" s="3" t="s">
+        <v>6248</v>
+      </c>
+      <c r="H1614" s="3"/>
+      <c r="I1614" s="3"/>
+      <c r="J1614" s="3"/>
+      <c r="K1614" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1614" s="3"/>
+      <c r="M1614" s="3"/>
+      <c r="N1614" s="3"/>
+    </row>
+    <row r="1615" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1615" s="3" t="s">
+        <v>6249</v>
+      </c>
+      <c r="B1615" s="3"/>
+      <c r="C1615" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1615" s="3" t="s">
+        <v>6250</v>
+      </c>
+      <c r="E1615" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1615" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="G1615" s="3" t="s">
+        <v>6251</v>
+      </c>
+      <c r="H1615" s="3"/>
+      <c r="I1615" s="3">
+        <v>17</v>
+      </c>
+      <c r="J1615" s="3"/>
+      <c r="K1615" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1615" s="3"/>
+      <c r="M1615" s="3"/>
+      <c r="N1615" s="3"/>
+    </row>
+    <row r="1616" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1616" s="3" t="s">
+        <v>6252</v>
+      </c>
+      <c r="B1616" s="3"/>
+      <c r="C1616" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1616" s="3" t="s">
+        <v>6253</v>
+      </c>
+      <c r="E1616" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1616" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G1616" s="3" t="s">
+        <v>6254</v>
+      </c>
+      <c r="H1616" s="3"/>
+      <c r="I1616" s="3">
+        <v>28</v>
+      </c>
+      <c r="J1616" s="3"/>
+      <c r="K1616" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1616" s="3"/>
+      <c r="M1616" s="3"/>
+      <c r="N1616" s="3"/>
+    </row>
+    <row r="1617" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1617" s="3" t="s">
+        <v>6255</v>
+      </c>
+      <c r="B1617" s="3"/>
+      <c r="C1617" s="3">
+        <v>409</v>
+      </c>
+      <c r="D1617" s="3" t="s">
+        <v>6256</v>
+      </c>
+      <c r="E1617" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F1617" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="G1617" s="3" t="s">
+        <v>6257</v>
+      </c>
+      <c r="H1617" s="3"/>
+      <c r="I1617" s="3">
+        <v>34</v>
+      </c>
+      <c r="J1617" s="3"/>
+      <c r="K1617" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1617" s="3"/>
+      <c r="M1617" s="3"/>
+      <c r="N1617" s="3"/>
+    </row>
+    <row r="1618" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1618" s="3" t="s">
+        <v>6258</v>
+      </c>
+      <c r="B1618" s="3"/>
+      <c r="C1618" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1618" s="3" t="s">
+        <v>6259</v>
+      </c>
+      <c r="E1618" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1618" s="3" t="s">
+        <v>2555</v>
+      </c>
+      <c r="G1618" s="3" t="s">
+        <v>6260</v>
+      </c>
+      <c r="H1618" s="3"/>
+      <c r="I1618" s="3">
+        <v>21</v>
+      </c>
+      <c r="J1618" s="3"/>
+      <c r="K1618" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1618" s="3"/>
+      <c r="M1618" s="3"/>
+      <c r="N1618" s="3"/>
+    </row>
+    <row r="1619" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1619" s="3" t="s">
+        <v>6261</v>
+      </c>
+      <c r="B1619" s="3"/>
+      <c r="C1619" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1619" s="3" t="s">
+        <v>6262</v>
+      </c>
+      <c r="E1619" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1619" s="3" t="s">
+        <v>2514</v>
+      </c>
+      <c r="G1619" s="3" t="s">
+        <v>6263</v>
+      </c>
+      <c r="H1619" s="3"/>
+      <c r="I1619" s="3">
+        <v>23</v>
+      </c>
+      <c r="J1619" s="3"/>
+      <c r="K1619" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1619" s="3"/>
+      <c r="M1619" s="3"/>
+      <c r="N1619" s="3"/>
+    </row>
+    <row r="1620" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1620" s="3" t="s">
+        <v>6264</v>
+      </c>
+      <c r="B1620" s="3"/>
+      <c r="C1620" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1620" s="3" t="s">
+        <v>6265</v>
+      </c>
+      <c r="E1620" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1620" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G1620" s="3" t="s">
+        <v>6266</v>
+      </c>
+      <c r="H1620" s="3"/>
+      <c r="I1620" s="3">
+        <v>17</v>
+      </c>
+      <c r="J1620" s="3"/>
+      <c r="K1620" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1620" s="3"/>
+      <c r="M1620" s="3"/>
+      <c r="N1620" s="3"/>
+    </row>
+    <row r="1621" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1621" s="3" t="s">
+        <v>6267</v>
+      </c>
+      <c r="B1621" s="3"/>
+      <c r="C1621" s="3">
+        <v>404</v>
+      </c>
+      <c r="D1621" s="3" t="s">
+        <v>6268</v>
+      </c>
+      <c r="E1621" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F1621" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G1621" s="3" t="s">
+        <v>6269</v>
+      </c>
+      <c r="H1621" s="3"/>
+      <c r="I1621" s="3">
+        <v>36</v>
+      </c>
+      <c r="J1621" s="3"/>
+      <c r="K1621" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1621" s="3"/>
+      <c r="M1621" s="3"/>
+      <c r="N1621" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
